--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1826,13 +1826,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46155.43894304398</v>
+        <v>46155.60560971065</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70656460648</v>
+        <v>46175.873231273144</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.70657782408</v>
+        <v>46175.87324449074</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1879,13 +1879,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46155.43905862268</v>
+        <v>46155.60572528935</v>
       </c>
       <c r="C5" s="9">
-        <v>46161.45673921297</v>
+        <v>46161.623405879625</v>
       </c>
       <c r="D5" s="9">
-        <v>46161.45675550926</v>
+        <v>46161.62342217592</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1942,13 +1942,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46155.4390644213</v>
+        <v>46155.60573108796</v>
       </c>
       <c r="C6" s="5">
-        <v>46161.456973761575</v>
+        <v>46161.62364042824</v>
       </c>
       <c r="D6" s="5">
-        <v>46161.45699003473</v>
+        <v>46161.623656701384</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2005,13 +2005,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46155.43906950232</v>
+        <v>46155.60573616898</v>
       </c>
       <c r="C7" s="9">
-        <v>46161.45699008102</v>
+        <v>46161.62365674769</v>
       </c>
       <c r="D7" s="9">
-        <v>46161.457162129635</v>
+        <v>46161.62382879629</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -2068,13 +2068,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46155.439074548616</v>
+        <v>46155.60574121527</v>
       </c>
       <c r="C8" s="5">
-        <v>46161.45752660879</v>
+        <v>46161.624193275464</v>
       </c>
       <c r="D8" s="5">
-        <v>46161.45754138889</v>
+        <v>46161.62420805555</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2131,13 +2131,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46155.43908016203</v>
+        <v>46155.6057468287</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.706550532406</v>
+        <v>46175.87321719907</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70656489584</v>
+        <v>46175.873231562495</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2194,11 +2194,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46155.43894832176</v>
+        <v>46155.605614988424</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46161.45758516203</v>
+        <v>46161.6242518287</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2241,13 +2241,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46155.43908570602</v>
+        <v>46155.605752372685</v>
       </c>
       <c r="C11" s="9">
-        <v>46161.45756530092</v>
+        <v>46161.624231967595</v>
       </c>
       <c r="D11" s="9">
-        <v>46161.45758122685</v>
+        <v>46161.62424789352</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2306,13 +2306,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46155.43909342593</v>
+        <v>46155.60576009259</v>
       </c>
       <c r="C12" s="5">
-        <v>46161.457571701394</v>
+        <v>46161.62423836805</v>
       </c>
       <c r="D12" s="5">
-        <v>46161.457587627316</v>
+        <v>46161.62425429398</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2371,13 +2371,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="9">
-        <v>46155.43910125</v>
+        <v>46155.60576791667</v>
       </c>
       <c r="C13" s="9">
-        <v>46161.45757961806</v>
+        <v>46161.62424628472</v>
       </c>
       <c r="D13" s="9">
-        <v>46162.01431777778</v>
+        <v>46162.18098444444</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>59</v>
@@ -2436,11 +2436,11 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46155.439108506944</v>
+        <v>46155.60577517361</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46162.01431766203</v>
+        <v>46162.180984328705</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2499,11 +2499,11 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46155.43895318287</v>
+        <v>46155.605619849535</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46161.45763800926</v>
+        <v>46161.62430467593</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>66</v>
@@ -2546,13 +2546,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46155.43911810185</v>
+        <v>46155.605784768515</v>
       </c>
       <c r="C16" s="5">
-        <v>46161.45762405093</v>
+        <v>46161.62429071759</v>
       </c>
       <c r="D16" s="5">
-        <v>46161.45764068287</v>
+        <v>46161.624307349535</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2611,13 +2611,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46155.439125624995</v>
+        <v>46155.605792291666</v>
       </c>
       <c r="C17" s="9">
-        <v>46161.457631875004</v>
+        <v>46161.62429854167</v>
       </c>
       <c r="D17" s="9">
-        <v>46161.45764758102</v>
+        <v>46161.62431424769</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2676,11 +2676,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46155.43913309027</v>
+        <v>46155.605799756944</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46169.693910312504</v>
+        <v>46169.86057697917</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2739,11 +2739,11 @@
         <v>78</v>
       </c>
       <c r="B19" s="9">
-        <v>46155.43914079861</v>
+        <v>46155.60580746528</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46181.00093259259</v>
+        <v>46181.167599259265</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>79</v>
@@ -2802,11 +2802,11 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46155.43914765047</v>
+        <v>46155.605814317125</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46181.0009324537</v>
+        <v>46181.16759912037</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2865,11 +2865,11 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46155.43915342593</v>
+        <v>46155.60582009259</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46181.000932372684</v>
+        <v>46181.167599039356</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2928,11 +2928,11 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46155.439158946756</v>
+        <v>46155.60582561343</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46181.000932361116</v>
+        <v>46181.16759902777</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2991,11 +2991,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46155.438957962964</v>
+        <v>46155.60562462963</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46182.52708107639</v>
+        <v>46182.693747743055</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -3038,13 +3038,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46155.439165104166</v>
+        <v>46155.60583177084</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.51061494213</v>
+        <v>46182.6772816088</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.510626655094</v>
+        <v>46182.67729332176</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -3103,13 +3103,13 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46155.439172025464</v>
+        <v>46155.60583869213</v>
       </c>
       <c r="C25" s="9">
-        <v>46182.48660795139</v>
+        <v>46182.65327461806</v>
       </c>
       <c r="D25" s="9">
-        <v>46182.48660934028</v>
+        <v>46182.653276006946</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3164,13 +3164,13 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46155.43917895833</v>
+        <v>46155.605845625</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.51060081019</v>
+        <v>46182.67726747685</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.51060231481</v>
+        <v>46182.67726898148</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3225,11 +3225,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46155.43918560185</v>
+        <v>46155.60585226852</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46179.02861765046</v>
+        <v>46179.19528431713</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3288,11 +3288,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46155.4391921412</v>
+        <v>46155.605858807874</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.6940775463</v>
+        <v>46169.86074421296</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3347,11 +3347,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46155.439198622684</v>
+        <v>46155.605865289355</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46178.00457575232</v>
+        <v>46178.17124241898</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3406,13 +3406,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46155.43925858796</v>
+        <v>46155.605925254626</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.52707278935</v>
+        <v>46182.69373945602</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.52708459491</v>
+        <v>46182.69375126157</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3471,13 +3471,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46155.439265821755</v>
+        <v>46155.605932488426</v>
       </c>
       <c r="C31" s="9">
-        <v>46182.48641747685</v>
+        <v>46182.653084143516</v>
       </c>
       <c r="D31" s="9">
-        <v>46182.48641987269</v>
+        <v>46182.65308653935</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3532,13 +3532,13 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46155.439272777774</v>
+        <v>46155.605939444446</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.510444328705</v>
+        <v>46182.67711099537</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.51044608797</v>
+        <v>46182.67711275463</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3593,13 +3593,13 @@
         <v>128</v>
       </c>
       <c r="B33" s="9">
-        <v>46155.43927920139</v>
+        <v>46155.605945868054</v>
       </c>
       <c r="C33" s="9">
-        <v>46182.527057245374</v>
+        <v>46182.69372391204</v>
       </c>
       <c r="D33" s="9">
-        <v>46182.52705878472</v>
+        <v>46182.69372545139</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -3654,11 +3654,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46155.439285625005</v>
+        <v>46155.60595229166</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.693841099535</v>
+        <v>46169.86050776621</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3717,11 +3717,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46155.439292118055</v>
+        <v>46155.60595878473</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.69419811343</v>
+        <v>46169.860864780094</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3776,11 +3776,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46155.43929873843</v>
+        <v>46155.60596540509</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.69421677083</v>
+        <v>46169.860883437505</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3835,11 +3835,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46155.439304942134</v>
+        <v>46155.60597160879</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.69385555555</v>
+        <v>46169.860522222225</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3898,11 +3898,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46155.439310104164</v>
+        <v>46155.605976770836</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.694250162036</v>
+        <v>46169.86091682871</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3951,11 +3951,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46155.43931646991</v>
+        <v>46155.60598313657</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69426056713</v>
+        <v>46169.86092723379</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -4004,11 +4004,11 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46155.4393222338</v>
+        <v>46155.60598890047</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.693867974536</v>
+        <v>46169.86053464121</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -4067,11 +4067,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46155.43932773148</v>
+        <v>46155.60599439815</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.694297905095</v>
+        <v>46169.86096457176</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -4120,11 +4120,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46155.43933353009</v>
+        <v>46155.606000196756</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69431443287</v>
+        <v>46169.86098109954</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -4173,11 +4173,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46155.439339502314</v>
+        <v>46155.60600616898</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.694330729166</v>
+        <v>46169.86099739584</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4226,11 +4226,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46155.43934405093</v>
+        <v>46155.60601071759</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.69389917824</v>
+        <v>46169.86056584491</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4289,11 +4289,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46155.439347569445</v>
+        <v>46155.60601423611</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.69436508101</v>
+        <v>46169.861031747685</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>
@@ -4342,11 +4342,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46155.43935210648</v>
+        <v>46155.60601877315</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.69439675926</v>
+        <v>46169.861063425924</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4395,11 +4395,11 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46155.43896273148</v>
+        <v>46155.60562939815</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46155.43957519676</v>
+        <v>46155.606241863425</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4442,11 +4442,11 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46155.43935697917</v>
+        <v>46155.60602364583</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.01939998842</v>
+        <v>46169.18606665509</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4505,11 +4505,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46155.43936440972</v>
+        <v>46155.606031076386</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46184.03358746528</v>
+        <v>46184.200254131945</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>181</v>
@@ -4568,11 +4568,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46155.43937197917</v>
+        <v>46155.606038645834</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46184.00237559028</v>
+        <v>46184.169042256945</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>82</v>
@@ -4629,11 +4629,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="9">
-        <v>46155.439425081015</v>
+        <v>46155.606091747686</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.46824752315</v>
+        <v>46155.63491418981</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>187</v>
@@ -4692,11 +4692,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46155.439433437496</v>
+        <v>46155.60610010417</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.47550032407</v>
+        <v>46155.64216699074</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4743,11 +4743,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="9">
-        <v>46155.43943960648</v>
+        <v>46155.606106273146</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.47551712963</v>
+        <v>46155.6421837963</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>192</v>
@@ -4794,11 +4794,11 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.43944538194</v>
+        <v>46155.60611204861</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.47552612268</v>
+        <v>46155.64219278935</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>192</v>
@@ -4845,11 +4845,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="9">
-        <v>46155.439450046295</v>
+        <v>46155.60611671297</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.47553416667</v>
+        <v>46155.64220083333</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>192</v>
@@ -4896,11 +4896,11 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46155.46824611111</v>
+        <v>46155.63491277778</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.47556417824</v>
+        <v>46155.64223084491</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>192</v>
@@ -4947,11 +4947,11 @@
         <v>199</v>
       </c>
       <c r="B57" s="9">
-        <v>46155.439454583335</v>
+        <v>46155.60612125</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46155.439577083336</v>
+        <v>46155.60624375</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>200</v>
@@ -4994,11 +4994,11 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46155.4394581713</v>
+        <v>46155.60612483796</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46155.439577997684</v>
+        <v>46155.60624466435</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>203</v>
@@ -5057,11 +5057,11 @@
         <v>207</v>
       </c>
       <c r="B59" s="9">
-        <v>46155.43946650463</v>
+        <v>46155.6061331713</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46176.03346377314</v>
+        <v>46176.200130439815</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>208</v>
@@ -5120,11 +5120,11 @@
         <v>211</v>
       </c>
       <c r="B60" s="5">
-        <v>46155.4394747801</v>
+        <v>46155.606141446755</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.439579502316</v>
+        <v>46155.60624616898</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>212</v>
@@ -5183,11 +5183,11 @@
         <v>214</v>
       </c>
       <c r="B61" s="9">
-        <v>46155.43948282408</v>
+        <v>46155.60614949074</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46176.03346363426</v>
+        <v>46176.20013030093</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>215</v>
@@ -5246,11 +5246,11 @@
         <v>217</v>
       </c>
       <c r="B62" s="5">
-        <v>46155.43948965278</v>
+        <v>46155.606156319445</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.43958078704</v>
+        <v>46155.6062474537</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5309,11 +5309,11 @@
         <v>220</v>
       </c>
       <c r="B63" s="9">
-        <v>46155.4394972338</v>
+        <v>46155.60616390046</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46155.441792893515</v>
+        <v>46155.608459560186</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>219</v>
@@ -5372,11 +5372,11 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46155.43950415509</v>
+        <v>46155.60617082176</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.43977484954</v>
+        <v>46155.6064415162</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5419,11 +5419,11 @@
         <v>224</v>
       </c>
       <c r="B65" s="9">
-        <v>46155.43950746528</v>
+        <v>46155.60617413194</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.44959052083</v>
+        <v>46155.6162571875</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>225</v>
@@ -5482,11 +5482,11 @@
         <v>228</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.4395159375</v>
+        <v>46155.60618260417</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.44072061343</v>
+        <v>46155.60738728009</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>229</v>
@@ -5535,11 +5535,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.43952439815</v>
+        <v>46155.60619106481</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.450112245366</v>
+        <v>46155.61677891204</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>229</v>
@@ -5588,11 +5588,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46155.439531689815</v>
+        <v>46155.60619835649</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.450133645834</v>
+        <v>46155.6168003125</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5641,11 +5641,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46155.43953877315</v>
+        <v>46155.60620543981</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.45016523148</v>
+        <v>46155.61683189815</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>229</v>
@@ -5694,11 +5694,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46155.44078685185</v>
+        <v>46155.60745351852</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.45072724537</v>
+        <v>46155.617393912034</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>229</v>
@@ -5747,11 +5747,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46155.43954597222</v>
+        <v>46155.606212638886</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.45109189815</v>
+        <v>46155.61775856481</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5810,11 +5810,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.43955232639</v>
+        <v>46155.60621899305</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.452611562505</v>
+        <v>46155.61927822916</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>229</v>
@@ -5863,11 +5863,11 @@
         <v>243</v>
       </c>
       <c r="B73" s="9">
-        <v>46155.439559872684</v>
+        <v>46155.606226539356</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.45263408565</v>
+        <v>46155.61930075231</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>229</v>
@@ -5916,11 +5916,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46155.43956733796</v>
+        <v>46155.606234004634</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.45265121528</v>
+        <v>46155.619317881945</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>229</v>
@@ -5969,11 +5969,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46155.4396175463</v>
+        <v>46155.60628421296</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.45268454861</v>
+        <v>46155.61935121528</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>229</v>
@@ -6022,11 +6022,11 @@
         <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.441023368054</v>
+        <v>46155.607690034725</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.45271111111</v>
+        <v>46155.61937777778</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>229</v>
@@ -6075,11 +6075,11 @@
         <v>248</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.43962524306</v>
+        <v>46155.606291909724</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.45244517361</v>
+        <v>46155.61911184028</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>249</v>
@@ -6138,11 +6138,11 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46155.43963217593</v>
+        <v>46155.60629884259</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.453958252314</v>
+        <v>46155.620624918985</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>229</v>
@@ -6191,11 +6191,11 @@
         <v>252</v>
       </c>
       <c r="B79" s="9">
-        <v>46155.43963956018</v>
+        <v>46155.60630622685</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46155.45399222222</v>
+        <v>46155.62065888889</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>229</v>
@@ -6244,11 +6244,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46155.43964677083</v>
+        <v>46155.6063134375</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46155.45401431713</v>
+        <v>46155.6206809838</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>229</v>
@@ -6297,11 +6297,11 @@
         <v>255</v>
       </c>
       <c r="B81" s="9">
-        <v>46155.43965305555</v>
+        <v>46155.606319722225</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46155.45404643519</v>
+        <v>46155.62071310185</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>229</v>
@@ -6350,11 +6350,11 @@
         <v>256</v>
       </c>
       <c r="B82" s="5">
-        <v>46155.45165628473</v>
+        <v>46155.618322951384</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.45406971065</v>
+        <v>46155.620736377314</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>229</v>
@@ -6401,11 +6401,11 @@
         <v>257</v>
       </c>
       <c r="B83" s="9">
-        <v>46155.43965876158</v>
+        <v>46155.60632542824</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.43977684028</v>
+        <v>46155.60644350694</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>200</v>
@@ -6448,11 +6448,11 @@
         <v>259</v>
       </c>
       <c r="B84" s="5">
-        <v>46155.43966201389</v>
+        <v>46155.60632868056</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.03281046296</v>
+        <v>46182.19947712963</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>260</v>
@@ -6509,11 +6509,11 @@
         <v>262</v>
       </c>
       <c r="B85" s="9">
-        <v>46155.439669837964</v>
+        <v>46155.60633650463</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46182.51061935185</v>
+        <v>46182.677286018516</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>263</v>
@@ -6572,11 +6572,11 @@
         <v>265</v>
       </c>
       <c r="B86" s="5">
-        <v>46155.43967736111</v>
+        <v>46155.60634402778</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.51046064815</v>
+        <v>46182.67712731482</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>266</v>
@@ -6635,11 +6635,11 @@
         <v>268</v>
       </c>
       <c r="B87" s="9">
-        <v>46155.43968510417</v>
+        <v>46155.60635177083</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.43977976852</v>
+        <v>46155.60644643518</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>269</v>
@@ -6698,11 +6698,11 @@
         <v>271</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.43969525463</v>
+        <v>46155.606361921295</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.4401133912</v>
+        <v>46155.606780057875</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>272</v>
@@ -6745,11 +6745,11 @@
         <v>274</v>
       </c>
       <c r="B89" s="9">
-        <v>46155.43969858796</v>
+        <v>46155.60636525463</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.45368895833</v>
+        <v>46155.620355625</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>275</v>
@@ -6808,11 +6808,11 @@
         <v>277</v>
       </c>
       <c r="B90" s="5">
-        <v>46155.43970785879</v>
+        <v>46155.606374525465</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.454952835644</v>
+        <v>46155.621619502315</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>229</v>
@@ -6861,11 +6861,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="9">
-        <v>46155.43971361111</v>
+        <v>46155.60638027778</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.454969363425</v>
+        <v>46155.62163603009</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>229</v>
@@ -6914,11 +6914,11 @@
         <v>280</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.439719166665</v>
+        <v>46155.60638583334</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.45499407407</v>
+        <v>46155.62166074074</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>229</v>
@@ -6967,11 +6967,11 @@
         <v>282</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.43972512732</v>
+        <v>46155.60639179398</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.45500732639</v>
+        <v>46155.62167399305</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>229</v>
@@ -7020,11 +7020,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46155.45309319445</v>
+        <v>46155.61975986111</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.45502841435</v>
+        <v>46155.62169508102</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>229</v>
@@ -7073,11 +7073,11 @@
         <v>285</v>
       </c>
       <c r="B95" s="9">
-        <v>46155.43973116898</v>
+        <v>46155.60639783565</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.455249189814</v>
+        <v>46155.62191585648</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>286</v>
@@ -7136,11 +7136,11 @@
         <v>287</v>
       </c>
       <c r="B96" s="5">
-        <v>46155.439737361114</v>
+        <v>46155.60640402778</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.45458469907</v>
+        <v>46155.62125136574</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>229</v>
@@ -7187,11 +7187,11 @@
         <v>290</v>
       </c>
       <c r="B97" s="9">
-        <v>46155.43974423611</v>
+        <v>46155.60641090278</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.454564513886</v>
+        <v>46155.62123118056</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>229</v>
@@ -7238,11 +7238,11 @@
         <v>291</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.4397509375</v>
+        <v>46155.60641760417</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.4545487037</v>
+        <v>46155.62121537037</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>229</v>
@@ -7289,11 +7289,11 @@
         <v>294</v>
       </c>
       <c r="B99" s="9">
-        <v>46155.43975982639</v>
+        <v>46155.60642649306</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.45452690972</v>
+        <v>46155.621193576386</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>229</v>
@@ -7340,11 +7340,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46155.45449280093</v>
+        <v>46155.62115946759</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.47573361111</v>
+        <v>46155.64240027778</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>229</v>
@@ -7391,11 +7391,11 @@
         <v>296</v>
       </c>
       <c r="B101" s="9">
-        <v>46155.43981565972</v>
+        <v>46155.60648232639</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.4650037963</v>
+        <v>46155.631670462964</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>297</v>
@@ -7454,11 +7454,11 @@
         <v>298</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.439823761575</v>
+        <v>46155.60649042824</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.45545721065</v>
+        <v>46155.622123877314</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>229</v>
@@ -7505,11 +7505,11 @@
         <v>300</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.439832662036</v>
+        <v>46155.6064993287</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.45547680555</v>
+        <v>46155.622143472225</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>229</v>
@@ -7556,11 +7556,11 @@
         <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46155.43984128472</v>
+        <v>46155.606507951394</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.455500393524</v>
+        <v>46155.62216706018</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>229</v>
@@ -7607,11 +7607,11 @@
         <v>303</v>
       </c>
       <c r="B105" s="9">
-        <v>46155.439850497685</v>
+        <v>46155.60651716436</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.455513865745</v>
+        <v>46155.6221805324</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>229</v>
@@ -7658,11 +7658,11 @@
         <v>305</v>
       </c>
       <c r="B106" s="5">
-        <v>46155.45551484954</v>
+        <v>46155.6221815162</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.465126828705</v>
+        <v>46155.63179349537</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>229</v>
@@ -7709,11 +7709,11 @@
         <v>307</v>
       </c>
       <c r="B107" s="9">
-        <v>46155.43985913195</v>
+        <v>46155.60652579861</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.46789329861</v>
+        <v>46155.63455996528</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>308</v>
@@ -7772,11 +7772,11 @@
         <v>310</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.43986636574</v>
+        <v>46155.606533032405</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.46794229167</v>
+        <v>46155.63460895834</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>192</v>
@@ -7823,11 +7823,11 @@
         <v>313</v>
       </c>
       <c r="B109" s="9">
-        <v>46155.43987479167</v>
+        <v>46155.60654145833</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.46795101852</v>
+        <v>46155.63461768518</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>192</v>
@@ -7874,11 +7874,11 @@
         <v>314</v>
       </c>
       <c r="B110" s="5">
-        <v>46155.439887326385</v>
+        <v>46155.60655399306</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.46796212963</v>
+        <v>46155.634628796295</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>192</v>
@@ -7925,11 +7925,11 @@
         <v>316</v>
       </c>
       <c r="B111" s="9">
-        <v>46155.43989596065</v>
+        <v>46155.60656262732</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.46797625</v>
+        <v>46155.634642916666</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>192</v>
@@ -7976,11 +7976,11 @@
         <v>318</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.46344958333</v>
+        <v>46155.63011625</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.46799295139</v>
+        <v>46155.63465961805</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>192</v>
@@ -8027,11 +8027,11 @@
         <v>320</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.439904432875</v>
+        <v>46155.60657109953</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.46910777778</v>
+        <v>46155.63577444444</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>321</v>
@@ -8090,11 +8090,11 @@
         <v>322</v>
       </c>
       <c r="B114" s="5">
-        <v>46155.43991166667</v>
+        <v>46155.60657833333</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.46846142361</v>
+        <v>46155.635128090275</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>192</v>
@@ -8143,11 +8143,11 @@
         <v>324</v>
       </c>
       <c r="B115" s="9">
-        <v>46155.43991973379</v>
+        <v>46155.60658640046</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.46858908565</v>
+        <v>46155.63525575231</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>192</v>
@@ -8196,11 +8196,11 @@
         <v>325</v>
       </c>
       <c r="B116" s="5">
-        <v>46155.43992741898</v>
+        <v>46155.60659408565</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.46860208333</v>
+        <v>46155.635268750004</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>192</v>
@@ -8249,11 +8249,11 @@
         <v>327</v>
       </c>
       <c r="B117" s="9">
-        <v>46155.4399356713</v>
+        <v>46155.60660233797</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.46862590278</v>
+        <v>46155.635292569445</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>192</v>
@@ -8302,11 +8302,11 @@
         <v>328</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.467314699075</v>
+        <v>46155.63398136574</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.46915189815</v>
+        <v>46155.63581856481</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>192</v>
@@ -8353,11 +8353,11 @@
         <v>329</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.439975243055</v>
+        <v>46155.60664190972</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.47028125</v>
+        <v>46155.63694791667</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>330</v>
@@ -8416,11 +8416,11 @@
         <v>332</v>
       </c>
       <c r="B120" s="5">
-        <v>46155.43998414352</v>
+        <v>46155.60665081019</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.47143363426</v>
+        <v>46155.63810030093</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>192</v>
@@ -8467,11 +8467,11 @@
         <v>334</v>
       </c>
       <c r="B121" s="9">
-        <v>46155.43999158565</v>
+        <v>46155.60665825232</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.47145516204</v>
+        <v>46155.6381218287</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>192</v>
@@ -8518,11 +8518,11 @@
         <v>336</v>
       </c>
       <c r="B122" s="5">
-        <v>46155.43999868055</v>
+        <v>46155.60666534722</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.47146984954</v>
+        <v>46155.63813651621</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>192</v>
@@ -8569,11 +8569,11 @@
         <v>337</v>
       </c>
       <c r="B123" s="9">
-        <v>46155.440005868055</v>
+        <v>46155.60667253472</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.47148512732</v>
+        <v>46155.63815179398</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>192</v>
@@ -8620,11 +8620,11 @@
         <v>338</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.46924918982</v>
+        <v>46155.63591585648</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.47150540509</v>
+        <v>46155.63817207176</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>192</v>
@@ -8671,11 +8671,11 @@
         <v>339</v>
       </c>
       <c r="B125" s="9">
-        <v>46155.44001283565</v>
+        <v>46155.606679502314</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.44022796296</v>
+        <v>46155.60689462963</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>340</v>
@@ -8718,11 +8718,11 @@
         <v>342</v>
       </c>
       <c r="B126" s="5">
-        <v>46155.44001667824</v>
+        <v>46155.60668334491</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.47136972222</v>
+        <v>46155.63803638889</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>343</v>
@@ -8779,11 +8779,11 @@
         <v>347</v>
       </c>
       <c r="B127" s="9">
-        <v>46155.4400250926</v>
+        <v>46155.606691759254</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.472361238426</v>
+        <v>46155.6390279051</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>192</v>
@@ -8830,11 +8830,11 @@
         <v>349</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.44003197917</v>
+        <v>46155.60669864583</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.47237116898</v>
+        <v>46155.639037835645</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>192</v>
@@ -8881,11 +8881,11 @@
         <v>350</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.44003949074</v>
+        <v>46155.60670615741</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.4723971412</v>
+        <v>46155.639063807874</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>192</v>
@@ -8932,11 +8932,11 @@
         <v>352</v>
       </c>
       <c r="B130" s="5">
-        <v>46155.44004634259</v>
+        <v>46155.606713009256</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.47240892361</v>
+        <v>46155.63907559028</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>192</v>
@@ -8983,11 +8983,11 @@
         <v>353</v>
       </c>
       <c r="B131" s="9">
-        <v>46155.470488900464</v>
+        <v>46155.63715556713</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.47243658565</v>
+        <v>46155.63910325231</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>192</v>
@@ -9034,11 +9034,11 @@
         <v>354</v>
       </c>
       <c r="B132" s="5">
-        <v>46155.44005320602</v>
+        <v>46155.60671987268</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.47224594907</v>
+        <v>46155.638912615745</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>355</v>
@@ -9097,11 +9097,11 @@
         <v>356</v>
       </c>
       <c r="B133" s="9">
-        <v>46155.44005991898</v>
+        <v>46155.60672658565</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.47315957176</v>
+        <v>46155.639826238425</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>192</v>
@@ -9150,11 +9150,11 @@
         <v>358</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.44006688657</v>
+        <v>46155.60673355324</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.47316949074</v>
+        <v>46155.63983615741</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>192</v>
@@ -9203,11 +9203,11 @@
         <v>360</v>
       </c>
       <c r="B135" s="9">
-        <v>46155.44007386574</v>
+        <v>46155.60674053241</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.47317827547</v>
+        <v>46155.639844942125</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>192</v>
@@ -9256,11 +9256,11 @@
         <v>361</v>
       </c>
       <c r="B136" s="5">
-        <v>46155.44008075232</v>
+        <v>46155.60674741898</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.47320202546</v>
+        <v>46155.63986869213</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>192</v>
@@ -9309,11 +9309,11 @@
         <v>362</v>
       </c>
       <c r="B137" s="9">
-        <v>46155.471635995375</v>
+        <v>46155.63830266204</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46155.47323336806</v>
+        <v>46155.63990003472</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>192</v>
@@ -9360,11 +9360,11 @@
         <v>363</v>
       </c>
       <c r="B138" s="5">
-        <v>46155.44008733796</v>
+        <v>46155.60675400463</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46155.473694976856</v>
+        <v>46155.64036164352</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>364</v>
@@ -9423,11 +9423,11 @@
         <v>365</v>
       </c>
       <c r="B139" s="9">
-        <v>46155.44009438658</v>
+        <v>46155.60676105324</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46155.47595208333</v>
+        <v>46155.642618750004</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>192</v>
@@ -9474,11 +9474,11 @@
         <v>367</v>
       </c>
       <c r="B140" s="5">
-        <v>46155.44010346065</v>
+        <v>46155.60677012731</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46155.475964247686</v>
+        <v>46155.64263091436</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>192</v>
@@ -9525,11 +9525,11 @@
         <v>368</v>
       </c>
       <c r="B141" s="9">
-        <v>46155.44015070602</v>
+        <v>46155.60681737268</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46155.475974444445</v>
+        <v>46155.64264111111</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>192</v>
@@ -9576,11 +9576,11 @@
         <v>370</v>
       </c>
       <c r="B142" s="5">
-        <v>46155.440158819445</v>
+        <v>46155.60682548611</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46155.47598528935</v>
+        <v>46155.64265195602</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>192</v>
@@ -9627,11 +9627,11 @@
         <v>371</v>
       </c>
       <c r="B143" s="9">
-        <v>46155.47261759259</v>
+        <v>46155.63928425926</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46155.476001689814</v>
+        <v>46155.64266835648</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>192</v>
@@ -9678,11 +9678,11 @@
         <v>372</v>
       </c>
       <c r="B144" s="5">
-        <v>46155.440165625</v>
+        <v>46155.60683229167</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46155.47531915509</v>
+        <v>46155.641985821756</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>373</v>
@@ -9741,11 +9741,11 @@
         <v>375</v>
       </c>
       <c r="B145" s="9">
-        <v>46155.44017381944</v>
+        <v>46155.606840486114</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46155.47540736111</v>
+        <v>46155.64207402778</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>192</v>
@@ -9792,11 +9792,11 @@
         <v>376</v>
       </c>
       <c r="B146" s="5">
-        <v>46155.440180798614</v>
+        <v>46155.60684746528</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46155.47541702546</v>
+        <v>46155.64208369213</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>192</v>
@@ -9843,11 +9843,11 @@
         <v>377</v>
       </c>
       <c r="B147" s="9">
-        <v>46155.44018721065</v>
+        <v>46155.60685387731</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46155.47542673611</v>
+        <v>46155.64209340278</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>192</v>
@@ -9894,11 +9894,11 @@
         <v>378</v>
       </c>
       <c r="B148" s="5">
-        <v>46155.44019435185</v>
+        <v>46155.60686101852</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46155.475440532406</v>
+        <v>46155.64210719908</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>192</v>
@@ -9945,11 +9945,11 @@
         <v>379</v>
       </c>
       <c r="B149" s="9">
-        <v>46155.47386108796</v>
+        <v>46155.64052775463</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46155.47546430556</v>
+        <v>46155.64213097222</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>192</v>
@@ -9996,11 +9996,11 @@
         <v>380</v>
       </c>
       <c r="B150" s="5">
-        <v>46155.440201307865</v>
+        <v>46155.60686797454</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46155.440229722226</v>
+        <v>46155.60689638889</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>381</v>
@@ -10043,11 +10043,11 @@
         <v>383</v>
       </c>
       <c r="B151" s="9">
-        <v>46155.44020540509</v>
+        <v>46155.60687207176</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46155.44023042824</v>
+        <v>46155.60689709491</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>384</v>
@@ -10106,11 +10106,11 @@
         <v>387</v>
       </c>
       <c r="B152" s="5">
-        <v>46155.44021259259</v>
+        <v>46155.606879259256</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46155.44023094907</v>
+        <v>46155.60689761574</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>388</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -2743,7 +2743,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46181.167599259265</v>
+        <v>46188.169931805554</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>79</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46181.16759912037</v>
+        <v>46188.16993363426</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46181.167599039356</v>
+        <v>46188.16993483796</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46181.16759902777</v>
+        <v>46188.16993618055</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -284,118 +284,118 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4316</t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1214777481542258</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma OT 4316</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4316</t>
+  </si>
+  <si>
+    <t>1214777561381920</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1214777561381936</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4316</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4316</t>
+  </si>
+  <si>
+    <t>1214739697907731</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe OT 4316 ,Materiales corte Laser OT 4316,rodete OT 4316,Motor OT 4316</t>
+  </si>
+  <si>
+    <t>1214777481578466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alabe OT 4316 </t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4316,Generación OC Alabe OT 4316</t>
+  </si>
+  <si>
+    <t>1214777481578487</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Alabe OT 4316,Alabe OT 4316 </t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1214777594099850</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4316</t>
+  </si>
+  <si>
+    <t>Alabe OT 4316 ,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214777561416071</t>
+  </si>
+  <si>
+    <t>rodete OT 4316</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4316,Generación OC Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>1214777561424621</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4316,rodete OT 4316</t>
+  </si>
+  <si>
+    <t>1214777561424645</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>rodete OT 4316,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214777626585671</t>
+  </si>
+  <si>
+    <t>Motor OT 4316</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4316,Fabricación motor OT 4316,Planos motor proveedor OT 4316</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214777481542258</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma OT 4316</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4316</t>
-  </si>
-  <si>
-    <t>1214777561381920</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1214777561381936</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4316</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4316</t>
-  </si>
-  <si>
-    <t>1214739697907731</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe OT 4316 ,Materiales corte Laser OT 4316,rodete OT 4316,Motor OT 4316</t>
-  </si>
-  <si>
-    <t>1214777481578466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alabe OT 4316 </t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4316,Generación OC Alabe OT 4316</t>
-  </si>
-  <si>
-    <t>1214777481578487</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Alabe OT 4316,Alabe OT 4316 </t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1214777594099850</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4316</t>
-  </si>
-  <si>
-    <t>Alabe OT 4316 ,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214777561416071</t>
-  </si>
-  <si>
-    <t>rodete OT 4316</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4316,Generación OC Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>1214777561424621</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4316,rodete OT 4316</t>
-  </si>
-  <si>
-    <t>1214777561424645</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>rodete OT 4316,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214777626585671</t>
-  </si>
-  <si>
-    <t>Motor OT 4316</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4316,Fabricación motor OT 4316,Planos motor proveedor OT 4316</t>
   </si>
   <si>
     <t>1214777626585692</t>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46188.169931805554</v>
+        <v>46189.193734155095</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>79</v>
@@ -2787,29 +2787,29 @@
       <c r="R19" s="9">
         <v>46188</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>84</v>
+      <c r="S19" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46155.605814317125</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46188.16993363426</v>
+        <v>46189.193734155095</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2842,7 +2842,7 @@
         <v>82</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2850,29 +2850,29 @@
       <c r="R20" s="5">
         <v>46188</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>84</v>
+      <c r="S20" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46155.60582009259</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46188.16993483796</v>
+        <v>46189.193734560184</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2905,7 +2905,7 @@
         <v>82</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2913,29 +2913,29 @@
       <c r="R21" s="9">
         <v>46188</v>
       </c>
-      <c r="S21" s="12" t="s">
-        <v>84</v>
+      <c r="S21" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46155.60582561343</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46188.16993618055</v>
+        <v>46189.193734201384</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2968,7 +2968,7 @@
         <v>82</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="5">
         <v>46185</v>
@@ -2976,19 +2976,19 @@
       <c r="R22" s="5">
         <v>46188</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>84</v>
+      <c r="S22" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46155.60562462963</v>
@@ -2998,7 +2998,7 @@
         <v>46182.693747743055</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -3022,7 +3022,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46155.60583177084</v>
@@ -3047,16 +3047,16 @@
         <v>46182.67729332176</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3074,13 +3074,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="5">
         <v>46157</v>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46155.60583869213</v>
@@ -3112,16 +3112,16 @@
         <v>46182.653276006946</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>101</v>
       </c>
       <c r="I25" s="9">
         <v>46157</v>
@@ -3139,29 +3139,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46155.605845625</v>
@@ -3173,16 +3173,16 @@
         <v>46182.67726898148</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I26" s="5">
         <v>46161</v>
@@ -3200,29 +3200,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46155.60585226852</v>
@@ -3232,16 +3232,16 @@
         <v>46179.19528431713</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>101</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
@@ -3259,13 +3259,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q27" s="9">
         <v>46157</v>
@@ -3280,12 +3280,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46155.605858807874</v>
@@ -3295,16 +3295,16 @@
         <v>46169.86074421296</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I28" s="5">
         <v>46157</v>
@@ -3322,29 +3322,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46155.605865289355</v>
@@ -3354,16 +3354,16 @@
         <v>46178.17124241898</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>101</v>
       </c>
       <c r="I29" s="9">
         <v>46161</v>
@@ -3381,29 +3381,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46155.605925254626</v>
@@ -3412,19 +3412,19 @@
         <v>46182.69373945602</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.69375126157</v>
+        <v>46189.18607957176</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3442,13 +3442,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q30" s="5">
         <v>46157</v>
@@ -3456,8 +3456,8 @@
       <c r="R30" s="5">
         <v>46196</v>
       </c>
-      <c r="S30" s="7" t="s">
-        <v>106</v>
+      <c r="S30" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3486,10 +3486,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>101</v>
       </c>
       <c r="I31" s="9">
         <v>46157</v>
@@ -3507,7 +3507,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>69</v>
@@ -3518,13 +3518,13 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3547,10 +3547,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3568,7 +3568,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>123</v>
@@ -3579,13 +3579,13 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3608,10 +3608,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>101</v>
       </c>
       <c r="I33" s="9">
         <v>46168</v>
@@ -3629,7 +3629,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>123</v>
@@ -3640,13 +3640,13 @@
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3688,13 +3688,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q34" s="5">
         <v>46189</v>
@@ -3703,13 +3703,13 @@
         <v>46199</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3762,13 +3762,13 @@
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3821,13 +3821,13 @@
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3869,7 +3869,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>144</v>
@@ -3884,13 +3884,13 @@
         <v>46199</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3905,7 +3905,7 @@
         <v>46169.86091682871</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3935,7 +3935,7 @@
         <v>143</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>146</v>
@@ -3988,7 +3988,7 @@
         <v>143</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>149</v>
@@ -4038,7 +4038,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>154</v>
@@ -4053,13 +4053,13 @@
         <v>46230</v>
       </c>
       <c r="S40" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4074,7 +4074,7 @@
         <v>46169.86096457176</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4104,7 +4104,7 @@
         <v>151</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>156</v>
@@ -4157,7 +4157,7 @@
         <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>159</v>
@@ -4260,7 +4260,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>166</v>
@@ -4275,13 +4275,13 @@
         <v>46210</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4296,7 +4296,7 @@
         <v>46169.861031747685</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4326,7 +4326,7 @@
         <v>165</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>168</v>
@@ -4379,7 +4379,7 @@
         <v>165</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>171</v>
@@ -4560,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4615,13 +4615,13 @@
         <v>46153</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4678,13 +4678,13 @@
         <v>46241</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -5043,13 +5043,13 @@
         <v>46203</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5112,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5169,13 +5169,13 @@
         <v>46203</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5295,13 +5295,13 @@
         <v>46212</v>
       </c>
       <c r="S62" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5358,13 +5358,13 @@
         <v>46216</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5468,13 +5468,13 @@
         <v>46219</v>
       </c>
       <c r="S65" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5796,13 +5796,13 @@
         <v>46226</v>
       </c>
       <c r="S71" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -6124,13 +6124,13 @@
         <v>46227</v>
       </c>
       <c r="S77" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6483,7 +6483,7 @@
         <v>200</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>261</v>
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6546,7 +6546,7 @@
         <v>200</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>264</v>
@@ -6621,7 +6621,7 @@
         <v>46197</v>
       </c>
       <c r="S86" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6684,13 +6684,13 @@
         <v>46231</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6794,13 +6794,13 @@
         <v>46234</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -7122,13 +7122,13 @@
         <v>46237</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7440,13 +7440,13 @@
         <v>46238</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7758,13 +7758,13 @@
         <v>46239</v>
       </c>
       <c r="S107" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -8076,13 +8076,13 @@
         <v>46240</v>
       </c>
       <c r="S113" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T113" s="10">
         <v>0</v>
       </c>
       <c r="U113" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
@@ -8402,13 +8402,13 @@
         <v>46244</v>
       </c>
       <c r="S119" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T119" s="10">
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -8765,13 +8765,13 @@
         <v>46245</v>
       </c>
       <c r="S126" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T126" s="6">
         <v>0</v>
       </c>
       <c r="U126" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
@@ -9083,13 +9083,13 @@
         <v>46246</v>
       </c>
       <c r="S132" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T132" s="6">
         <v>0</v>
       </c>
       <c r="U132" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
@@ -9409,13 +9409,13 @@
         <v>46247</v>
       </c>
       <c r="S138" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T138" s="6">
         <v>0</v>
       </c>
       <c r="U138" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
@@ -9727,13 +9727,13 @@
         <v>46248</v>
       </c>
       <c r="S144" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T144" s="6">
         <v>0</v>
       </c>
       <c r="U144" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
@@ -10092,13 +10092,13 @@
         <v>46255</v>
       </c>
       <c r="S151" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T151" s="10">
         <v>0</v>
       </c>
       <c r="U151" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
@@ -10155,13 +10155,13 @@
         <v>46255</v>
       </c>
       <c r="S152" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T152" s="6">
         <v>0</v>
       </c>
       <c r="U152" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -3721,7 +3721,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.860864780094</v>
+        <v>46190.169097499995</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.86091682871</v>
+        <v>46190.16909938658</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>87</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.861031747685</v>
+        <v>46190.1691007176</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>90</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -6576,7 +6576,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.67712731482</v>
+        <v>46190.1908316551</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>266</v>
@@ -6620,8 +6620,8 @@
       <c r="R86" s="5">
         <v>46197</v>
       </c>
-      <c r="S86" s="7" t="s">
-        <v>105</v>
+      <c r="S86" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -3658,7 +3658,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.86050776621</v>
+        <v>46192.17448341435</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3702,8 +3702,8 @@
       <c r="R34" s="5">
         <v>46199</v>
       </c>
-      <c r="S34" s="7" t="s">
-        <v>105</v>
+      <c r="S34" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.860522222225</v>
+        <v>46192.17454548611</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3883,8 +3883,8 @@
       <c r="R37" s="9">
         <v>46199</v>
       </c>
-      <c r="S37" s="7" t="s">
-        <v>105</v>
+      <c r="S37" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="385">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -173,7 +173,7 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Ingenieria Detalle,Analisis de costeo,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214777594013137</t>
@@ -185,7 +185,7 @@
     <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
   </si>
   <si>
-    <t>Analisis de costeo,propuesta motor,Ingenieria Jefe de proyecto:</t>
+    <t>propuesta motor,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>1214777594013163</t>
@@ -203,7 +203,7 @@
 </t>
   </si>
   <si>
-    <t>Analisis de costeo,propuesta alabes,propuesta nucleo rodeteOT 4316,Ingenieria Jefe de proyecto:</t>
+    <t>propuesta alabes,propuesta nucleo rodeteOT 4316,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>1214777626422407</t>
@@ -212,19 +212,7 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1214777481523019</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
+    <t>Ingenieria Jefe de proyecto:,Planos preliminar</t>
   </si>
   <si>
     <t>1214739697907729</t>
@@ -1197,9 +1185,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Despacho</t>
   </si>
 </sst>
 </file>
@@ -1723,7 +1708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U152"/>
+  <dimension ref="A1:U151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2198,7 +2183,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46161.6242518287</v>
+        <v>46195.546774409726</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2225,7 +2210,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2234,7 +2219,9 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="U10" s="12" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -2247,7 +2234,7 @@
         <v>46161.624231967595</v>
       </c>
       <c r="D11" s="9">
-        <v>46161.62424789352</v>
+        <v>46195.54676366899</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2312,7 +2299,7 @@
         <v>46161.62423836805</v>
       </c>
       <c r="D12" s="5">
-        <v>46161.62425429398</v>
+        <v>46195.54676375</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2377,7 +2364,7 @@
         <v>46161.62424628472</v>
       </c>
       <c r="D13" s="9">
-        <v>46162.18098444444</v>
+        <v>46195.546763645834</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>59</v>
@@ -2436,30 +2423,24 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46155.60577517361</v>
+        <v>46155.605619849535</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46162.180984328705</v>
+        <v>46161.62430467593</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="5">
-        <v>46153</v>
-      </c>
-      <c r="J14" s="5">
-        <v>46161</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
         <v>26</v>
       </c>
@@ -2467,95 +2448,103 @@
         <v>26</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>46153</v>
-      </c>
-      <c r="R14" s="5">
-        <v>46161</v>
-      </c>
-      <c r="S14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="12" t="s">
-        <v>64</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46155.605784768515</v>
+      </c>
+      <c r="C15" s="9">
+        <v>46161.62429071759</v>
+      </c>
+      <c r="D15" s="9">
+        <v>46161.624307349535</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="9">
-        <v>46155.605619849535</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="9">
-        <v>46161.62430467593</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="F15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="9">
+        <v>46155</v>
+      </c>
+      <c r="J15" s="9">
+        <v>46156</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
+      <c r="Q15" s="9">
+        <v>46155</v>
+      </c>
+      <c r="R15" s="9">
+        <v>46156</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="10">
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46155.605792291666</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46161.62429854167</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46161.62431424769</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="B16" s="5">
-        <v>46155.605784768515</v>
-      </c>
-      <c r="C16" s="5">
-        <v>46161.62429071759</v>
-      </c>
-      <c r="D16" s="5">
-        <v>46161.624307349535</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2582,13 +2571,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q16" s="5">
         <v>46155</v>
@@ -2608,28 +2597,26 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46155.605799756944</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9">
+        <v>46169.86057697917</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="9">
-        <v>46155.605792291666</v>
-      </c>
-      <c r="C17" s="9">
-        <v>46161.62429854167</v>
-      </c>
-      <c r="D17" s="9">
-        <v>46161.62431424769</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="H17" s="10" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="I17" s="9">
         <v>46155</v>
@@ -2647,7 +2634,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>55</v>
@@ -2665,10 +2652,10 @@
         <v>33</v>
       </c>
       <c r="T17" s="10">
-        <v>1</v>
-      </c>
-      <c r="U17" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U17" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2676,11 +2663,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46155.605799756944</v>
+        <v>46155.60580746528</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46169.86057697917</v>
+        <v>46189.193734155095</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2692,13 +2679,13 @@
         <v>76</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I18" s="5">
-        <v>46155</v>
+        <v>46185</v>
       </c>
       <c r="J18" s="5">
-        <v>46156</v>
+        <v>46188</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>26</v>
@@ -2710,19 +2697,19 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
-        <v>46155</v>
+        <v>46185</v>
       </c>
       <c r="R18" s="5">
-        <v>46156</v>
+        <v>46188</v>
       </c>
       <c r="S18" s="11" t="s">
         <v>33</v>
@@ -2730,32 +2717,32 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>64</v>
+      <c r="U18" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46155.60580746528</v>
+        <v>46155.605814317125</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
         <v>46189.193734155095</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I19" s="9">
         <v>46185</v>
@@ -2773,10 +2760,10 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>83</v>
@@ -2794,31 +2781,31 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46155.605814317125</v>
+        <v>46155.60582009259</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46189.193734155095</v>
+        <v>46189.193734560184</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I20" s="5">
         <v>46185</v>
@@ -2836,13 +2823,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2857,31 +2844,31 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46155.60582009259</v>
+        <v>46155.60582561343</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.193734560184</v>
+        <v>46189.193734201384</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I21" s="9">
         <v>46185</v>
@@ -2899,13 +2886,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2920,95 +2907,87 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46155.60582561343</v>
+        <v>46155.60562462963</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46189.193734201384</v>
+        <v>46182.693747743055</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="I22" s="5">
-        <v>46185</v>
-      </c>
-      <c r="J22" s="5">
-        <v>46188</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="P22" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>46185</v>
-      </c>
-      <c r="R22" s="5">
-        <v>46188</v>
-      </c>
-      <c r="S22" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46155.60583177084</v>
+      </c>
+      <c r="C23" s="9">
+        <v>46182.6772816088</v>
+      </c>
+      <c r="D23" s="9">
+        <v>46182.67729332176</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="9">
-        <v>46155.60562462963</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="9">
-        <v>46182.693747743055</v>
-      </c>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+      <c r="H23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="9">
+        <v>46157</v>
+      </c>
+      <c r="J23" s="9">
+        <v>46162</v>
+      </c>
       <c r="K23" s="10" t="s">
         <v>26</v>
       </c>
@@ -3016,53 +2995,63 @@
         <v>26</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>46157</v>
+      </c>
+      <c r="R23" s="9">
+        <v>46162</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" s="10">
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46155.60583177084</v>
+        <v>46155.60583869213</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.6772816088</v>
+        <v>46182.65327461806</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.67729332176</v>
+        <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
       </c>
       <c r="J24" s="5">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>26</v>
@@ -3074,28 +3063,24 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="P24" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>46157</v>
-      </c>
-      <c r="R24" s="5">
-        <v>46162</v>
-      </c>
-      <c r="S24" s="11" t="s">
-        <v>33</v>
-      </c>
       <c r="T24" s="6">
-        <v>1</v>
-      </c>
-      <c r="U24" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3103,13 +3088,13 @@
         <v>102</v>
       </c>
       <c r="B25" s="9">
-        <v>46155.60583869213</v>
+        <v>46155.605845625</v>
       </c>
       <c r="C25" s="9">
-        <v>46182.65327461806</v>
+        <v>46182.67726747685</v>
       </c>
       <c r="D25" s="9">
-        <v>46182.653276006946</v>
+        <v>46182.67726898148</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>103</v>
@@ -3118,31 +3103,31 @@
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I25" s="9">
+        <v>46161</v>
+      </c>
+      <c r="J25" s="9">
+        <v>46162</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="O25" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I25" s="9">
-        <v>46157</v>
-      </c>
-      <c r="J25" s="9">
-        <v>46160</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="O25" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>104</v>
@@ -3150,104 +3135,106 @@
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46155.60585226852</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5">
+        <v>46179.19528431713</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B26" s="5">
-        <v>46155.605845625</v>
-      </c>
-      <c r="C26" s="5">
-        <v>46182.67726747685</v>
-      </c>
-      <c r="D26" s="5">
-        <v>46182.67726898148</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26" s="5">
+        <v>46157</v>
+      </c>
+      <c r="J26" s="5">
+        <v>46178</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="O26" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="5">
-        <v>46161</v>
-      </c>
-      <c r="J26" s="5">
-        <v>46162</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="P26" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="7" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>46157</v>
+      </c>
+      <c r="R26" s="5">
+        <v>46178</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
-        <v>46155.60585226852</v>
+        <v>46155.605858807874</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46179.19528431713</v>
+        <v>46169.86074421296</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
       </c>
       <c r="J27" s="9">
-        <v>46178</v>
+        <v>46160</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>26</v>
@@ -3259,146 +3246,148 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>46157</v>
-      </c>
-      <c r="R27" s="9">
-        <v>46178</v>
-      </c>
-      <c r="S27" s="11" t="s">
-        <v>33</v>
+        <v>110</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46155.605858807874</v>
+        <v>46155.605865289355</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.86074421296</v>
+        <v>46178.17124241898</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I28" s="5">
+        <v>46161</v>
+      </c>
+      <c r="J28" s="5">
+        <v>46178</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P28" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I28" s="5">
-        <v>46157</v>
-      </c>
-      <c r="J28" s="5">
-        <v>46160</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="9">
+        <v>46155.605925254626</v>
+      </c>
+      <c r="C29" s="9">
+        <v>46182.69373945602</v>
+      </c>
+      <c r="D29" s="9">
+        <v>46189.18607957176</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="9">
-        <v>46155.605865289355</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="9">
-        <v>46178.17124241898</v>
-      </c>
-      <c r="E29" s="10" t="s">
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I29" s="9">
+        <v>46157</v>
+      </c>
+      <c r="J29" s="9">
+        <v>46196</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O29" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I29" s="9">
-        <v>46161</v>
-      </c>
-      <c r="J29" s="9">
-        <v>46178</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>113</v>
-      </c>
       <c r="P29" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>46157</v>
+      </c>
+      <c r="R29" s="9">
+        <v>46196</v>
+      </c>
+      <c r="S29" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="7" t="s">
-        <v>105</v>
-      </c>
       <c r="T29" s="10">
-        <v>0</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3406,13 +3395,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46155.605925254626</v>
+        <v>46155.605932488426</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.69373945602</v>
+        <v>46182.653084143516</v>
       </c>
       <c r="D30" s="5">
-        <v>46189.18607957176</v>
+        <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3421,16 +3410,16 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
       </c>
       <c r="J30" s="5">
-        <v>46196</v>
+        <v>46167</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -3442,121 +3431,117 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="P30" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="P30" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>46157</v>
-      </c>
-      <c r="R30" s="5">
-        <v>46196</v>
-      </c>
-      <c r="S30" s="12" t="s">
-        <v>121</v>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="T30" s="6">
-        <v>1</v>
-      </c>
-      <c r="U30" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U30" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46155.605939444446</v>
+      </c>
+      <c r="C31" s="9">
+        <v>46182.67711099537</v>
+      </c>
+      <c r="D31" s="9">
+        <v>46182.67711275463</v>
+      </c>
+      <c r="E31" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="9">
-        <v>46155.605932488426</v>
-      </c>
-      <c r="C31" s="9">
-        <v>46182.653084143516</v>
-      </c>
-      <c r="D31" s="9">
-        <v>46182.65308653935</v>
-      </c>
-      <c r="E31" s="10" t="s">
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I31" s="9">
+        <v>46168</v>
+      </c>
+      <c r="J31" s="9">
+        <v>46196</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="O31" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="P31" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I31" s="9">
-        <v>46157</v>
-      </c>
-      <c r="J31" s="9">
-        <v>46167</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P31" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46155.605945868054</v>
+      </c>
+      <c r="C32" s="5">
+        <v>46182.69372391204</v>
+      </c>
+      <c r="D32" s="5">
+        <v>46182.69372545139</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="5">
-        <v>46155.605939444446</v>
-      </c>
-      <c r="C32" s="5">
-        <v>46182.67711099537</v>
-      </c>
-      <c r="D32" s="5">
-        <v>46182.67711275463</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
       </c>
       <c r="J32" s="5">
-        <v>46196</v>
+        <v>46176</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3568,56 +3553,54 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46155.60595229166</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9">
+        <v>46192.17448341435</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B33" s="9">
-        <v>46155.605945868054</v>
-      </c>
-      <c r="C33" s="9">
-        <v>46182.69372391204</v>
-      </c>
-      <c r="D33" s="9">
-        <v>46182.69372545139</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="H33" s="10" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="I33" s="9">
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="J33" s="9">
-        <v>46176</v>
+        <v>46199</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>26</v>
@@ -3629,54 +3612,58 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="7" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>46189</v>
+      </c>
+      <c r="R33" s="9">
+        <v>46199</v>
+      </c>
+      <c r="S33" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46155.60595229166</v>
+        <v>46155.60595878473</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46192.17448341435</v>
+        <v>46190.169097499995</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
       </c>
       <c r="J34" s="5">
-        <v>46199</v>
+        <v>46190</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
@@ -3688,114 +3675,110 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>46189</v>
-      </c>
-      <c r="R34" s="5">
-        <v>46199</v>
-      </c>
-      <c r="S34" s="12" t="s">
-        <v>121</v>
+        <v>134</v>
+      </c>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46155.60595878473</v>
+        <v>46155.60596540509</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46190.169097499995</v>
+        <v>46169.860883437505</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I35" s="9">
+        <v>46191</v>
+      </c>
+      <c r="J35" s="9">
+        <v>46199</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="O35" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="P35" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="I35" s="9">
-        <v>46189</v>
-      </c>
-      <c r="J35" s="9">
-        <v>46190</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="P35" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46155.60596540509</v>
+        <v>46155.60597160879</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.860883437505</v>
+        <v>46192.17454548611</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="J36" s="5">
         <v>46199</v>
@@ -3810,54 +3793,58 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="7" t="s">
-        <v>105</v>
+        <v>26</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>46189</v>
+      </c>
+      <c r="R36" s="5">
+        <v>46199</v>
+      </c>
+      <c r="S36" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46155.60597160879</v>
+        <v>46155.605976770836</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46192.17454548611</v>
+        <v>46190.16909938658</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
       </c>
       <c r="J37" s="9">
-        <v>46199</v>
+        <v>46190</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>26</v>
@@ -3869,58 +3856,48 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q37" s="9">
-        <v>46189</v>
-      </c>
-      <c r="R37" s="9">
-        <v>46199</v>
-      </c>
-      <c r="S37" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="T37" s="10">
-        <v>0</v>
-      </c>
-      <c r="U37" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46155.605976770836</v>
+        <v>46155.60598313657</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46190.16909938658</v>
+        <v>46169.86092723379</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="J38" s="5">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>26</v>
@@ -3932,13 +3909,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3948,32 +3925,32 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46155.60598313657</v>
+        <v>46155.60598890047</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.86092723379</v>
+        <v>46169.86053464121</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>133</v>
-      </c>
       <c r="H39" s="10" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="J39" s="9">
-        <v>46199</v>
+        <v>46230</v>
       </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
@@ -3985,48 +3962,58 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>46189</v>
+      </c>
+      <c r="R39" s="9">
+        <v>46230</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T39" s="10">
+        <v>0</v>
+      </c>
+      <c r="U39" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46155.60598890047</v>
+        <v>46155.60599439815</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.86053464121</v>
+        <v>46169.86096457176</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>151</v>
+        <v>89</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
       </c>
       <c r="J40" s="5">
-        <v>46230</v>
+        <v>46197</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -4038,58 +4025,48 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>154</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>46189</v>
-      </c>
-      <c r="R40" s="5">
-        <v>46230</v>
-      </c>
-      <c r="S40" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T40" s="6">
-        <v>0</v>
-      </c>
-      <c r="U40" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46155.60599439815</v>
+        <v>46155.606000196756</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.86096457176</v>
+        <v>46169.86098109954</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I41" s="9">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="J41" s="9">
-        <v>46197</v>
+        <v>46226</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>26</v>
@@ -4101,13 +4078,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4117,32 +4094,32 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46155.606000196756</v>
+        <v>46155.60600616898</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.86098109954</v>
+        <v>46169.86099739584</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="H42" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
-        <v>46198</v>
+        <v>46227</v>
       </c>
       <c r="J42" s="5">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>26</v>
@@ -4154,13 +4131,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4173,11 +4150,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46155.60600616898</v>
+        <v>46155.60601071759</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.86099739584</v>
+        <v>46169.86056584491</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4186,69 +4163,79 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I43" s="9">
+        <v>46189</v>
+      </c>
+      <c r="J43" s="9">
+        <v>46210</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O43" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="H43" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I43" s="9">
-        <v>46227</v>
-      </c>
-      <c r="J43" s="9">
-        <v>46230</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>158</v>
-      </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="10"/>
-      <c r="U43" s="10"/>
+      <c r="Q43" s="9">
+        <v>46189</v>
+      </c>
+      <c r="R43" s="9">
+        <v>46210</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T43" s="10">
+        <v>0</v>
+      </c>
+      <c r="U43" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46155.60601071759</v>
+        <v>46155.60601423611</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.86056584491</v>
+        <v>46190.1691007176</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
       </c>
       <c r="J44" s="5">
-        <v>46210</v>
+        <v>46190</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4260,58 +4247,48 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>46189</v>
-      </c>
-      <c r="R44" s="5">
-        <v>46210</v>
-      </c>
-      <c r="S44" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
-        <v>46155.60601423611</v>
+        <v>46155.60601877315</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46190.1691007176</v>
+        <v>46169.861063425924</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>90</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I45" s="9">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="J45" s="9">
-        <v>46190</v>
+        <v>46210</v>
       </c>
       <c r="K45" s="10" t="s">
         <v>26</v>
@@ -4323,13 +4300,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4339,50 +4316,44 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46155.60601877315</v>
+        <v>46155.60562939815</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.861063425924</v>
+        <v>46155.606241863425</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O46" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="I46" s="5">
-        <v>46191</v>
-      </c>
-      <c r="J46" s="5">
-        <v>46210</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="P46" s="6" t="s">
-        <v>171</v>
+        <v>26</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4392,27 +4363,33 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
-        <v>46155.60562939815</v>
+        <v>46155.60602364583</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46155.606241863425</v>
+        <v>46169.18606665509</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+      <c r="H47" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I47" s="9">
+        <v>46162</v>
+      </c>
+      <c r="J47" s="9">
+        <v>46168</v>
+      </c>
       <c r="K47" s="10" t="s">
         <v>26</v>
       </c>
@@ -4420,75 +4397,85 @@
         <v>26</v>
       </c>
       <c r="M47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="O47" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>46162</v>
+      </c>
+      <c r="R47" s="9">
+        <v>46168</v>
+      </c>
+      <c r="S47" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="N47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O47" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
+      <c r="U47" s="12" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46155.60602364583</v>
+        <v>46155.606031076386</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.18606665509</v>
+        <v>46184.200254131945</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I48" s="5">
+        <v>46177</v>
+      </c>
+      <c r="J48" s="5">
+        <v>46183</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="O48" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="I48" s="5">
-        <v>46162</v>
-      </c>
-      <c r="J48" s="5">
-        <v>46168</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>179</v>
       </c>
       <c r="Q48" s="5">
-        <v>46162</v>
+        <v>46146</v>
       </c>
       <c r="R48" s="5">
-        <v>46168</v>
+        <v>46183</v>
       </c>
       <c r="S48" s="11" t="s">
         <v>33</v>
@@ -4496,8 +4483,8 @@
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="12" t="s">
-        <v>64</v>
+      <c r="U48" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4505,90 +4492,90 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46155.606031076386</v>
+        <v>46155.606038645834</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46184.200254131945</v>
+        <v>46184.169042256945</v>
       </c>
       <c r="E49" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I49" s="10"/>
+      <c r="J49" s="9">
+        <v>46184</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="O49" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="P49" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="I49" s="9">
-        <v>46177</v>
-      </c>
-      <c r="J49" s="9">
-        <v>46183</v>
-      </c>
-      <c r="K49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="O49" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="P49" s="10" t="s">
-        <v>183</v>
-      </c>
       <c r="Q49" s="9">
-        <v>46146</v>
+        <v>46184</v>
       </c>
       <c r="R49" s="9">
-        <v>46183</v>
-      </c>
-      <c r="S49" s="11" t="s">
-        <v>33</v>
+        <v>46153</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46155.606038645834</v>
+        <v>46155.606091747686</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46184.169042256945</v>
+        <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I50" s="6"/>
+        <v>185</v>
+      </c>
+      <c r="I50" s="5">
+        <v>46241</v>
+      </c>
       <c r="J50" s="5">
-        <v>46184</v>
+        <v>46241</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>26</v>
@@ -4600,56 +4587,54 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="Q50" s="5">
-        <v>46184</v>
+        <v>46241</v>
       </c>
       <c r="R50" s="5">
-        <v>46153</v>
+        <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="9">
-        <v>46155.606091747686</v>
+        <v>46155.60610010417</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.63491418981</v>
+        <v>46155.64216699074</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I51" s="9">
-        <v>46241</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="I51" s="10"/>
       <c r="J51" s="9">
         <v>46241</v>
       </c>
@@ -4663,52 +4648,42 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q51" s="9">
-        <v>46241</v>
-      </c>
-      <c r="R51" s="9">
-        <v>46241</v>
-      </c>
-      <c r="S51" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T51" s="10">
-        <v>0</v>
-      </c>
-      <c r="U51" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46155.60610010417</v>
+        <v>46155.606106273146</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.64216699074</v>
+        <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4724,13 +4699,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4740,26 +4715,26 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B53" s="9">
-        <v>46155.606106273146</v>
+        <v>46155.60611204861</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.6421837963</v>
+        <v>46155.64219278935</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4775,13 +4750,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4791,26 +4766,26 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.60611204861</v>
+        <v>46155.60611671297</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.64219278935</v>
+        <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4826,13 +4801,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4842,26 +4817,26 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B55" s="9">
-        <v>46155.60611671297</v>
+        <v>46155.63491277778</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.64220083333</v>
+        <v>46155.64223084491</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4877,13 +4852,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4893,31 +4868,27 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
-        <v>46155.63491277778</v>
+        <v>46155.60612125</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.64223084491</v>
+        <v>46155.60624375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>189</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H56" s="6"/>
       <c r="I56" s="6"/>
-      <c r="J56" s="5">
-        <v>46241</v>
-      </c>
+      <c r="J56" s="6"/>
       <c r="K56" s="6" t="s">
         <v>26</v>
       </c>
@@ -4925,16 +4896,16 @@
         <v>26</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4944,27 +4915,33 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="9">
-        <v>46155.60612125</v>
+        <v>46155.60612483796</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46155.60624375</v>
+        <v>46155.60624466435</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
+      <c r="H57" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="I57" s="9">
+        <v>46202</v>
+      </c>
+      <c r="J57" s="9">
+        <v>46203</v>
+      </c>
       <c r="K57" s="10" t="s">
         <v>26</v>
       </c>
@@ -4972,84 +4949,94 @@
         <v>26</v>
       </c>
       <c r="M57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="O57" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q57" s="9">
+        <v>46202</v>
+      </c>
+      <c r="R57" s="9">
+        <v>46203</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T57" s="10">
         <v>0</v>
       </c>
-      <c r="N57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q57" s="10"/>
-      <c r="R57" s="10"/>
-      <c r="S57" s="10"/>
-      <c r="T57" s="10"/>
-      <c r="U57" s="10"/>
+      <c r="U57" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46155.60612483796</v>
+        <v>46155.6061331713</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46155.60624466435</v>
+        <v>46176.200130439815</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="H58" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I58" s="5">
+        <v>46204</v>
+      </c>
+      <c r="J58" s="5">
+        <v>46205</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="O58" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="I58" s="5">
-        <v>46202</v>
-      </c>
-      <c r="J58" s="5">
-        <v>46203</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>206</v>
       </c>
       <c r="Q58" s="5">
-        <v>46202</v>
+        <v>46174</v>
       </c>
       <c r="R58" s="5">
-        <v>46203</v>
-      </c>
-      <c r="S58" s="7" t="s">
-        <v>105</v>
+        <v>46175</v>
+      </c>
+      <c r="S58" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5057,11 +5044,11 @@
         <v>207</v>
       </c>
       <c r="B59" s="9">
-        <v>46155.6061331713</v>
+        <v>46155.606141446755</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46176.200130439815</v>
+        <v>46155.60624616898</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>208</v>
@@ -5070,16 +5057,16 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="I59" s="9">
-        <v>46204</v>
+        <v>46202</v>
       </c>
       <c r="J59" s="9">
-        <v>46205</v>
+        <v>46203</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>26</v>
@@ -5091,184 +5078,184 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="P59" s="10" t="s">
-        <v>210</v>
-      </c>
       <c r="Q59" s="9">
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="R59" s="9">
-        <v>46175</v>
-      </c>
-      <c r="S59" s="11" t="s">
-        <v>33</v>
+        <v>46203</v>
+      </c>
+      <c r="S59" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
-        <v>46155.606141446755</v>
+        <v>46155.60614949074</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.60624616898</v>
+        <v>46176.20013030093</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I60" s="5">
+        <v>46204</v>
+      </c>
+      <c r="J60" s="5">
+        <v>46205</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="I60" s="5">
-        <v>46202</v>
-      </c>
-      <c r="J60" s="5">
-        <v>46203</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>213</v>
-      </c>
       <c r="Q60" s="5">
-        <v>46202</v>
+        <v>46174</v>
       </c>
       <c r="R60" s="5">
-        <v>46203</v>
-      </c>
-      <c r="S60" s="7" t="s">
-        <v>105</v>
+        <v>46175</v>
+      </c>
+      <c r="S60" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B61" s="9">
-        <v>46155.60614949074</v>
+        <v>46155.606156319445</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46176.20013030093</v>
+        <v>46155.6062474537</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="I61" s="9">
+        <v>46211</v>
+      </c>
+      <c r="J61" s="9">
+        <v>46212</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="O61" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I61" s="9">
-        <v>46204</v>
-      </c>
-      <c r="J61" s="9">
-        <v>46205</v>
-      </c>
-      <c r="K61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="O61" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>216</v>
-      </c>
       <c r="Q61" s="9">
-        <v>46174</v>
+        <v>46211</v>
       </c>
       <c r="R61" s="9">
-        <v>46175</v>
-      </c>
-      <c r="S61" s="11" t="s">
-        <v>33</v>
+        <v>46212</v>
+      </c>
+      <c r="S61" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46155.606156319445</v>
+        <v>46155.60616390046</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.6062474537</v>
+        <v>46155.608459560186</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="I62" s="5">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="J62" s="5">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
@@ -5280,116 +5267,106 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="5">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="R62" s="5">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="S62" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B63" s="9">
-        <v>46155.60616390046</v>
+        <v>46155.60617082176</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46155.608459560186</v>
+        <v>46155.6064415162</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" s="10"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O63" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I63" s="9">
-        <v>46213</v>
-      </c>
-      <c r="J63" s="9">
-        <v>46216</v>
-      </c>
-      <c r="K63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="O63" s="10" t="s">
-        <v>218</v>
-      </c>
       <c r="P63" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q63" s="9">
-        <v>46213</v>
-      </c>
-      <c r="R63" s="9">
-        <v>46216</v>
-      </c>
-      <c r="S63" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T63" s="10">
-        <v>0</v>
-      </c>
-      <c r="U63" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46155.60617082176</v>
+        <v>46155.60617413194</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.6064415162</v>
+        <v>46155.6162571875</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
+      <c r="H64" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="I64" s="5">
+        <v>46217</v>
+      </c>
+      <c r="J64" s="5">
+        <v>46219</v>
+      </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
       </c>
@@ -5397,33 +5374,43 @@
         <v>26</v>
       </c>
       <c r="M64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>46217</v>
+      </c>
+      <c r="R64" s="5">
+        <v>46219</v>
+      </c>
+      <c r="S64" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="N64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+      <c r="U64" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>224</v>
       </c>
       <c r="B65" s="9">
-        <v>46155.60617413194</v>
+        <v>46155.60618260417</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.6162571875</v>
+        <v>46155.60738728009</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>225</v>
@@ -5432,10 +5419,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5453,52 +5440,42 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>46217</v>
-      </c>
-      <c r="R65" s="9">
-        <v>46219</v>
-      </c>
-      <c r="S65" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T65" s="10">
-        <v>0</v>
-      </c>
-      <c r="U65" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>228</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.60618260417</v>
+        <v>46155.60619106481</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.60738728009</v>
+        <v>46155.61677891204</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5516,13 +5493,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5532,26 +5509,26 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.60619106481</v>
+        <v>46155.60619835649</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.61677891204</v>
+        <v>46155.6168003125</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5569,13 +5546,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5585,26 +5562,26 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
-        <v>46155.60619835649</v>
+        <v>46155.60620543981</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.6168003125</v>
+        <v>46155.61683189815</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5622,13 +5599,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5638,26 +5615,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46155.60620543981</v>
+        <v>46155.60745351852</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.61683189815</v>
+        <v>46155.617393912034</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I69" s="9">
         <v>46217</v>
@@ -5675,13 +5652,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5691,32 +5668,32 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46155.60745351852</v>
+        <v>46155.606212638886</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.617393912034</v>
+        <v>46155.61775856481</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I70" s="5">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="J70" s="5">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
@@ -5728,42 +5705,52 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
+        <v>218</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>46220</v>
+      </c>
+      <c r="R70" s="5">
+        <v>46226</v>
+      </c>
+      <c r="S70" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T70" s="6">
+        <v>0</v>
+      </c>
+      <c r="U70" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B71" s="9">
-        <v>46155.606212638886</v>
+        <v>46155.60621899305</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.61775856481</v>
+        <v>46155.61927822916</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5781,52 +5768,42 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q71" s="9">
-        <v>46220</v>
-      </c>
-      <c r="R71" s="9">
-        <v>46226</v>
-      </c>
-      <c r="S71" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T71" s="10">
-        <v>0</v>
-      </c>
-      <c r="U71" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.60621899305</v>
+        <v>46155.606226539356</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.61927822916</v>
+        <v>46155.61930075231</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5844,13 +5821,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5860,26 +5837,26 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
-        <v>46155.606226539356</v>
+        <v>46155.606234004634</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.61930075231</v>
+        <v>46155.619317881945</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I73" s="9">
         <v>46220</v>
@@ -5897,13 +5874,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5913,26 +5890,26 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46155.606234004634</v>
+        <v>46155.60628421296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.619317881945</v>
+        <v>46155.61935121528</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -5950,13 +5927,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5966,26 +5943,26 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B75" s="9">
-        <v>46155.60628421296</v>
+        <v>46155.607690034725</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.61935121528</v>
+        <v>46155.61937777778</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I75" s="9">
         <v>46220</v>
@@ -6003,13 +5980,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6019,32 +5996,32 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.607690034725</v>
+        <v>46155.606291909724</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.61937777778</v>
+        <v>46155.61911184028</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>226</v>
+        <v>158</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>227</v>
+        <v>159</v>
       </c>
       <c r="I76" s="5">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="J76" s="5">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
@@ -6056,42 +6033,52 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
+        <v>218</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>46227</v>
+      </c>
+      <c r="R76" s="5">
+        <v>46227</v>
+      </c>
+      <c r="S76" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0</v>
+      </c>
+      <c r="U76" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.606291909724</v>
+        <v>46155.60629884259</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.61911184028</v>
+        <v>46155.620624918985</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6109,52 +6096,42 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q77" s="9">
-        <v>46227</v>
-      </c>
-      <c r="R77" s="9">
-        <v>46227</v>
-      </c>
-      <c r="S77" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T77" s="10">
-        <v>0</v>
-      </c>
-      <c r="U77" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
-        <v>46155.60629884259</v>
+        <v>46155.60630622685</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.620624918985</v>
+        <v>46155.62065888889</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6172,13 +6149,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6188,26 +6165,26 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B79" s="9">
-        <v>46155.60630622685</v>
+        <v>46155.6063134375</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46155.62065888889</v>
+        <v>46155.6206809838</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I79" s="9">
         <v>46227</v>
@@ -6225,13 +6202,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6241,26 +6218,26 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
-        <v>46155.6063134375</v>
+        <v>46155.606319722225</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46155.6206809838</v>
+        <v>46155.62071310185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6278,13 +6255,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6294,30 +6271,28 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B81" s="9">
-        <v>46155.606319722225</v>
+        <v>46155.618322951384</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46155.62071310185</v>
+        <v>46155.620736377314</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I81" s="9">
-        <v>46227</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="I81" s="10"/>
       <c r="J81" s="9">
         <v>46227</v>
       </c>
@@ -6331,13 +6306,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6347,31 +6322,27 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B82" s="5">
-        <v>46155.618322951384</v>
+        <v>46155.60632542824</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.620736377314</v>
+        <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>163</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="6"/>
-      <c r="J82" s="5">
-        <v>46227</v>
-      </c>
+      <c r="J82" s="6"/>
       <c r="K82" s="6" t="s">
         <v>26</v>
       </c>
@@ -6379,16 +6350,16 @@
         <v>26</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>249</v>
+        <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>251</v>
+        <v>26</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6398,27 +6369,31 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B83" s="9">
-        <v>46155.60632542824</v>
+        <v>46155.60632868056</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.60644350694</v>
+        <v>46182.19947712963</v>
       </c>
       <c r="E83" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F83" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="10"/>
+      <c r="H83" s="10" t="s">
+        <v>201</v>
+      </c>
       <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
+      <c r="J83" s="9">
+        <v>46181</v>
+      </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
       </c>
@@ -6426,73 +6401,85 @@
         <v>26</v>
       </c>
       <c r="M83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="P83" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>46181</v>
+      </c>
+      <c r="R83" s="9">
+        <v>46181</v>
+      </c>
+      <c r="S83" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T83" s="10">
         <v>0</v>
       </c>
-      <c r="N83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O83" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q83" s="10"/>
-      <c r="R83" s="10"/>
-      <c r="S83" s="10"/>
-      <c r="T83" s="10"/>
-      <c r="U83" s="10"/>
+      <c r="U83" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B84" s="5">
-        <v>46155.60632868056</v>
+        <v>46155.60633650463</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.19947712963</v>
+        <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I84" s="5">
+        <v>46164</v>
+      </c>
+      <c r="J84" s="5">
+        <v>46164</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="F84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="I84" s="6"/>
-      <c r="J84" s="5">
-        <v>46181</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>261</v>
-      </c>
       <c r="Q84" s="5">
-        <v>46181</v>
+        <v>46164</v>
       </c>
       <c r="R84" s="5">
-        <v>46181</v>
+        <v>46164</v>
       </c>
       <c r="S84" s="11" t="s">
         <v>33</v>
@@ -6500,268 +6487,268 @@
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="11" t="s">
-        <v>84</v>
+      <c r="U84" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B85" s="9">
-        <v>46155.60633650463</v>
+        <v>46155.60634402778</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46182.677286018516</v>
+        <v>46190.1908316551</v>
       </c>
       <c r="E85" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="I85" s="9">
+        <v>46197</v>
+      </c>
+      <c r="J85" s="9">
+        <v>46197</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="O85" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="P85" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="I85" s="9">
-        <v>46164</v>
-      </c>
-      <c r="J85" s="9">
-        <v>46164</v>
-      </c>
-      <c r="K85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="O85" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>264</v>
-      </c>
       <c r="Q85" s="9">
-        <v>46164</v>
+        <v>46197</v>
       </c>
       <c r="R85" s="9">
-        <v>46164</v>
-      </c>
-      <c r="S85" s="11" t="s">
-        <v>33</v>
+        <v>46197</v>
+      </c>
+      <c r="S85" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T85" s="10">
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B86" s="5">
-        <v>46155.60634402778</v>
+        <v>46155.60635177083</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46190.1908316551</v>
+        <v>46155.60644643518</v>
       </c>
       <c r="E86" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I86" s="5">
+        <v>46231</v>
+      </c>
+      <c r="J86" s="5">
+        <v>46231</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="F86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="I86" s="5">
-        <v>46197</v>
-      </c>
-      <c r="J86" s="5">
-        <v>46197</v>
-      </c>
-      <c r="K86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N86" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>267</v>
-      </c>
       <c r="Q86" s="5">
-        <v>46197</v>
+        <v>46231</v>
       </c>
       <c r="R86" s="5">
-        <v>46197</v>
-      </c>
-      <c r="S86" s="12" t="s">
-        <v>121</v>
+        <v>46231</v>
+      </c>
+      <c r="S86" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="12" t="s">
-        <v>64</v>
+      <c r="U86" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B87" s="9">
-        <v>46155.60635177083</v>
+        <v>46155.606361921295</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.60644643518</v>
+        <v>46155.606780057875</v>
       </c>
       <c r="E87" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H87" s="10"/>
+      <c r="I87" s="10"/>
+      <c r="J87" s="10"/>
+      <c r="K87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="N87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O87" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="I87" s="9">
-        <v>46231</v>
-      </c>
-      <c r="J87" s="9">
-        <v>46231</v>
-      </c>
-      <c r="K87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="O87" s="10" t="s">
-        <v>158</v>
-      </c>
       <c r="P87" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q87" s="9">
-        <v>46231</v>
-      </c>
-      <c r="R87" s="9">
-        <v>46231</v>
-      </c>
-      <c r="S87" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T87" s="10">
-        <v>0</v>
-      </c>
-      <c r="U87" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="10"/>
+      <c r="U87" s="10"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.606361921295</v>
+        <v>46155.60636525463</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.606780057875</v>
+        <v>46155.620355625</v>
       </c>
       <c r="E88" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I88" s="5">
+        <v>46230</v>
+      </c>
+      <c r="J88" s="5">
+        <v>46234</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="O88" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M88" s="6" t="s">
+      <c r="P88" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>46230</v>
+      </c>
+      <c r="R88" s="5">
+        <v>46234</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="N88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
+      <c r="U88" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B89" s="9">
-        <v>46155.60636525463</v>
+        <v>46155.606374525465</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.620355625</v>
+        <v>46155.621619502315</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I89" s="9">
         <v>46230</v>
@@ -6779,52 +6766,42 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q89" s="9">
-        <v>46230</v>
-      </c>
-      <c r="R89" s="9">
-        <v>46234</v>
-      </c>
-      <c r="S89" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T89" s="10">
-        <v>0</v>
-      </c>
-      <c r="U89" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B90" s="5">
-        <v>46155.606374525465</v>
+        <v>46155.60638027778</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.621619502315</v>
+        <v>46155.62163603009</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I90" s="5">
         <v>46230</v>
@@ -6842,10 +6819,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6858,26 +6835,26 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B91" s="9">
-        <v>46155.60638027778</v>
+        <v>46155.60638583334</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.62163603009</v>
+        <v>46155.62166074074</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I91" s="9">
         <v>46230</v>
@@ -6895,13 +6872,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>26</v>
+        <v>277</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6911,26 +6888,26 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.60638583334</v>
+        <v>46155.60639179398</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.62166074074</v>
+        <v>46155.62167399305</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I92" s="5">
         <v>46230</v>
@@ -6948,13 +6925,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6964,26 +6941,26 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.60639179398</v>
+        <v>46155.61975986111</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.62167399305</v>
+        <v>46155.62169508102</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I93" s="9">
         <v>46230</v>
@@ -7001,13 +6978,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7017,32 +6994,32 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B94" s="5">
-        <v>46155.61975986111</v>
+        <v>46155.60639783565</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.62169508102</v>
+        <v>46155.62191585648</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>229</v>
+        <v>282</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I94" s="5">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J94" s="5">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
@@ -7054,46 +7031,54 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+        <v>268</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46237</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46237</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T94" s="6">
+        <v>0</v>
+      </c>
+      <c r="U94" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B95" s="9">
-        <v>46155.60639783565</v>
+        <v>46155.60640402778</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.62191585648</v>
+        <v>46155.62125136574</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>286</v>
+        <v>225</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I95" s="9">
-        <v>46237</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I95" s="10"/>
       <c r="J95" s="9">
         <v>46237</v>
       </c>
@@ -7107,52 +7092,42 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q95" s="9">
-        <v>46237</v>
-      </c>
-      <c r="R95" s="9">
-        <v>46237</v>
-      </c>
-      <c r="S95" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T95" s="10">
-        <v>0</v>
-      </c>
-      <c r="U95" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
+      <c r="U95" s="10"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B96" s="5">
-        <v>46155.60640402778</v>
+        <v>46155.60641090278</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.62125136574</v>
+        <v>46155.62123118056</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7168,13 +7143,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7184,26 +7159,26 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B97" s="9">
-        <v>46155.60641090278</v>
+        <v>46155.60641760417</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.62123118056</v>
+        <v>46155.62121537037</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7219,7 +7194,7 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>288</v>
@@ -7235,26 +7210,26 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.60641760417</v>
+        <v>46155.60642649306</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.62121537037</v>
+        <v>46155.621193576386</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7270,13 +7245,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7286,26 +7261,26 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B99" s="9">
-        <v>46155.60642649306</v>
+        <v>46155.62115946759</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.621193576386</v>
+        <v>46155.64240027778</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
@@ -7321,13 +7296,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>292</v>
+        <v>225</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7337,30 +7312,32 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B100" s="5">
-        <v>46155.62115946759</v>
+        <v>46155.60648232639</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.64240027778</v>
+        <v>46155.631670462964</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I100" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="I100" s="5">
+        <v>46238</v>
+      </c>
       <c r="J100" s="5">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>26</v>
@@ -7372,46 +7349,54 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
+        <v>268</v>
+      </c>
+      <c r="Q100" s="5">
+        <v>46238</v>
+      </c>
+      <c r="R100" s="5">
+        <v>46238</v>
+      </c>
+      <c r="S100" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T100" s="6">
+        <v>0</v>
+      </c>
+      <c r="U100" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B101" s="9">
-        <v>46155.60648232639</v>
+        <v>46155.60649042824</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.631670462964</v>
+        <v>46155.622123877314</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I101" s="9">
-        <v>46238</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I101" s="10"/>
       <c r="J101" s="9">
         <v>46238</v>
       </c>
@@ -7425,52 +7410,42 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>216</v>
+        <v>295</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q101" s="9">
-        <v>46238</v>
-      </c>
-      <c r="R101" s="9">
-        <v>46238</v>
-      </c>
-      <c r="S101" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T101" s="10">
-        <v>0</v>
-      </c>
-      <c r="U101" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="10"/>
+      <c r="U101" s="10"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.60649042824</v>
+        <v>46155.6064993287</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.622123877314</v>
+        <v>46155.622143472225</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7486,13 +7461,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7502,26 +7477,26 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.6064993287</v>
+        <v>46155.606507951394</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.622143472225</v>
+        <v>46155.62216706018</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7537,13 +7512,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7553,26 +7528,26 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B104" s="5">
-        <v>46155.606507951394</v>
+        <v>46155.60651716436</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.62216706018</v>
+        <v>46155.6221805324</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7588,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7604,26 +7579,26 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B105" s="9">
-        <v>46155.60651716436</v>
+        <v>46155.6221815162</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.6221805324</v>
+        <v>46155.63179349537</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7639,10 +7614,10 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>304</v>
+        <v>225</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>302</v>
@@ -7655,30 +7630,32 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B106" s="5">
-        <v>46155.6221815162</v>
+        <v>46155.60652579861</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.63179349537</v>
+        <v>46155.63455996528</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>229</v>
+        <v>304</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I106" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="I106" s="5">
+        <v>46239</v>
+      </c>
       <c r="J106" s="5">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>26</v>
@@ -7690,46 +7667,54 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6"/>
+        <v>268</v>
+      </c>
+      <c r="Q106" s="5">
+        <v>46239</v>
+      </c>
+      <c r="R106" s="5">
+        <v>46239</v>
+      </c>
+      <c r="S106" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T106" s="6">
+        <v>0</v>
+      </c>
+      <c r="U106" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B107" s="9">
-        <v>46155.60652579861</v>
+        <v>46155.606533032405</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.63455996528</v>
+        <v>46155.63460895834</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>308</v>
+        <v>188</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I107" s="9">
-        <v>46239</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I107" s="10"/>
       <c r="J107" s="9">
         <v>46239</v>
       </c>
@@ -7743,52 +7728,42 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q107" s="9">
-        <v>46239</v>
-      </c>
-      <c r="R107" s="9">
-        <v>46239</v>
-      </c>
-      <c r="S107" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T107" s="10">
-        <v>0</v>
-      </c>
-      <c r="U107" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="10"/>
+      <c r="S107" s="10"/>
+      <c r="T107" s="10"/>
+      <c r="U107" s="10"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.606533032405</v>
+        <v>46155.60654145833</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.63460895834</v>
+        <v>46155.63461768518</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7804,13 +7779,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>308</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>312</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7820,26 +7795,26 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B109" s="9">
-        <v>46155.60654145833</v>
+        <v>46155.60655399306</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.63461768518</v>
+        <v>46155.634628796295</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I109" s="10"/>
       <c r="J109" s="9">
@@ -7855,13 +7830,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>311</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7871,26 +7846,26 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B110" s="5">
-        <v>46155.60655399306</v>
+        <v>46155.60656262732</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.634628796295</v>
+        <v>46155.634642916666</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -7906,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7922,26 +7897,26 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B111" s="9">
-        <v>46155.60656262732</v>
+        <v>46155.63011625</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.634642916666</v>
+        <v>46155.63465961805</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I111" s="10"/>
       <c r="J111" s="9">
@@ -7957,13 +7932,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>317</v>
+        <v>225</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7973,30 +7948,32 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.63011625</v>
+        <v>46155.60657109953</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.63465961805</v>
+        <v>46155.63577444444</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>192</v>
+        <v>317</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I112" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="I112" s="5">
+        <v>46240</v>
+      </c>
       <c r="J112" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>26</v>
@@ -8008,42 +7985,52 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>308</v>
+        <v>268</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q112" s="6"/>
-      <c r="R112" s="6"/>
-      <c r="S112" s="6"/>
-      <c r="T112" s="6"/>
-      <c r="U112" s="6"/>
+        <v>268</v>
+      </c>
+      <c r="Q112" s="5">
+        <v>46240</v>
+      </c>
+      <c r="R112" s="5">
+        <v>46240</v>
+      </c>
+      <c r="S112" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T112" s="6">
+        <v>0</v>
+      </c>
+      <c r="U112" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.60657109953</v>
+        <v>46155.60657833333</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.63577444444</v>
+        <v>46155.635128090275</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>321</v>
+        <v>188</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I113" s="9">
         <v>46240</v>
@@ -8061,52 +8048,42 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>309</v>
+        <v>188</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q113" s="9">
-        <v>46240</v>
-      </c>
-      <c r="R113" s="9">
-        <v>46240</v>
-      </c>
-      <c r="S113" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T113" s="10">
-        <v>0</v>
-      </c>
-      <c r="U113" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="Q113" s="10"/>
+      <c r="R113" s="10"/>
+      <c r="S113" s="10"/>
+      <c r="T113" s="10"/>
+      <c r="U113" s="10"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B114" s="5">
-        <v>46155.60657833333</v>
+        <v>46155.60658640046</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.635128090275</v>
+        <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I114" s="5">
         <v>46240</v>
@@ -8124,13 +8101,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8140,26 +8117,26 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B115" s="9">
-        <v>46155.60658640046</v>
+        <v>46155.60659408565</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.63525575231</v>
+        <v>46155.635268750004</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I115" s="9">
         <v>46240</v>
@@ -8177,13 +8154,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8193,26 +8170,26 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B116" s="5">
-        <v>46155.60659408565</v>
+        <v>46155.60660233797</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.635268750004</v>
+        <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I116" s="5">
         <v>46240</v>
@@ -8230,13 +8207,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8246,30 +8223,28 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B117" s="9">
-        <v>46155.60660233797</v>
+        <v>46155.63398136574</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.635292569445</v>
+        <v>46155.63581856481</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I117" s="9">
-        <v>46240</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I117" s="10"/>
       <c r="J117" s="9">
         <v>46240</v>
       </c>
@@ -8283,13 +8258,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8299,30 +8274,32 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.63398136574</v>
+        <v>46155.60664190972</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.63581856481</v>
+        <v>46155.63694791667</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>192</v>
+        <v>326</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I118" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="I118" s="5">
+        <v>46244</v>
+      </c>
       <c r="J118" s="5">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>26</v>
@@ -8334,46 +8311,54 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="6"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-      <c r="U118" s="6"/>
+        <v>327</v>
+      </c>
+      <c r="Q118" s="5">
+        <v>46244</v>
+      </c>
+      <c r="R118" s="5">
+        <v>46244</v>
+      </c>
+      <c r="S118" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T118" s="6">
+        <v>0</v>
+      </c>
+      <c r="U118" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.60664190972</v>
+        <v>46155.60665081019</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.63694791667</v>
+        <v>46155.63810030093</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>330</v>
+        <v>188</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I119" s="9">
-        <v>46244</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I119" s="10"/>
       <c r="J119" s="9">
         <v>46244</v>
       </c>
@@ -8387,52 +8372,42 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>309</v>
+        <v>188</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q119" s="9">
-        <v>46244</v>
-      </c>
-      <c r="R119" s="9">
-        <v>46244</v>
-      </c>
-      <c r="S119" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T119" s="10">
-        <v>0</v>
-      </c>
-      <c r="U119" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="Q119" s="10"/>
+      <c r="R119" s="10"/>
+      <c r="S119" s="10"/>
+      <c r="T119" s="10"/>
+      <c r="U119" s="10"/>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B120" s="5">
-        <v>46155.60665081019</v>
+        <v>46155.60665825232</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.63810030093</v>
+        <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8448,13 +8423,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8464,26 +8439,26 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B121" s="9">
-        <v>46155.60665825232</v>
+        <v>46155.60666534722</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.6381218287</v>
+        <v>46155.63813651621</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I121" s="10"/>
       <c r="J121" s="9">
@@ -8499,13 +8474,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8515,26 +8490,26 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B122" s="5">
-        <v>46155.60666534722</v>
+        <v>46155.60667253472</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.63813651621</v>
+        <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8550,13 +8525,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8566,26 +8541,26 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B123" s="9">
-        <v>46155.60667253472</v>
+        <v>46155.63591585648</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.63815179398</v>
+        <v>46155.63817207176</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I123" s="10"/>
       <c r="J123" s="9">
@@ -8601,13 +8576,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8617,31 +8592,27 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.63591585648</v>
+        <v>46155.606679502314</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.63817207176</v>
+        <v>46155.60689462963</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>192</v>
+        <v>336</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
       <c r="I124" s="6"/>
-      <c r="J124" s="5">
-        <v>46244</v>
-      </c>
+      <c r="J124" s="6"/>
       <c r="K124" s="6" t="s">
         <v>26</v>
       </c>
@@ -8649,16 +8620,16 @@
         <v>26</v>
       </c>
       <c r="M124" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>330</v>
+        <v>26</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>335</v>
+        <v>26</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8668,27 +8639,31 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B125" s="9">
-        <v>46155.606679502314</v>
+        <v>46155.60668334491</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.60689462963</v>
+        <v>46155.63803638889</v>
       </c>
       <c r="E125" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="F125" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G125" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="F125" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="10"/>
+      <c r="H125" s="10" t="s">
+        <v>341</v>
+      </c>
       <c r="I125" s="10"/>
-      <c r="J125" s="10"/>
+      <c r="J125" s="9">
+        <v>46245</v>
+      </c>
       <c r="K125" s="10" t="s">
         <v>26</v>
       </c>
@@ -8696,45 +8671,55 @@
         <v>26</v>
       </c>
       <c r="M125" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N125" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="O125" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="P125" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q125" s="9">
+        <v>46245</v>
+      </c>
+      <c r="R125" s="9">
+        <v>46245</v>
+      </c>
+      <c r="S125" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T125" s="10">
         <v>0</v>
       </c>
-      <c r="N125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O125" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="P125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q125" s="10"/>
-      <c r="R125" s="10"/>
-      <c r="S125" s="10"/>
-      <c r="T125" s="10"/>
-      <c r="U125" s="10"/>
+      <c r="U125" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B126" s="5">
-        <v>46155.60668334491</v>
+        <v>46155.606691759254</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.63803638889</v>
+        <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>343</v>
+        <v>188</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8750,52 +8735,42 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>346</v>
+        <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q126" s="5">
-        <v>46245</v>
-      </c>
-      <c r="R126" s="5">
-        <v>46245</v>
-      </c>
-      <c r="S126" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T126" s="6">
-        <v>0</v>
-      </c>
-      <c r="U126" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="Q126" s="6"/>
+      <c r="R126" s="6"/>
+      <c r="S126" s="6"/>
+      <c r="T126" s="6"/>
+      <c r="U126" s="6"/>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B127" s="9">
-        <v>46155.606691759254</v>
+        <v>46155.60669864583</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.6390279051</v>
+        <v>46155.639037835645</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8811,13 +8786,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8827,26 +8802,26 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.60669864583</v>
+        <v>46155.60670615741</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.639037835645</v>
+        <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8862,13 +8837,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8878,26 +8853,26 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.60670615741</v>
+        <v>46155.606713009256</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.639063807874</v>
+        <v>46155.63907559028</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -8913,13 +8888,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8929,26 +8904,26 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B130" s="5">
-        <v>46155.606713009256</v>
+        <v>46155.63715556713</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.63907559028</v>
+        <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -8964,13 +8939,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8980,30 +8955,32 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B131" s="9">
-        <v>46155.63715556713</v>
+        <v>46155.60671987268</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.63910325231</v>
+        <v>46155.638912615745</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>192</v>
+        <v>351</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>344</v>
+        <v>72</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="I131" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="I131" s="9">
+        <v>46246</v>
+      </c>
       <c r="J131" s="9">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K131" s="10" t="s">
         <v>26</v>
@@ -9015,42 +8992,52 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q131" s="10"/>
-      <c r="R131" s="10"/>
-      <c r="S131" s="10"/>
-      <c r="T131" s="10"/>
-      <c r="U131" s="10"/>
+        <v>336</v>
+      </c>
+      <c r="Q131" s="9">
+        <v>46246</v>
+      </c>
+      <c r="R131" s="9">
+        <v>46246</v>
+      </c>
+      <c r="S131" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T131" s="10">
+        <v>0</v>
+      </c>
+      <c r="U131" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B132" s="5">
-        <v>46155.60671987268</v>
+        <v>46155.60672658565</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.638912615745</v>
+        <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>355</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I132" s="5">
         <v>46246</v>
@@ -9068,52 +9055,42 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>309</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q132" s="5">
-        <v>46246</v>
-      </c>
-      <c r="R132" s="5">
-        <v>46246</v>
-      </c>
-      <c r="S132" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T132" s="6">
-        <v>0</v>
-      </c>
-      <c r="U132" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="Q132" s="6"/>
+      <c r="R132" s="6"/>
+      <c r="S132" s="6"/>
+      <c r="T132" s="6"/>
+      <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B133" s="9">
-        <v>46155.60672658565</v>
+        <v>46155.60673355324</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.639826238425</v>
+        <v>46155.63983615741</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I133" s="9">
         <v>46246</v>
@@ -9131,13 +9108,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="O133" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P133" s="10" t="s">
         <v>355</v>
-      </c>
-      <c r="O133" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="P133" s="10" t="s">
-        <v>357</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9147,26 +9124,26 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.60673355324</v>
+        <v>46155.60674053241</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.63983615741</v>
+        <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I134" s="5">
         <v>46246</v>
@@ -9184,13 +9161,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9200,26 +9177,26 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B135" s="9">
-        <v>46155.60674053241</v>
+        <v>46155.60674741898</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.639844942125</v>
+        <v>46155.63986869213</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I135" s="9">
         <v>46246</v>
@@ -9237,13 +9214,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="O135" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P135" s="10" t="s">
         <v>355</v>
-      </c>
-      <c r="O135" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="P135" s="10" t="s">
-        <v>357</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9253,30 +9230,28 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B136" s="5">
-        <v>46155.60674741898</v>
+        <v>46155.63830266204</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.63986869213</v>
+        <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I136" s="5">
-        <v>46246</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I136" s="6"/>
       <c r="J136" s="5">
         <v>46246</v>
       </c>
@@ -9290,13 +9265,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9306,30 +9281,32 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B137" s="9">
-        <v>46155.63830266204</v>
+        <v>46155.60675400463</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46155.63990003472</v>
+        <v>46155.64036164352</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>192</v>
+        <v>360</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>76</v>
+        <v>222</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I137" s="10"/>
+        <v>223</v>
+      </c>
+      <c r="I137" s="9">
+        <v>46247</v>
+      </c>
       <c r="J137" s="9">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K137" s="10" t="s">
         <v>26</v>
@@ -9341,46 +9318,54 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q137" s="10"/>
-      <c r="R137" s="10"/>
-      <c r="S137" s="10"/>
-      <c r="T137" s="10"/>
-      <c r="U137" s="10"/>
+        <v>336</v>
+      </c>
+      <c r="Q137" s="9">
+        <v>46247</v>
+      </c>
+      <c r="R137" s="9">
+        <v>46247</v>
+      </c>
+      <c r="S137" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T137" s="10">
+        <v>0</v>
+      </c>
+      <c r="U137" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B138" s="5">
-        <v>46155.60675400463</v>
+        <v>46155.60676105324</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46155.64036164352</v>
+        <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>364</v>
+        <v>188</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="I138" s="5">
-        <v>46247</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="I138" s="6"/>
       <c r="J138" s="5">
         <v>46247</v>
       </c>
@@ -9394,52 +9379,42 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>309</v>
+        <v>188</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q138" s="5">
-        <v>46247</v>
-      </c>
-      <c r="R138" s="5">
-        <v>46247</v>
-      </c>
-      <c r="S138" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T138" s="6">
-        <v>0</v>
-      </c>
-      <c r="U138" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="Q138" s="6"/>
+      <c r="R138" s="6"/>
+      <c r="S138" s="6"/>
+      <c r="T138" s="6"/>
+      <c r="U138" s="6"/>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B139" s="9">
-        <v>46155.60676105324</v>
+        <v>46155.60677012731</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46155.642618750004</v>
+        <v>46155.64263091436</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I139" s="10"/>
       <c r="J139" s="9">
@@ -9455,13 +9430,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9471,26 +9446,26 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B140" s="5">
-        <v>46155.60677012731</v>
+        <v>46155.60681737268</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46155.64263091436</v>
+        <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9506,13 +9481,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9522,26 +9497,26 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B141" s="9">
-        <v>46155.60681737268</v>
+        <v>46155.60682548611</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46155.64264111111</v>
+        <v>46155.64265195602</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I141" s="10"/>
       <c r="J141" s="9">
@@ -9557,13 +9532,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9573,26 +9548,26 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B142" s="5">
-        <v>46155.60682548611</v>
+        <v>46155.63928425926</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46155.64265195602</v>
+        <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9608,13 +9583,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9624,30 +9599,32 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B143" s="9">
-        <v>46155.63928425926</v>
+        <v>46155.60683229167</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46155.64266835648</v>
+        <v>46155.641985821756</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>192</v>
+        <v>369</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="I143" s="10"/>
+        <v>223</v>
+      </c>
+      <c r="I143" s="9">
+        <v>46248</v>
+      </c>
       <c r="J143" s="9">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K143" s="10" t="s">
         <v>26</v>
@@ -9659,46 +9636,54 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q143" s="10"/>
-      <c r="R143" s="10"/>
-      <c r="S143" s="10"/>
-      <c r="T143" s="10"/>
-      <c r="U143" s="10"/>
+        <v>370</v>
+      </c>
+      <c r="Q143" s="9">
+        <v>46248</v>
+      </c>
+      <c r="R143" s="9">
+        <v>46248</v>
+      </c>
+      <c r="S143" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T143" s="10">
+        <v>0</v>
+      </c>
+      <c r="U143" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B144" s="5">
-        <v>46155.60683229167</v>
+        <v>46155.606840486114</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46155.641985821756</v>
+        <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>373</v>
+        <v>188</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="I144" s="5">
-        <v>46248</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="I144" s="6"/>
       <c r="J144" s="5">
         <v>46248</v>
       </c>
@@ -9712,52 +9697,42 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>309</v>
+        <v>188</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="Q144" s="5">
-        <v>46248</v>
-      </c>
-      <c r="R144" s="5">
-        <v>46248</v>
-      </c>
-      <c r="S144" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T144" s="6">
-        <v>0</v>
-      </c>
-      <c r="U144" s="11" t="s">
-        <v>84</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="Q144" s="6"/>
+      <c r="R144" s="6"/>
+      <c r="S144" s="6"/>
+      <c r="T144" s="6"/>
+      <c r="U144" s="6"/>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B145" s="9">
-        <v>46155.606840486114</v>
+        <v>46155.60684746528</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46155.64207402778</v>
+        <v>46155.64208369213</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I145" s="10"/>
       <c r="J145" s="9">
@@ -9773,13 +9748,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9789,26 +9764,26 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B146" s="5">
-        <v>46155.60684746528</v>
+        <v>46155.60685387731</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46155.64208369213</v>
+        <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9824,13 +9799,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9840,26 +9815,26 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B147" s="9">
-        <v>46155.60685387731</v>
+        <v>46155.60686101852</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46155.64209340278</v>
+        <v>46155.64210719908</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I147" s="10"/>
       <c r="J147" s="9">
@@ -9875,13 +9850,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9891,26 +9866,26 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B148" s="5">
-        <v>46155.60686101852</v>
+        <v>46155.64052775463</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46155.64210719908</v>
+        <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -9926,13 +9901,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9942,31 +9917,27 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B149" s="9">
-        <v>46155.64052775463</v>
+        <v>46155.60686797454</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46155.64213097222</v>
+        <v>46155.60689638889</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>192</v>
+        <v>377</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>227</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H149" s="10"/>
       <c r="I149" s="10"/>
-      <c r="J149" s="9">
-        <v>46248</v>
-      </c>
+      <c r="J149" s="10"/>
       <c r="K149" s="10" t="s">
         <v>26</v>
       </c>
@@ -9974,16 +9945,16 @@
         <v>26</v>
       </c>
       <c r="M149" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>373</v>
+        <v>26</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>192</v>
+        <v>378</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>373</v>
+        <v>26</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -9993,27 +9964,33 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B150" s="5">
-        <v>46155.60686797454</v>
+        <v>46155.60687207176</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46155.60689638889</v>
+        <v>46155.60689709491</v>
       </c>
       <c r="E150" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G150" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="F150" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
+      <c r="H150" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="I150" s="5">
+        <v>46251</v>
+      </c>
+      <c r="J150" s="5">
+        <v>46255</v>
+      </c>
       <c r="K150" s="6" t="s">
         <v>26</v>
       </c>
@@ -10021,33 +9998,43 @@
         <v>26</v>
       </c>
       <c r="M150" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N150" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="O150" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="P150" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q150" s="5">
+        <v>46251</v>
+      </c>
+      <c r="R150" s="5">
+        <v>46255</v>
+      </c>
+      <c r="S150" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="T150" s="6">
         <v>0</v>
       </c>
-      <c r="N150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O150" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="P150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q150" s="6"/>
-      <c r="R150" s="6"/>
-      <c r="S150" s="6"/>
-      <c r="T150" s="6"/>
-      <c r="U150" s="6"/>
+      <c r="U150" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
         <v>383</v>
       </c>
       <c r="B151" s="9">
-        <v>46155.60687207176</v>
+        <v>46155.606879259256</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46155.60689709491</v>
+        <v>46195.54676386574</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>384</v>
@@ -10056,10 +10043,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>385</v>
+        <v>36</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>386</v>
+        <v>37</v>
       </c>
       <c r="I151" s="9">
         <v>46251</v>
@@ -10077,13 +10064,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="Q151" s="9">
         <v>46251</v>
@@ -10092,76 +10079,13 @@
         <v>46255</v>
       </c>
       <c r="S151" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="T151" s="10">
         <v>0</v>
       </c>
       <c r="U151" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="B152" s="5">
-        <v>46155.606879259256</v>
-      </c>
-      <c r="C152" s="6"/>
-      <c r="D152" s="5">
-        <v>46155.60689761574</v>
-      </c>
-      <c r="E152" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G152" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I152" s="5">
-        <v>46251</v>
-      </c>
-      <c r="J152" s="5">
-        <v>46255</v>
-      </c>
-      <c r="K152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N152" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="O152" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="P152" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q152" s="5">
-        <v>46251</v>
-      </c>
-      <c r="R152" s="5">
-        <v>46255</v>
-      </c>
-      <c r="S152" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T152" s="6">
-        <v>0</v>
-      </c>
-      <c r="U152" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="385">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -272,70 +272,70 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4316</t>
   </si>
   <si>
+    <t>1214777481542258</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma OT 4316</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4316</t>
+  </si>
+  <si>
+    <t>1214777561381920</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1214777561381936</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4316</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4316</t>
+  </si>
+  <si>
+    <t>1214739697907731</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe OT 4316 ,Materiales corte Laser OT 4316,rodete OT 4316,Motor OT 4316</t>
+  </si>
+  <si>
+    <t>1214777481578466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alabe OT 4316 </t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4316,Generación OC Alabe OT 4316</t>
+  </si>
+  <si>
+    <t>1214777481578487</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Alabe OT 4316,Alabe OT 4316 </t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214777481542258</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma OT 4316</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4316</t>
-  </si>
-  <si>
-    <t>1214777561381920</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1214777561381936</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4316</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4316</t>
-  </si>
-  <si>
-    <t>1214739697907731</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe OT 4316 ,Materiales corte Laser OT 4316,rodete OT 4316,Motor OT 4316</t>
-  </si>
-  <si>
-    <t>1214777481578466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alabe OT 4316 </t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4316,Generación OC Alabe OT 4316</t>
-  </si>
-  <si>
-    <t>1214777481578487</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Alabe OT 4316,Alabe OT 4316 </t>
-  </si>
-  <si>
-    <t>Baja</t>
   </si>
   <si>
     <t>1214777594099850</t>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46189.193734155095</v>
+        <v>46195.94769405093</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2717,23 +2717,23 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
-        <v>80</v>
+      <c r="U18" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="9">
         <v>46155.605814317125</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46189.193734155095</v>
+        <v>46195.947693634254</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2766,7 +2766,7 @@
         <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="9">
         <v>46185</v>
@@ -2780,23 +2780,23 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
-        <v>80</v>
+      <c r="U19" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46155.60582009259</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46189.193734560184</v>
+        <v>46195.94769378472</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2829,7 +2829,7 @@
         <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2843,23 +2843,23 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="11" t="s">
-        <v>80</v>
+      <c r="U20" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="9">
         <v>46155.60582561343</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.193734201384</v>
+        <v>46195.94769402778</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2892,7 +2892,7 @@
         <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2906,13 +2906,13 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="11" t="s">
-        <v>80</v>
+      <c r="U21" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46155.60562462963</v>
@@ -2922,7 +2922,7 @@
         <v>46182.693747743055</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2946,7 +2946,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="9">
         <v>46155.60583177084</v>
@@ -2971,16 +2971,16 @@
         <v>46182.67729332176</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46157</v>
@@ -2998,13 +2998,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="9">
         <v>46157</v>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46155.60583869213</v>
@@ -3036,16 +3036,16 @@
         <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3063,24 +3063,24 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3103,10 +3103,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46161</v>
@@ -3124,10 +3124,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>104</v>
@@ -3135,13 +3135,13 @@
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3162,10 +3162,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3183,13 +3183,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3225,10 +3225,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
@@ -3257,13 +3257,13 @@
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3284,10 +3284,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3316,13 +3316,13 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3345,10 +3345,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3366,13 +3366,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q29" s="9">
         <v>46157</v>
@@ -3410,10 +3410,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3442,13 +3442,13 @@
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3471,10 +3471,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3503,13 +3503,13 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3532,10 +3532,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3564,13 +3564,13 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3612,13 +3612,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q33" s="9">
         <v>46189</v>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3686,13 +3686,13 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3745,13 +3745,13 @@
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3793,7 +3793,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>140</v>
@@ -3814,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3829,7 +3829,7 @@
         <v>46190.16909938658</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3859,7 +3859,7 @@
         <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>142</v>
@@ -3912,7 +3912,7 @@
         <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>145</v>
@@ -3962,7 +3962,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>150</v>
@@ -3977,13 +3977,13 @@
         <v>46230</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3998,7 +3998,7 @@
         <v>46169.86096457176</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4028,7 +4028,7 @@
         <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>152</v>
@@ -4081,7 +4081,7 @@
         <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>155</v>
@@ -4184,7 +4184,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>162</v>
@@ -4199,13 +4199,13 @@
         <v>46210</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4220,7 +4220,7 @@
         <v>46190.1691007176</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4250,7 +4250,7 @@
         <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>164</v>
@@ -4303,7 +4303,7 @@
         <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>167</v>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46155.606241863425</v>
+        <v>46195.94762173611</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4359,7 +4359,9 @@
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="U46" s="12" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -4368,9 +4370,11 @@
       <c r="B47" s="9">
         <v>46155.60602364583</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46195.94740237268</v>
+      </c>
       <c r="D47" s="9">
-        <v>46169.18606665509</v>
+        <v>46195.947424224534</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>172</v>
@@ -4418,10 +4422,10 @@
         <v>33</v>
       </c>
       <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="12" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4431,9 +4435,11 @@
       <c r="B48" s="5">
         <v>46155.606031076386</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46195.94760157407</v>
+      </c>
       <c r="D48" s="5">
-        <v>46184.200254131945</v>
+        <v>46195.94761828704</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4481,10 +4487,10 @@
         <v>33</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>80</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4494,9 +4500,11 @@
       <c r="B49" s="9">
         <v>46155.606038645834</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46195.94765166666</v>
+      </c>
       <c r="D49" s="9">
-        <v>46184.169042256945</v>
+        <v>46195.947667824075</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>78</v>
@@ -4539,13 +4547,13 @@
         <v>46153</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T49" s="10">
-        <v>0</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>80</v>
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4602,13 +4610,13 @@
         <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4922,7 +4930,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46155.60624466435</v>
+        <v>46196.18431344908</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>199</v>
@@ -4966,14 +4974,14 @@
       <c r="R57" s="9">
         <v>46203</v>
       </c>
-      <c r="S57" s="7" t="s">
-        <v>101</v>
+      <c r="S57" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5036,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5048,7 +5056,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46155.60624616898</v>
+        <v>46196.184313425925</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>208</v>
@@ -5092,14 +5100,14 @@
       <c r="R59" s="9">
         <v>46203</v>
       </c>
-      <c r="S59" s="7" t="s">
-        <v>101</v>
+      <c r="S59" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5162,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5219,13 +5227,13 @@
         <v>46212</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5282,13 +5290,13 @@
         <v>46216</v>
       </c>
       <c r="S62" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5392,13 +5400,13 @@
         <v>46219</v>
       </c>
       <c r="S64" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5720,13 +5728,13 @@
         <v>46226</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5738,7 +5746,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.61927822916</v>
+        <v>46195.9476830787</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>225</v>
@@ -5791,7 +5799,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.61930075231</v>
+        <v>46195.9476728125</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>225</v>
@@ -5844,7 +5852,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.619317881945</v>
+        <v>46195.94767699074</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>225</v>
@@ -5897,7 +5905,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.61935121528</v>
+        <v>46195.94767966435</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>225</v>
@@ -6048,13 +6056,13 @@
         <v>46227</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6066,7 +6074,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.620624918985</v>
+        <v>46195.947673518516</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>225</v>
@@ -6119,7 +6127,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.62065888889</v>
+        <v>46195.947674131945</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>225</v>
@@ -6172,7 +6180,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46155.6206809838</v>
+        <v>46195.94768039352</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>225</v>
@@ -6225,7 +6233,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46155.62071310185</v>
+        <v>46195.94768090278</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>225</v>
@@ -6425,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6608,13 +6616,13 @@
         <v>46231</v>
       </c>
       <c r="S86" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6718,13 +6726,13 @@
         <v>46234</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7046,13 +7054,13 @@
         <v>46237</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7064,7 +7072,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.62125136574</v>
+        <v>46195.947681273145</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>225</v>
@@ -7115,7 +7123,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.62123118056</v>
+        <v>46195.94768182871</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>225</v>
@@ -7166,7 +7174,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.62121537037</v>
+        <v>46195.94768232639</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>225</v>
@@ -7217,7 +7225,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.621193576386</v>
+        <v>46195.947674641204</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>225</v>
@@ -7364,13 +7372,13 @@
         <v>46238</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7382,7 +7390,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.622123877314</v>
+        <v>46195.947675324074</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>225</v>
@@ -7433,7 +7441,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.622143472225</v>
+        <v>46195.947678958335</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>225</v>
@@ -7484,7 +7492,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.62216706018</v>
+        <v>46195.94768271991</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>225</v>
@@ -7535,7 +7543,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.6221805324</v>
+        <v>46195.94768359954</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>225</v>
@@ -7682,13 +7690,13 @@
         <v>46239</v>
       </c>
       <c r="S106" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -7700,7 +7708,7 @@
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.63460895834</v>
+        <v>46195.94767760417</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>188</v>
@@ -7751,7 +7759,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.63461768518</v>
+        <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>188</v>
@@ -7802,7 +7810,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.634628796295</v>
+        <v>46195.947675868054</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>188</v>
@@ -7853,7 +7861,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.634642916666</v>
+        <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>188</v>
@@ -8000,13 +8008,13 @@
         <v>46240</v>
       </c>
       <c r="S112" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8326,13 +8334,13 @@
         <v>46244</v>
       </c>
       <c r="S118" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
       </c>
       <c r="U118" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -8689,13 +8697,13 @@
         <v>46245</v>
       </c>
       <c r="S125" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -9007,13 +9015,13 @@
         <v>46246</v>
       </c>
       <c r="S131" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T131" s="10">
         <v>0</v>
       </c>
       <c r="U131" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -9333,13 +9341,13 @@
         <v>46247</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -9651,13 +9659,13 @@
         <v>46248</v>
       </c>
       <c r="S143" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T143" s="10">
         <v>0</v>
       </c>
       <c r="U143" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
@@ -10016,13 +10024,13 @@
         <v>46255</v>
       </c>
       <c r="S150" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
       </c>
       <c r="U150" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
@@ -10079,13 +10087,13 @@
         <v>46255</v>
       </c>
       <c r="S151" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T151" s="10">
         <v>0</v>
       </c>
       <c r="U151" s="11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46161.62430467593</v>
+        <v>46196.64233724537</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2665,9 +2665,11 @@
       <c r="B18" s="5">
         <v>46155.60580746528</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46196.64233232639</v>
+      </c>
       <c r="D18" s="5">
-        <v>46195.94769405093</v>
+        <v>46196.64234802083</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2715,10 +2717,10 @@
         <v>33</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2791,9 +2793,11 @@
       <c r="B20" s="5">
         <v>46155.60582009259</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46196.64393914352</v>
+      </c>
       <c r="D20" s="5">
-        <v>46195.94769378472</v>
+        <v>46196.643954976855</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2841,10 +2845,10 @@
         <v>33</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -2854,9 +2858,11 @@
       <c r="B21" s="9">
         <v>46155.60582561343</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46196.64456515046</v>
+      </c>
       <c r="D21" s="9">
-        <v>46195.94769402778</v>
+        <v>46196.644582037035</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>87</v>
@@ -2904,10 +2910,10 @@
         <v>33</v>
       </c>
       <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3645,7 +3651,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46190.169097499995</v>
+        <v>46196.642338564816</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3995,7 +4001,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.86096457176</v>
+        <v>46196.6445728588</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>88</v>
@@ -4217,7 +4223,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46190.1691007176</v>
+        <v>46196.64394635417</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>85</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -3936,9 +3936,11 @@
       <c r="B39" s="9">
         <v>46155.60598890047</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46196.6948721875</v>
+      </c>
       <c r="D39" s="9">
-        <v>46169.86053464121</v>
+        <v>46196.694887627316</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -3986,10 +3988,10 @@
         <v>100</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3999,9 +4001,11 @@
       <c r="B40" s="5">
         <v>46155.60599439815</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46196.69342611112</v>
+      </c>
       <c r="D40" s="5">
-        <v>46196.6445728588</v>
+        <v>46196.69342819444</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>88</v>
@@ -4052,9 +4056,11 @@
       <c r="B41" s="9">
         <v>46155.606000196756</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46196.693492025464</v>
+      </c>
       <c r="D41" s="9">
-        <v>46169.86098109954</v>
+        <v>46196.69349420139</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4107,7 +4113,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.86099739584</v>
+        <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -6577,7 +6583,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.60644643518</v>
+        <v>46196.693516562504</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>265</v>
@@ -6627,8 +6633,8 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="11" t="s">
-        <v>101</v>
+      <c r="U86" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="385">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -383,49 +383,49 @@
     <t>Generación OC motor OT 4316,Fabricación motor OT 4316,Planos motor proveedor OT 4316</t>
   </si>
   <si>
+    <t>1214777626585692</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4316</t>
+  </si>
+  <si>
+    <t>Motor OT 4316,Fabricación motor OT 4316,Planos motor proveedor OT 4316</t>
+  </si>
+  <si>
+    <t>1214777292917666</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4316</t>
+  </si>
+  <si>
+    <t>Motor OT 4316,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214777481699352</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4316</t>
+  </si>
+  <si>
+    <t>Motor OT 4316,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214777481716964</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4316</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser OT 4316 ,Generación OC materiales corte Laser OT 4316</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777626585692</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4316</t>
-  </si>
-  <si>
-    <t>Motor OT 4316,Fabricación motor OT 4316,Planos motor proveedor OT 4316</t>
-  </si>
-  <si>
-    <t>1214777292917666</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4316</t>
-  </si>
-  <si>
-    <t>Motor OT 4316,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214777481699352</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4316</t>
-  </si>
-  <si>
-    <t>Motor OT 4316,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214777481716964</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4316</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser OT 4316 ,Generación OC materiales corte Laser OT 4316</t>
   </si>
   <si>
     <t>1214777481716985</t>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46196.64233724537</v>
+        <v>46197.50229224537</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2463,7 +2463,9 @@
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="U14" s="12" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2602,9 +2604,11 @@
       <c r="B17" s="9">
         <v>46155.605799756944</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="9">
+        <v>46197.50227302083</v>
+      </c>
       <c r="D17" s="9">
-        <v>46169.86057697917</v>
+        <v>46197.502289386575</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2652,10 +2656,10 @@
         <v>33</v>
       </c>
       <c r="T17" s="10">
-        <v>0</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -3222,7 +3226,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.86074421296</v>
+        <v>46197.502279444445</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>109</v>
@@ -3342,7 +3346,7 @@
         <v>46182.69373945602</v>
       </c>
       <c r="D29" s="9">
-        <v>46189.18607957176</v>
+        <v>46197.18498747685</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>115</v>
@@ -3386,8 +3390,8 @@
       <c r="R29" s="9">
         <v>46196</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>117</v>
+      <c r="S29" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3398,7 +3402,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46155.605932488426</v>
@@ -3410,7 +3414,7 @@
         <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3443,7 +3447,7 @@
         <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3459,7 +3463,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46155.605939444446</v>
@@ -3471,7 +3475,7 @@
         <v>46182.67711275463</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3501,10 +3505,10 @@
         <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3520,7 +3524,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46155.605945868054</v>
@@ -3532,7 +3536,7 @@
         <v>46182.69372545139</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3562,10 +3566,10 @@
         <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3581,7 +3585,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46155.60595229166</v>
@@ -3591,16 +3595,16 @@
         <v>46192.17448341435</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I33" s="9">
         <v>46189</v>
@@ -3621,7 +3625,7 @@
         <v>90</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>90</v>
@@ -3633,7 +3637,7 @@
         <v>46199</v>
       </c>
       <c r="S33" s="12" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
@@ -3660,10 +3664,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3681,7 +3685,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>75</v>
@@ -3719,10 +3723,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46191</v>
@@ -3740,7 +3744,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>133</v>
@@ -3778,10 +3782,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3814,7 +3818,7 @@
         <v>46199</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3841,10 +3845,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
@@ -3894,10 +3898,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -4175,10 +4179,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46189</v>
@@ -4238,10 +4242,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4291,10 +4295,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46191</v>
@@ -4987,7 +4991,7 @@
         <v>46203</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
@@ -5113,7 +5117,7 @@
         <v>46203</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
@@ -6520,7 +6524,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46190.1908316551</v>
+        <v>46197.169061875</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>262</v>
@@ -6553,7 +6557,7 @@
         <v>196</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>263</v>
@@ -6565,7 +6569,7 @@
         <v>46197</v>
       </c>
       <c r="S85" s="12" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="T85" s="10">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1811,13 +1811,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46155.60560971065</v>
+        <v>46155.43894304398</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.873231273144</v>
+        <v>46175.70656460648</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87324449074</v>
+        <v>46175.70657782408</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1864,13 +1864,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46155.60572528935</v>
+        <v>46155.43905862268</v>
       </c>
       <c r="C5" s="9">
-        <v>46161.623405879625</v>
+        <v>46161.45673921297</v>
       </c>
       <c r="D5" s="9">
-        <v>46161.62342217592</v>
+        <v>46161.45675550926</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1927,13 +1927,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46155.60573108796</v>
+        <v>46155.4390644213</v>
       </c>
       <c r="C6" s="5">
-        <v>46161.62364042824</v>
+        <v>46161.456973761575</v>
       </c>
       <c r="D6" s="5">
-        <v>46161.623656701384</v>
+        <v>46161.45699003473</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1990,13 +1990,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46155.60573616898</v>
+        <v>46155.43906950232</v>
       </c>
       <c r="C7" s="9">
-        <v>46161.62365674769</v>
+        <v>46161.45699008102</v>
       </c>
       <c r="D7" s="9">
-        <v>46161.62382879629</v>
+        <v>46161.457162129635</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -2053,13 +2053,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46155.60574121527</v>
+        <v>46155.439074548616</v>
       </c>
       <c r="C8" s="5">
-        <v>46161.624193275464</v>
+        <v>46161.45752660879</v>
       </c>
       <c r="D8" s="5">
-        <v>46161.62420805555</v>
+        <v>46161.45754138889</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2116,13 +2116,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46155.6057468287</v>
+        <v>46155.43908016203</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87321719907</v>
+        <v>46175.706550532406</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.873231562495</v>
+        <v>46175.70656489584</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2179,11 +2179,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46155.605614988424</v>
+        <v>46155.43894832176</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.546774409726</v>
+        <v>46195.380107743054</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2228,13 +2228,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46155.605752372685</v>
+        <v>46155.43908570602</v>
       </c>
       <c r="C11" s="9">
-        <v>46161.624231967595</v>
+        <v>46161.45756530092</v>
       </c>
       <c r="D11" s="9">
-        <v>46195.54676366899</v>
+        <v>46195.380097002315</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2293,13 +2293,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46155.60576009259</v>
+        <v>46155.43909342593</v>
       </c>
       <c r="C12" s="5">
-        <v>46161.62423836805</v>
+        <v>46161.457571701394</v>
       </c>
       <c r="D12" s="5">
-        <v>46195.54676375</v>
+        <v>46195.38009708333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2358,13 +2358,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="9">
-        <v>46155.60576791667</v>
+        <v>46155.43910125</v>
       </c>
       <c r="C13" s="9">
-        <v>46161.62424628472</v>
+        <v>46161.45757961806</v>
       </c>
       <c r="D13" s="9">
-        <v>46195.546763645834</v>
+        <v>46195.38009697916</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>59</v>
@@ -2423,11 +2423,11 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46155.605619849535</v>
+        <v>46155.43895318287</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.50229224537</v>
+        <v>46197.33562557871</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2472,13 +2472,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="9">
-        <v>46155.605784768515</v>
+        <v>46155.43911810185</v>
       </c>
       <c r="C15" s="9">
-        <v>46161.62429071759</v>
+        <v>46161.45762405093</v>
       </c>
       <c r="D15" s="9">
-        <v>46161.624307349535</v>
+        <v>46161.45764068287</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>65</v>
@@ -2537,13 +2537,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46155.605792291666</v>
+        <v>46155.439125624995</v>
       </c>
       <c r="C16" s="5">
-        <v>46161.62429854167</v>
+        <v>46161.457631875004</v>
       </c>
       <c r="D16" s="5">
-        <v>46161.62431424769</v>
+        <v>46161.45764758102</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2602,13 +2602,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46155.605799756944</v>
+        <v>46155.43913309027</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.50227302083</v>
+        <v>46197.335606354165</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.502289386575</v>
+        <v>46197.33562271991</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2667,13 +2667,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46155.60580746528</v>
+        <v>46155.43914079861</v>
       </c>
       <c r="C18" s="5">
-        <v>46196.64233232639</v>
+        <v>46196.475665659724</v>
       </c>
       <c r="D18" s="5">
-        <v>46196.64234802083</v>
+        <v>46196.47568135417</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2732,11 +2732,11 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46155.605814317125</v>
+        <v>46155.43914765047</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46195.947693634254</v>
+        <v>46195.7810269676</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2795,13 +2795,13 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46155.60582009259</v>
+        <v>46155.43915342593</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.64393914352</v>
+        <v>46196.477272476855</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.643954976855</v>
+        <v>46196.47728831018</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2860,13 +2860,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="9">
-        <v>46155.60582561343</v>
+        <v>46155.439158946756</v>
       </c>
       <c r="C21" s="9">
-        <v>46196.64456515046</v>
+        <v>46196.4778984838</v>
       </c>
       <c r="D21" s="9">
-        <v>46196.644582037035</v>
+        <v>46196.47791537037</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>87</v>
@@ -2925,11 +2925,11 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46155.60562462963</v>
+        <v>46155.438957962964</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46182.693747743055</v>
+        <v>46182.52708107639</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2972,13 +2972,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="9">
-        <v>46155.60583177084</v>
+        <v>46155.439165104166</v>
       </c>
       <c r="C23" s="9">
-        <v>46182.6772816088</v>
+        <v>46182.51061494213</v>
       </c>
       <c r="D23" s="9">
-        <v>46182.67729332176</v>
+        <v>46182.510626655094</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>93</v>
@@ -3037,13 +3037,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46155.60583869213</v>
+        <v>46155.439172025464</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.65327461806</v>
+        <v>46182.48660795139</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.653276006946</v>
+        <v>46182.48660934028</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3098,13 +3098,13 @@
         <v>102</v>
       </c>
       <c r="B25" s="9">
-        <v>46155.605845625</v>
+        <v>46155.43917895833</v>
       </c>
       <c r="C25" s="9">
-        <v>46182.67726747685</v>
+        <v>46182.51060081019</v>
       </c>
       <c r="D25" s="9">
-        <v>46182.67726898148</v>
+        <v>46182.51060231481</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>103</v>
@@ -3159,11 +3159,11 @@
         <v>105</v>
       </c>
       <c r="B26" s="5">
-        <v>46155.60585226852</v>
+        <v>46155.43918560185</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.19528431713</v>
+        <v>46179.02861765046</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>106</v>
@@ -3222,11 +3222,11 @@
         <v>108</v>
       </c>
       <c r="B27" s="9">
-        <v>46155.605858807874</v>
+        <v>46155.4391921412</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.502279444445</v>
+        <v>46197.33561277778</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>109</v>
@@ -3281,11 +3281,11 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46155.605865289355</v>
+        <v>46155.439198622684</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.17124241898</v>
+        <v>46178.00457575232</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3340,13 +3340,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="9">
-        <v>46155.605925254626</v>
+        <v>46155.43925858796</v>
       </c>
       <c r="C29" s="9">
-        <v>46182.69373945602</v>
+        <v>46182.52707278935</v>
       </c>
       <c r="D29" s="9">
-        <v>46197.18498747685</v>
+        <v>46197.01832081018</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>115</v>
@@ -3405,13 +3405,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46155.605932488426</v>
+        <v>46155.439265821755</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.653084143516</v>
+        <v>46182.48641747685</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.65308653935</v>
+        <v>46182.48641987269</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3466,13 +3466,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="9">
-        <v>46155.605939444446</v>
+        <v>46155.439272777774</v>
       </c>
       <c r="C31" s="9">
-        <v>46182.67711099537</v>
+        <v>46182.510444328705</v>
       </c>
       <c r="D31" s="9">
-        <v>46182.67711275463</v>
+        <v>46182.51044608797</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>121</v>
@@ -3527,13 +3527,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46155.605945868054</v>
+        <v>46155.43927920139</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.69372391204</v>
+        <v>46182.527057245374</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.69372545139</v>
+        <v>46182.52705878472</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3588,11 +3588,11 @@
         <v>126</v>
       </c>
       <c r="B33" s="9">
-        <v>46155.60595229166</v>
+        <v>46155.439285625005</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46192.17448341435</v>
+        <v>46192.00781674769</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>127</v>
@@ -3651,11 +3651,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46155.60595878473</v>
+        <v>46155.439292118055</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46196.642338564816</v>
+        <v>46196.47567189815</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3710,11 +3710,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46155.60596540509</v>
+        <v>46155.43929873843</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.860883437505</v>
+        <v>46169.69421677083</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -3769,11 +3769,11 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46155.60597160879</v>
+        <v>46155.439304942134</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.17454548611</v>
+        <v>46192.007878819444</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3832,11 +3832,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46155.605976770836</v>
+        <v>46155.439310104164</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46190.16909938658</v>
+        <v>46190.002432719906</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>82</v>
@@ -3885,11 +3885,11 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46155.60598313657</v>
+        <v>46155.43931646991</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.86092723379</v>
+        <v>46169.69426056713</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -3938,13 +3938,13 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46155.60598890047</v>
+        <v>46155.4393222338</v>
       </c>
       <c r="C39" s="9">
-        <v>46196.6948721875</v>
+        <v>46196.52820552084</v>
       </c>
       <c r="D39" s="9">
-        <v>46196.694887627316</v>
+        <v>46196.52822096065</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4003,13 +4003,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46155.60599439815</v>
+        <v>46155.43932773148</v>
       </c>
       <c r="C40" s="5">
-        <v>46196.69342611112</v>
+        <v>46196.526759444445</v>
       </c>
       <c r="D40" s="5">
-        <v>46196.69342819444</v>
+        <v>46196.52676152778</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>88</v>
@@ -4058,13 +4058,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46155.606000196756</v>
+        <v>46155.43933353009</v>
       </c>
       <c r="C41" s="9">
-        <v>46196.693492025464</v>
+        <v>46196.5268253588</v>
       </c>
       <c r="D41" s="9">
-        <v>46196.69349420139</v>
+        <v>46196.52682753472</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4113,11 +4113,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46155.60600616898</v>
+        <v>46155.439339502314</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.69350203704</v>
+        <v>46196.52683537037</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4166,11 +4166,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46155.60601071759</v>
+        <v>46155.43934405093</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.86056584491</v>
+        <v>46169.69389917824</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4229,11 +4229,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46155.60601423611</v>
+        <v>46155.439347569445</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.64394635417</v>
+        <v>46196.477279687504</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>85</v>
@@ -4282,11 +4282,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="9">
-        <v>46155.60601877315</v>
+        <v>46155.43935210648</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.861063425924</v>
+        <v>46169.69439675926</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>166</v>
@@ -4335,11 +4335,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46155.60562939815</v>
+        <v>46155.43896273148</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.94762173611</v>
+        <v>46195.780955069444</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4384,13 +4384,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="9">
-        <v>46155.60602364583</v>
+        <v>46155.43935697917</v>
       </c>
       <c r="C47" s="9">
-        <v>46195.94740237268</v>
+        <v>46195.78073570602</v>
       </c>
       <c r="D47" s="9">
-        <v>46195.947424224534</v>
+        <v>46195.78075755787</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>172</v>
@@ -4449,13 +4449,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46155.606031076386</v>
+        <v>46155.43936440972</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.94760157407</v>
+        <v>46195.78093490741</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.94761828704</v>
+        <v>46195.78095162037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4514,13 +4514,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46155.606038645834</v>
+        <v>46155.43937197917</v>
       </c>
       <c r="C49" s="9">
-        <v>46195.94765166666</v>
+        <v>46195.780985000005</v>
       </c>
       <c r="D49" s="9">
-        <v>46195.947667824075</v>
+        <v>46195.781001157404</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>78</v>
@@ -4577,11 +4577,11 @@
         <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46155.606091747686</v>
+        <v>46155.439425081015</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.63491418981</v>
+        <v>46155.46824752315</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>183</v>
@@ -4640,11 +4640,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="9">
-        <v>46155.60610010417</v>
+        <v>46155.439433437496</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.64216699074</v>
+        <v>46155.47550032407</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4691,11 +4691,11 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46155.606106273146</v>
+        <v>46155.43943960648</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.6421837963</v>
+        <v>46155.47551712963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4742,11 +4742,11 @@
         <v>192</v>
       </c>
       <c r="B53" s="9">
-        <v>46155.60611204861</v>
+        <v>46155.43944538194</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.64219278935</v>
+        <v>46155.47552612268</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>188</v>
@@ -4793,11 +4793,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.60611671297</v>
+        <v>46155.439450046295</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.64220083333</v>
+        <v>46155.47553416667</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>188</v>
@@ -4844,11 +4844,11 @@
         <v>194</v>
       </c>
       <c r="B55" s="9">
-        <v>46155.63491277778</v>
+        <v>46155.46824611111</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.64223084491</v>
+        <v>46155.47556417824</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>188</v>
@@ -4895,11 +4895,11 @@
         <v>195</v>
       </c>
       <c r="B56" s="5">
-        <v>46155.60612125</v>
+        <v>46155.439454583335</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.60624375</v>
+        <v>46155.439577083336</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -4942,11 +4942,11 @@
         <v>198</v>
       </c>
       <c r="B57" s="9">
-        <v>46155.60612483796</v>
+        <v>46155.4394581713</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46196.18431344908</v>
+        <v>46196.017646782406</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>199</v>
@@ -5005,11 +5005,11 @@
         <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46155.6061331713</v>
+        <v>46155.43946650463</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46176.200130439815</v>
+        <v>46176.03346377314</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>204</v>
@@ -5068,11 +5068,11 @@
         <v>207</v>
       </c>
       <c r="B59" s="9">
-        <v>46155.606141446755</v>
+        <v>46155.4394747801</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46196.184313425925</v>
+        <v>46196.01764675926</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>208</v>
@@ -5131,11 +5131,11 @@
         <v>210</v>
       </c>
       <c r="B60" s="5">
-        <v>46155.60614949074</v>
+        <v>46155.43948282408</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46176.20013030093</v>
+        <v>46176.03346363426</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5194,11 +5194,11 @@
         <v>213</v>
       </c>
       <c r="B61" s="9">
-        <v>46155.606156319445</v>
+        <v>46155.43948965278</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.6062474537</v>
+        <v>46155.43958078704</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>214</v>
@@ -5257,11 +5257,11 @@
         <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46155.60616390046</v>
+        <v>46155.4394972338</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.608459560186</v>
+        <v>46155.441792893515</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5320,11 +5320,11 @@
         <v>217</v>
       </c>
       <c r="B63" s="9">
-        <v>46155.60617082176</v>
+        <v>46155.43950415509</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46155.6064415162</v>
+        <v>46155.43977484954</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>218</v>
@@ -5367,11 +5367,11 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46155.60617413194</v>
+        <v>46155.43950746528</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.6162571875</v>
+        <v>46155.44959052083</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5430,11 +5430,11 @@
         <v>224</v>
       </c>
       <c r="B65" s="9">
-        <v>46155.60618260417</v>
+        <v>46155.4395159375</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.60738728009</v>
+        <v>46155.44072061343</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>225</v>
@@ -5483,11 +5483,11 @@
         <v>228</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.60619106481</v>
+        <v>46155.43952439815</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.61677891204</v>
+        <v>46155.450112245366</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>225</v>
@@ -5536,11 +5536,11 @@
         <v>230</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.60619835649</v>
+        <v>46155.439531689815</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.6168003125</v>
+        <v>46155.450133645834</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>225</v>
@@ -5589,11 +5589,11 @@
         <v>232</v>
       </c>
       <c r="B68" s="5">
-        <v>46155.60620543981</v>
+        <v>46155.43953877315</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.61683189815</v>
+        <v>46155.45016523148</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>225</v>
@@ -5642,11 +5642,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46155.60745351852</v>
+        <v>46155.44078685185</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.617393912034</v>
+        <v>46155.45072724537</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>225</v>
@@ -5695,11 +5695,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46155.606212638886</v>
+        <v>46155.43954597222</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.61775856481</v>
+        <v>46155.45109189815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>235</v>
@@ -5758,11 +5758,11 @@
         <v>236</v>
       </c>
       <c r="B71" s="9">
-        <v>46155.60621899305</v>
+        <v>46155.43955232639</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46195.9476830787</v>
+        <v>46195.78101641204</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>225</v>
@@ -5811,11 +5811,11 @@
         <v>239</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.606226539356</v>
+        <v>46155.439559872684</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.9476728125</v>
+        <v>46195.78100614583</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>225</v>
@@ -5864,11 +5864,11 @@
         <v>241</v>
       </c>
       <c r="B73" s="9">
-        <v>46155.606234004634</v>
+        <v>46155.43956733796</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46195.94767699074</v>
+        <v>46195.78101032408</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>225</v>
@@ -5917,11 +5917,11 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46155.60628421296</v>
+        <v>46155.4396175463</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.94767966435</v>
+        <v>46195.781012997686</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>225</v>
@@ -5970,11 +5970,11 @@
         <v>243</v>
       </c>
       <c r="B75" s="9">
-        <v>46155.607690034725</v>
+        <v>46155.441023368054</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.61937777778</v>
+        <v>46155.45271111111</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>225</v>
@@ -6023,11 +6023,11 @@
         <v>244</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.606291909724</v>
+        <v>46155.43962524306</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.61911184028</v>
+        <v>46155.45244517361</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>245</v>
@@ -6086,11 +6086,11 @@
         <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.60629884259</v>
+        <v>46155.43963217593</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46195.947673518516</v>
+        <v>46195.78100685185</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>225</v>
@@ -6139,11 +6139,11 @@
         <v>248</v>
       </c>
       <c r="B78" s="5">
-        <v>46155.60630622685</v>
+        <v>46155.43963956018</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.947674131945</v>
+        <v>46195.78100746528</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>225</v>
@@ -6192,11 +6192,11 @@
         <v>249</v>
       </c>
       <c r="B79" s="9">
-        <v>46155.6063134375</v>
+        <v>46155.43964677083</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46195.94768039352</v>
+        <v>46195.78101372685</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>225</v>
@@ -6245,11 +6245,11 @@
         <v>251</v>
       </c>
       <c r="B80" s="5">
-        <v>46155.606319722225</v>
+        <v>46155.43965305555</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.94768090278</v>
+        <v>46195.78101423611</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>225</v>
@@ -6298,11 +6298,11 @@
         <v>252</v>
       </c>
       <c r="B81" s="9">
-        <v>46155.618322951384</v>
+        <v>46155.45165628473</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46155.620736377314</v>
+        <v>46155.45406971065</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>225</v>
@@ -6349,11 +6349,11 @@
         <v>253</v>
       </c>
       <c r="B82" s="5">
-        <v>46155.60632542824</v>
+        <v>46155.43965876158</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.60644350694</v>
+        <v>46155.43977684028</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>196</v>
@@ -6396,11 +6396,11 @@
         <v>255</v>
       </c>
       <c r="B83" s="9">
-        <v>46155.60632868056</v>
+        <v>46155.43966201389</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46182.19947712963</v>
+        <v>46182.03281046296</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>256</v>
@@ -6457,11 +6457,11 @@
         <v>258</v>
       </c>
       <c r="B84" s="5">
-        <v>46155.60633650463</v>
+        <v>46155.439669837964</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.677286018516</v>
+        <v>46182.51061935185</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>259</v>
@@ -6520,11 +6520,11 @@
         <v>261</v>
       </c>
       <c r="B85" s="9">
-        <v>46155.60634402778</v>
+        <v>46155.43967736111</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46197.169061875</v>
+        <v>46197.00239520833</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>262</v>
@@ -6583,11 +6583,11 @@
         <v>264</v>
       </c>
       <c r="B86" s="5">
-        <v>46155.60635177083</v>
+        <v>46155.43968510417</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46196.693516562504</v>
+        <v>46196.52684989583</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>265</v>
@@ -6646,11 +6646,11 @@
         <v>267</v>
       </c>
       <c r="B87" s="9">
-        <v>46155.606361921295</v>
+        <v>46155.43969525463</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.606780057875</v>
+        <v>46155.4401133912</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>268</v>
@@ -6693,11 +6693,11 @@
         <v>270</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.60636525463</v>
+        <v>46155.43969858796</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.620355625</v>
+        <v>46155.45368895833</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>271</v>
@@ -6756,11 +6756,11 @@
         <v>273</v>
       </c>
       <c r="B89" s="9">
-        <v>46155.606374525465</v>
+        <v>46155.43970785879</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.621619502315</v>
+        <v>46155.454952835644</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>225</v>
@@ -6809,11 +6809,11 @@
         <v>275</v>
       </c>
       <c r="B90" s="5">
-        <v>46155.60638027778</v>
+        <v>46155.43971361111</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.62163603009</v>
+        <v>46155.454969363425</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>225</v>
@@ -6862,11 +6862,11 @@
         <v>276</v>
       </c>
       <c r="B91" s="9">
-        <v>46155.60638583334</v>
+        <v>46155.439719166665</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.62166074074</v>
+        <v>46155.45499407407</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>225</v>
@@ -6915,11 +6915,11 @@
         <v>278</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.60639179398</v>
+        <v>46155.43972512732</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.62167399305</v>
+        <v>46155.45500732639</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>225</v>
@@ -6968,11 +6968,11 @@
         <v>280</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.61975986111</v>
+        <v>46155.45309319445</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.62169508102</v>
+        <v>46155.45502841435</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>225</v>
@@ -7021,11 +7021,11 @@
         <v>281</v>
       </c>
       <c r="B94" s="5">
-        <v>46155.60639783565</v>
+        <v>46155.43973116898</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.62191585648</v>
+        <v>46155.455249189814</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>282</v>
@@ -7084,11 +7084,11 @@
         <v>283</v>
       </c>
       <c r="B95" s="9">
-        <v>46155.60640402778</v>
+        <v>46155.439737361114</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46195.947681273145</v>
+        <v>46195.78101460648</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>225</v>
@@ -7135,11 +7135,11 @@
         <v>286</v>
       </c>
       <c r="B96" s="5">
-        <v>46155.60641090278</v>
+        <v>46155.43974423611</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.94768182871</v>
+        <v>46195.781015162036</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>225</v>
@@ -7186,11 +7186,11 @@
         <v>287</v>
       </c>
       <c r="B97" s="9">
-        <v>46155.60641760417</v>
+        <v>46155.4397509375</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46195.94768232639</v>
+        <v>46195.781015659726</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>225</v>
@@ -7237,11 +7237,11 @@
         <v>290</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.60642649306</v>
+        <v>46155.43975982639</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.947674641204</v>
+        <v>46195.78100797454</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>225</v>
@@ -7288,11 +7288,11 @@
         <v>291</v>
       </c>
       <c r="B99" s="9">
-        <v>46155.62115946759</v>
+        <v>46155.45449280093</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.64240027778</v>
+        <v>46155.47573361111</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>225</v>
@@ -7339,11 +7339,11 @@
         <v>292</v>
       </c>
       <c r="B100" s="5">
-        <v>46155.60648232639</v>
+        <v>46155.43981565972</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.631670462964</v>
+        <v>46155.4650037963</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>293</v>
@@ -7402,11 +7402,11 @@
         <v>294</v>
       </c>
       <c r="B101" s="9">
-        <v>46155.60649042824</v>
+        <v>46155.439823761575</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46195.947675324074</v>
+        <v>46195.7810086574</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>225</v>
@@ -7453,11 +7453,11 @@
         <v>296</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.6064993287</v>
+        <v>46155.439832662036</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.947678958335</v>
+        <v>46195.78101229167</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>225</v>
@@ -7504,11 +7504,11 @@
         <v>297</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.606507951394</v>
+        <v>46155.43984128472</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46195.94768271991</v>
+        <v>46195.78101605324</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>225</v>
@@ -7555,11 +7555,11 @@
         <v>299</v>
       </c>
       <c r="B104" s="5">
-        <v>46155.60651716436</v>
+        <v>46155.439850497685</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46195.94768359954</v>
+        <v>46195.78101693287</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>225</v>
@@ -7606,11 +7606,11 @@
         <v>301</v>
       </c>
       <c r="B105" s="9">
-        <v>46155.6221815162</v>
+        <v>46155.45551484954</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.63179349537</v>
+        <v>46155.465126828705</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>225</v>
@@ -7657,11 +7657,11 @@
         <v>303</v>
       </c>
       <c r="B106" s="5">
-        <v>46155.60652579861</v>
+        <v>46155.43985913195</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.63455996528</v>
+        <v>46155.46789329861</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>304</v>
@@ -7720,11 +7720,11 @@
         <v>306</v>
       </c>
       <c r="B107" s="9">
-        <v>46155.606533032405</v>
+        <v>46155.43986636574</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46195.94767760417</v>
+        <v>46195.7810109375</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>188</v>
@@ -7771,11 +7771,11 @@
         <v>309</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.60654145833</v>
+        <v>46155.43987479167</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46195.947678344906</v>
+        <v>46195.78101167824</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>188</v>
@@ -7822,11 +7822,11 @@
         <v>310</v>
       </c>
       <c r="B109" s="9">
-        <v>46155.60655399306</v>
+        <v>46155.439887326385</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46195.947675868054</v>
+        <v>46195.78100920139</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>188</v>
@@ -7873,11 +7873,11 @@
         <v>312</v>
       </c>
       <c r="B110" s="5">
-        <v>46155.60656262732</v>
+        <v>46155.43989596065</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46195.947676435186</v>
+        <v>46195.781009768514</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>188</v>
@@ -7924,11 +7924,11 @@
         <v>314</v>
       </c>
       <c r="B111" s="9">
-        <v>46155.63011625</v>
+        <v>46155.46344958333</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.63465961805</v>
+        <v>46155.46799295139</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>188</v>
@@ -7975,11 +7975,11 @@
         <v>316</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.60657109953</v>
+        <v>46155.439904432875</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.63577444444</v>
+        <v>46155.46910777778</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>317</v>
@@ -8038,11 +8038,11 @@
         <v>318</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.60657833333</v>
+        <v>46155.43991166667</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.635128090275</v>
+        <v>46155.46846142361</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>188</v>
@@ -8091,11 +8091,11 @@
         <v>320</v>
       </c>
       <c r="B114" s="5">
-        <v>46155.60658640046</v>
+        <v>46155.43991973379</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.63525575231</v>
+        <v>46155.46858908565</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>188</v>
@@ -8144,11 +8144,11 @@
         <v>321</v>
       </c>
       <c r="B115" s="9">
-        <v>46155.60659408565</v>
+        <v>46155.43992741898</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.635268750004</v>
+        <v>46155.46860208333</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>188</v>
@@ -8197,11 +8197,11 @@
         <v>323</v>
       </c>
       <c r="B116" s="5">
-        <v>46155.60660233797</v>
+        <v>46155.4399356713</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.635292569445</v>
+        <v>46155.46862590278</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>188</v>
@@ -8250,11 +8250,11 @@
         <v>324</v>
       </c>
       <c r="B117" s="9">
-        <v>46155.63398136574</v>
+        <v>46155.467314699075</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.63581856481</v>
+        <v>46155.46915189815</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>188</v>
@@ -8301,11 +8301,11 @@
         <v>325</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.60664190972</v>
+        <v>46155.439975243055</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.63694791667</v>
+        <v>46155.47028125</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>326</v>
@@ -8364,11 +8364,11 @@
         <v>328</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.60665081019</v>
+        <v>46155.43998414352</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.63810030093</v>
+        <v>46155.47143363426</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>188</v>
@@ -8415,11 +8415,11 @@
         <v>330</v>
       </c>
       <c r="B120" s="5">
-        <v>46155.60665825232</v>
+        <v>46155.43999158565</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.6381218287</v>
+        <v>46155.47145516204</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>188</v>
@@ -8466,11 +8466,11 @@
         <v>332</v>
       </c>
       <c r="B121" s="9">
-        <v>46155.60666534722</v>
+        <v>46155.43999868055</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.63813651621</v>
+        <v>46155.47146984954</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>188</v>
@@ -8517,11 +8517,11 @@
         <v>333</v>
       </c>
       <c r="B122" s="5">
-        <v>46155.60667253472</v>
+        <v>46155.440005868055</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.63815179398</v>
+        <v>46155.47148512732</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>188</v>
@@ -8568,11 +8568,11 @@
         <v>334</v>
       </c>
       <c r="B123" s="9">
-        <v>46155.63591585648</v>
+        <v>46155.46924918982</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.63817207176</v>
+        <v>46155.47150540509</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>188</v>
@@ -8619,11 +8619,11 @@
         <v>335</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.606679502314</v>
+        <v>46155.44001283565</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.60689462963</v>
+        <v>46155.44022796296</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>336</v>
@@ -8666,11 +8666,11 @@
         <v>338</v>
       </c>
       <c r="B125" s="9">
-        <v>46155.60668334491</v>
+        <v>46155.44001667824</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.63803638889</v>
+        <v>46155.47136972222</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>339</v>
@@ -8727,11 +8727,11 @@
         <v>343</v>
       </c>
       <c r="B126" s="5">
-        <v>46155.606691759254</v>
+        <v>46155.4400250926</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.6390279051</v>
+        <v>46155.472361238426</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>188</v>
@@ -8778,11 +8778,11 @@
         <v>345</v>
       </c>
       <c r="B127" s="9">
-        <v>46155.60669864583</v>
+        <v>46155.44003197917</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.639037835645</v>
+        <v>46155.47237116898</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>188</v>
@@ -8829,11 +8829,11 @@
         <v>346</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.60670615741</v>
+        <v>46155.44003949074</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.639063807874</v>
+        <v>46155.4723971412</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>188</v>
@@ -8880,11 +8880,11 @@
         <v>348</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.606713009256</v>
+        <v>46155.44004634259</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.63907559028</v>
+        <v>46155.47240892361</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>188</v>
@@ -8931,11 +8931,11 @@
         <v>349</v>
       </c>
       <c r="B130" s="5">
-        <v>46155.63715556713</v>
+        <v>46155.470488900464</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.63910325231</v>
+        <v>46155.47243658565</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>188</v>
@@ -8982,11 +8982,11 @@
         <v>350</v>
       </c>
       <c r="B131" s="9">
-        <v>46155.60671987268</v>
+        <v>46155.44005320602</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.638912615745</v>
+        <v>46155.47224594907</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>351</v>
@@ -9045,11 +9045,11 @@
         <v>352</v>
       </c>
       <c r="B132" s="5">
-        <v>46155.60672658565</v>
+        <v>46155.44005991898</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.639826238425</v>
+        <v>46155.47315957176</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>188</v>
@@ -9098,11 +9098,11 @@
         <v>354</v>
       </c>
       <c r="B133" s="9">
-        <v>46155.60673355324</v>
+        <v>46155.44006688657</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.63983615741</v>
+        <v>46155.47316949074</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>188</v>
@@ -9151,11 +9151,11 @@
         <v>356</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.60674053241</v>
+        <v>46155.44007386574</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.639844942125</v>
+        <v>46155.47317827547</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>188</v>
@@ -9204,11 +9204,11 @@
         <v>357</v>
       </c>
       <c r="B135" s="9">
-        <v>46155.60674741898</v>
+        <v>46155.44008075232</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.63986869213</v>
+        <v>46155.47320202546</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>188</v>
@@ -9257,11 +9257,11 @@
         <v>358</v>
       </c>
       <c r="B136" s="5">
-        <v>46155.63830266204</v>
+        <v>46155.471635995375</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.63990003472</v>
+        <v>46155.47323336806</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>188</v>
@@ -9308,11 +9308,11 @@
         <v>359</v>
       </c>
       <c r="B137" s="9">
-        <v>46155.60675400463</v>
+        <v>46155.44008733796</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46155.64036164352</v>
+        <v>46155.473694976856</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>360</v>
@@ -9371,11 +9371,11 @@
         <v>361</v>
       </c>
       <c r="B138" s="5">
-        <v>46155.60676105324</v>
+        <v>46155.44009438658</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46155.642618750004</v>
+        <v>46155.47595208333</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>188</v>
@@ -9422,11 +9422,11 @@
         <v>363</v>
       </c>
       <c r="B139" s="9">
-        <v>46155.60677012731</v>
+        <v>46155.44010346065</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46155.64263091436</v>
+        <v>46155.475964247686</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>188</v>
@@ -9473,11 +9473,11 @@
         <v>364</v>
       </c>
       <c r="B140" s="5">
-        <v>46155.60681737268</v>
+        <v>46155.44015070602</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46155.64264111111</v>
+        <v>46155.475974444445</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>188</v>
@@ -9524,11 +9524,11 @@
         <v>366</v>
       </c>
       <c r="B141" s="9">
-        <v>46155.60682548611</v>
+        <v>46155.440158819445</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46155.64265195602</v>
+        <v>46155.47598528935</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>188</v>
@@ -9575,11 +9575,11 @@
         <v>367</v>
       </c>
       <c r="B142" s="5">
-        <v>46155.63928425926</v>
+        <v>46155.47261759259</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46155.64266835648</v>
+        <v>46155.476001689814</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>188</v>
@@ -9626,11 +9626,11 @@
         <v>368</v>
       </c>
       <c r="B143" s="9">
-        <v>46155.60683229167</v>
+        <v>46155.440165625</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46155.641985821756</v>
+        <v>46155.47531915509</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>369</v>
@@ -9689,11 +9689,11 @@
         <v>371</v>
       </c>
       <c r="B144" s="5">
-        <v>46155.606840486114</v>
+        <v>46155.44017381944</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46155.64207402778</v>
+        <v>46155.47540736111</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>188</v>
@@ -9740,11 +9740,11 @@
         <v>372</v>
       </c>
       <c r="B145" s="9">
-        <v>46155.60684746528</v>
+        <v>46155.440180798614</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46155.64208369213</v>
+        <v>46155.47541702546</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>188</v>
@@ -9791,11 +9791,11 @@
         <v>373</v>
       </c>
       <c r="B146" s="5">
-        <v>46155.60685387731</v>
+        <v>46155.44018721065</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46155.64209340278</v>
+        <v>46155.47542673611</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>188</v>
@@ -9842,11 +9842,11 @@
         <v>374</v>
       </c>
       <c r="B147" s="9">
-        <v>46155.60686101852</v>
+        <v>46155.44019435185</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46155.64210719908</v>
+        <v>46155.475440532406</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>188</v>
@@ -9893,11 +9893,11 @@
         <v>375</v>
       </c>
       <c r="B148" s="5">
-        <v>46155.64052775463</v>
+        <v>46155.47386108796</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46155.64213097222</v>
+        <v>46155.47546430556</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>188</v>
@@ -9944,11 +9944,11 @@
         <v>376</v>
       </c>
       <c r="B149" s="9">
-        <v>46155.60686797454</v>
+        <v>46155.440201307865</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46155.60689638889</v>
+        <v>46155.440229722226</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>377</v>
@@ -9991,11 +9991,11 @@
         <v>379</v>
       </c>
       <c r="B150" s="5">
-        <v>46155.60687207176</v>
+        <v>46155.44020540509</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46155.60689709491</v>
+        <v>46155.44023042824</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>380</v>
@@ -10054,11 +10054,11 @@
         <v>383</v>
       </c>
       <c r="B151" s="9">
-        <v>46155.606879259256</v>
+        <v>46155.44021259259</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46195.54676386574</v>
+        <v>46195.38009719907</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>384</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -6520,7 +6520,7 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46197.169061875</v>
+        <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>264</v>
@@ -6564,8 +6564,8 @@
       <c r="R85" s="8">
         <v>46197</v>
       </c>
-      <c r="S85" s="12" t="s">
-        <v>131</v>
+      <c r="S85" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T85" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1817,13 +1817,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46155.60560971065</v>
+        <v>46155.43894304398</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.873231273144</v>
+        <v>46175.70656460648</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.71343847222</v>
+        <v>46197.54677180556</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1866,13 +1866,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46155.60572528935</v>
+        <v>46155.43905862268</v>
       </c>
       <c r="C5" s="8">
-        <v>46161.623405879625</v>
+        <v>46161.45673921297</v>
       </c>
       <c r="D5" s="8">
-        <v>46161.62342217592</v>
+        <v>46161.45675550926</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1929,13 +1929,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46155.60573108796</v>
+        <v>46155.4390644213</v>
       </c>
       <c r="C6" s="5">
-        <v>46161.62364042824</v>
+        <v>46161.456973761575</v>
       </c>
       <c r="D6" s="5">
-        <v>46161.623656701384</v>
+        <v>46161.45699003473</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1992,13 +1992,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46155.60573616898</v>
+        <v>46155.43906950232</v>
       </c>
       <c r="C7" s="8">
-        <v>46161.62365674769</v>
+        <v>46161.45699008102</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.62382879629</v>
+        <v>46161.457162129635</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2055,13 +2055,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46155.60574121527</v>
+        <v>46155.439074548616</v>
       </c>
       <c r="C8" s="5">
-        <v>46161.624193275464</v>
+        <v>46161.45752660879</v>
       </c>
       <c r="D8" s="5">
-        <v>46161.62420805555</v>
+        <v>46161.45754138889</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2118,13 +2118,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46155.6057468287</v>
+        <v>46155.43908016203</v>
       </c>
       <c r="C9" s="8">
-        <v>46175.87321719907</v>
+        <v>46175.706550532406</v>
       </c>
       <c r="D9" s="8">
-        <v>46175.873231562495</v>
+        <v>46175.70656489584</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2181,11 +2181,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46155.605614988424</v>
+        <v>46155.43894832176</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.71331710648</v>
+        <v>46197.546650439814</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2228,13 +2228,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46155.605752372685</v>
+        <v>46155.43908570602</v>
       </c>
       <c r="C11" s="8">
-        <v>46161.624231967595</v>
+        <v>46161.45756530092</v>
       </c>
       <c r="D11" s="8">
-        <v>46195.54676366899</v>
+        <v>46195.380097002315</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2293,13 +2293,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46155.60576009259</v>
+        <v>46155.43909342593</v>
       </c>
       <c r="C12" s="5">
-        <v>46161.62423836805</v>
+        <v>46161.457571701394</v>
       </c>
       <c r="D12" s="5">
-        <v>46195.54676375</v>
+        <v>46195.38009708333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2358,13 +2358,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46155.60576791667</v>
+        <v>46155.43910125</v>
       </c>
       <c r="C13" s="8">
-        <v>46161.62424628472</v>
+        <v>46161.45757961806</v>
       </c>
       <c r="D13" s="8">
-        <v>46195.546763645834</v>
+        <v>46195.38009697916</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2423,11 +2423,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46155.605619849535</v>
+        <v>46155.43895318287</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.71329697917</v>
+        <v>46197.5466303125</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2470,13 +2470,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46155.605784768515</v>
+        <v>46155.43911810185</v>
       </c>
       <c r="C15" s="8">
-        <v>46161.62429071759</v>
+        <v>46161.45762405093</v>
       </c>
       <c r="D15" s="8">
-        <v>46161.624307349535</v>
+        <v>46161.45764068287</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2535,13 +2535,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46155.605792291666</v>
+        <v>46155.439125624995</v>
       </c>
       <c r="C16" s="5">
-        <v>46161.62429854167</v>
+        <v>46161.457631875004</v>
       </c>
       <c r="D16" s="5">
-        <v>46161.62431424769</v>
+        <v>46161.45764758102</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2600,13 +2600,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46155.605799756944</v>
+        <v>46155.43913309027</v>
       </c>
       <c r="C17" s="8">
-        <v>46197.50227302083</v>
+        <v>46197.335606354165</v>
       </c>
       <c r="D17" s="8">
-        <v>46197.502289386575</v>
+        <v>46197.33562271991</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2665,13 +2665,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46155.60580746528</v>
+        <v>46155.43914079861</v>
       </c>
       <c r="C18" s="5">
-        <v>46196.64233232639</v>
+        <v>46196.475665659724</v>
       </c>
       <c r="D18" s="5">
-        <v>46196.64234802083</v>
+        <v>46196.47568135417</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2730,11 +2730,11 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46155.605814317125</v>
+        <v>46155.43914765047</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46195.947693634254</v>
+        <v>46195.7810269676</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2793,13 +2793,13 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46155.60582009259</v>
+        <v>46155.43915342593</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.64393914352</v>
+        <v>46196.477272476855</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.643954976855</v>
+        <v>46196.47728831018</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2858,13 +2858,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46155.60582561343</v>
+        <v>46155.439158946756</v>
       </c>
       <c r="C21" s="8">
-        <v>46196.64456515046</v>
+        <v>46196.4778984838</v>
       </c>
       <c r="D21" s="8">
-        <v>46196.644582037035</v>
+        <v>46196.47791537037</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2923,11 +2923,11 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46155.60562462963</v>
+        <v>46155.438957962964</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46182.693747743055</v>
+        <v>46182.52708107639</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2970,13 +2970,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46155.60583177084</v>
+        <v>46155.439165104166</v>
       </c>
       <c r="C23" s="8">
-        <v>46182.6772816088</v>
+        <v>46182.51061494213</v>
       </c>
       <c r="D23" s="8">
-        <v>46182.67729332176</v>
+        <v>46182.510626655094</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -3035,13 +3035,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46155.60583869213</v>
+        <v>46155.439172025464</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.65327461806</v>
+        <v>46182.48660795139</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.653276006946</v>
+        <v>46182.48660934028</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3096,13 +3096,13 @@
         <v>102</v>
       </c>
       <c r="B25" s="8">
-        <v>46155.605845625</v>
+        <v>46155.43917895833</v>
       </c>
       <c r="C25" s="8">
-        <v>46182.67726747685</v>
+        <v>46182.51060081019</v>
       </c>
       <c r="D25" s="8">
-        <v>46182.67726898148</v>
+        <v>46182.51060231481</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>103</v>
@@ -3157,11 +3157,11 @@
         <v>105</v>
       </c>
       <c r="B26" s="5">
-        <v>46155.60585226852</v>
+        <v>46155.43918560185</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.19528431713</v>
+        <v>46179.02861765046</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>106</v>
@@ -3220,11 +3220,11 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46155.605858807874</v>
+        <v>46155.4391921412</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46197.502279444445</v>
+        <v>46197.33561277778</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -3279,11 +3279,11 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46155.605865289355</v>
+        <v>46155.439198622684</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.17124241898</v>
+        <v>46178.00457575232</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3338,13 +3338,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46155.605925254626</v>
+        <v>46155.43925858796</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.69373945602</v>
+        <v>46182.52707278935</v>
       </c>
       <c r="D29" s="8">
-        <v>46197.18498747685</v>
+        <v>46197.01832081018</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3403,13 +3403,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46155.605932488426</v>
+        <v>46155.439265821755</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.653084143516</v>
+        <v>46182.48641747685</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.65308653935</v>
+        <v>46182.48641987269</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3464,13 +3464,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46155.605939444446</v>
+        <v>46155.439272777774</v>
       </c>
       <c r="C31" s="8">
-        <v>46182.67711099537</v>
+        <v>46182.510444328705</v>
       </c>
       <c r="D31" s="8">
-        <v>46182.67711275463</v>
+        <v>46182.51044608797</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3525,13 +3525,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46155.605945868054</v>
+        <v>46155.43927920139</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.69372391204</v>
+        <v>46182.527057245374</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.69372545139</v>
+        <v>46182.52705878472</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3586,11 +3586,11 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46155.60595229166</v>
+        <v>46155.439285625005</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46192.17448341435</v>
+        <v>46192.00781674769</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3649,11 +3649,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46155.60595878473</v>
+        <v>46155.439292118055</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46196.642338564816</v>
+        <v>46196.47567189815</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3708,11 +3708,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="8">
-        <v>46155.60596540509</v>
+        <v>46155.43929873843</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46169.860883437505</v>
+        <v>46169.69421677083</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3767,11 +3767,11 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46155.60597160879</v>
+        <v>46155.439304942134</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.17454548611</v>
+        <v>46192.007878819444</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3830,11 +3830,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="8">
-        <v>46155.605976770836</v>
+        <v>46155.439310104164</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46190.16909938658</v>
+        <v>46190.002432719906</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>81</v>
@@ -3883,11 +3883,11 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46155.60598313657</v>
+        <v>46155.43931646991</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.86092723379</v>
+        <v>46169.69426056713</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -3936,13 +3936,13 @@
         <v>146</v>
       </c>
       <c r="B39" s="8">
-        <v>46155.60598890047</v>
+        <v>46155.4393222338</v>
       </c>
       <c r="C39" s="8">
-        <v>46196.6948721875</v>
+        <v>46196.52820552084</v>
       </c>
       <c r="D39" s="8">
-        <v>46196.694887627316</v>
+        <v>46196.52822096065</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>147</v>
@@ -4001,13 +4001,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46155.60599439815</v>
+        <v>46155.43932773148</v>
       </c>
       <c r="C40" s="5">
-        <v>46196.69342611112</v>
+        <v>46196.526759444445</v>
       </c>
       <c r="D40" s="5">
-        <v>46196.69342819444</v>
+        <v>46196.52676152778</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>88</v>
@@ -4056,13 +4056,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46155.606000196756</v>
+        <v>46155.43933353009</v>
       </c>
       <c r="C41" s="8">
-        <v>46196.693492025464</v>
+        <v>46196.5268253588</v>
       </c>
       <c r="D41" s="8">
-        <v>46196.69349420139</v>
+        <v>46196.52682753472</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -4111,11 +4111,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46155.60600616898</v>
+        <v>46155.439339502314</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.69350203704</v>
+        <v>46196.52683537037</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4164,11 +4164,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46155.60601071759</v>
+        <v>46155.43934405093</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46169.86056584491</v>
+        <v>46169.69389917824</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -4227,11 +4227,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46155.60601423611</v>
+        <v>46155.439347569445</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.64394635417</v>
+        <v>46196.477279687504</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>85</v>
@@ -4280,11 +4280,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46155.60601877315</v>
+        <v>46155.43935210648</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46169.861063425924</v>
+        <v>46169.69439675926</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4333,11 +4333,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46155.60562939815</v>
+        <v>46155.43896273148</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.71336900463</v>
+        <v>46197.54670233796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4380,13 +4380,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46155.60602364583</v>
+        <v>46155.43935697917</v>
       </c>
       <c r="C47" s="8">
-        <v>46195.94740237268</v>
+        <v>46195.78073570602</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.71427196759</v>
+        <v>46197.547605300926</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4445,13 +4445,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46155.606031076386</v>
+        <v>46155.43936440972</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.94760157407</v>
+        <v>46195.78093490741</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.71433108796</v>
+        <v>46197.5476644213</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4510,13 +4510,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46155.606038645834</v>
+        <v>46155.43937197917</v>
       </c>
       <c r="C49" s="8">
-        <v>46195.94765166666</v>
+        <v>46195.780985000005</v>
       </c>
       <c r="D49" s="8">
-        <v>46195.947667824075</v>
+        <v>46195.781001157404</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>77</v>
@@ -4573,11 +4573,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46155.606091747686</v>
+        <v>46155.439425081015</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.63491418981</v>
+        <v>46155.46824752315</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4636,11 +4636,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="8">
-        <v>46155.60610010417</v>
+        <v>46155.439433437496</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46155.64216699074</v>
+        <v>46155.47550032407</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>190</v>
@@ -4687,11 +4687,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46155.606106273146</v>
+        <v>46155.43943960648</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.6421837963</v>
+        <v>46155.47551712963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4738,11 +4738,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46155.60611204861</v>
+        <v>46155.43944538194</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46155.64219278935</v>
+        <v>46155.47552612268</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>190</v>
@@ -4789,11 +4789,11 @@
         <v>195</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.60611671297</v>
+        <v>46155.439450046295</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.64220083333</v>
+        <v>46155.47553416667</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4840,11 +4840,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="8">
-        <v>46155.63491277778</v>
+        <v>46155.46824611111</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46155.64223084491</v>
+        <v>46155.47556417824</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>190</v>
@@ -4891,11 +4891,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46155.60612125</v>
+        <v>46155.439454583335</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.60624375</v>
+        <v>46155.439577083336</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4938,11 +4938,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46155.60612483796</v>
+        <v>46155.4394581713</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46196.18431344908</v>
+        <v>46196.017646782406</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5001,11 +5001,11 @@
         <v>205</v>
       </c>
       <c r="B58" s="5">
-        <v>46155.6061331713</v>
+        <v>46155.43946650463</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46176.200130439815</v>
+        <v>46176.03346377314</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>206</v>
@@ -5064,11 +5064,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46155.606141446755</v>
+        <v>46155.4394747801</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46196.184313425925</v>
+        <v>46196.01764675926</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>210</v>
@@ -5127,11 +5127,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46155.60614949074</v>
+        <v>46155.43948282408</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46176.20013030093</v>
+        <v>46176.03346363426</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5190,11 +5190,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="8">
-        <v>46155.606156319445</v>
+        <v>46155.43948965278</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46155.6062474537</v>
+        <v>46155.43958078704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5253,11 +5253,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46155.60616390046</v>
+        <v>46155.4394972338</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.608459560186</v>
+        <v>46155.441792893515</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>217</v>
@@ -5316,11 +5316,11 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46155.60617082176</v>
+        <v>46155.43950415509</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46155.6064415162</v>
+        <v>46155.43977484954</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>220</v>
@@ -5363,11 +5363,11 @@
         <v>222</v>
       </c>
       <c r="B64" s="5">
-        <v>46155.60617413194</v>
+        <v>46155.43950746528</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.6162571875</v>
+        <v>46155.44959052083</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>223</v>
@@ -5426,11 +5426,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="8">
-        <v>46155.60618260417</v>
+        <v>46155.4395159375</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46155.60738728009</v>
+        <v>46155.44072061343</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>227</v>
@@ -5479,11 +5479,11 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.60619106481</v>
+        <v>46155.43952439815</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.61677891204</v>
+        <v>46155.450112245366</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>227</v>
@@ -5532,11 +5532,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="8">
-        <v>46155.60619835649</v>
+        <v>46155.439531689815</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46155.6168003125</v>
+        <v>46155.450133645834</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>227</v>
@@ -5585,11 +5585,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46155.60620543981</v>
+        <v>46155.43953877315</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.61683189815</v>
+        <v>46155.45016523148</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5638,11 +5638,11 @@
         <v>235</v>
       </c>
       <c r="B69" s="8">
-        <v>46155.60745351852</v>
+        <v>46155.44078685185</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46155.617393912034</v>
+        <v>46155.45072724537</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>227</v>
@@ -5691,11 +5691,11 @@
         <v>236</v>
       </c>
       <c r="B70" s="5">
-        <v>46155.606212638886</v>
+        <v>46155.43954597222</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.61775856481</v>
+        <v>46155.45109189815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>237</v>
@@ -5754,11 +5754,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="8">
-        <v>46155.60621899305</v>
+        <v>46155.43955232639</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.9476830787</v>
+        <v>46195.78101641204</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>227</v>
@@ -5807,11 +5807,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.606226539356</v>
+        <v>46155.439559872684</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.9476728125</v>
+        <v>46195.78100614583</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>227</v>
@@ -5860,11 +5860,11 @@
         <v>243</v>
       </c>
       <c r="B73" s="8">
-        <v>46155.606234004634</v>
+        <v>46155.43956733796</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.94767699074</v>
+        <v>46195.78101032408</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>227</v>
@@ -5913,11 +5913,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46155.60628421296</v>
+        <v>46155.4396175463</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.94767966435</v>
+        <v>46195.781012997686</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>227</v>
@@ -5966,11 +5966,11 @@
         <v>245</v>
       </c>
       <c r="B75" s="8">
-        <v>46155.607690034725</v>
+        <v>46155.441023368054</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46155.61937777778</v>
+        <v>46155.45271111111</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>227</v>
@@ -6019,11 +6019,11 @@
         <v>246</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.606291909724</v>
+        <v>46155.43962524306</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.61911184028</v>
+        <v>46155.45244517361</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>247</v>
@@ -6082,11 +6082,11 @@
         <v>248</v>
       </c>
       <c r="B77" s="8">
-        <v>46155.60629884259</v>
+        <v>46155.43963217593</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.947673518516</v>
+        <v>46195.78100685185</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>227</v>
@@ -6135,11 +6135,11 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46155.60630622685</v>
+        <v>46155.43963956018</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.947674131945</v>
+        <v>46195.78100746528</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>227</v>
@@ -6188,11 +6188,11 @@
         <v>251</v>
       </c>
       <c r="B79" s="8">
-        <v>46155.6063134375</v>
+        <v>46155.43964677083</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.94768039352</v>
+        <v>46195.78101372685</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>227</v>
@@ -6241,11 +6241,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46155.606319722225</v>
+        <v>46155.43965305555</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.94768090278</v>
+        <v>46195.78101423611</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>227</v>
@@ -6294,11 +6294,11 @@
         <v>254</v>
       </c>
       <c r="B81" s="8">
-        <v>46155.618322951384</v>
+        <v>46155.45165628473</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46155.620736377314</v>
+        <v>46155.45406971065</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>227</v>
@@ -6345,11 +6345,11 @@
         <v>255</v>
       </c>
       <c r="B82" s="5">
-        <v>46155.60632542824</v>
+        <v>46155.43965876158</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.60644350694</v>
+        <v>46155.43977684028</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>198</v>
@@ -6392,11 +6392,11 @@
         <v>257</v>
       </c>
       <c r="B83" s="8">
-        <v>46155.60632868056</v>
+        <v>46155.43966201389</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46182.19947712963</v>
+        <v>46182.03281046296</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>258</v>
@@ -6453,11 +6453,11 @@
         <v>260</v>
       </c>
       <c r="B84" s="5">
-        <v>46155.60633650463</v>
+        <v>46155.439669837964</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.677286018516</v>
+        <v>46182.51061935185</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>261</v>
@@ -6516,11 +6516,11 @@
         <v>263</v>
       </c>
       <c r="B85" s="8">
-        <v>46155.60634402778</v>
+        <v>46155.43967736111</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46198.182506087964</v>
+        <v>46198.01583942129</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>264</v>
@@ -6579,11 +6579,11 @@
         <v>266</v>
       </c>
       <c r="B86" s="5">
-        <v>46155.60635177083</v>
+        <v>46155.43968510417</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46196.693516562504</v>
+        <v>46196.52684989583</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>267</v>
@@ -6642,11 +6642,11 @@
         <v>269</v>
       </c>
       <c r="B87" s="8">
-        <v>46155.606361921295</v>
+        <v>46155.43969525463</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46155.606780057875</v>
+        <v>46155.4401133912</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -6689,11 +6689,11 @@
         <v>272</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.60636525463</v>
+        <v>46155.43969858796</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.620355625</v>
+        <v>46155.45368895833</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>273</v>
@@ -6752,11 +6752,11 @@
         <v>275</v>
       </c>
       <c r="B89" s="8">
-        <v>46155.606374525465</v>
+        <v>46155.43970785879</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.621619502315</v>
+        <v>46155.454952835644</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>227</v>
@@ -6805,11 +6805,11 @@
         <v>277</v>
       </c>
       <c r="B90" s="5">
-        <v>46155.60638027778</v>
+        <v>46155.43971361111</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.62163603009</v>
+        <v>46155.454969363425</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>227</v>
@@ -6858,11 +6858,11 @@
         <v>278</v>
       </c>
       <c r="B91" s="8">
-        <v>46155.60638583334</v>
+        <v>46155.439719166665</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46155.62166074074</v>
+        <v>46155.45499407407</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>227</v>
@@ -6911,11 +6911,11 @@
         <v>280</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.60639179398</v>
+        <v>46155.43972512732</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.62167399305</v>
+        <v>46155.45500732639</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>227</v>
@@ -6964,11 +6964,11 @@
         <v>282</v>
       </c>
       <c r="B93" s="8">
-        <v>46155.61975986111</v>
+        <v>46155.45309319445</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46155.62169508102</v>
+        <v>46155.45502841435</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>227</v>
@@ -7017,11 +7017,11 @@
         <v>283</v>
       </c>
       <c r="B94" s="5">
-        <v>46155.60639783565</v>
+        <v>46155.43973116898</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.62191585648</v>
+        <v>46155.455249189814</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>284</v>
@@ -7080,11 +7080,11 @@
         <v>285</v>
       </c>
       <c r="B95" s="8">
-        <v>46155.60640402778</v>
+        <v>46155.439737361114</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.947681273145</v>
+        <v>46195.78101460648</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>227</v>
@@ -7131,11 +7131,11 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46155.60641090278</v>
+        <v>46155.43974423611</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.94768182871</v>
+        <v>46195.781015162036</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>227</v>
@@ -7182,11 +7182,11 @@
         <v>289</v>
       </c>
       <c r="B97" s="8">
-        <v>46155.60641760417</v>
+        <v>46155.4397509375</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.94768232639</v>
+        <v>46195.781015659726</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>227</v>
@@ -7233,11 +7233,11 @@
         <v>292</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.60642649306</v>
+        <v>46155.43975982639</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.947674641204</v>
+        <v>46195.78100797454</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>227</v>
@@ -7284,11 +7284,11 @@
         <v>293</v>
       </c>
       <c r="B99" s="8">
-        <v>46155.62115946759</v>
+        <v>46155.45449280093</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46155.64240027778</v>
+        <v>46155.47573361111</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>227</v>
@@ -7335,11 +7335,11 @@
         <v>294</v>
       </c>
       <c r="B100" s="5">
-        <v>46155.60648232639</v>
+        <v>46155.43981565972</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.631670462964</v>
+        <v>46155.4650037963</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>295</v>
@@ -7398,11 +7398,11 @@
         <v>296</v>
       </c>
       <c r="B101" s="8">
-        <v>46155.60649042824</v>
+        <v>46155.439823761575</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.947675324074</v>
+        <v>46195.7810086574</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>227</v>
@@ -7449,11 +7449,11 @@
         <v>298</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.6064993287</v>
+        <v>46155.439832662036</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.947678958335</v>
+        <v>46195.78101229167</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>227</v>
@@ -7500,11 +7500,11 @@
         <v>299</v>
       </c>
       <c r="B103" s="8">
-        <v>46155.606507951394</v>
+        <v>46155.43984128472</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.94768271991</v>
+        <v>46195.78101605324</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>227</v>
@@ -7551,11 +7551,11 @@
         <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46155.60651716436</v>
+        <v>46155.439850497685</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46195.94768359954</v>
+        <v>46195.78101693287</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>227</v>
@@ -7602,11 +7602,11 @@
         <v>303</v>
       </c>
       <c r="B105" s="8">
-        <v>46155.6221815162</v>
+        <v>46155.45551484954</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46155.63179349537</v>
+        <v>46155.465126828705</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>227</v>
@@ -7653,11 +7653,11 @@
         <v>305</v>
       </c>
       <c r="B106" s="5">
-        <v>46155.60652579861</v>
+        <v>46155.43985913195</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.63455996528</v>
+        <v>46155.46789329861</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>306</v>
@@ -7716,11 +7716,11 @@
         <v>308</v>
       </c>
       <c r="B107" s="8">
-        <v>46155.606533032405</v>
+        <v>46155.43986636574</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46195.94767760417</v>
+        <v>46195.7810109375</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>190</v>
@@ -7767,11 +7767,11 @@
         <v>311</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.60654145833</v>
+        <v>46155.43987479167</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46195.947678344906</v>
+        <v>46195.78101167824</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>190</v>
@@ -7818,11 +7818,11 @@
         <v>312</v>
       </c>
       <c r="B109" s="8">
-        <v>46155.60655399306</v>
+        <v>46155.439887326385</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46195.947675868054</v>
+        <v>46195.78100920139</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>190</v>
@@ -7869,11 +7869,11 @@
         <v>314</v>
       </c>
       <c r="B110" s="5">
-        <v>46155.60656262732</v>
+        <v>46155.43989596065</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46195.947676435186</v>
+        <v>46195.781009768514</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -7920,11 +7920,11 @@
         <v>316</v>
       </c>
       <c r="B111" s="8">
-        <v>46155.63011625</v>
+        <v>46155.46344958333</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46155.63465961805</v>
+        <v>46155.46799295139</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>190</v>
@@ -7971,11 +7971,11 @@
         <v>318</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.60657109953</v>
+        <v>46155.439904432875</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.63577444444</v>
+        <v>46155.46910777778</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>319</v>
@@ -8034,11 +8034,11 @@
         <v>320</v>
       </c>
       <c r="B113" s="8">
-        <v>46155.60657833333</v>
+        <v>46155.43991166667</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46155.635128090275</v>
+        <v>46155.46846142361</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>190</v>
@@ -8087,11 +8087,11 @@
         <v>322</v>
       </c>
       <c r="B114" s="5">
-        <v>46155.60658640046</v>
+        <v>46155.43991973379</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.63525575231</v>
+        <v>46155.46858908565</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>190</v>
@@ -8140,11 +8140,11 @@
         <v>323</v>
       </c>
       <c r="B115" s="8">
-        <v>46155.60659408565</v>
+        <v>46155.43992741898</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46155.635268750004</v>
+        <v>46155.46860208333</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>190</v>
@@ -8193,11 +8193,11 @@
         <v>325</v>
       </c>
       <c r="B116" s="5">
-        <v>46155.60660233797</v>
+        <v>46155.4399356713</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.635292569445</v>
+        <v>46155.46862590278</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8246,11 +8246,11 @@
         <v>326</v>
       </c>
       <c r="B117" s="8">
-        <v>46155.63398136574</v>
+        <v>46155.467314699075</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46155.63581856481</v>
+        <v>46155.46915189815</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>190</v>
@@ -8297,11 +8297,11 @@
         <v>327</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.60664190972</v>
+        <v>46155.439975243055</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.63694791667</v>
+        <v>46155.47028125</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>328</v>
@@ -8360,11 +8360,11 @@
         <v>330</v>
       </c>
       <c r="B119" s="8">
-        <v>46155.60665081019</v>
+        <v>46155.43998414352</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46155.63810030093</v>
+        <v>46155.47143363426</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>190</v>
@@ -8411,11 +8411,11 @@
         <v>332</v>
       </c>
       <c r="B120" s="5">
-        <v>46155.60665825232</v>
+        <v>46155.43999158565</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.6381218287</v>
+        <v>46155.47145516204</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8462,11 +8462,11 @@
         <v>334</v>
       </c>
       <c r="B121" s="8">
-        <v>46155.60666534722</v>
+        <v>46155.43999868055</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46155.63813651621</v>
+        <v>46155.47146984954</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>190</v>
@@ -8513,11 +8513,11 @@
         <v>335</v>
       </c>
       <c r="B122" s="5">
-        <v>46155.60667253472</v>
+        <v>46155.440005868055</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.63815179398</v>
+        <v>46155.47148512732</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8564,11 +8564,11 @@
         <v>336</v>
       </c>
       <c r="B123" s="8">
-        <v>46155.63591585648</v>
+        <v>46155.46924918982</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46155.63817207176</v>
+        <v>46155.47150540509</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>190</v>
@@ -8615,11 +8615,11 @@
         <v>337</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.606679502314</v>
+        <v>46155.44001283565</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.60689462963</v>
+        <v>46155.44022796296</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>338</v>
@@ -8662,11 +8662,11 @@
         <v>340</v>
       </c>
       <c r="B125" s="8">
-        <v>46155.60668334491</v>
+        <v>46155.44001667824</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46155.63803638889</v>
+        <v>46155.47136972222</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>341</v>
@@ -8723,11 +8723,11 @@
         <v>345</v>
       </c>
       <c r="B126" s="5">
-        <v>46155.606691759254</v>
+        <v>46155.4400250926</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.6390279051</v>
+        <v>46155.472361238426</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8774,11 +8774,11 @@
         <v>347</v>
       </c>
       <c r="B127" s="8">
-        <v>46155.60669864583</v>
+        <v>46155.44003197917</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46155.639037835645</v>
+        <v>46155.47237116898</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>190</v>
@@ -8825,11 +8825,11 @@
         <v>348</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.60670615741</v>
+        <v>46155.44003949074</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.639063807874</v>
+        <v>46155.4723971412</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -8876,11 +8876,11 @@
         <v>350</v>
       </c>
       <c r="B129" s="8">
-        <v>46155.606713009256</v>
+        <v>46155.44004634259</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46155.63907559028</v>
+        <v>46155.47240892361</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>190</v>
@@ -8927,11 +8927,11 @@
         <v>351</v>
       </c>
       <c r="B130" s="5">
-        <v>46155.63715556713</v>
+        <v>46155.470488900464</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.63910325231</v>
+        <v>46155.47243658565</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>190</v>
@@ -8978,11 +8978,11 @@
         <v>352</v>
       </c>
       <c r="B131" s="8">
-        <v>46155.60671987268</v>
+        <v>46155.44005320602</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46155.638912615745</v>
+        <v>46155.47224594907</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>353</v>
@@ -9041,11 +9041,11 @@
         <v>354</v>
       </c>
       <c r="B132" s="5">
-        <v>46155.60672658565</v>
+        <v>46155.44005991898</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.639826238425</v>
+        <v>46155.47315957176</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9094,11 +9094,11 @@
         <v>356</v>
       </c>
       <c r="B133" s="8">
-        <v>46155.60673355324</v>
+        <v>46155.44006688657</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46155.63983615741</v>
+        <v>46155.47316949074</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>190</v>
@@ -9147,11 +9147,11 @@
         <v>358</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.60674053241</v>
+        <v>46155.44007386574</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.639844942125</v>
+        <v>46155.47317827547</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9200,11 +9200,11 @@
         <v>359</v>
       </c>
       <c r="B135" s="8">
-        <v>46155.60674741898</v>
+        <v>46155.44008075232</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46155.63986869213</v>
+        <v>46155.47320202546</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>190</v>
@@ -9253,11 +9253,11 @@
         <v>360</v>
       </c>
       <c r="B136" s="5">
-        <v>46155.63830266204</v>
+        <v>46155.471635995375</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.63990003472</v>
+        <v>46155.47323336806</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9304,11 +9304,11 @@
         <v>361</v>
       </c>
       <c r="B137" s="8">
-        <v>46155.60675400463</v>
+        <v>46155.44008733796</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46155.64036164352</v>
+        <v>46155.473694976856</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>362</v>
@@ -9367,11 +9367,11 @@
         <v>363</v>
       </c>
       <c r="B138" s="5">
-        <v>46155.60676105324</v>
+        <v>46155.44009438658</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46155.642618750004</v>
+        <v>46155.47595208333</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9418,11 +9418,11 @@
         <v>365</v>
       </c>
       <c r="B139" s="8">
-        <v>46155.60677012731</v>
+        <v>46155.44010346065</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46155.64263091436</v>
+        <v>46155.475964247686</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>190</v>
@@ -9469,11 +9469,11 @@
         <v>366</v>
       </c>
       <c r="B140" s="5">
-        <v>46155.60681737268</v>
+        <v>46155.44015070602</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46155.64264111111</v>
+        <v>46155.475974444445</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9520,11 +9520,11 @@
         <v>368</v>
       </c>
       <c r="B141" s="8">
-        <v>46155.60682548611</v>
+        <v>46155.440158819445</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46155.64265195602</v>
+        <v>46155.47598528935</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>190</v>
@@ -9571,11 +9571,11 @@
         <v>369</v>
       </c>
       <c r="B142" s="5">
-        <v>46155.63928425926</v>
+        <v>46155.47261759259</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46155.64266835648</v>
+        <v>46155.476001689814</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>190</v>
@@ -9622,11 +9622,11 @@
         <v>370</v>
       </c>
       <c r="B143" s="8">
-        <v>46155.60683229167</v>
+        <v>46155.440165625</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46155.641985821756</v>
+        <v>46155.47531915509</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>371</v>
@@ -9685,11 +9685,11 @@
         <v>373</v>
       </c>
       <c r="B144" s="5">
-        <v>46155.606840486114</v>
+        <v>46155.44017381944</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46155.64207402778</v>
+        <v>46155.47540736111</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9736,11 +9736,11 @@
         <v>374</v>
       </c>
       <c r="B145" s="8">
-        <v>46155.60684746528</v>
+        <v>46155.440180798614</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46155.64208369213</v>
+        <v>46155.47541702546</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>190</v>
@@ -9787,11 +9787,11 @@
         <v>375</v>
       </c>
       <c r="B146" s="5">
-        <v>46155.60685387731</v>
+        <v>46155.44018721065</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46155.64209340278</v>
+        <v>46155.47542673611</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -9838,11 +9838,11 @@
         <v>376</v>
       </c>
       <c r="B147" s="8">
-        <v>46155.60686101852</v>
+        <v>46155.44019435185</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46155.64210719908</v>
+        <v>46155.475440532406</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>190</v>
@@ -9889,11 +9889,11 @@
         <v>377</v>
       </c>
       <c r="B148" s="5">
-        <v>46155.64052775463</v>
+        <v>46155.47386108796</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46155.64213097222</v>
+        <v>46155.47546430556</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>
@@ -9940,11 +9940,11 @@
         <v>378</v>
       </c>
       <c r="B149" s="8">
-        <v>46155.60686797454</v>
+        <v>46155.440201307865</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46155.60689638889</v>
+        <v>46155.440229722226</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>379</v>
@@ -9987,11 +9987,11 @@
         <v>381</v>
       </c>
       <c r="B150" s="5">
-        <v>46155.60687207176</v>
+        <v>46155.44020540509</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46155.60689709491</v>
+        <v>46155.44023042824</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>382</v>
@@ -10050,11 +10050,11 @@
         <v>385</v>
       </c>
       <c r="B151" s="8">
-        <v>46155.606879259256</v>
+        <v>46155.44021259259</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46195.54676386574</v>
+        <v>46195.38009719907</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>386</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1817,13 +1817,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46155.43894304398</v>
+        <v>46155.60560971065</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70656460648</v>
+        <v>46175.873231273144</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.54677180556</v>
+        <v>46197.71343847222</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1866,13 +1866,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46155.43905862268</v>
+        <v>46155.60572528935</v>
       </c>
       <c r="C5" s="8">
-        <v>46161.45673921297</v>
+        <v>46161.623405879625</v>
       </c>
       <c r="D5" s="8">
-        <v>46161.45675550926</v>
+        <v>46161.62342217592</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1929,13 +1929,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46155.4390644213</v>
+        <v>46155.60573108796</v>
       </c>
       <c r="C6" s="5">
-        <v>46161.456973761575</v>
+        <v>46161.62364042824</v>
       </c>
       <c r="D6" s="5">
-        <v>46161.45699003473</v>
+        <v>46161.623656701384</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1992,13 +1992,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46155.43906950232</v>
+        <v>46155.60573616898</v>
       </c>
       <c r="C7" s="8">
-        <v>46161.45699008102</v>
+        <v>46161.62365674769</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.457162129635</v>
+        <v>46161.62382879629</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2055,13 +2055,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46155.439074548616</v>
+        <v>46155.60574121527</v>
       </c>
       <c r="C8" s="5">
-        <v>46161.45752660879</v>
+        <v>46161.624193275464</v>
       </c>
       <c r="D8" s="5">
-        <v>46161.45754138889</v>
+        <v>46161.62420805555</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2118,13 +2118,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46155.43908016203</v>
+        <v>46155.6057468287</v>
       </c>
       <c r="C9" s="8">
-        <v>46175.706550532406</v>
+        <v>46175.87321719907</v>
       </c>
       <c r="D9" s="8">
-        <v>46175.70656489584</v>
+        <v>46175.873231562495</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2181,11 +2181,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46155.43894832176</v>
+        <v>46155.605614988424</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.546650439814</v>
+        <v>46197.71331710648</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2228,13 +2228,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46155.43908570602</v>
+        <v>46155.605752372685</v>
       </c>
       <c r="C11" s="8">
-        <v>46161.45756530092</v>
+        <v>46161.624231967595</v>
       </c>
       <c r="D11" s="8">
-        <v>46195.380097002315</v>
+        <v>46195.54676366899</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2293,13 +2293,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46155.43909342593</v>
+        <v>46155.60576009259</v>
       </c>
       <c r="C12" s="5">
-        <v>46161.457571701394</v>
+        <v>46161.62423836805</v>
       </c>
       <c r="D12" s="5">
-        <v>46195.38009708333</v>
+        <v>46195.54676375</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2358,13 +2358,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46155.43910125</v>
+        <v>46155.60576791667</v>
       </c>
       <c r="C13" s="8">
-        <v>46161.45757961806</v>
+        <v>46161.62424628472</v>
       </c>
       <c r="D13" s="8">
-        <v>46195.38009697916</v>
+        <v>46195.546763645834</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2423,11 +2423,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46155.43895318287</v>
+        <v>46155.605619849535</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.5466303125</v>
+        <v>46197.71329697917</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2470,13 +2470,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46155.43911810185</v>
+        <v>46155.605784768515</v>
       </c>
       <c r="C15" s="8">
-        <v>46161.45762405093</v>
+        <v>46161.62429071759</v>
       </c>
       <c r="D15" s="8">
-        <v>46161.45764068287</v>
+        <v>46161.624307349535</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2535,13 +2535,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46155.439125624995</v>
+        <v>46155.605792291666</v>
       </c>
       <c r="C16" s="5">
-        <v>46161.457631875004</v>
+        <v>46161.62429854167</v>
       </c>
       <c r="D16" s="5">
-        <v>46161.45764758102</v>
+        <v>46161.62431424769</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2600,13 +2600,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46155.43913309027</v>
+        <v>46155.605799756944</v>
       </c>
       <c r="C17" s="8">
-        <v>46197.335606354165</v>
+        <v>46197.50227302083</v>
       </c>
       <c r="D17" s="8">
-        <v>46197.33562271991</v>
+        <v>46197.502289386575</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2665,13 +2665,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46155.43914079861</v>
+        <v>46155.60580746528</v>
       </c>
       <c r="C18" s="5">
-        <v>46196.475665659724</v>
+        <v>46196.64233232639</v>
       </c>
       <c r="D18" s="5">
-        <v>46196.47568135417</v>
+        <v>46196.64234802083</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2730,11 +2730,11 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46155.43914765047</v>
+        <v>46155.605814317125</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46195.7810269676</v>
+        <v>46195.947693634254</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2793,13 +2793,13 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46155.43915342593</v>
+        <v>46155.60582009259</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.477272476855</v>
+        <v>46196.64393914352</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.47728831018</v>
+        <v>46196.643954976855</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2858,13 +2858,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46155.439158946756</v>
+        <v>46155.60582561343</v>
       </c>
       <c r="C21" s="8">
-        <v>46196.4778984838</v>
+        <v>46196.64456515046</v>
       </c>
       <c r="D21" s="8">
-        <v>46196.47791537037</v>
+        <v>46196.644582037035</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2923,11 +2923,11 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46155.438957962964</v>
+        <v>46155.60562462963</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46182.52708107639</v>
+        <v>46182.693747743055</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2970,13 +2970,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46155.439165104166</v>
+        <v>46155.60583177084</v>
       </c>
       <c r="C23" s="8">
-        <v>46182.51061494213</v>
+        <v>46182.6772816088</v>
       </c>
       <c r="D23" s="8">
-        <v>46182.510626655094</v>
+        <v>46182.67729332176</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -3035,13 +3035,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46155.439172025464</v>
+        <v>46155.60583869213</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.48660795139</v>
+        <v>46182.65327461806</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.48660934028</v>
+        <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3096,13 +3096,13 @@
         <v>102</v>
       </c>
       <c r="B25" s="8">
-        <v>46155.43917895833</v>
+        <v>46155.605845625</v>
       </c>
       <c r="C25" s="8">
-        <v>46182.51060081019</v>
+        <v>46182.67726747685</v>
       </c>
       <c r="D25" s="8">
-        <v>46182.51060231481</v>
+        <v>46182.67726898148</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>103</v>
@@ -3157,11 +3157,11 @@
         <v>105</v>
       </c>
       <c r="B26" s="5">
-        <v>46155.43918560185</v>
+        <v>46155.60585226852</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.02861765046</v>
+        <v>46179.19528431713</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>106</v>
@@ -3220,11 +3220,11 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46155.4391921412</v>
+        <v>46155.605858807874</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46197.33561277778</v>
+        <v>46197.502279444445</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -3279,11 +3279,11 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46155.439198622684</v>
+        <v>46155.605865289355</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.00457575232</v>
+        <v>46178.17124241898</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3338,13 +3338,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46155.43925858796</v>
+        <v>46155.605925254626</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.52707278935</v>
+        <v>46182.69373945602</v>
       </c>
       <c r="D29" s="8">
-        <v>46197.01832081018</v>
+        <v>46197.18498747685</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3403,13 +3403,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46155.439265821755</v>
+        <v>46155.605932488426</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.48641747685</v>
+        <v>46182.653084143516</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.48641987269</v>
+        <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3464,13 +3464,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46155.439272777774</v>
+        <v>46155.605939444446</v>
       </c>
       <c r="C31" s="8">
-        <v>46182.510444328705</v>
+        <v>46182.67711099537</v>
       </c>
       <c r="D31" s="8">
-        <v>46182.51044608797</v>
+        <v>46182.67711275463</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3525,13 +3525,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46155.43927920139</v>
+        <v>46155.605945868054</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.527057245374</v>
+        <v>46182.69372391204</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.52705878472</v>
+        <v>46182.69372545139</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3586,11 +3586,11 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46155.439285625005</v>
+        <v>46155.60595229166</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46192.00781674769</v>
+        <v>46192.17448341435</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3649,11 +3649,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46155.439292118055</v>
+        <v>46155.60595878473</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46196.47567189815</v>
+        <v>46196.642338564816</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3708,11 +3708,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="8">
-        <v>46155.43929873843</v>
+        <v>46155.60596540509</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46169.69421677083</v>
+        <v>46169.860883437505</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3767,11 +3767,11 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46155.439304942134</v>
+        <v>46155.60597160879</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.007878819444</v>
+        <v>46192.17454548611</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3830,11 +3830,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="8">
-        <v>46155.439310104164</v>
+        <v>46155.605976770836</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46190.002432719906</v>
+        <v>46190.16909938658</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>81</v>
@@ -3883,11 +3883,11 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46155.43931646991</v>
+        <v>46155.60598313657</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.69426056713</v>
+        <v>46169.86092723379</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -3936,13 +3936,13 @@
         <v>146</v>
       </c>
       <c r="B39" s="8">
-        <v>46155.4393222338</v>
+        <v>46155.60598890047</v>
       </c>
       <c r="C39" s="8">
-        <v>46196.52820552084</v>
+        <v>46196.6948721875</v>
       </c>
       <c r="D39" s="8">
-        <v>46196.52822096065</v>
+        <v>46196.694887627316</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>147</v>
@@ -4001,13 +4001,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46155.43932773148</v>
+        <v>46155.60599439815</v>
       </c>
       <c r="C40" s="5">
-        <v>46196.526759444445</v>
+        <v>46196.69342611112</v>
       </c>
       <c r="D40" s="5">
-        <v>46196.52676152778</v>
+        <v>46196.69342819444</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>88</v>
@@ -4056,13 +4056,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46155.43933353009</v>
+        <v>46155.606000196756</v>
       </c>
       <c r="C41" s="8">
-        <v>46196.5268253588</v>
+        <v>46196.693492025464</v>
       </c>
       <c r="D41" s="8">
-        <v>46196.52682753472</v>
+        <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -4111,11 +4111,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46155.439339502314</v>
+        <v>46155.60600616898</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.52683537037</v>
+        <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4164,11 +4164,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46155.43934405093</v>
+        <v>46155.60601071759</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46169.69389917824</v>
+        <v>46169.86056584491</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -4227,11 +4227,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46155.439347569445</v>
+        <v>46155.60601423611</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.477279687504</v>
+        <v>46196.64394635417</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>85</v>
@@ -4280,11 +4280,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46155.43935210648</v>
+        <v>46155.60601877315</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46169.69439675926</v>
+        <v>46169.861063425924</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4333,11 +4333,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46155.43896273148</v>
+        <v>46155.60562939815</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.54670233796</v>
+        <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4380,13 +4380,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46155.43935697917</v>
+        <v>46155.60602364583</v>
       </c>
       <c r="C47" s="8">
-        <v>46195.78073570602</v>
+        <v>46195.94740237268</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.547605300926</v>
+        <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4445,13 +4445,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46155.43936440972</v>
+        <v>46155.606031076386</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.78093490741</v>
+        <v>46195.94760157407</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.5476644213</v>
+        <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4510,13 +4510,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46155.43937197917</v>
+        <v>46155.606038645834</v>
       </c>
       <c r="C49" s="8">
-        <v>46195.780985000005</v>
+        <v>46195.94765166666</v>
       </c>
       <c r="D49" s="8">
-        <v>46195.781001157404</v>
+        <v>46195.947667824075</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>77</v>
@@ -4573,11 +4573,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46155.439425081015</v>
+        <v>46155.606091747686</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.46824752315</v>
+        <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4636,11 +4636,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="8">
-        <v>46155.439433437496</v>
+        <v>46155.60610010417</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46155.47550032407</v>
+        <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>190</v>
@@ -4687,11 +4687,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46155.43943960648</v>
+        <v>46155.606106273146</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.47551712963</v>
+        <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4738,11 +4738,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46155.43944538194</v>
+        <v>46155.60611204861</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46155.47552612268</v>
+        <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>190</v>
@@ -4789,11 +4789,11 @@
         <v>195</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.439450046295</v>
+        <v>46155.60611671297</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.47553416667</v>
+        <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4840,11 +4840,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="8">
-        <v>46155.46824611111</v>
+        <v>46155.63491277778</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46155.47556417824</v>
+        <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>190</v>
@@ -4891,11 +4891,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46155.439454583335</v>
+        <v>46155.60612125</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.439577083336</v>
+        <v>46155.60624375</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4938,11 +4938,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46155.4394581713</v>
+        <v>46155.60612483796</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46196.017646782406</v>
+        <v>46196.18431344908</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5001,11 +5001,11 @@
         <v>205</v>
       </c>
       <c r="B58" s="5">
-        <v>46155.43946650463</v>
+        <v>46155.6061331713</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46176.03346377314</v>
+        <v>46176.200130439815</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>206</v>
@@ -5064,11 +5064,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46155.4394747801</v>
+        <v>46155.606141446755</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46196.01764675926</v>
+        <v>46196.184313425925</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>210</v>
@@ -5127,11 +5127,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46155.43948282408</v>
+        <v>46155.60614949074</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46176.03346363426</v>
+        <v>46176.20013030093</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5190,11 +5190,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="8">
-        <v>46155.43948965278</v>
+        <v>46155.606156319445</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46155.43958078704</v>
+        <v>46155.6062474537</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5253,11 +5253,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46155.4394972338</v>
+        <v>46155.60616390046</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.441792893515</v>
+        <v>46155.608459560186</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>217</v>
@@ -5316,11 +5316,11 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46155.43950415509</v>
+        <v>46155.60617082176</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46155.43977484954</v>
+        <v>46155.6064415162</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>220</v>
@@ -5363,11 +5363,11 @@
         <v>222</v>
       </c>
       <c r="B64" s="5">
-        <v>46155.43950746528</v>
+        <v>46155.60617413194</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.44959052083</v>
+        <v>46155.6162571875</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>223</v>
@@ -5426,11 +5426,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="8">
-        <v>46155.4395159375</v>
+        <v>46155.60618260417</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46155.44072061343</v>
+        <v>46155.60738728009</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>227</v>
@@ -5479,11 +5479,11 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.43952439815</v>
+        <v>46155.60619106481</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.450112245366</v>
+        <v>46155.61677891204</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>227</v>
@@ -5532,11 +5532,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="8">
-        <v>46155.439531689815</v>
+        <v>46155.60619835649</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46155.450133645834</v>
+        <v>46155.6168003125</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>227</v>
@@ -5585,11 +5585,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46155.43953877315</v>
+        <v>46155.60620543981</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.45016523148</v>
+        <v>46155.61683189815</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5638,11 +5638,11 @@
         <v>235</v>
       </c>
       <c r="B69" s="8">
-        <v>46155.44078685185</v>
+        <v>46155.60745351852</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46155.45072724537</v>
+        <v>46155.617393912034</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>227</v>
@@ -5691,11 +5691,11 @@
         <v>236</v>
       </c>
       <c r="B70" s="5">
-        <v>46155.43954597222</v>
+        <v>46155.606212638886</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.45109189815</v>
+        <v>46155.61775856481</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>237</v>
@@ -5754,11 +5754,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="8">
-        <v>46155.43955232639</v>
+        <v>46155.60621899305</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.78101641204</v>
+        <v>46195.9476830787</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>227</v>
@@ -5807,11 +5807,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.439559872684</v>
+        <v>46155.606226539356</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.78100614583</v>
+        <v>46195.9476728125</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>227</v>
@@ -5860,11 +5860,11 @@
         <v>243</v>
       </c>
       <c r="B73" s="8">
-        <v>46155.43956733796</v>
+        <v>46155.606234004634</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.78101032408</v>
+        <v>46195.94767699074</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>227</v>
@@ -5913,11 +5913,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46155.4396175463</v>
+        <v>46155.60628421296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.781012997686</v>
+        <v>46195.94767966435</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>227</v>
@@ -5966,11 +5966,11 @@
         <v>245</v>
       </c>
       <c r="B75" s="8">
-        <v>46155.441023368054</v>
+        <v>46155.607690034725</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46155.45271111111</v>
+        <v>46155.61937777778</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>227</v>
@@ -6019,11 +6019,11 @@
         <v>246</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.43962524306</v>
+        <v>46155.606291909724</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.45244517361</v>
+        <v>46155.61911184028</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>247</v>
@@ -6082,11 +6082,11 @@
         <v>248</v>
       </c>
       <c r="B77" s="8">
-        <v>46155.43963217593</v>
+        <v>46155.60629884259</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.78100685185</v>
+        <v>46195.947673518516</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>227</v>
@@ -6135,11 +6135,11 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46155.43963956018</v>
+        <v>46155.60630622685</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.78100746528</v>
+        <v>46195.947674131945</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>227</v>
@@ -6188,11 +6188,11 @@
         <v>251</v>
       </c>
       <c r="B79" s="8">
-        <v>46155.43964677083</v>
+        <v>46155.6063134375</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.78101372685</v>
+        <v>46195.94768039352</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>227</v>
@@ -6241,11 +6241,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46155.43965305555</v>
+        <v>46155.606319722225</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.78101423611</v>
+        <v>46195.94768090278</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>227</v>
@@ -6294,11 +6294,11 @@
         <v>254</v>
       </c>
       <c r="B81" s="8">
-        <v>46155.45165628473</v>
+        <v>46155.618322951384</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46155.45406971065</v>
+        <v>46155.620736377314</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>227</v>
@@ -6345,11 +6345,11 @@
         <v>255</v>
       </c>
       <c r="B82" s="5">
-        <v>46155.43965876158</v>
+        <v>46155.60632542824</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.43977684028</v>
+        <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>198</v>
@@ -6392,11 +6392,11 @@
         <v>257</v>
       </c>
       <c r="B83" s="8">
-        <v>46155.43966201389</v>
+        <v>46155.60632868056</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46182.03281046296</v>
+        <v>46182.19947712963</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>258</v>
@@ -6453,11 +6453,11 @@
         <v>260</v>
       </c>
       <c r="B84" s="5">
-        <v>46155.439669837964</v>
+        <v>46155.60633650463</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.51061935185</v>
+        <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>261</v>
@@ -6516,11 +6516,11 @@
         <v>263</v>
       </c>
       <c r="B85" s="8">
-        <v>46155.43967736111</v>
+        <v>46155.60634402778</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46198.01583942129</v>
+        <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>264</v>
@@ -6579,11 +6579,11 @@
         <v>266</v>
       </c>
       <c r="B86" s="5">
-        <v>46155.43968510417</v>
+        <v>46155.60635177083</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46196.52684989583</v>
+        <v>46196.693516562504</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>267</v>
@@ -6642,11 +6642,11 @@
         <v>269</v>
       </c>
       <c r="B87" s="8">
-        <v>46155.43969525463</v>
+        <v>46155.606361921295</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46155.4401133912</v>
+        <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -6689,11 +6689,11 @@
         <v>272</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.43969858796</v>
+        <v>46155.60636525463</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.45368895833</v>
+        <v>46155.620355625</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>273</v>
@@ -6752,11 +6752,11 @@
         <v>275</v>
       </c>
       <c r="B89" s="8">
-        <v>46155.43970785879</v>
+        <v>46155.606374525465</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.454952835644</v>
+        <v>46155.621619502315</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>227</v>
@@ -6805,11 +6805,11 @@
         <v>277</v>
       </c>
       <c r="B90" s="5">
-        <v>46155.43971361111</v>
+        <v>46155.60638027778</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.454969363425</v>
+        <v>46155.62163603009</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>227</v>
@@ -6858,11 +6858,11 @@
         <v>278</v>
       </c>
       <c r="B91" s="8">
-        <v>46155.439719166665</v>
+        <v>46155.60638583334</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46155.45499407407</v>
+        <v>46155.62166074074</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>227</v>
@@ -6911,11 +6911,11 @@
         <v>280</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.43972512732</v>
+        <v>46155.60639179398</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.45500732639</v>
+        <v>46155.62167399305</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>227</v>
@@ -6964,11 +6964,11 @@
         <v>282</v>
       </c>
       <c r="B93" s="8">
-        <v>46155.45309319445</v>
+        <v>46155.61975986111</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46155.45502841435</v>
+        <v>46155.62169508102</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>227</v>
@@ -7017,11 +7017,11 @@
         <v>283</v>
       </c>
       <c r="B94" s="5">
-        <v>46155.43973116898</v>
+        <v>46155.60639783565</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.455249189814</v>
+        <v>46155.62191585648</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>284</v>
@@ -7080,11 +7080,11 @@
         <v>285</v>
       </c>
       <c r="B95" s="8">
-        <v>46155.439737361114</v>
+        <v>46155.60640402778</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.78101460648</v>
+        <v>46195.947681273145</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>227</v>
@@ -7131,11 +7131,11 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46155.43974423611</v>
+        <v>46155.60641090278</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.781015162036</v>
+        <v>46195.94768182871</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>227</v>
@@ -7182,11 +7182,11 @@
         <v>289</v>
       </c>
       <c r="B97" s="8">
-        <v>46155.4397509375</v>
+        <v>46155.60641760417</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.781015659726</v>
+        <v>46195.94768232639</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>227</v>
@@ -7233,11 +7233,11 @@
         <v>292</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.43975982639</v>
+        <v>46155.60642649306</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.78100797454</v>
+        <v>46195.947674641204</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>227</v>
@@ -7284,11 +7284,11 @@
         <v>293</v>
       </c>
       <c r="B99" s="8">
-        <v>46155.45449280093</v>
+        <v>46155.62115946759</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46155.47573361111</v>
+        <v>46155.64240027778</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>227</v>
@@ -7335,11 +7335,11 @@
         <v>294</v>
       </c>
       <c r="B100" s="5">
-        <v>46155.43981565972</v>
+        <v>46155.60648232639</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.4650037963</v>
+        <v>46155.631670462964</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>295</v>
@@ -7398,11 +7398,11 @@
         <v>296</v>
       </c>
       <c r="B101" s="8">
-        <v>46155.439823761575</v>
+        <v>46155.60649042824</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.7810086574</v>
+        <v>46195.947675324074</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>227</v>
@@ -7449,11 +7449,11 @@
         <v>298</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.439832662036</v>
+        <v>46155.6064993287</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.78101229167</v>
+        <v>46195.947678958335</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>227</v>
@@ -7500,11 +7500,11 @@
         <v>299</v>
       </c>
       <c r="B103" s="8">
-        <v>46155.43984128472</v>
+        <v>46155.606507951394</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.78101605324</v>
+        <v>46195.94768271991</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>227</v>
@@ -7551,11 +7551,11 @@
         <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46155.439850497685</v>
+        <v>46155.60651716436</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46195.78101693287</v>
+        <v>46195.94768359954</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>227</v>
@@ -7602,11 +7602,11 @@
         <v>303</v>
       </c>
       <c r="B105" s="8">
-        <v>46155.45551484954</v>
+        <v>46155.6221815162</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46155.465126828705</v>
+        <v>46155.63179349537</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>227</v>
@@ -7653,11 +7653,11 @@
         <v>305</v>
       </c>
       <c r="B106" s="5">
-        <v>46155.43985913195</v>
+        <v>46155.60652579861</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.46789329861</v>
+        <v>46155.63455996528</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>306</v>
@@ -7716,11 +7716,11 @@
         <v>308</v>
       </c>
       <c r="B107" s="8">
-        <v>46155.43986636574</v>
+        <v>46155.606533032405</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46195.7810109375</v>
+        <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>190</v>
@@ -7767,11 +7767,11 @@
         <v>311</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.43987479167</v>
+        <v>46155.60654145833</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46195.78101167824</v>
+        <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>190</v>
@@ -7818,11 +7818,11 @@
         <v>312</v>
       </c>
       <c r="B109" s="8">
-        <v>46155.439887326385</v>
+        <v>46155.60655399306</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46195.78100920139</v>
+        <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>190</v>
@@ -7869,11 +7869,11 @@
         <v>314</v>
       </c>
       <c r="B110" s="5">
-        <v>46155.43989596065</v>
+        <v>46155.60656262732</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46195.781009768514</v>
+        <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -7920,11 +7920,11 @@
         <v>316</v>
       </c>
       <c r="B111" s="8">
-        <v>46155.46344958333</v>
+        <v>46155.63011625</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46155.46799295139</v>
+        <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>190</v>
@@ -7971,11 +7971,11 @@
         <v>318</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.439904432875</v>
+        <v>46155.60657109953</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.46910777778</v>
+        <v>46155.63577444444</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>319</v>
@@ -8034,11 +8034,11 @@
         <v>320</v>
       </c>
       <c r="B113" s="8">
-        <v>46155.43991166667</v>
+        <v>46155.60657833333</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46155.46846142361</v>
+        <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>190</v>
@@ -8087,11 +8087,11 @@
         <v>322</v>
       </c>
       <c r="B114" s="5">
-        <v>46155.43991973379</v>
+        <v>46155.60658640046</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.46858908565</v>
+        <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>190</v>
@@ -8140,11 +8140,11 @@
         <v>323</v>
       </c>
       <c r="B115" s="8">
-        <v>46155.43992741898</v>
+        <v>46155.60659408565</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46155.46860208333</v>
+        <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>190</v>
@@ -8193,11 +8193,11 @@
         <v>325</v>
       </c>
       <c r="B116" s="5">
-        <v>46155.4399356713</v>
+        <v>46155.60660233797</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.46862590278</v>
+        <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8246,11 +8246,11 @@
         <v>326</v>
       </c>
       <c r="B117" s="8">
-        <v>46155.467314699075</v>
+        <v>46155.63398136574</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46155.46915189815</v>
+        <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>190</v>
@@ -8297,11 +8297,11 @@
         <v>327</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.439975243055</v>
+        <v>46155.60664190972</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.47028125</v>
+        <v>46155.63694791667</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>328</v>
@@ -8360,11 +8360,11 @@
         <v>330</v>
       </c>
       <c r="B119" s="8">
-        <v>46155.43998414352</v>
+        <v>46155.60665081019</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46155.47143363426</v>
+        <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>190</v>
@@ -8411,11 +8411,11 @@
         <v>332</v>
       </c>
       <c r="B120" s="5">
-        <v>46155.43999158565</v>
+        <v>46155.60665825232</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.47145516204</v>
+        <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8462,11 +8462,11 @@
         <v>334</v>
       </c>
       <c r="B121" s="8">
-        <v>46155.43999868055</v>
+        <v>46155.60666534722</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46155.47146984954</v>
+        <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>190</v>
@@ -8513,11 +8513,11 @@
         <v>335</v>
       </c>
       <c r="B122" s="5">
-        <v>46155.440005868055</v>
+        <v>46155.60667253472</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.47148512732</v>
+        <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8564,11 +8564,11 @@
         <v>336</v>
       </c>
       <c r="B123" s="8">
-        <v>46155.46924918982</v>
+        <v>46155.63591585648</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46155.47150540509</v>
+        <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>190</v>
@@ -8615,11 +8615,11 @@
         <v>337</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.44001283565</v>
+        <v>46155.606679502314</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.44022796296</v>
+        <v>46155.60689462963</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>338</v>
@@ -8662,11 +8662,11 @@
         <v>340</v>
       </c>
       <c r="B125" s="8">
-        <v>46155.44001667824</v>
+        <v>46155.60668334491</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46155.47136972222</v>
+        <v>46155.63803638889</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>341</v>
@@ -8723,11 +8723,11 @@
         <v>345</v>
       </c>
       <c r="B126" s="5">
-        <v>46155.4400250926</v>
+        <v>46155.606691759254</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.472361238426</v>
+        <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8774,11 +8774,11 @@
         <v>347</v>
       </c>
       <c r="B127" s="8">
-        <v>46155.44003197917</v>
+        <v>46155.60669864583</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46155.47237116898</v>
+        <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>190</v>
@@ -8825,11 +8825,11 @@
         <v>348</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.44003949074</v>
+        <v>46155.60670615741</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.4723971412</v>
+        <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -8876,11 +8876,11 @@
         <v>350</v>
       </c>
       <c r="B129" s="8">
-        <v>46155.44004634259</v>
+        <v>46155.606713009256</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46155.47240892361</v>
+        <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>190</v>
@@ -8927,11 +8927,11 @@
         <v>351</v>
       </c>
       <c r="B130" s="5">
-        <v>46155.470488900464</v>
+        <v>46155.63715556713</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.47243658565</v>
+        <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>190</v>
@@ -8978,11 +8978,11 @@
         <v>352</v>
       </c>
       <c r="B131" s="8">
-        <v>46155.44005320602</v>
+        <v>46155.60671987268</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46155.47224594907</v>
+        <v>46155.638912615745</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>353</v>
@@ -9041,11 +9041,11 @@
         <v>354</v>
       </c>
       <c r="B132" s="5">
-        <v>46155.44005991898</v>
+        <v>46155.60672658565</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.47315957176</v>
+        <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9094,11 +9094,11 @@
         <v>356</v>
       </c>
       <c r="B133" s="8">
-        <v>46155.44006688657</v>
+        <v>46155.60673355324</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46155.47316949074</v>
+        <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>190</v>
@@ -9147,11 +9147,11 @@
         <v>358</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.44007386574</v>
+        <v>46155.60674053241</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.47317827547</v>
+        <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9200,11 +9200,11 @@
         <v>359</v>
       </c>
       <c r="B135" s="8">
-        <v>46155.44008075232</v>
+        <v>46155.60674741898</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46155.47320202546</v>
+        <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>190</v>
@@ -9253,11 +9253,11 @@
         <v>360</v>
       </c>
       <c r="B136" s="5">
-        <v>46155.471635995375</v>
+        <v>46155.63830266204</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.47323336806</v>
+        <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9304,11 +9304,11 @@
         <v>361</v>
       </c>
       <c r="B137" s="8">
-        <v>46155.44008733796</v>
+        <v>46155.60675400463</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46155.473694976856</v>
+        <v>46155.64036164352</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>362</v>
@@ -9367,11 +9367,11 @@
         <v>363</v>
       </c>
       <c r="B138" s="5">
-        <v>46155.44009438658</v>
+        <v>46155.60676105324</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46155.47595208333</v>
+        <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9418,11 +9418,11 @@
         <v>365</v>
       </c>
       <c r="B139" s="8">
-        <v>46155.44010346065</v>
+        <v>46155.60677012731</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46155.475964247686</v>
+        <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>190</v>
@@ -9469,11 +9469,11 @@
         <v>366</v>
       </c>
       <c r="B140" s="5">
-        <v>46155.44015070602</v>
+        <v>46155.60681737268</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46155.475974444445</v>
+        <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9520,11 +9520,11 @@
         <v>368</v>
       </c>
       <c r="B141" s="8">
-        <v>46155.440158819445</v>
+        <v>46155.60682548611</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46155.47598528935</v>
+        <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>190</v>
@@ -9571,11 +9571,11 @@
         <v>369</v>
       </c>
       <c r="B142" s="5">
-        <v>46155.47261759259</v>
+        <v>46155.63928425926</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46155.476001689814</v>
+        <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>190</v>
@@ -9622,11 +9622,11 @@
         <v>370</v>
       </c>
       <c r="B143" s="8">
-        <v>46155.440165625</v>
+        <v>46155.60683229167</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46155.47531915509</v>
+        <v>46155.641985821756</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>371</v>
@@ -9685,11 +9685,11 @@
         <v>373</v>
       </c>
       <c r="B144" s="5">
-        <v>46155.44017381944</v>
+        <v>46155.606840486114</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46155.47540736111</v>
+        <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9736,11 +9736,11 @@
         <v>374</v>
       </c>
       <c r="B145" s="8">
-        <v>46155.440180798614</v>
+        <v>46155.60684746528</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46155.47541702546</v>
+        <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>190</v>
@@ -9787,11 +9787,11 @@
         <v>375</v>
       </c>
       <c r="B146" s="5">
-        <v>46155.44018721065</v>
+        <v>46155.60685387731</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46155.47542673611</v>
+        <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -9838,11 +9838,11 @@
         <v>376</v>
       </c>
       <c r="B147" s="8">
-        <v>46155.44019435185</v>
+        <v>46155.60686101852</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46155.475440532406</v>
+        <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>190</v>
@@ -9889,11 +9889,11 @@
         <v>377</v>
       </c>
       <c r="B148" s="5">
-        <v>46155.47386108796</v>
+        <v>46155.64052775463</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46155.47546430556</v>
+        <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>
@@ -9940,11 +9940,11 @@
         <v>378</v>
       </c>
       <c r="B149" s="8">
-        <v>46155.440201307865</v>
+        <v>46155.60686797454</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46155.440229722226</v>
+        <v>46155.60689638889</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>379</v>
@@ -9987,11 +9987,11 @@
         <v>381</v>
       </c>
       <c r="B150" s="5">
-        <v>46155.44020540509</v>
+        <v>46155.60687207176</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46155.44023042824</v>
+        <v>46155.60689709491</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>382</v>
@@ -10050,11 +10050,11 @@
         <v>385</v>
       </c>
       <c r="B151" s="8">
-        <v>46155.44021259259</v>
+        <v>46155.606879259256</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46195.38009719907</v>
+        <v>46195.54676386574</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>386</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46192.17448341435</v>
+        <v>46199.1700083912</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46169.860883437505</v>
+        <v>46199.17001361111</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.17454548611</v>
+        <v>46199.17001090277</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.86092723379</v>
+        <v>46199.170012291666</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="388">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -441,6 +441,10 @@
   </si>
   <si>
     <t xml:space="preserve">Fabricacion Corte Laser OT 4316 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
   </si>
   <si>
     <t>Materiales corte Laser OT 4316,Recepcion materiales corte laser</t>
@@ -3590,7 +3594,7 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46199.1700083912</v>
+        <v>46199.55808965278</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3651,9 +3655,11 @@
       <c r="B34" s="5">
         <v>46155.60595878473</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46199.55808454861</v>
+      </c>
       <c r="D34" s="5">
-        <v>46196.642338564816</v>
+        <v>46199.55831050926</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3712,7 +3718,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46199.17001361111</v>
+        <v>46199.55878317129</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3736,7 +3742,7 @@
         <v>26</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="M35" s="9" t="s">
         <v>26</v>
@@ -3748,7 +3754,7 @@
         <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3764,7 +3770,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46155.60597160879</v>
@@ -3774,7 +3780,7 @@
         <v>46199.17001090277</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3804,7 +3810,7 @@
         <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3827,7 +3833,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="8">
         <v>46155.605976770836</v>
@@ -3864,13 +3870,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3880,7 +3886,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46155.60598313657</v>
@@ -3890,7 +3896,7 @@
         <v>46199.170012291666</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3917,13 +3923,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3933,7 +3939,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B39" s="8">
         <v>46155.60598890047</v>
@@ -3945,16 +3951,16 @@
         <v>46196.694887627316</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I39" s="8">
         <v>46189</v>
@@ -3975,7 +3981,7 @@
         <v>90</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3998,7 +4004,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46155.60599439815</v>
@@ -4016,10 +4022,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4037,13 +4043,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4053,7 +4059,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="8">
         <v>46155.606000196756</v>
@@ -4065,16 +4071,16 @@
         <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46198</v>
@@ -4092,13 +4098,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>88</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4108,7 +4114,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46155.60600616898</v>
@@ -4118,16 +4124,16 @@
         <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4145,10 +4151,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4161,17 +4167,19 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B43" s="8">
         <v>46155.60601071759</v>
       </c>
-      <c r="C43" s="9"/>
+      <c r="C43" s="8">
+        <v>46199.563258622686</v>
+      </c>
       <c r="D43" s="8">
-        <v>46169.86056584491</v>
+        <v>46199.56327399306</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4201,7 +4209,7 @@
         <v>90</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4216,22 +4224,24 @@
         <v>100</v>
       </c>
       <c r="T43" s="9">
-        <v>0</v>
-      </c>
-      <c r="U43" s="10" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U43" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46199.563196041665</v>
+      </c>
       <c r="D44" s="5">
-        <v>46196.64394635417</v>
+        <v>46199.56319799769</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>85</v>
@@ -4261,13 +4271,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4277,17 +4287,19 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
       </c>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8">
+        <v>46199.563244351855</v>
+      </c>
       <c r="D45" s="8">
-        <v>46169.861063425924</v>
+        <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4314,13 +4326,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4330,7 +4342,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4340,7 +4352,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4364,7 +4376,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4377,7 +4389,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4389,16 +4401,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4416,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>58</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4442,7 +4454,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4454,16 +4466,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4481,13 +4493,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4507,7 +4519,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4525,10 +4537,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4544,13 +4556,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4570,7 +4582,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4580,16 +4592,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4607,10 +4619,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4633,7 +4645,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4643,16 +4655,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4668,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4684,7 +4696,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4694,16 +4706,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4719,13 +4731,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4735,7 +4747,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4745,16 +4757,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4770,13 +4782,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4786,7 +4798,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4796,16 +4808,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4821,13 +4833,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4837,7 +4849,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4847,16 +4859,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4872,13 +4884,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4888,7 +4900,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4898,7 +4910,7 @@
         <v>46155.60624375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4922,7 +4934,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4935,7 +4947,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4945,16 +4957,16 @@
         <v>46196.18431344908</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -4972,13 +4984,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>136</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -4998,7 +5010,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5008,16 +5020,16 @@
         <v>46176.200130439815</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I58" s="5">
         <v>46204</v>
@@ -5035,13 +5047,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5061,7 +5073,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5071,16 +5083,16 @@
         <v>46196.184313425925</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5098,13 +5110,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5124,7 +5136,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5134,16 +5146,16 @@
         <v>46176.20013030093</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I60" s="5">
         <v>46204</v>
@@ -5161,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5187,26 +5199,26 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46155.6062474537</v>
+        <v>46199.563261076386</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5224,13 +5236,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5244,13 +5256,13 @@
       <c r="T61" s="9">
         <v>0</v>
       </c>
-      <c r="U61" s="10" t="s">
-        <v>101</v>
+      <c r="U61" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46155.60616390046</v>
@@ -5260,16 +5272,16 @@
         <v>46155.608459560186</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I62" s="5">
         <v>46213</v>
@@ -5287,13 +5299,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5313,7 +5325,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46155.60617082176</v>
@@ -5323,7 +5335,7 @@
         <v>46155.6064415162</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5347,7 +5359,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5360,7 +5372,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46155.60617413194</v>
@@ -5370,16 +5382,16 @@
         <v>46155.6162571875</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5397,13 +5409,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46217</v>
@@ -5423,7 +5435,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46155.60618260417</v>
@@ -5433,16 +5445,16 @@
         <v>46155.60738728009</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I65" s="8">
         <v>46217</v>
@@ -5460,13 +5472,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5476,7 +5488,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46155.60619106481</v>
@@ -5486,16 +5498,16 @@
         <v>46155.61677891204</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5513,13 +5525,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5529,7 +5541,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="8">
         <v>46155.60619835649</v>
@@ -5539,16 +5551,16 @@
         <v>46155.6168003125</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I67" s="8">
         <v>46217</v>
@@ -5566,13 +5578,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5582,7 +5594,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46155.60620543981</v>
@@ -5592,16 +5604,16 @@
         <v>46155.61683189815</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5619,13 +5631,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5635,7 +5647,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" s="8">
         <v>46155.60745351852</v>
@@ -5645,16 +5657,16 @@
         <v>46155.617393912034</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I69" s="8">
         <v>46217</v>
@@ -5672,13 +5684,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5688,7 +5700,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46155.606212638886</v>
@@ -5698,16 +5710,16 @@
         <v>46155.61775856481</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5725,13 +5737,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5751,7 +5763,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46155.60621899305</v>
@@ -5761,16 +5773,16 @@
         <v>46195.9476830787</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I71" s="8">
         <v>46220</v>
@@ -5788,13 +5800,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5804,7 +5816,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46155.606226539356</v>
@@ -5814,16 +5826,16 @@
         <v>46195.9476728125</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5841,13 +5853,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5857,7 +5869,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46155.606234004634</v>
@@ -5867,16 +5879,16 @@
         <v>46195.94767699074</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I73" s="8">
         <v>46220</v>
@@ -5894,13 +5906,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5910,7 +5922,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46155.60628421296</v>
@@ -5920,16 +5932,16 @@
         <v>46195.94767966435</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -5947,13 +5959,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5963,7 +5975,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="8">
         <v>46155.607690034725</v>
@@ -5973,16 +5985,16 @@
         <v>46155.61937777778</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I75" s="8">
         <v>46220</v>
@@ -6000,13 +6012,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6016,7 +6028,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46155.606291909724</v>
@@ -6026,16 +6038,16 @@
         <v>46155.61911184028</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6053,13 +6065,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q76" s="5">
         <v>46227</v>
@@ -6079,7 +6091,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46155.60629884259</v>
@@ -6089,16 +6101,16 @@
         <v>46195.947673518516</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I77" s="8">
         <v>46227</v>
@@ -6116,13 +6128,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6132,7 +6144,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46155.60630622685</v>
@@ -6142,16 +6154,16 @@
         <v>46195.947674131945</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6169,13 +6181,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6185,7 +6197,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46155.6063134375</v>
@@ -6195,16 +6207,16 @@
         <v>46195.94768039352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I79" s="8">
         <v>46227</v>
@@ -6222,13 +6234,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6238,7 +6250,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46155.606319722225</v>
@@ -6248,16 +6260,16 @@
         <v>46195.94768090278</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6275,13 +6287,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6291,7 +6303,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B81" s="8">
         <v>46155.618322951384</v>
@@ -6301,16 +6313,16 @@
         <v>46155.620736377314</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6326,13 +6338,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6342,7 +6354,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46155.60632542824</v>
@@ -6352,7 +6364,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6376,7 +6388,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6389,7 +6401,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B83" s="8">
         <v>46155.60632868056</v>
@@ -6399,16 +6411,16 @@
         <v>46182.19947712963</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6424,13 +6436,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="8">
         <v>46181</v>
@@ -6450,7 +6462,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46155.60633650463</v>
@@ -6460,16 +6472,16 @@
         <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6487,13 +6499,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q84" s="5">
         <v>46164</v>
@@ -6513,7 +6525,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46155.60634402778</v>
@@ -6523,16 +6535,16 @@
         <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6550,13 +6562,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>121</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q85" s="8">
         <v>46197</v>
@@ -6576,7 +6588,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46155.60635177083</v>
@@ -6586,16 +6598,16 @@
         <v>46196.693516562504</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6613,13 +6625,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="5">
         <v>46231</v>
@@ -6639,7 +6651,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B87" s="8">
         <v>46155.606361921295</v>
@@ -6649,7 +6661,7 @@
         <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6673,7 +6685,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6686,7 +6698,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46155.60636525463</v>
@@ -6696,7 +6708,7 @@
         <v>46155.620355625</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6723,13 +6735,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q88" s="5">
         <v>46230</v>
@@ -6749,7 +6761,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="8">
         <v>46155.606374525465</v>
@@ -6759,7 +6771,7 @@
         <v>46155.621619502315</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6786,10 +6798,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>26</v>
@@ -6802,7 +6814,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46155.60638027778</v>
@@ -6812,7 +6824,7 @@
         <v>46155.62163603009</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6839,10 +6851,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6855,7 +6867,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46155.60638583334</v>
@@ -6865,7 +6877,7 @@
         <v>46155.62166074074</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6892,13 +6904,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6908,7 +6920,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46155.60639179398</v>
@@ -6918,7 +6930,7 @@
         <v>46155.62167399305</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6945,13 +6957,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6961,7 +6973,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
         <v>46155.61975986111</v>
@@ -6971,7 +6983,7 @@
         <v>46155.62169508102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -6998,13 +7010,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7014,7 +7026,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46155.60639783565</v>
@@ -7024,7 +7036,7 @@
         <v>46155.62191585648</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7051,13 +7063,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q94" s="5">
         <v>46237</v>
@@ -7077,7 +7089,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B95" s="8">
         <v>46155.60640402778</v>
@@ -7087,7 +7099,7 @@
         <v>46195.947681273145</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7112,13 +7124,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7128,7 +7140,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46155.60641090278</v>
@@ -7138,7 +7150,7 @@
         <v>46195.94768182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7163,13 +7175,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7179,7 +7191,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B97" s="8">
         <v>46155.60641760417</v>
@@ -7189,7 +7201,7 @@
         <v>46195.94768232639</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7214,13 +7226,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7230,7 +7242,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46155.60642649306</v>
@@ -7240,7 +7252,7 @@
         <v>46195.947674641204</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7265,13 +7277,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7281,7 +7293,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B99" s="8">
         <v>46155.62115946759</v>
@@ -7291,7 +7303,7 @@
         <v>46155.64240027778</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7316,13 +7328,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7332,7 +7344,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46155.60648232639</v>
@@ -7342,7 +7354,7 @@
         <v>46155.631670462964</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7369,13 +7381,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q100" s="5">
         <v>46238</v>
@@ -7395,7 +7407,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B101" s="8">
         <v>46155.60649042824</v>
@@ -7405,7 +7417,7 @@
         <v>46195.947675324074</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7430,13 +7442,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7446,7 +7458,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B102" s="5">
         <v>46155.6064993287</v>
@@ -7456,7 +7468,7 @@
         <v>46195.947678958335</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7481,13 +7493,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7497,7 +7509,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B103" s="8">
         <v>46155.606507951394</v>
@@ -7507,7 +7519,7 @@
         <v>46195.94768271991</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7532,13 +7544,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7548,7 +7560,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B104" s="5">
         <v>46155.60651716436</v>
@@ -7558,7 +7570,7 @@
         <v>46195.94768359954</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7583,13 +7595,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7599,7 +7611,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B105" s="8">
         <v>46155.6221815162</v>
@@ -7609,7 +7621,7 @@
         <v>46155.63179349537</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7634,13 +7646,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7650,7 +7662,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B106" s="5">
         <v>46155.60652579861</v>
@@ -7660,7 +7672,7 @@
         <v>46155.63455996528</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7687,13 +7699,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q106" s="5">
         <v>46239</v>
@@ -7713,7 +7725,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B107" s="8">
         <v>46155.606533032405</v>
@@ -7723,7 +7735,7 @@
         <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7748,13 +7760,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7764,7 +7776,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
         <v>46155.60654145833</v>
@@ -7774,7 +7786,7 @@
         <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7799,13 +7811,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7815,7 +7827,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B109" s="8">
         <v>46155.60655399306</v>
@@ -7825,7 +7837,7 @@
         <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7850,13 +7862,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -7866,7 +7878,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B110" s="5">
         <v>46155.60656262732</v>
@@ -7876,7 +7888,7 @@
         <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7901,13 +7913,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7917,7 +7929,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B111" s="8">
         <v>46155.63011625</v>
@@ -7927,7 +7939,7 @@
         <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -7952,13 +7964,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -7968,7 +7980,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
         <v>46155.60657109953</v>
@@ -7978,7 +7990,7 @@
         <v>46155.63577444444</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8005,13 +8017,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q112" s="5">
         <v>46240</v>
@@ -8031,7 +8043,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B113" s="8">
         <v>46155.60657833333</v>
@@ -8041,7 +8053,7 @@
         <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8068,13 +8080,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8084,7 +8096,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
         <v>46155.60658640046</v>
@@ -8094,7 +8106,7 @@
         <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8121,13 +8133,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8137,7 +8149,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B115" s="8">
         <v>46155.60659408565</v>
@@ -8147,7 +8159,7 @@
         <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8174,13 +8186,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8190,7 +8202,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B116" s="5">
         <v>46155.60660233797</v>
@@ -8200,7 +8212,7 @@
         <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8227,13 +8239,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8243,7 +8255,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B117" s="8">
         <v>46155.63398136574</v>
@@ -8253,7 +8265,7 @@
         <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8278,13 +8290,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8294,7 +8306,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B118" s="5">
         <v>46155.60664190972</v>
@@ -8304,7 +8316,7 @@
         <v>46155.63694791667</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8331,13 +8343,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q118" s="5">
         <v>46244</v>
@@ -8357,7 +8369,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B119" s="8">
         <v>46155.60665081019</v>
@@ -8367,7 +8379,7 @@
         <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8392,13 +8404,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8408,7 +8420,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B120" s="5">
         <v>46155.60665825232</v>
@@ -8418,7 +8430,7 @@
         <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8443,13 +8455,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8459,7 +8471,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B121" s="8">
         <v>46155.60666534722</v>
@@ -8469,7 +8481,7 @@
         <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8494,13 +8506,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8510,7 +8522,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B122" s="5">
         <v>46155.60667253472</v>
@@ -8520,7 +8532,7 @@
         <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8545,13 +8557,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8561,7 +8573,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B123" s="8">
         <v>46155.63591585648</v>
@@ -8571,7 +8583,7 @@
         <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8596,13 +8608,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8612,7 +8624,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B124" s="5">
         <v>46155.606679502314</v>
@@ -8622,7 +8634,7 @@
         <v>46155.60689462963</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>25</v>
@@ -8646,7 +8658,7 @@
         <v>26</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>26</v>
@@ -8659,7 +8671,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B125" s="8">
         <v>46155.60668334491</v>
@@ -8669,16 +8681,16 @@
         <v>46155.63803638889</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -8694,13 +8706,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q125" s="8">
         <v>46245</v>
@@ -8720,7 +8732,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B126" s="5">
         <v>46155.606691759254</v>
@@ -8730,16 +8742,16 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8755,13 +8767,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8771,7 +8783,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B127" s="8">
         <v>46155.60669864583</v>
@@ -8781,16 +8793,16 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -8806,13 +8818,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -8822,7 +8834,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B128" s="5">
         <v>46155.60670615741</v>
@@ -8832,16 +8844,16 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8857,13 +8869,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8873,7 +8885,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B129" s="8">
         <v>46155.606713009256</v>
@@ -8883,16 +8895,16 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -8908,13 +8920,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -8924,7 +8936,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B130" s="5">
         <v>46155.63715556713</v>
@@ -8934,16 +8946,16 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -8959,13 +8971,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8975,7 +8987,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B131" s="8">
         <v>46155.60671987268</v>
@@ -8985,7 +8997,7 @@
         <v>46155.638912615745</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9012,13 +9024,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q131" s="8">
         <v>46246</v>
@@ -9038,7 +9050,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B132" s="5">
         <v>46155.60672658565</v>
@@ -9048,7 +9060,7 @@
         <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9075,13 +9087,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9091,7 +9103,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B133" s="8">
         <v>46155.60673355324</v>
@@ -9101,7 +9113,7 @@
         <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9128,13 +9140,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9144,7 +9156,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B134" s="5">
         <v>46155.60674053241</v>
@@ -9154,7 +9166,7 @@
         <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9181,13 +9193,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9197,7 +9209,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B135" s="8">
         <v>46155.60674741898</v>
@@ -9207,7 +9219,7 @@
         <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9234,13 +9246,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9250,7 +9262,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B136" s="5">
         <v>46155.63830266204</v>
@@ -9260,7 +9272,7 @@
         <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9285,13 +9297,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9301,7 +9313,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B137" s="8">
         <v>46155.60675400463</v>
@@ -9311,16 +9323,16 @@
         <v>46155.64036164352</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I137" s="8">
         <v>46247</v>
@@ -9338,13 +9350,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q137" s="8">
         <v>46247</v>
@@ -9364,7 +9376,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B138" s="5">
         <v>46155.60676105324</v>
@@ -9374,16 +9386,16 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9399,13 +9411,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9415,7 +9427,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B139" s="8">
         <v>46155.60677012731</v>
@@ -9425,16 +9437,16 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9450,13 +9462,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9466,7 +9478,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B140" s="5">
         <v>46155.60681737268</v>
@@ -9476,16 +9488,16 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9501,13 +9513,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9517,7 +9529,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B141" s="8">
         <v>46155.60682548611</v>
@@ -9527,16 +9539,16 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9552,13 +9564,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9568,7 +9580,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B142" s="5">
         <v>46155.63928425926</v>
@@ -9578,16 +9590,16 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9603,13 +9615,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9619,7 +9631,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B143" s="8">
         <v>46155.60683229167</v>
@@ -9629,16 +9641,16 @@
         <v>46155.641985821756</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I143" s="8">
         <v>46248</v>
@@ -9656,13 +9668,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q143" s="8">
         <v>46248</v>
@@ -9682,7 +9694,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B144" s="5">
         <v>46155.606840486114</v>
@@ -9692,16 +9704,16 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9717,13 +9729,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9733,7 +9745,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B145" s="8">
         <v>46155.60684746528</v>
@@ -9743,16 +9755,16 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9768,13 +9780,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -9784,7 +9796,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B146" s="5">
         <v>46155.60685387731</v>
@@ -9794,16 +9806,16 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9819,13 +9831,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9835,7 +9847,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B147" s="8">
         <v>46155.60686101852</v>
@@ -9845,16 +9857,16 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -9870,13 +9882,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -9886,7 +9898,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B148" s="5">
         <v>46155.64052775463</v>
@@ -9896,16 +9908,16 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -9921,13 +9933,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9937,7 +9949,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B149" s="8">
         <v>46155.60686797454</v>
@@ -9947,7 +9959,7 @@
         <v>46155.60689638889</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>25</v>
@@ -9971,7 +9983,7 @@
         <v>26</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -9984,7 +9996,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B150" s="5">
         <v>46155.60687207176</v>
@@ -9994,16 +10006,16 @@
         <v>46155.60689709491</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I150" s="5">
         <v>46251</v>
@@ -10021,13 +10033,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q150" s="5">
         <v>46251</v>
@@ -10047,7 +10059,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B151" s="8">
         <v>46155.606879259256</v>
@@ -10057,7 +10069,7 @@
         <v>46195.54676386574</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10084,13 +10096,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q151" s="8">
         <v>46251</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -425,9 +425,6 @@
     <t>Fabricacion Corte Laser OT 4316 ,Generación OC materiales corte Laser OT 4316</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>1214777481716985</t>
   </si>
   <si>
@@ -649,6 +646,9 @@
   </si>
   <si>
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214777626772872</t>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46199.55808965278</v>
+        <v>46200.20644892361</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3638,8 +3638,8 @@
       <c r="R33" s="8">
         <v>46199</v>
       </c>
-      <c r="S33" s="12" t="s">
-        <v>131</v>
+      <c r="S33" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46155.60595878473</v>
@@ -3662,7 +3662,7 @@
         <v>46199.55831050926</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3695,7 +3695,7 @@
         <v>74</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46155.60596540509</v>
@@ -3721,7 +3721,7 @@
         <v>46199.55878317129</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3742,7 +3742,7 @@
         <v>26</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M35" s="9" t="s">
         <v>26</v>
@@ -3751,10 +3751,10 @@
         <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3770,17 +3770,17 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46155.60597160879</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46199.17001090277</v>
+        <v>46200.20645215278</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3810,7 +3810,7 @@
         <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3821,8 +3821,8 @@
       <c r="R36" s="5">
         <v>46199</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>131</v>
+      <c r="S36" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3833,7 +3833,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8">
         <v>46155.605976770836</v>
@@ -3870,13 +3870,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3886,7 +3886,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46155.60598313657</v>
@@ -3896,7 +3896,7 @@
         <v>46199.170012291666</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3923,13 +3923,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46155.60598890047</v>
@@ -3951,16 +3951,16 @@
         <v>46196.694887627316</v>
       </c>
       <c r="E39" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
+      <c r="H39" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="I39" s="8">
         <v>46189</v>
@@ -3981,7 +3981,7 @@
         <v>90</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46155.60599439815</v>
@@ -4022,10 +4022,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4043,13 +4043,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46155.606000196756</v>
@@ -4071,16 +4071,16 @@
         <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46198</v>
@@ -4098,13 +4098,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>88</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46155.60600616898</v>
@@ -4124,16 +4124,16 @@
         <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4151,10 +4151,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46155.60601071759</v>
@@ -4179,7 +4179,7 @@
         <v>46199.56327399306</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4209,7 +4209,7 @@
         <v>90</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4232,7 +4232,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4271,13 +4271,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4299,7 +4299,7 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4326,13 +4326,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4342,7 +4342,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4352,7 +4352,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4376,7 +4376,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4389,7 +4389,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4401,16 +4401,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4428,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>58</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4466,16 +4466,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4493,13 +4493,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4537,10 +4537,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4556,13 +4556,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4582,7 +4582,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4592,16 +4592,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4619,10 +4619,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4655,16 +4655,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4680,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4706,16 +4706,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4731,13 +4731,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4757,16 +4757,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4782,13 +4782,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4808,16 +4808,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4833,13 +4833,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4849,7 +4849,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4859,16 +4859,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4884,13 +4884,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4910,7 +4910,7 @@
         <v>46155.60624375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4934,7 +4934,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4947,7 +4947,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4957,16 +4957,16 @@
         <v>46196.18431344908</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -4984,13 +4984,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -4999,7 +4999,7 @@
         <v>46203</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>131</v>
+        <v>205</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
@@ -5026,10 +5026,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I58" s="5">
         <v>46204</v>
@@ -5047,7 +5047,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>208</v>
@@ -5089,10 +5089,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5110,10 +5110,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>212</v>
@@ -5125,7 +5125,7 @@
         <v>46203</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>131</v>
+        <v>205</v>
       </c>
       <c r="T59" s="9">
         <v>0</v>
@@ -5152,10 +5152,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I60" s="5">
         <v>46204</v>
@@ -5173,7 +5173,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>211</v>
@@ -5215,10 +5215,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5236,10 +5236,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>218</v>
@@ -5278,10 +5278,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I62" s="5">
         <v>46213</v>
@@ -5299,7 +5299,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>217</v>
@@ -6044,10 +6044,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6107,10 +6107,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I77" s="8">
         <v>46227</v>
@@ -6160,10 +6160,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6213,10 +6213,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I79" s="8">
         <v>46227</v>
@@ -6266,10 +6266,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6319,10 +6319,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6364,7 +6364,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6417,10 +6417,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6436,7 +6436,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>112</v>
@@ -6478,10 +6478,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6499,7 +6499,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>103</v>
@@ -6541,10 +6541,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6562,7 +6562,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>121</v>
@@ -6604,10 +6604,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6625,10 +6625,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>269</v>
@@ -7735,7 +7735,7 @@
         <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7786,7 +7786,7 @@
         <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7837,7 +7837,7 @@
         <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7888,7 +7888,7 @@
         <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7939,7 +7939,7 @@
         <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8053,7 +8053,7 @@
         <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8083,7 +8083,7 @@
         <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>322</v>
@@ -8106,7 +8106,7 @@
         <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8136,7 +8136,7 @@
         <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>322</v>
@@ -8159,7 +8159,7 @@
         <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8212,7 +8212,7 @@
         <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8265,7 +8265,7 @@
         <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8293,7 +8293,7 @@
         <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>322</v>
@@ -8379,7 +8379,7 @@
         <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8407,7 +8407,7 @@
         <v>329</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>332</v>
@@ -8430,7 +8430,7 @@
         <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8458,7 +8458,7 @@
         <v>329</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>334</v>
@@ -8481,7 +8481,7 @@
         <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8509,7 +8509,7 @@
         <v>329</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>332</v>
@@ -8532,7 +8532,7 @@
         <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8560,7 +8560,7 @@
         <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>334</v>
@@ -8583,7 +8583,7 @@
         <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8611,7 +8611,7 @@
         <v>329</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>334</v>
@@ -8742,7 +8742,7 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8770,7 +8770,7 @@
         <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>347</v>
@@ -8793,7 +8793,7 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8821,7 +8821,7 @@
         <v>342</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>347</v>
@@ -8844,7 +8844,7 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8872,7 +8872,7 @@
         <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>350</v>
@@ -8895,7 +8895,7 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -8923,7 +8923,7 @@
         <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>347</v>
@@ -8946,7 +8946,7 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8974,7 +8974,7 @@
         <v>342</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>347</v>
@@ -9060,7 +9060,7 @@
         <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9090,7 +9090,7 @@
         <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>356</v>
@@ -9113,7 +9113,7 @@
         <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9143,7 +9143,7 @@
         <v>354</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>358</v>
@@ -9166,7 +9166,7 @@
         <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9196,7 +9196,7 @@
         <v>354</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>356</v>
@@ -9219,7 +9219,7 @@
         <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9249,7 +9249,7 @@
         <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>358</v>
@@ -9272,7 +9272,7 @@
         <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9300,7 +9300,7 @@
         <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>356</v>
@@ -9386,7 +9386,7 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9414,7 +9414,7 @@
         <v>363</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>365</v>
@@ -9437,7 +9437,7 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9465,7 +9465,7 @@
         <v>363</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>365</v>
@@ -9488,7 +9488,7 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9516,7 +9516,7 @@
         <v>363</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>368</v>
@@ -9539,7 +9539,7 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9567,7 +9567,7 @@
         <v>363</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>368</v>
@@ -9590,7 +9590,7 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9618,7 +9618,7 @@
         <v>363</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>368</v>
@@ -9704,7 +9704,7 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9732,7 +9732,7 @@
         <v>372</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>372</v>
@@ -9755,7 +9755,7 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -9783,7 +9783,7 @@
         <v>372</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>372</v>
@@ -9806,7 +9806,7 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -9834,7 +9834,7 @@
         <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>372</v>
@@ -9857,7 +9857,7 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -9885,7 +9885,7 @@
         <v>372</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>372</v>
@@ -9908,7 +9908,7 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -9936,7 +9936,7 @@
         <v>372</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>372</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -522,6 +522,9 @@
     <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214777561549676</t>
   </si>
   <si>
@@ -646,9 +649,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214777626772872</t>
@@ -4176,7 +4176,7 @@
         <v>46199.563258622686</v>
       </c>
       <c r="D43" s="8">
-        <v>46199.56327399306</v>
+        <v>46203.20832019676</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -4220,8 +4220,8 @@
       <c r="R43" s="8">
         <v>46210</v>
       </c>
-      <c r="S43" s="11" t="s">
-        <v>100</v>
+      <c r="S43" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4232,7 +4232,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4277,7 +4277,7 @@
         <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4299,7 +4299,7 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4332,7 +4332,7 @@
         <v>85</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4342,7 +4342,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4352,7 +4352,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4376,7 +4376,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4389,7 +4389,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4401,16 +4401,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4428,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>58</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4466,16 +4466,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4493,13 +4493,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4537,10 +4537,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4556,13 +4556,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4582,7 +4582,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4592,16 +4592,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4619,10 +4619,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4655,16 +4655,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4680,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4706,16 +4706,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4731,13 +4731,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4757,16 +4757,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4782,13 +4782,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4808,16 +4808,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4833,13 +4833,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4849,7 +4849,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4859,16 +4859,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4884,13 +4884,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4910,7 +4910,7 @@
         <v>46155.60624375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4934,7 +4934,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4947,26 +4947,26 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46196.18431344908</v>
+        <v>46203.170198692125</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -4984,13 +4984,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>135</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -4999,7 +4999,7 @@
         <v>46203</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
@@ -5047,7 +5047,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>208</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46196.184313425925</v>
+        <v>46203.17019615741</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>211</v>
@@ -5089,10 +5089,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5110,7 +5110,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>144</v>
@@ -5125,7 +5125,7 @@
         <v>46203</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="T59" s="9">
         <v>0</v>
@@ -5173,7 +5173,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>211</v>
@@ -5215,10 +5215,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5236,10 +5236,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>218</v>
@@ -5299,7 +5299,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>217</v>
@@ -6364,7 +6364,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6417,10 +6417,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6436,7 +6436,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>112</v>
@@ -6478,10 +6478,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6499,7 +6499,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>103</v>
@@ -6541,10 +6541,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6562,7 +6562,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>121</v>
@@ -6604,10 +6604,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6625,7 +6625,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>154</v>
@@ -7735,7 +7735,7 @@
         <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7786,7 +7786,7 @@
         <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7837,7 +7837,7 @@
         <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7888,7 +7888,7 @@
         <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7939,7 +7939,7 @@
         <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8053,7 +8053,7 @@
         <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8083,7 +8083,7 @@
         <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>322</v>
@@ -8106,7 +8106,7 @@
         <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8136,7 +8136,7 @@
         <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>322</v>
@@ -8159,7 +8159,7 @@
         <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8212,7 +8212,7 @@
         <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8265,7 +8265,7 @@
         <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8293,7 +8293,7 @@
         <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>322</v>
@@ -8379,7 +8379,7 @@
         <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8407,7 +8407,7 @@
         <v>329</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>332</v>
@@ -8430,7 +8430,7 @@
         <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8458,7 +8458,7 @@
         <v>329</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>334</v>
@@ -8481,7 +8481,7 @@
         <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8509,7 +8509,7 @@
         <v>329</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>332</v>
@@ -8532,7 +8532,7 @@
         <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8560,7 +8560,7 @@
         <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>334</v>
@@ -8583,7 +8583,7 @@
         <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8611,7 +8611,7 @@
         <v>329</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>334</v>
@@ -8742,7 +8742,7 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8770,7 +8770,7 @@
         <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>347</v>
@@ -8793,7 +8793,7 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8821,7 +8821,7 @@
         <v>342</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>347</v>
@@ -8844,7 +8844,7 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8872,7 +8872,7 @@
         <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>350</v>
@@ -8895,7 +8895,7 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -8923,7 +8923,7 @@
         <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>347</v>
@@ -8946,7 +8946,7 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8974,7 +8974,7 @@
         <v>342</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>347</v>
@@ -9060,7 +9060,7 @@
         <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9090,7 +9090,7 @@
         <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>356</v>
@@ -9113,7 +9113,7 @@
         <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9143,7 +9143,7 @@
         <v>354</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>358</v>
@@ -9166,7 +9166,7 @@
         <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9196,7 +9196,7 @@
         <v>354</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>356</v>
@@ -9219,7 +9219,7 @@
         <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9249,7 +9249,7 @@
         <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>358</v>
@@ -9272,7 +9272,7 @@
         <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9300,7 +9300,7 @@
         <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>356</v>
@@ -9386,7 +9386,7 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9414,7 +9414,7 @@
         <v>363</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>365</v>
@@ -9437,7 +9437,7 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9465,7 +9465,7 @@
         <v>363</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>365</v>
@@ -9488,7 +9488,7 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9516,7 +9516,7 @@
         <v>363</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>368</v>
@@ -9539,7 +9539,7 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9567,7 +9567,7 @@
         <v>363</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>368</v>
@@ -9590,7 +9590,7 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9618,7 +9618,7 @@
         <v>363</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>368</v>
@@ -9704,7 +9704,7 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9732,7 +9732,7 @@
         <v>372</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>372</v>
@@ -9755,7 +9755,7 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -9783,7 +9783,7 @@
         <v>372</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>372</v>
@@ -9806,7 +9806,7 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -9834,7 +9834,7 @@
         <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>372</v>
@@ -9857,7 +9857,7 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -9885,7 +9885,7 @@
         <v>372</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>372</v>
@@ -9908,7 +9908,7 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -9936,7 +9936,7 @@
         <v>372</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>372</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46203.170198692125</v>
+        <v>46204.190036064814</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>202</v>
@@ -4998,8 +4998,8 @@
       <c r="R57" s="8">
         <v>46203</v>
       </c>
-      <c r="S57" s="12" t="s">
-        <v>163</v>
+      <c r="S57" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46203.17019615741</v>
+        <v>46204.19003640046</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>211</v>
@@ -5124,8 +5124,8 @@
       <c r="R59" s="8">
         <v>46203</v>
       </c>
-      <c r="S59" s="12" t="s">
-        <v>163</v>
+      <c r="S59" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T59" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="388">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -278,9 +278,6 @@
     <t>Generación OC Corte Plasma  OT 4316</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1214777561381920</t>
   </si>
   <si>
@@ -688,6 +685,9 @@
   </si>
   <si>
     <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214777561702202</t>
@@ -2187,9 +2187,11 @@
       <c r="B10" s="5">
         <v>46155.605614988424</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46204.91629298611</v>
+      </c>
       <c r="D10" s="5">
-        <v>46197.71331710648</v>
+        <v>46204.91630894676</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2224,8 +2226,12 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -2429,9 +2435,11 @@
       <c r="B14" s="5">
         <v>46155.605619849535</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46204.91619311343</v>
+      </c>
       <c r="D14" s="5">
-        <v>46197.71329697917</v>
+        <v>46204.91621174768</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2466,8 +2474,12 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -2736,9 +2748,11 @@
       <c r="B19" s="8">
         <v>46155.605814317125</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="8">
+        <v>46204.9161715625</v>
+      </c>
       <c r="D19" s="8">
-        <v>46195.947693634254</v>
+        <v>46204.916238564816</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2786,15 +2800,15 @@
         <v>32</v>
       </c>
       <c r="T19" s="9">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46155.60582009259</v>
@@ -2806,7 +2820,7 @@
         <v>46196.643954976855</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2839,7 +2853,7 @@
         <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2859,7 +2873,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8">
         <v>46155.60582561343</v>
@@ -2871,7 +2885,7 @@
         <v>46196.644582037035</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2904,7 +2918,7 @@
         <v>77</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46185</v>
@@ -2924,7 +2938,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46155.60562462963</v>
@@ -2934,7 +2948,7 @@
         <v>46182.693747743055</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2958,7 +2972,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2971,7 +2985,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46155.60583177084</v>
@@ -2983,16 +2997,16 @@
         <v>46182.67729332176</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46157</v>
@@ -3010,13 +3024,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q23" s="8">
         <v>46157</v>
@@ -3036,7 +3050,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46155.60583869213</v>
@@ -3048,16 +3062,16 @@
         <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3075,29 +3089,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B25" s="8">
         <v>46155.605845625</v>
@@ -3109,16 +3123,16 @@
         <v>46182.67726898148</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="I25" s="8">
         <v>46161</v>
@@ -3136,29 +3150,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46155.60585226852</v>
@@ -3168,16 +3182,16 @@
         <v>46179.19528431713</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3195,13 +3209,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3216,12 +3230,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46155.605858807874</v>
@@ -3231,16 +3245,16 @@
         <v>46197.502279444445</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="I27" s="8">
         <v>46157</v>
@@ -3258,29 +3272,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46155.605865289355</v>
@@ -3290,16 +3304,16 @@
         <v>46178.17124241898</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3317,29 +3331,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46155.605925254626</v>
@@ -3351,16 +3365,16 @@
         <v>46197.18498747685</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="I29" s="8">
         <v>46157</v>
@@ -3378,13 +3392,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q29" s="8">
         <v>46157</v>
@@ -3404,7 +3418,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46155.605932488426</v>
@@ -3416,16 +3430,16 @@
         <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3443,29 +3457,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46155.605939444446</v>
@@ -3477,16 +3491,16 @@
         <v>46182.67711275463</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="I31" s="8">
         <v>46168</v>
@@ -3504,29 +3518,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46155.605945868054</v>
@@ -3538,16 +3552,16 @@
         <v>46182.69372545139</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3565,29 +3579,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46155.60595229166</v>
@@ -3597,16 +3611,16 @@
         <v>46200.20644892361</v>
       </c>
       <c r="E33" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="I33" s="8">
         <v>46189</v>
@@ -3624,13 +3638,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q33" s="8">
         <v>46189</v>
@@ -3645,12 +3659,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46155.60595878473</v>
@@ -3662,16 +3676,16 @@
         <v>46199.55831050926</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3689,29 +3703,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46155.60596540509</v>
@@ -3721,16 +3735,16 @@
         <v>46199.55878317129</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="I35" s="8">
         <v>46191</v>
@@ -3742,35 +3756,35 @@
         <v>26</v>
       </c>
       <c r="L35" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="P35" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46155.60597160879</v>
@@ -3780,16 +3794,16 @@
         <v>46200.20645215278</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3807,10 +3821,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3828,19 +3842,19 @@
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46155.605976770836</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46190.16909938658</v>
+        <v>46204.91618141204</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>81</v>
@@ -3849,10 +3863,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="I37" s="8">
         <v>46189</v>
@@ -3870,13 +3884,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3886,7 +3900,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46155.60598313657</v>
@@ -3896,16 +3910,16 @@
         <v>46199.170012291666</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3923,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3939,7 +3953,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46155.60598890047</v>
@@ -3951,16 +3965,16 @@
         <v>46196.694887627316</v>
       </c>
       <c r="E39" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
+      <c r="H39" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46189</v>
@@ -3978,10 +3992,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3993,7 +4007,7 @@
         <v>46230</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4004,7 +4018,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46155.60599439815</v>
@@ -4016,16 +4030,16 @@
         <v>46196.69342819444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4043,13 +4057,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4059,7 +4073,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46155.606000196756</v>
@@ -4071,16 +4085,16 @@
         <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46198</v>
@@ -4098,13 +4112,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4114,7 +4128,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46155.60600616898</v>
@@ -4124,16 +4138,16 @@
         <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4151,10 +4165,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4167,7 +4181,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46155.60601071759</v>
@@ -4179,16 +4193,16 @@
         <v>46203.20832019676</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="I43" s="8">
         <v>46189</v>
@@ -4206,10 +4220,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4221,7 +4235,7 @@
         <v>46210</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4232,7 +4246,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4244,16 +4258,16 @@
         <v>46199.56319799769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4271,13 +4285,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4287,7 +4301,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4299,16 +4313,16 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="I45" s="8">
         <v>46191</v>
@@ -4326,13 +4340,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4342,7 +4356,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4352,7 +4366,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4376,7 +4390,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4389,7 +4403,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4401,16 +4415,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4428,13 +4442,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>58</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4454,7 +4468,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4466,16 +4480,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4493,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4519,7 +4533,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4537,10 +4551,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4556,13 +4570,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4571,7 +4585,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4582,7 +4596,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4592,16 +4606,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4619,10 +4633,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4634,18 +4648,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4655,16 +4669,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4680,13 +4694,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4696,7 +4710,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4706,16 +4720,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4731,13 +4745,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4747,7 +4761,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4757,16 +4771,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4782,13 +4796,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4798,7 +4812,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4808,16 +4822,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4833,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4849,7 +4863,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4859,16 +4873,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4884,13 +4898,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4900,7 +4914,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4910,7 +4924,7 @@
         <v>46155.60624375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4934,7 +4948,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4947,7 +4961,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4957,16 +4971,16 @@
         <v>46204.190036064814</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -4984,13 +4998,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5005,12 +5019,12 @@
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5020,16 +5034,16 @@
         <v>46176.200130439815</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46204</v>
@@ -5047,13 +5061,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5068,12 +5082,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5083,16 +5097,16 @@
         <v>46204.19003640046</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5110,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5131,12 +5145,12 @@
         <v>0</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5146,16 +5160,16 @@
         <v>46176.20013030093</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I60" s="5">
         <v>46204</v>
@@ -5173,13 +5187,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5194,12 +5208,12 @@
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
@@ -5209,16 +5223,16 @@
         <v>46199.563261076386</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5236,13 +5250,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5251,13 +5265,13 @@
         <v>46212</v>
       </c>
       <c r="S61" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T61" s="9">
         <v>0</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>82</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5272,16 +5286,16 @@
         <v>46155.608459560186</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I62" s="5">
         <v>46213</v>
@@ -5299,13 +5313,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5314,13 +5328,13 @@
         <v>46216</v>
       </c>
       <c r="S62" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
       <c r="U62" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5412,7 +5426,7 @@
         <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>221</v>
@@ -5424,13 +5438,13 @@
         <v>46219</v>
       </c>
       <c r="S64" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5740,7 +5754,7 @@
         <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>221</v>
@@ -5752,13 +5766,13 @@
         <v>46226</v>
       </c>
       <c r="S70" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -6044,10 +6058,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6068,7 +6082,7 @@
         <v>221</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>221</v>
@@ -6080,13 +6094,13 @@
         <v>46227</v>
       </c>
       <c r="S76" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6107,10 +6121,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I77" s="8">
         <v>46227</v>
@@ -6160,10 +6174,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6213,10 +6227,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I79" s="8">
         <v>46227</v>
@@ -6266,10 +6280,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6319,10 +6333,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6364,7 +6378,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6417,10 +6431,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6436,10 +6450,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>260</v>
@@ -6457,7 +6471,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6478,10 +6492,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6499,10 +6513,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>263</v>
@@ -6520,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>82</v>
+        <v>218</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6541,10 +6555,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6562,10 +6576,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>266</v>
@@ -6583,7 +6597,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>82</v>
+        <v>218</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6604,10 +6618,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6625,10 +6639,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>269</v>
@@ -6640,13 +6654,13 @@
         <v>46231</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>82</v>
+        <v>218</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6750,13 +6764,13 @@
         <v>46234</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7066,7 +7080,7 @@
         <v>271</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>271</v>
@@ -7078,13 +7092,13 @@
         <v>46237</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7384,7 +7398,7 @@
         <v>271</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>271</v>
@@ -7396,13 +7410,13 @@
         <v>46238</v>
       </c>
       <c r="S100" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7714,13 +7728,13 @@
         <v>46239</v>
       </c>
       <c r="S106" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
       <c r="U106" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -7735,7 +7749,7 @@
         <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7786,7 +7800,7 @@
         <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7837,7 +7851,7 @@
         <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7888,7 +7902,7 @@
         <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7939,7 +7953,7 @@
         <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8032,13 +8046,13 @@
         <v>46240</v>
       </c>
       <c r="S112" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8053,7 +8067,7 @@
         <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8083,7 +8097,7 @@
         <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>322</v>
@@ -8106,7 +8120,7 @@
         <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8136,7 +8150,7 @@
         <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>322</v>
@@ -8159,7 +8173,7 @@
         <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8212,7 +8226,7 @@
         <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8265,7 +8279,7 @@
         <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8293,7 +8307,7 @@
         <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>322</v>
@@ -8358,13 +8372,13 @@
         <v>46244</v>
       </c>
       <c r="S118" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
       </c>
       <c r="U118" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -8379,7 +8393,7 @@
         <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8407,7 +8421,7 @@
         <v>329</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>332</v>
@@ -8430,7 +8444,7 @@
         <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8458,7 +8472,7 @@
         <v>329</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>334</v>
@@ -8481,7 +8495,7 @@
         <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8509,7 +8523,7 @@
         <v>329</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>332</v>
@@ -8532,7 +8546,7 @@
         <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8560,7 +8574,7 @@
         <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>334</v>
@@ -8583,7 +8597,7 @@
         <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8611,7 +8625,7 @@
         <v>329</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>334</v>
@@ -8721,13 +8735,13 @@
         <v>46245</v>
       </c>
       <c r="S125" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
       </c>
       <c r="U125" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -8742,7 +8756,7 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8770,7 +8784,7 @@
         <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>347</v>
@@ -8793,7 +8807,7 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8821,7 +8835,7 @@
         <v>342</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>347</v>
@@ -8844,7 +8858,7 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8872,7 +8886,7 @@
         <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>350</v>
@@ -8895,7 +8909,7 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -8923,7 +8937,7 @@
         <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>347</v>
@@ -8946,7 +8960,7 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8974,7 +8988,7 @@
         <v>342</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>347</v>
@@ -9039,13 +9053,13 @@
         <v>46246</v>
       </c>
       <c r="S131" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
       </c>
       <c r="U131" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -9060,7 +9074,7 @@
         <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9090,7 +9104,7 @@
         <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>356</v>
@@ -9113,7 +9127,7 @@
         <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9143,7 +9157,7 @@
         <v>354</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>358</v>
@@ -9166,7 +9180,7 @@
         <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9196,7 +9210,7 @@
         <v>354</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>356</v>
@@ -9219,7 +9233,7 @@
         <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9249,7 +9263,7 @@
         <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>358</v>
@@ -9272,7 +9286,7 @@
         <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9300,7 +9314,7 @@
         <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>356</v>
@@ -9365,13 +9379,13 @@
         <v>46247</v>
       </c>
       <c r="S137" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
       </c>
       <c r="U137" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -9386,7 +9400,7 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9414,7 +9428,7 @@
         <v>363</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>365</v>
@@ -9437,7 +9451,7 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9465,7 +9479,7 @@
         <v>363</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>365</v>
@@ -9488,7 +9502,7 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9516,7 +9530,7 @@
         <v>363</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>368</v>
@@ -9539,7 +9553,7 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9567,7 +9581,7 @@
         <v>363</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>368</v>
@@ -9590,7 +9604,7 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9618,7 +9632,7 @@
         <v>363</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>368</v>
@@ -9683,13 +9697,13 @@
         <v>46248</v>
       </c>
       <c r="S143" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
       </c>
       <c r="U143" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
@@ -9704,7 +9718,7 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9732,7 +9746,7 @@
         <v>372</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>372</v>
@@ -9755,7 +9769,7 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -9783,7 +9797,7 @@
         <v>372</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>372</v>
@@ -9806,7 +9820,7 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -9834,7 +9848,7 @@
         <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>372</v>
@@ -9857,7 +9871,7 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -9885,7 +9899,7 @@
         <v>372</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>372</v>
@@ -9908,7 +9922,7 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -9936,7 +9950,7 @@
         <v>372</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>372</v>
@@ -10048,13 +10062,13 @@
         <v>46255</v>
       </c>
       <c r="S150" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
       </c>
       <c r="U150" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
@@ -10111,13 +10125,13 @@
         <v>46255</v>
       </c>
       <c r="S151" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T151" s="9">
         <v>0</v>
       </c>
       <c r="U151" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1821,13 +1821,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46155.60560971065</v>
+        <v>46155.43894304398</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.873231273144</v>
+        <v>46175.70656460648</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.71343847222</v>
+        <v>46197.54677180556</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1870,13 +1870,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46155.60572528935</v>
+        <v>46155.43905862268</v>
       </c>
       <c r="C5" s="8">
-        <v>46161.623405879625</v>
+        <v>46161.45673921297</v>
       </c>
       <c r="D5" s="8">
-        <v>46161.62342217592</v>
+        <v>46161.45675550926</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1933,13 +1933,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46155.60573108796</v>
+        <v>46155.4390644213</v>
       </c>
       <c r="C6" s="5">
-        <v>46161.62364042824</v>
+        <v>46161.456973761575</v>
       </c>
       <c r="D6" s="5">
-        <v>46161.623656701384</v>
+        <v>46161.45699003473</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1996,13 +1996,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46155.60573616898</v>
+        <v>46155.43906950232</v>
       </c>
       <c r="C7" s="8">
-        <v>46161.62365674769</v>
+        <v>46161.45699008102</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.62382879629</v>
+        <v>46161.457162129635</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2059,13 +2059,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46155.60574121527</v>
+        <v>46155.439074548616</v>
       </c>
       <c r="C8" s="5">
-        <v>46161.624193275464</v>
+        <v>46161.45752660879</v>
       </c>
       <c r="D8" s="5">
-        <v>46161.62420805555</v>
+        <v>46161.45754138889</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2122,13 +2122,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46155.6057468287</v>
+        <v>46155.43908016203</v>
       </c>
       <c r="C9" s="8">
-        <v>46175.87321719907</v>
+        <v>46175.706550532406</v>
       </c>
       <c r="D9" s="8">
-        <v>46175.873231562495</v>
+        <v>46175.70656489584</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2185,13 +2185,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46155.605614988424</v>
+        <v>46155.43894832176</v>
       </c>
       <c r="C10" s="5">
-        <v>46204.91629298611</v>
+        <v>46204.74962631945</v>
       </c>
       <c r="D10" s="5">
-        <v>46204.91630894676</v>
+        <v>46204.74964228009</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2238,13 +2238,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46155.605752372685</v>
+        <v>46155.43908570602</v>
       </c>
       <c r="C11" s="8">
-        <v>46161.624231967595</v>
+        <v>46161.45756530092</v>
       </c>
       <c r="D11" s="8">
-        <v>46195.54676366899</v>
+        <v>46195.380097002315</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2303,13 +2303,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46155.60576009259</v>
+        <v>46155.43909342593</v>
       </c>
       <c r="C12" s="5">
-        <v>46161.62423836805</v>
+        <v>46161.457571701394</v>
       </c>
       <c r="D12" s="5">
-        <v>46195.54676375</v>
+        <v>46195.38009708333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2368,13 +2368,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46155.60576791667</v>
+        <v>46155.43910125</v>
       </c>
       <c r="C13" s="8">
-        <v>46161.62424628472</v>
+        <v>46161.45757961806</v>
       </c>
       <c r="D13" s="8">
-        <v>46195.546763645834</v>
+        <v>46195.38009697916</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2433,13 +2433,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46155.605619849535</v>
+        <v>46155.43895318287</v>
       </c>
       <c r="C14" s="5">
-        <v>46204.91619311343</v>
+        <v>46204.74952644676</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.91621174768</v>
+        <v>46204.749545081024</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2486,13 +2486,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46155.605784768515</v>
+        <v>46155.43911810185</v>
       </c>
       <c r="C15" s="8">
-        <v>46161.62429071759</v>
+        <v>46161.45762405093</v>
       </c>
       <c r="D15" s="8">
-        <v>46161.624307349535</v>
+        <v>46161.45764068287</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2551,13 +2551,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46155.605792291666</v>
+        <v>46155.439125624995</v>
       </c>
       <c r="C16" s="5">
-        <v>46161.62429854167</v>
+        <v>46161.457631875004</v>
       </c>
       <c r="D16" s="5">
-        <v>46161.62431424769</v>
+        <v>46161.45764758102</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2616,13 +2616,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46155.605799756944</v>
+        <v>46155.43913309027</v>
       </c>
       <c r="C17" s="8">
-        <v>46197.50227302083</v>
+        <v>46197.335606354165</v>
       </c>
       <c r="D17" s="8">
-        <v>46197.502289386575</v>
+        <v>46197.33562271991</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2681,13 +2681,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46155.60580746528</v>
+        <v>46155.43914079861</v>
       </c>
       <c r="C18" s="5">
-        <v>46196.64233232639</v>
+        <v>46196.475665659724</v>
       </c>
       <c r="D18" s="5">
-        <v>46196.64234802083</v>
+        <v>46196.47568135417</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2746,13 +2746,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46155.605814317125</v>
+        <v>46155.43914765047</v>
       </c>
       <c r="C19" s="8">
-        <v>46204.9161715625</v>
+        <v>46204.74950489584</v>
       </c>
       <c r="D19" s="8">
-        <v>46204.916238564816</v>
+        <v>46204.74957189815</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2811,13 +2811,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46155.60582009259</v>
+        <v>46155.43915342593</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.64393914352</v>
+        <v>46196.477272476855</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.643954976855</v>
+        <v>46196.47728831018</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2876,13 +2876,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46155.60582561343</v>
+        <v>46155.439158946756</v>
       </c>
       <c r="C21" s="8">
-        <v>46196.64456515046</v>
+        <v>46196.4778984838</v>
       </c>
       <c r="D21" s="8">
-        <v>46196.644582037035</v>
+        <v>46196.47791537037</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2941,11 +2941,11 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46155.60562462963</v>
+        <v>46155.438957962964</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46182.693747743055</v>
+        <v>46182.52708107639</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2988,13 +2988,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46155.60583177084</v>
+        <v>46155.439165104166</v>
       </c>
       <c r="C23" s="8">
-        <v>46182.6772816088</v>
+        <v>46182.51061494213</v>
       </c>
       <c r="D23" s="8">
-        <v>46182.67729332176</v>
+        <v>46182.510626655094</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -3053,13 +3053,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46155.60583869213</v>
+        <v>46155.439172025464</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.65327461806</v>
+        <v>46182.48660795139</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.653276006946</v>
+        <v>46182.48660934028</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -3114,13 +3114,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46155.605845625</v>
+        <v>46155.43917895833</v>
       </c>
       <c r="C25" s="8">
-        <v>46182.67726747685</v>
+        <v>46182.51060081019</v>
       </c>
       <c r="D25" s="8">
-        <v>46182.67726898148</v>
+        <v>46182.51060231481</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -3175,11 +3175,11 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46155.60585226852</v>
+        <v>46155.43918560185</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.19528431713</v>
+        <v>46179.02861765046</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -3238,11 +3238,11 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46155.605858807874</v>
+        <v>46155.4391921412</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46197.502279444445</v>
+        <v>46197.33561277778</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -3297,11 +3297,11 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46155.605865289355</v>
+        <v>46155.439198622684</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.17124241898</v>
+        <v>46178.00457575232</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3356,13 +3356,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46155.605925254626</v>
+        <v>46155.43925858796</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.69373945602</v>
+        <v>46182.52707278935</v>
       </c>
       <c r="D29" s="8">
-        <v>46197.18498747685</v>
+        <v>46197.01832081018</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3421,13 +3421,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46155.605932488426</v>
+        <v>46155.439265821755</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.653084143516</v>
+        <v>46182.48641747685</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.65308653935</v>
+        <v>46182.48641987269</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3482,13 +3482,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46155.605939444446</v>
+        <v>46155.439272777774</v>
       </c>
       <c r="C31" s="8">
-        <v>46182.67711099537</v>
+        <v>46182.510444328705</v>
       </c>
       <c r="D31" s="8">
-        <v>46182.67711275463</v>
+        <v>46182.51044608797</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3543,13 +3543,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46155.605945868054</v>
+        <v>46155.43927920139</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.69372391204</v>
+        <v>46182.527057245374</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.69372545139</v>
+        <v>46182.52705878472</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3604,11 +3604,11 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46155.60595229166</v>
+        <v>46155.439285625005</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46200.20644892361</v>
+        <v>46200.03978225694</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3667,13 +3667,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46155.60595878473</v>
+        <v>46155.439292118055</v>
       </c>
       <c r="C34" s="5">
-        <v>46199.55808454861</v>
+        <v>46199.39141788194</v>
       </c>
       <c r="D34" s="5">
-        <v>46199.55831050926</v>
+        <v>46199.391643842595</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3728,11 +3728,11 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46155.60596540509</v>
+        <v>46155.43929873843</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46199.55878317129</v>
+        <v>46199.392116504634</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3787,11 +3787,11 @@
         <v>137</v>
       </c>
       <c r="B36" s="5">
-        <v>46155.60597160879</v>
+        <v>46155.439304942134</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46200.20645215278</v>
+        <v>46200.03978548611</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>138</v>
@@ -3850,11 +3850,11 @@
         <v>140</v>
       </c>
       <c r="B37" s="8">
-        <v>46155.605976770836</v>
+        <v>46155.439310104164</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46204.91618141204</v>
+        <v>46204.749514745374</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>81</v>
@@ -3903,11 +3903,11 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46155.60598313657</v>
+        <v>46155.43931646991</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46199.170012291666</v>
+        <v>46199.003345624995</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3956,13 +3956,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46155.60598890047</v>
+        <v>46155.4393222338</v>
       </c>
       <c r="C39" s="8">
-        <v>46196.6948721875</v>
+        <v>46196.52820552084</v>
       </c>
       <c r="D39" s="8">
-        <v>46196.694887627316</v>
+        <v>46196.52822096065</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -4021,13 +4021,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46155.60599439815</v>
+        <v>46155.43932773148</v>
       </c>
       <c r="C40" s="5">
-        <v>46196.69342611112</v>
+        <v>46196.526759444445</v>
       </c>
       <c r="D40" s="5">
-        <v>46196.69342819444</v>
+        <v>46196.52676152778</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>87</v>
@@ -4076,13 +4076,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46155.606000196756</v>
+        <v>46155.43933353009</v>
       </c>
       <c r="C41" s="8">
-        <v>46196.693492025464</v>
+        <v>46196.5268253588</v>
       </c>
       <c r="D41" s="8">
-        <v>46196.69349420139</v>
+        <v>46196.52682753472</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -4131,11 +4131,11 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46155.60600616898</v>
+        <v>46155.439339502314</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.69350203704</v>
+        <v>46196.52683537037</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -4184,13 +4184,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46155.60601071759</v>
+        <v>46155.43934405093</v>
       </c>
       <c r="C43" s="8">
-        <v>46199.563258622686</v>
+        <v>46199.396591956014</v>
       </c>
       <c r="D43" s="8">
-        <v>46203.20832019676</v>
+        <v>46203.04165353009</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4249,13 +4249,13 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46155.60601423611</v>
+        <v>46155.439347569445</v>
       </c>
       <c r="C44" s="5">
-        <v>46199.563196041665</v>
+        <v>46199.396529375</v>
       </c>
       <c r="D44" s="5">
-        <v>46199.56319799769</v>
+        <v>46199.39653133102</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>84</v>
@@ -4304,13 +4304,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46155.60601877315</v>
+        <v>46155.43935210648</v>
       </c>
       <c r="C45" s="8">
-        <v>46199.563244351855</v>
+        <v>46199.396577685184</v>
       </c>
       <c r="D45" s="8">
-        <v>46199.56324628472</v>
+        <v>46199.39657961806</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4359,11 +4359,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46155.60562939815</v>
+        <v>46155.43896273148</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.71336900463</v>
+        <v>46197.54670233796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4406,13 +4406,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46155.60602364583</v>
+        <v>46155.43935697917</v>
       </c>
       <c r="C47" s="8">
-        <v>46195.94740237268</v>
+        <v>46195.78073570602</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.71427196759</v>
+        <v>46197.547605300926</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4471,13 +4471,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46155.606031076386</v>
+        <v>46155.43936440972</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.94760157407</v>
+        <v>46195.78093490741</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.71433108796</v>
+        <v>46197.5476644213</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4536,13 +4536,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46155.606038645834</v>
+        <v>46155.43937197917</v>
       </c>
       <c r="C49" s="8">
-        <v>46195.94765166666</v>
+        <v>46195.780985000005</v>
       </c>
       <c r="D49" s="8">
-        <v>46195.947667824075</v>
+        <v>46195.781001157404</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>77</v>
@@ -4599,11 +4599,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46155.606091747686</v>
+        <v>46155.439425081015</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.63491418981</v>
+        <v>46155.46824752315</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4662,11 +4662,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="8">
-        <v>46155.60610010417</v>
+        <v>46155.439433437496</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46155.64216699074</v>
+        <v>46155.47550032407</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>190</v>
@@ -4713,11 +4713,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46155.606106273146</v>
+        <v>46155.43943960648</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.6421837963</v>
+        <v>46155.47551712963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4764,11 +4764,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46155.60611204861</v>
+        <v>46155.43944538194</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46155.64219278935</v>
+        <v>46155.47552612268</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>190</v>
@@ -4815,11 +4815,11 @@
         <v>195</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.60611671297</v>
+        <v>46155.439450046295</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.64220083333</v>
+        <v>46155.47553416667</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4866,11 +4866,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="8">
-        <v>46155.63491277778</v>
+        <v>46155.46824611111</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46155.64223084491</v>
+        <v>46155.47556417824</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>190</v>
@@ -4917,11 +4917,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46155.60612125</v>
+        <v>46155.439454583335</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.60624375</v>
+        <v>46155.439577083336</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4964,11 +4964,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46155.60612483796</v>
+        <v>46155.4394581713</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46204.190036064814</v>
+        <v>46204.02336939815</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5027,11 +5027,11 @@
         <v>205</v>
       </c>
       <c r="B58" s="5">
-        <v>46155.6061331713</v>
+        <v>46155.43946650463</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46176.200130439815</v>
+        <v>46205.00182856481</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>206</v>
@@ -5090,11 +5090,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46155.606141446755</v>
+        <v>46155.4394747801</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46204.19003640046</v>
+        <v>46204.0233697338</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>210</v>
@@ -5153,11 +5153,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46155.60614949074</v>
+        <v>46155.43948282408</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46176.20013030093</v>
+        <v>46205.00182502315</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5216,11 +5216,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="8">
-        <v>46155.606156319445</v>
+        <v>46155.43948965278</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46199.563261076386</v>
+        <v>46205.01169863426</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5264,8 +5264,8 @@
       <c r="R61" s="8">
         <v>46212</v>
       </c>
-      <c r="S61" s="11" t="s">
-        <v>99</v>
+      <c r="S61" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="T61" s="9">
         <v>0</v>
@@ -5279,11 +5279,11 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46155.60616390046</v>
+        <v>46155.4394972338</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.608459560186</v>
+        <v>46155.441792893515</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>217</v>
@@ -5342,11 +5342,11 @@
         <v>220</v>
       </c>
       <c r="B63" s="8">
-        <v>46155.60617082176</v>
+        <v>46155.43950415509</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46155.6064415162</v>
+        <v>46155.43977484954</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>221</v>
@@ -5389,11 +5389,11 @@
         <v>223</v>
       </c>
       <c r="B64" s="5">
-        <v>46155.60617413194</v>
+        <v>46155.43950746528</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.6162571875</v>
+        <v>46155.44959052083</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>224</v>
@@ -5452,11 +5452,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="8">
-        <v>46155.60618260417</v>
+        <v>46155.4395159375</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46155.60738728009</v>
+        <v>46155.44072061343</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5505,11 +5505,11 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.60619106481</v>
+        <v>46155.43952439815</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.61677891204</v>
+        <v>46155.450112245366</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5558,11 +5558,11 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46155.60619835649</v>
+        <v>46155.439531689815</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46155.6168003125</v>
+        <v>46155.450133645834</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -5611,11 +5611,11 @@
         <v>235</v>
       </c>
       <c r="B68" s="5">
-        <v>46155.60620543981</v>
+        <v>46155.43953877315</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.61683189815</v>
+        <v>46155.45016523148</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5664,11 +5664,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="8">
-        <v>46155.60745351852</v>
+        <v>46155.44078685185</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46155.617393912034</v>
+        <v>46155.45072724537</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>228</v>
@@ -5717,11 +5717,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46155.606212638886</v>
+        <v>46155.43954597222</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.61775856481</v>
+        <v>46155.45109189815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>238</v>
@@ -5780,11 +5780,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46155.60621899305</v>
+        <v>46155.43955232639</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.9476830787</v>
+        <v>46195.78101641204</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>228</v>
@@ -5833,11 +5833,11 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.606226539356</v>
+        <v>46155.439559872684</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.9476728125</v>
+        <v>46195.78100614583</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5886,11 +5886,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46155.606234004634</v>
+        <v>46155.43956733796</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.94767699074</v>
+        <v>46195.78101032408</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>228</v>
@@ -5939,11 +5939,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46155.60628421296</v>
+        <v>46155.4396175463</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.94767966435</v>
+        <v>46195.781012997686</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>228</v>
@@ -5992,11 +5992,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46155.607690034725</v>
+        <v>46155.441023368054</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46155.61937777778</v>
+        <v>46155.45271111111</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>228</v>
@@ -6045,11 +6045,11 @@
         <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.606291909724</v>
+        <v>46155.43962524306</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.61911184028</v>
+        <v>46155.45244517361</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>248</v>
@@ -6108,11 +6108,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="8">
-        <v>46155.60629884259</v>
+        <v>46155.43963217593</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.947673518516</v>
+        <v>46195.78100685185</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>228</v>
@@ -6161,11 +6161,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46155.60630622685</v>
+        <v>46155.43963956018</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.947674131945</v>
+        <v>46195.78100746528</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>228</v>
@@ -6214,11 +6214,11 @@
         <v>252</v>
       </c>
       <c r="B79" s="8">
-        <v>46155.6063134375</v>
+        <v>46155.43964677083</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.94768039352</v>
+        <v>46195.78101372685</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>228</v>
@@ -6267,11 +6267,11 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46155.606319722225</v>
+        <v>46155.43965305555</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.94768090278</v>
+        <v>46195.78101423611</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>228</v>
@@ -6320,11 +6320,11 @@
         <v>255</v>
       </c>
       <c r="B81" s="8">
-        <v>46155.618322951384</v>
+        <v>46155.45165628473</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46155.620736377314</v>
+        <v>46155.45406971065</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>228</v>
@@ -6371,11 +6371,11 @@
         <v>256</v>
       </c>
       <c r="B82" s="5">
-        <v>46155.60632542824</v>
+        <v>46155.43965876158</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.60644350694</v>
+        <v>46155.43977684028</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>198</v>
@@ -6418,11 +6418,11 @@
         <v>258</v>
       </c>
       <c r="B83" s="8">
-        <v>46155.60632868056</v>
+        <v>46155.43966201389</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46182.19947712963</v>
+        <v>46182.03281046296</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>259</v>
@@ -6479,11 +6479,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46155.60633650463</v>
+        <v>46155.439669837964</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.677286018516</v>
+        <v>46182.51061935185</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>262</v>
@@ -6542,11 +6542,11 @@
         <v>264</v>
       </c>
       <c r="B85" s="8">
-        <v>46155.60634402778</v>
+        <v>46155.43967736111</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46198.182506087964</v>
+        <v>46198.01583942129</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>265</v>
@@ -6605,11 +6605,11 @@
         <v>267</v>
       </c>
       <c r="B86" s="5">
-        <v>46155.60635177083</v>
+        <v>46155.43968510417</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46196.693516562504</v>
+        <v>46196.52684989583</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>268</v>
@@ -6668,11 +6668,11 @@
         <v>270</v>
       </c>
       <c r="B87" s="8">
-        <v>46155.606361921295</v>
+        <v>46155.43969525463</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46155.606780057875</v>
+        <v>46155.4401133912</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>271</v>
@@ -6715,11 +6715,11 @@
         <v>273</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.60636525463</v>
+        <v>46155.43969858796</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.620355625</v>
+        <v>46155.45368895833</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>274</v>
@@ -6778,11 +6778,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="8">
-        <v>46155.606374525465</v>
+        <v>46155.43970785879</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.621619502315</v>
+        <v>46155.454952835644</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>228</v>
@@ -6831,11 +6831,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46155.60638027778</v>
+        <v>46155.43971361111</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.62163603009</v>
+        <v>46155.454969363425</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>228</v>
@@ -6884,11 +6884,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46155.60638583334</v>
+        <v>46155.439719166665</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46155.62166074074</v>
+        <v>46155.45499407407</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>228</v>
@@ -6937,11 +6937,11 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.60639179398</v>
+        <v>46155.43972512732</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.62167399305</v>
+        <v>46155.45500732639</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>228</v>
@@ -6990,11 +6990,11 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46155.61975986111</v>
+        <v>46155.45309319445</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46155.62169508102</v>
+        <v>46155.45502841435</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>228</v>
@@ -7043,11 +7043,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46155.60639783565</v>
+        <v>46155.43973116898</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.62191585648</v>
+        <v>46155.455249189814</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -7106,11 +7106,11 @@
         <v>286</v>
       </c>
       <c r="B95" s="8">
-        <v>46155.60640402778</v>
+        <v>46155.439737361114</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.947681273145</v>
+        <v>46195.78101460648</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>228</v>
@@ -7157,11 +7157,11 @@
         <v>289</v>
       </c>
       <c r="B96" s="5">
-        <v>46155.60641090278</v>
+        <v>46155.43974423611</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.94768182871</v>
+        <v>46195.781015162036</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>228</v>
@@ -7208,11 +7208,11 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46155.60641760417</v>
+        <v>46155.4397509375</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.94768232639</v>
+        <v>46195.781015659726</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>228</v>
@@ -7259,11 +7259,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.60642649306</v>
+        <v>46155.43975982639</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.947674641204</v>
+        <v>46195.78100797454</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>228</v>
@@ -7310,11 +7310,11 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46155.62115946759</v>
+        <v>46155.45449280093</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46155.64240027778</v>
+        <v>46155.47573361111</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>228</v>
@@ -7361,11 +7361,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46155.60648232639</v>
+        <v>46155.43981565972</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.631670462964</v>
+        <v>46155.4650037963</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7424,11 +7424,11 @@
         <v>297</v>
       </c>
       <c r="B101" s="8">
-        <v>46155.60649042824</v>
+        <v>46155.439823761575</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.947675324074</v>
+        <v>46195.7810086574</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>228</v>
@@ -7475,11 +7475,11 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.6064993287</v>
+        <v>46155.439832662036</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.947678958335</v>
+        <v>46195.78101229167</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>228</v>
@@ -7526,11 +7526,11 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46155.606507951394</v>
+        <v>46155.43984128472</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.94768271991</v>
+        <v>46195.78101605324</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>228</v>
@@ -7577,11 +7577,11 @@
         <v>302</v>
       </c>
       <c r="B104" s="5">
-        <v>46155.60651716436</v>
+        <v>46155.439850497685</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46195.94768359954</v>
+        <v>46195.78101693287</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>228</v>
@@ -7628,11 +7628,11 @@
         <v>304</v>
       </c>
       <c r="B105" s="8">
-        <v>46155.6221815162</v>
+        <v>46155.45551484954</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46155.63179349537</v>
+        <v>46155.465126828705</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>228</v>
@@ -7679,11 +7679,11 @@
         <v>306</v>
       </c>
       <c r="B106" s="5">
-        <v>46155.60652579861</v>
+        <v>46155.43985913195</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.63455996528</v>
+        <v>46155.46789329861</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>307</v>
@@ -7742,11 +7742,11 @@
         <v>309</v>
       </c>
       <c r="B107" s="8">
-        <v>46155.606533032405</v>
+        <v>46155.43986636574</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46195.94767760417</v>
+        <v>46195.7810109375</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>190</v>
@@ -7793,11 +7793,11 @@
         <v>312</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.60654145833</v>
+        <v>46155.43987479167</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46195.947678344906</v>
+        <v>46195.78101167824</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>190</v>
@@ -7844,11 +7844,11 @@
         <v>313</v>
       </c>
       <c r="B109" s="8">
-        <v>46155.60655399306</v>
+        <v>46155.439887326385</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46195.947675868054</v>
+        <v>46195.78100920139</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>190</v>
@@ -7895,11 +7895,11 @@
         <v>315</v>
       </c>
       <c r="B110" s="5">
-        <v>46155.60656262732</v>
+        <v>46155.43989596065</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46195.947676435186</v>
+        <v>46195.781009768514</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -7946,11 +7946,11 @@
         <v>317</v>
       </c>
       <c r="B111" s="8">
-        <v>46155.63011625</v>
+        <v>46155.46344958333</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46155.63465961805</v>
+        <v>46155.46799295139</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>190</v>
@@ -7997,11 +7997,11 @@
         <v>319</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.60657109953</v>
+        <v>46155.439904432875</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.63577444444</v>
+        <v>46155.46910777778</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>320</v>
@@ -8060,11 +8060,11 @@
         <v>321</v>
       </c>
       <c r="B113" s="8">
-        <v>46155.60657833333</v>
+        <v>46155.43991166667</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46155.635128090275</v>
+        <v>46155.46846142361</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>190</v>
@@ -8113,11 +8113,11 @@
         <v>323</v>
       </c>
       <c r="B114" s="5">
-        <v>46155.60658640046</v>
+        <v>46155.43991973379</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.63525575231</v>
+        <v>46155.46858908565</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>190</v>
@@ -8166,11 +8166,11 @@
         <v>324</v>
       </c>
       <c r="B115" s="8">
-        <v>46155.60659408565</v>
+        <v>46155.43992741898</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46155.635268750004</v>
+        <v>46155.46860208333</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>190</v>
@@ -8219,11 +8219,11 @@
         <v>326</v>
       </c>
       <c r="B116" s="5">
-        <v>46155.60660233797</v>
+        <v>46155.4399356713</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.635292569445</v>
+        <v>46155.46862590278</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8272,11 +8272,11 @@
         <v>327</v>
       </c>
       <c r="B117" s="8">
-        <v>46155.63398136574</v>
+        <v>46155.467314699075</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46155.63581856481</v>
+        <v>46155.46915189815</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>190</v>
@@ -8323,11 +8323,11 @@
         <v>328</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.60664190972</v>
+        <v>46155.439975243055</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.63694791667</v>
+        <v>46155.47028125</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>329</v>
@@ -8386,11 +8386,11 @@
         <v>331</v>
       </c>
       <c r="B119" s="8">
-        <v>46155.60665081019</v>
+        <v>46155.43998414352</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46155.63810030093</v>
+        <v>46155.47143363426</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>190</v>
@@ -8437,11 +8437,11 @@
         <v>333</v>
       </c>
       <c r="B120" s="5">
-        <v>46155.60665825232</v>
+        <v>46155.43999158565</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.6381218287</v>
+        <v>46155.47145516204</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8488,11 +8488,11 @@
         <v>335</v>
       </c>
       <c r="B121" s="8">
-        <v>46155.60666534722</v>
+        <v>46155.43999868055</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46155.63813651621</v>
+        <v>46155.47146984954</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>190</v>
@@ -8539,11 +8539,11 @@
         <v>336</v>
       </c>
       <c r="B122" s="5">
-        <v>46155.60667253472</v>
+        <v>46155.440005868055</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.63815179398</v>
+        <v>46155.47148512732</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8590,11 +8590,11 @@
         <v>337</v>
       </c>
       <c r="B123" s="8">
-        <v>46155.63591585648</v>
+        <v>46155.46924918982</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46155.63817207176</v>
+        <v>46155.47150540509</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>190</v>
@@ -8641,11 +8641,11 @@
         <v>338</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.606679502314</v>
+        <v>46155.44001283565</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.60689462963</v>
+        <v>46155.44022796296</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>339</v>
@@ -8688,11 +8688,11 @@
         <v>341</v>
       </c>
       <c r="B125" s="8">
-        <v>46155.60668334491</v>
+        <v>46155.44001667824</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46155.63803638889</v>
+        <v>46155.47136972222</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>342</v>
@@ -8749,11 +8749,11 @@
         <v>346</v>
       </c>
       <c r="B126" s="5">
-        <v>46155.606691759254</v>
+        <v>46155.4400250926</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.6390279051</v>
+        <v>46155.472361238426</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8800,11 +8800,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="8">
-        <v>46155.60669864583</v>
+        <v>46155.44003197917</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46155.639037835645</v>
+        <v>46155.47237116898</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>190</v>
@@ -8851,11 +8851,11 @@
         <v>349</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.60670615741</v>
+        <v>46155.44003949074</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.639063807874</v>
+        <v>46155.4723971412</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -8902,11 +8902,11 @@
         <v>351</v>
       </c>
       <c r="B129" s="8">
-        <v>46155.606713009256</v>
+        <v>46155.44004634259</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46155.63907559028</v>
+        <v>46155.47240892361</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>190</v>
@@ -8953,11 +8953,11 @@
         <v>352</v>
       </c>
       <c r="B130" s="5">
-        <v>46155.63715556713</v>
+        <v>46155.470488900464</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.63910325231</v>
+        <v>46155.47243658565</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>190</v>
@@ -9004,11 +9004,11 @@
         <v>353</v>
       </c>
       <c r="B131" s="8">
-        <v>46155.60671987268</v>
+        <v>46155.44005320602</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46155.638912615745</v>
+        <v>46155.47224594907</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>354</v>
@@ -9067,11 +9067,11 @@
         <v>355</v>
       </c>
       <c r="B132" s="5">
-        <v>46155.60672658565</v>
+        <v>46155.44005991898</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.639826238425</v>
+        <v>46155.47315957176</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9120,11 +9120,11 @@
         <v>357</v>
       </c>
       <c r="B133" s="8">
-        <v>46155.60673355324</v>
+        <v>46155.44006688657</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46155.63983615741</v>
+        <v>46155.47316949074</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>190</v>
@@ -9173,11 +9173,11 @@
         <v>359</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.60674053241</v>
+        <v>46155.44007386574</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.639844942125</v>
+        <v>46155.47317827547</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9226,11 +9226,11 @@
         <v>360</v>
       </c>
       <c r="B135" s="8">
-        <v>46155.60674741898</v>
+        <v>46155.44008075232</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46155.63986869213</v>
+        <v>46155.47320202546</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>190</v>
@@ -9279,11 +9279,11 @@
         <v>361</v>
       </c>
       <c r="B136" s="5">
-        <v>46155.63830266204</v>
+        <v>46155.471635995375</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.63990003472</v>
+        <v>46155.47323336806</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9330,11 +9330,11 @@
         <v>362</v>
       </c>
       <c r="B137" s="8">
-        <v>46155.60675400463</v>
+        <v>46155.44008733796</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46155.64036164352</v>
+        <v>46155.473694976856</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>363</v>
@@ -9393,11 +9393,11 @@
         <v>364</v>
       </c>
       <c r="B138" s="5">
-        <v>46155.60676105324</v>
+        <v>46155.44009438658</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46155.642618750004</v>
+        <v>46155.47595208333</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9444,11 +9444,11 @@
         <v>366</v>
       </c>
       <c r="B139" s="8">
-        <v>46155.60677012731</v>
+        <v>46155.44010346065</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46155.64263091436</v>
+        <v>46155.475964247686</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>190</v>
@@ -9495,11 +9495,11 @@
         <v>367</v>
       </c>
       <c r="B140" s="5">
-        <v>46155.60681737268</v>
+        <v>46155.44015070602</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46155.64264111111</v>
+        <v>46155.475974444445</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9546,11 +9546,11 @@
         <v>369</v>
       </c>
       <c r="B141" s="8">
-        <v>46155.60682548611</v>
+        <v>46155.440158819445</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46155.64265195602</v>
+        <v>46155.47598528935</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>190</v>
@@ -9597,11 +9597,11 @@
         <v>370</v>
       </c>
       <c r="B142" s="5">
-        <v>46155.63928425926</v>
+        <v>46155.47261759259</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46155.64266835648</v>
+        <v>46155.476001689814</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>190</v>
@@ -9648,11 +9648,11 @@
         <v>371</v>
       </c>
       <c r="B143" s="8">
-        <v>46155.60683229167</v>
+        <v>46155.440165625</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46155.641985821756</v>
+        <v>46155.47531915509</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>372</v>
@@ -9711,11 +9711,11 @@
         <v>374</v>
       </c>
       <c r="B144" s="5">
-        <v>46155.606840486114</v>
+        <v>46155.44017381944</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46155.64207402778</v>
+        <v>46155.47540736111</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9762,11 +9762,11 @@
         <v>375</v>
       </c>
       <c r="B145" s="8">
-        <v>46155.60684746528</v>
+        <v>46155.440180798614</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46155.64208369213</v>
+        <v>46155.47541702546</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>190</v>
@@ -9813,11 +9813,11 @@
         <v>376</v>
       </c>
       <c r="B146" s="5">
-        <v>46155.60685387731</v>
+        <v>46155.44018721065</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46155.64209340278</v>
+        <v>46155.47542673611</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -9864,11 +9864,11 @@
         <v>377</v>
       </c>
       <c r="B147" s="8">
-        <v>46155.60686101852</v>
+        <v>46155.44019435185</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46155.64210719908</v>
+        <v>46155.475440532406</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>190</v>
@@ -9915,11 +9915,11 @@
         <v>378</v>
       </c>
       <c r="B148" s="5">
-        <v>46155.64052775463</v>
+        <v>46155.47386108796</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46155.64213097222</v>
+        <v>46155.47546430556</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>
@@ -9966,11 +9966,11 @@
         <v>379</v>
       </c>
       <c r="B149" s="8">
-        <v>46155.60686797454</v>
+        <v>46155.440201307865</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46155.60689638889</v>
+        <v>46155.440229722226</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>380</v>
@@ -10013,11 +10013,11 @@
         <v>382</v>
       </c>
       <c r="B150" s="5">
-        <v>46155.60687207176</v>
+        <v>46155.44020540509</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46155.60689709491</v>
+        <v>46155.44023042824</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>383</v>
@@ -10076,11 +10076,11 @@
         <v>386</v>
       </c>
       <c r="B151" s="8">
-        <v>46155.606879259256</v>
+        <v>46155.44021259259</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46195.54676386574</v>
+        <v>46195.38009719907</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>387</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -648,6 +648,9 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1214777626772872</t>
   </si>
   <si>
@@ -685,9 +688,6 @@
   </si>
   <si>
     <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214777561702202</t>
@@ -1821,13 +1821,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46155.43894304398</v>
+        <v>46155.60560971065</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70656460648</v>
+        <v>46175.873231273144</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.54677180556</v>
+        <v>46197.71343847222</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1870,13 +1870,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46155.43905862268</v>
+        <v>46155.60572528935</v>
       </c>
       <c r="C5" s="8">
-        <v>46161.45673921297</v>
+        <v>46161.623405879625</v>
       </c>
       <c r="D5" s="8">
-        <v>46161.45675550926</v>
+        <v>46161.62342217592</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1933,13 +1933,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46155.4390644213</v>
+        <v>46155.60573108796</v>
       </c>
       <c r="C6" s="5">
-        <v>46161.456973761575</v>
+        <v>46161.62364042824</v>
       </c>
       <c r="D6" s="5">
-        <v>46161.45699003473</v>
+        <v>46161.623656701384</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1996,13 +1996,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46155.43906950232</v>
+        <v>46155.60573616898</v>
       </c>
       <c r="C7" s="8">
-        <v>46161.45699008102</v>
+        <v>46161.62365674769</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.457162129635</v>
+        <v>46161.62382879629</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2059,13 +2059,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46155.439074548616</v>
+        <v>46155.60574121527</v>
       </c>
       <c r="C8" s="5">
-        <v>46161.45752660879</v>
+        <v>46161.624193275464</v>
       </c>
       <c r="D8" s="5">
-        <v>46161.45754138889</v>
+        <v>46161.62420805555</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2122,13 +2122,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46155.43908016203</v>
+        <v>46155.6057468287</v>
       </c>
       <c r="C9" s="8">
-        <v>46175.706550532406</v>
+        <v>46175.87321719907</v>
       </c>
       <c r="D9" s="8">
-        <v>46175.70656489584</v>
+        <v>46175.873231562495</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2185,13 +2185,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46155.43894832176</v>
+        <v>46155.605614988424</v>
       </c>
       <c r="C10" s="5">
-        <v>46204.74962631945</v>
+        <v>46204.91629298611</v>
       </c>
       <c r="D10" s="5">
-        <v>46204.74964228009</v>
+        <v>46204.91630894676</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2238,13 +2238,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46155.43908570602</v>
+        <v>46155.605752372685</v>
       </c>
       <c r="C11" s="8">
-        <v>46161.45756530092</v>
+        <v>46161.624231967595</v>
       </c>
       <c r="D11" s="8">
-        <v>46195.380097002315</v>
+        <v>46195.54676366899</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2303,13 +2303,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46155.43909342593</v>
+        <v>46155.60576009259</v>
       </c>
       <c r="C12" s="5">
-        <v>46161.457571701394</v>
+        <v>46161.62423836805</v>
       </c>
       <c r="D12" s="5">
-        <v>46195.38009708333</v>
+        <v>46195.54676375</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2368,13 +2368,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46155.43910125</v>
+        <v>46155.60576791667</v>
       </c>
       <c r="C13" s="8">
-        <v>46161.45757961806</v>
+        <v>46161.62424628472</v>
       </c>
       <c r="D13" s="8">
-        <v>46195.38009697916</v>
+        <v>46195.546763645834</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2433,13 +2433,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46155.43895318287</v>
+        <v>46155.605619849535</v>
       </c>
       <c r="C14" s="5">
-        <v>46204.74952644676</v>
+        <v>46204.91619311343</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.749545081024</v>
+        <v>46204.91621174768</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2486,13 +2486,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46155.43911810185</v>
+        <v>46155.605784768515</v>
       </c>
       <c r="C15" s="8">
-        <v>46161.45762405093</v>
+        <v>46161.62429071759</v>
       </c>
       <c r="D15" s="8">
-        <v>46161.45764068287</v>
+        <v>46161.624307349535</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2551,13 +2551,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46155.439125624995</v>
+        <v>46155.605792291666</v>
       </c>
       <c r="C16" s="5">
-        <v>46161.457631875004</v>
+        <v>46161.62429854167</v>
       </c>
       <c r="D16" s="5">
-        <v>46161.45764758102</v>
+        <v>46161.62431424769</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2616,13 +2616,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46155.43913309027</v>
+        <v>46155.605799756944</v>
       </c>
       <c r="C17" s="8">
-        <v>46197.335606354165</v>
+        <v>46197.50227302083</v>
       </c>
       <c r="D17" s="8">
-        <v>46197.33562271991</v>
+        <v>46197.502289386575</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2681,13 +2681,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46155.43914079861</v>
+        <v>46155.60580746528</v>
       </c>
       <c r="C18" s="5">
-        <v>46196.475665659724</v>
+        <v>46196.64233232639</v>
       </c>
       <c r="D18" s="5">
-        <v>46196.47568135417</v>
+        <v>46196.64234802083</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2746,13 +2746,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46155.43914765047</v>
+        <v>46155.605814317125</v>
       </c>
       <c r="C19" s="8">
-        <v>46204.74950489584</v>
+        <v>46204.9161715625</v>
       </c>
       <c r="D19" s="8">
-        <v>46204.74957189815</v>
+        <v>46204.916238564816</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2811,13 +2811,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46155.43915342593</v>
+        <v>46155.60582009259</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.477272476855</v>
+        <v>46196.64393914352</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.47728831018</v>
+        <v>46196.643954976855</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2876,13 +2876,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46155.439158946756</v>
+        <v>46155.60582561343</v>
       </c>
       <c r="C21" s="8">
-        <v>46196.4778984838</v>
+        <v>46196.64456515046</v>
       </c>
       <c r="D21" s="8">
-        <v>46196.47791537037</v>
+        <v>46196.644582037035</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2941,11 +2941,11 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46155.438957962964</v>
+        <v>46155.60562462963</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46182.52708107639</v>
+        <v>46205.6092119213</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2988,13 +2988,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46155.439165104166</v>
+        <v>46155.60583177084</v>
       </c>
       <c r="C23" s="8">
-        <v>46182.51061494213</v>
+        <v>46182.6772816088</v>
       </c>
       <c r="D23" s="8">
-        <v>46182.510626655094</v>
+        <v>46182.67729332176</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -3053,13 +3053,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46155.439172025464</v>
+        <v>46155.60583869213</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.48660795139</v>
+        <v>46182.65327461806</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.48660934028</v>
+        <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -3114,13 +3114,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46155.43917895833</v>
+        <v>46155.605845625</v>
       </c>
       <c r="C25" s="8">
-        <v>46182.51060081019</v>
+        <v>46182.67726747685</v>
       </c>
       <c r="D25" s="8">
-        <v>46182.51060231481</v>
+        <v>46182.67726898148</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -3175,11 +3175,11 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46155.43918560185</v>
+        <v>46155.60585226852</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.02861765046</v>
+        <v>46179.19528431713</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -3238,11 +3238,11 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46155.4391921412</v>
+        <v>46155.605858807874</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46197.33561277778</v>
+        <v>46197.502279444445</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -3297,11 +3297,11 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46155.439198622684</v>
+        <v>46155.605865289355</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.00457575232</v>
+        <v>46178.17124241898</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3356,13 +3356,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46155.43925858796</v>
+        <v>46155.605925254626</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.52707278935</v>
+        <v>46182.69373945602</v>
       </c>
       <c r="D29" s="8">
-        <v>46197.01832081018</v>
+        <v>46197.18498747685</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3421,13 +3421,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46155.439265821755</v>
+        <v>46155.605932488426</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.48641747685</v>
+        <v>46182.653084143516</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.48641987269</v>
+        <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3482,13 +3482,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46155.439272777774</v>
+        <v>46155.605939444446</v>
       </c>
       <c r="C31" s="8">
-        <v>46182.510444328705</v>
+        <v>46182.67711099537</v>
       </c>
       <c r="D31" s="8">
-        <v>46182.51044608797</v>
+        <v>46182.67711275463</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3543,13 +3543,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46155.43927920139</v>
+        <v>46155.605945868054</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.527057245374</v>
+        <v>46182.69372391204</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.52705878472</v>
+        <v>46182.69372545139</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3604,11 +3604,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46155.439285625005</v>
-      </c>
-      <c r="C33" s="9"/>
+        <v>46155.60595229166</v>
+      </c>
+      <c r="C33" s="8">
+        <v>46205.60920104166</v>
+      </c>
       <c r="D33" s="8">
-        <v>46200.03978225694</v>
+        <v>46205.60921498842</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3656,10 +3658,10 @@
         <v>32</v>
       </c>
       <c r="T33" s="9">
-        <v>0</v>
-      </c>
-      <c r="U33" s="10" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3667,13 +3669,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46155.439292118055</v>
+        <v>46155.60595878473</v>
       </c>
       <c r="C34" s="5">
-        <v>46199.39141788194</v>
+        <v>46199.55808454861</v>
       </c>
       <c r="D34" s="5">
-        <v>46199.391643842595</v>
+        <v>46199.55831050926</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3728,11 +3730,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46155.43929873843</v>
-      </c>
-      <c r="C35" s="9"/>
+        <v>46155.60596540509</v>
+      </c>
+      <c r="C35" s="8">
+        <v>46205.609186828704</v>
+      </c>
       <c r="D35" s="8">
-        <v>46199.392116504634</v>
+        <v>46205.609188692135</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3787,11 +3791,13 @@
         <v>137</v>
       </c>
       <c r="B36" s="5">
-        <v>46155.439304942134</v>
-      </c>
-      <c r="C36" s="6"/>
+        <v>46155.60597160879</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46205.60960152777</v>
+      </c>
       <c r="D36" s="5">
-        <v>46200.03978548611</v>
+        <v>46205.60961208333</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>138</v>
@@ -3839,10 +3845,10 @@
         <v>32</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="10" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3850,11 +3856,13 @@
         <v>140</v>
       </c>
       <c r="B37" s="8">
-        <v>46155.439310104164</v>
-      </c>
-      <c r="C37" s="9"/>
+        <v>46155.605976770836</v>
+      </c>
+      <c r="C37" s="8">
+        <v>46205.609531967595</v>
+      </c>
       <c r="D37" s="8">
-        <v>46204.749514745374</v>
+        <v>46205.609533587965</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>81</v>
@@ -3903,11 +3911,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46155.43931646991</v>
-      </c>
-      <c r="C38" s="6"/>
+        <v>46155.60598313657</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46205.60958564815</v>
+      </c>
       <c r="D38" s="5">
-        <v>46199.003345624995</v>
+        <v>46205.60958704861</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3956,13 +3966,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46155.4393222338</v>
+        <v>46155.60598890047</v>
       </c>
       <c r="C39" s="8">
-        <v>46196.52820552084</v>
+        <v>46196.6948721875</v>
       </c>
       <c r="D39" s="8">
-        <v>46196.52822096065</v>
+        <v>46196.694887627316</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -4021,13 +4031,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46155.43932773148</v>
+        <v>46155.60599439815</v>
       </c>
       <c r="C40" s="5">
-        <v>46196.526759444445</v>
+        <v>46196.69342611112</v>
       </c>
       <c r="D40" s="5">
-        <v>46196.52676152778</v>
+        <v>46196.69342819444</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>87</v>
@@ -4076,13 +4086,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46155.43933353009</v>
+        <v>46155.606000196756</v>
       </c>
       <c r="C41" s="8">
-        <v>46196.5268253588</v>
+        <v>46196.693492025464</v>
       </c>
       <c r="D41" s="8">
-        <v>46196.52682753472</v>
+        <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -4131,11 +4141,11 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46155.439339502314</v>
+        <v>46155.60600616898</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.52683537037</v>
+        <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -4184,13 +4194,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46155.43934405093</v>
+        <v>46155.60601071759</v>
       </c>
       <c r="C43" s="8">
-        <v>46199.396591956014</v>
+        <v>46199.563258622686</v>
       </c>
       <c r="D43" s="8">
-        <v>46203.04165353009</v>
+        <v>46203.20832019676</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4249,13 +4259,13 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46155.439347569445</v>
+        <v>46155.60601423611</v>
       </c>
       <c r="C44" s="5">
-        <v>46199.396529375</v>
+        <v>46199.563196041665</v>
       </c>
       <c r="D44" s="5">
-        <v>46199.39653133102</v>
+        <v>46199.56319799769</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>84</v>
@@ -4304,13 +4314,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46155.43935210648</v>
+        <v>46155.60601877315</v>
       </c>
       <c r="C45" s="8">
-        <v>46199.396577685184</v>
+        <v>46199.563244351855</v>
       </c>
       <c r="D45" s="8">
-        <v>46199.39657961806</v>
+        <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4359,11 +4369,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46155.43896273148</v>
+        <v>46155.60562939815</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.54670233796</v>
+        <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4406,13 +4416,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46155.43935697917</v>
+        <v>46155.60602364583</v>
       </c>
       <c r="C47" s="8">
-        <v>46195.78073570602</v>
+        <v>46195.94740237268</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.547605300926</v>
+        <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4471,13 +4481,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46155.43936440972</v>
+        <v>46155.606031076386</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.78093490741</v>
+        <v>46195.94760157407</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.5476644213</v>
+        <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4536,13 +4546,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46155.43937197917</v>
+        <v>46155.606038645834</v>
       </c>
       <c r="C49" s="8">
-        <v>46195.780985000005</v>
+        <v>46195.94765166666</v>
       </c>
       <c r="D49" s="8">
-        <v>46195.781001157404</v>
+        <v>46195.947667824075</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>77</v>
@@ -4599,11 +4609,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46155.439425081015</v>
+        <v>46155.606091747686</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.46824752315</v>
+        <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4662,11 +4672,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="8">
-        <v>46155.439433437496</v>
+        <v>46155.60610010417</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46155.47550032407</v>
+        <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>190</v>
@@ -4713,11 +4723,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46155.43943960648</v>
+        <v>46155.606106273146</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.47551712963</v>
+        <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4764,11 +4774,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46155.43944538194</v>
+        <v>46155.60611204861</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46155.47552612268</v>
+        <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>190</v>
@@ -4815,11 +4825,11 @@
         <v>195</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.439450046295</v>
+        <v>46155.60611671297</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.47553416667</v>
+        <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4866,11 +4876,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="8">
-        <v>46155.46824611111</v>
+        <v>46155.63491277778</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46155.47556417824</v>
+        <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>190</v>
@@ -4917,11 +4927,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46155.439454583335</v>
+        <v>46155.60612125</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.439577083336</v>
+        <v>46155.60624375</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4964,11 +4974,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46155.4394581713</v>
+        <v>46155.60612483796</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46204.02336939815</v>
+        <v>46205.60920457176</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5018,23 +5028,23 @@
       <c r="T57" s="9">
         <v>0</v>
       </c>
-      <c r="U57" s="10" t="s">
-        <v>100</v>
+      <c r="U57" s="12" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46155.43946650463</v>
+        <v>46155.6061331713</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46205.00182856481</v>
+        <v>46205.16849523148</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5064,10 +5074,10 @@
         <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5087,17 +5097,17 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="8">
-        <v>46155.4394747801</v>
+        <v>46155.606141446755</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46204.0233697338</v>
+        <v>46205.6096034838</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -5130,7 +5140,7 @@
         <v>143</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5144,23 +5154,23 @@
       <c r="T59" s="9">
         <v>0</v>
       </c>
-      <c r="U59" s="10" t="s">
-        <v>100</v>
+      <c r="U59" s="12" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
-        <v>46155.43948282408</v>
+        <v>46155.60614949074</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46205.00182502315</v>
+        <v>46205.168491689816</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5190,10 +5200,10 @@
         <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5213,17 +5223,17 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
-        <v>46155.43948965278</v>
+        <v>46155.606156319445</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46205.01169863426</v>
+        <v>46205.178365300926</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5256,7 +5266,7 @@
         <v>166</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5271,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5279,14 +5289,14 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46155.4394972338</v>
+        <v>46155.60616390046</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.441792893515</v>
+        <v>46155.608459560186</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5316,10 +5326,10 @@
         <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5342,11 +5352,11 @@
         <v>220</v>
       </c>
       <c r="B63" s="8">
-        <v>46155.43950415509</v>
+        <v>46155.60617082176</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46155.43977484954</v>
+        <v>46155.6064415162</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>221</v>
@@ -5389,11 +5399,11 @@
         <v>223</v>
       </c>
       <c r="B64" s="5">
-        <v>46155.43950746528</v>
+        <v>46155.60617413194</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.44959052083</v>
+        <v>46155.6162571875</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>224</v>
@@ -5426,7 +5436,7 @@
         <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>221</v>
@@ -5452,11 +5462,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="8">
-        <v>46155.4395159375</v>
+        <v>46155.60618260417</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46155.44072061343</v>
+        <v>46155.60738728009</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5505,11 +5515,11 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.43952439815</v>
+        <v>46155.60619106481</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.450112245366</v>
+        <v>46155.61677891204</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5558,11 +5568,11 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46155.439531689815</v>
+        <v>46155.60619835649</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46155.450133645834</v>
+        <v>46155.6168003125</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -5611,11 +5621,11 @@
         <v>235</v>
       </c>
       <c r="B68" s="5">
-        <v>46155.43953877315</v>
+        <v>46155.60620543981</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.45016523148</v>
+        <v>46155.61683189815</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5664,11 +5674,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="8">
-        <v>46155.44078685185</v>
+        <v>46155.60745351852</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46155.45072724537</v>
+        <v>46155.617393912034</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>228</v>
@@ -5717,11 +5727,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46155.43954597222</v>
+        <v>46155.606212638886</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.45109189815</v>
+        <v>46155.61775856481</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>238</v>
@@ -5754,7 +5764,7 @@
         <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>221</v>
@@ -5780,11 +5790,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46155.43955232639</v>
+        <v>46155.60621899305</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.78101641204</v>
+        <v>46195.9476830787</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>228</v>
@@ -5833,11 +5843,11 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.439559872684</v>
+        <v>46155.606226539356</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.78100614583</v>
+        <v>46195.9476728125</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5886,11 +5896,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46155.43956733796</v>
+        <v>46155.606234004634</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.78101032408</v>
+        <v>46195.94767699074</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>228</v>
@@ -5939,11 +5949,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46155.4396175463</v>
+        <v>46155.60628421296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.781012997686</v>
+        <v>46195.94767966435</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>228</v>
@@ -5992,11 +6002,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46155.441023368054</v>
+        <v>46155.607690034725</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46155.45271111111</v>
+        <v>46155.61937777778</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>228</v>
@@ -6045,11 +6055,11 @@
         <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.43962524306</v>
+        <v>46155.606291909724</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.45244517361</v>
+        <v>46155.61911184028</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>248</v>
@@ -6082,7 +6092,7 @@
         <v>221</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>221</v>
@@ -6108,11 +6118,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="8">
-        <v>46155.43963217593</v>
+        <v>46155.60629884259</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.78100685185</v>
+        <v>46195.947673518516</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>228</v>
@@ -6161,11 +6171,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46155.43963956018</v>
+        <v>46155.60630622685</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.78100746528</v>
+        <v>46195.947674131945</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>228</v>
@@ -6214,11 +6224,11 @@
         <v>252</v>
       </c>
       <c r="B79" s="8">
-        <v>46155.43964677083</v>
+        <v>46155.6063134375</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.78101372685</v>
+        <v>46195.94768039352</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>228</v>
@@ -6267,11 +6277,11 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46155.43965305555</v>
+        <v>46155.606319722225</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.78101423611</v>
+        <v>46195.94768090278</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>228</v>
@@ -6320,11 +6330,11 @@
         <v>255</v>
       </c>
       <c r="B81" s="8">
-        <v>46155.45165628473</v>
+        <v>46155.618322951384</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46155.45406971065</v>
+        <v>46155.620736377314</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>228</v>
@@ -6371,11 +6381,11 @@
         <v>256</v>
       </c>
       <c r="B82" s="5">
-        <v>46155.43965876158</v>
+        <v>46155.60632542824</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.43977684028</v>
+        <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>198</v>
@@ -6418,11 +6428,11 @@
         <v>258</v>
       </c>
       <c r="B83" s="8">
-        <v>46155.43966201389</v>
+        <v>46155.60632868056</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46182.03281046296</v>
+        <v>46182.19947712963</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>259</v>
@@ -6479,11 +6489,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46155.439669837964</v>
+        <v>46155.60633650463</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.51061935185</v>
+        <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>262</v>
@@ -6534,7 +6544,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6542,11 +6552,11 @@
         <v>264</v>
       </c>
       <c r="B85" s="8">
-        <v>46155.43967736111</v>
+        <v>46155.60634402778</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46198.01583942129</v>
+        <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>265</v>
@@ -6597,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6605,11 +6615,11 @@
         <v>267</v>
       </c>
       <c r="B86" s="5">
-        <v>46155.43968510417</v>
+        <v>46155.60635177083</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46196.52684989583</v>
+        <v>46196.693516562504</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>268</v>
@@ -6660,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6668,11 +6678,11 @@
         <v>270</v>
       </c>
       <c r="B87" s="8">
-        <v>46155.43969525463</v>
+        <v>46155.606361921295</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46155.4401133912</v>
+        <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>271</v>
@@ -6715,11 +6725,11 @@
         <v>273</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.43969858796</v>
+        <v>46155.60636525463</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.45368895833</v>
+        <v>46155.620355625</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>274</v>
@@ -6778,11 +6788,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="8">
-        <v>46155.43970785879</v>
+        <v>46155.606374525465</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.454952835644</v>
+        <v>46155.621619502315</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>228</v>
@@ -6831,11 +6841,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46155.43971361111</v>
+        <v>46155.60638027778</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.454969363425</v>
+        <v>46155.62163603009</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>228</v>
@@ -6884,11 +6894,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46155.439719166665</v>
+        <v>46155.60638583334</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46155.45499407407</v>
+        <v>46155.62166074074</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>228</v>
@@ -6937,11 +6947,11 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.43972512732</v>
+        <v>46155.60639179398</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.45500732639</v>
+        <v>46155.62167399305</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>228</v>
@@ -6990,11 +7000,11 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46155.45309319445</v>
+        <v>46155.61975986111</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46155.45502841435</v>
+        <v>46155.62169508102</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>228</v>
@@ -7043,11 +7053,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46155.43973116898</v>
+        <v>46155.60639783565</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.455249189814</v>
+        <v>46155.62191585648</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -7080,7 +7090,7 @@
         <v>271</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>271</v>
@@ -7106,11 +7116,11 @@
         <v>286</v>
       </c>
       <c r="B95" s="8">
-        <v>46155.439737361114</v>
+        <v>46155.60640402778</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.78101460648</v>
+        <v>46195.947681273145</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>228</v>
@@ -7157,11 +7167,11 @@
         <v>289</v>
       </c>
       <c r="B96" s="5">
-        <v>46155.43974423611</v>
+        <v>46155.60641090278</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.781015162036</v>
+        <v>46195.94768182871</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>228</v>
@@ -7208,11 +7218,11 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46155.4397509375</v>
+        <v>46155.60641760417</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.781015659726</v>
+        <v>46195.94768232639</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>228</v>
@@ -7259,11 +7269,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.43975982639</v>
+        <v>46155.60642649306</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.78100797454</v>
+        <v>46195.947674641204</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>228</v>
@@ -7310,11 +7320,11 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46155.45449280093</v>
+        <v>46155.62115946759</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46155.47573361111</v>
+        <v>46155.64240027778</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>228</v>
@@ -7361,11 +7371,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46155.43981565972</v>
+        <v>46155.60648232639</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.4650037963</v>
+        <v>46155.631670462964</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7398,7 +7408,7 @@
         <v>271</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>271</v>
@@ -7424,11 +7434,11 @@
         <v>297</v>
       </c>
       <c r="B101" s="8">
-        <v>46155.439823761575</v>
+        <v>46155.60649042824</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.7810086574</v>
+        <v>46195.947675324074</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>228</v>
@@ -7475,11 +7485,11 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.439832662036</v>
+        <v>46155.6064993287</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.78101229167</v>
+        <v>46195.947678958335</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>228</v>
@@ -7526,11 +7536,11 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46155.43984128472</v>
+        <v>46155.606507951394</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.78101605324</v>
+        <v>46195.94768271991</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>228</v>
@@ -7577,11 +7587,11 @@
         <v>302</v>
       </c>
       <c r="B104" s="5">
-        <v>46155.439850497685</v>
+        <v>46155.60651716436</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46195.78101693287</v>
+        <v>46195.94768359954</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>228</v>
@@ -7628,11 +7638,11 @@
         <v>304</v>
       </c>
       <c r="B105" s="8">
-        <v>46155.45551484954</v>
+        <v>46155.6221815162</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46155.465126828705</v>
+        <v>46155.63179349537</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>228</v>
@@ -7679,11 +7689,11 @@
         <v>306</v>
       </c>
       <c r="B106" s="5">
-        <v>46155.43985913195</v>
+        <v>46155.60652579861</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.46789329861</v>
+        <v>46155.63455996528</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>307</v>
@@ -7742,11 +7752,11 @@
         <v>309</v>
       </c>
       <c r="B107" s="8">
-        <v>46155.43986636574</v>
+        <v>46155.606533032405</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46195.7810109375</v>
+        <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>190</v>
@@ -7793,11 +7803,11 @@
         <v>312</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.43987479167</v>
+        <v>46155.60654145833</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46195.78101167824</v>
+        <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>190</v>
@@ -7844,11 +7854,11 @@
         <v>313</v>
       </c>
       <c r="B109" s="8">
-        <v>46155.439887326385</v>
+        <v>46155.60655399306</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46195.78100920139</v>
+        <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>190</v>
@@ -7895,11 +7905,11 @@
         <v>315</v>
       </c>
       <c r="B110" s="5">
-        <v>46155.43989596065</v>
+        <v>46155.60656262732</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46195.781009768514</v>
+        <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -7946,11 +7956,11 @@
         <v>317</v>
       </c>
       <c r="B111" s="8">
-        <v>46155.46344958333</v>
+        <v>46155.63011625</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46155.46799295139</v>
+        <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>190</v>
@@ -7997,11 +8007,11 @@
         <v>319</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.439904432875</v>
+        <v>46155.60657109953</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.46910777778</v>
+        <v>46155.63577444444</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>320</v>
@@ -8060,11 +8070,11 @@
         <v>321</v>
       </c>
       <c r="B113" s="8">
-        <v>46155.43991166667</v>
+        <v>46155.60657833333</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46155.46846142361</v>
+        <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>190</v>
@@ -8113,11 +8123,11 @@
         <v>323</v>
       </c>
       <c r="B114" s="5">
-        <v>46155.43991973379</v>
+        <v>46155.60658640046</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.46858908565</v>
+        <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>190</v>
@@ -8166,11 +8176,11 @@
         <v>324</v>
       </c>
       <c r="B115" s="8">
-        <v>46155.43992741898</v>
+        <v>46155.60659408565</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46155.46860208333</v>
+        <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>190</v>
@@ -8219,11 +8229,11 @@
         <v>326</v>
       </c>
       <c r="B116" s="5">
-        <v>46155.4399356713</v>
+        <v>46155.60660233797</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.46862590278</v>
+        <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8272,11 +8282,11 @@
         <v>327</v>
       </c>
       <c r="B117" s="8">
-        <v>46155.467314699075</v>
+        <v>46155.63398136574</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46155.46915189815</v>
+        <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>190</v>
@@ -8323,11 +8333,11 @@
         <v>328</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.439975243055</v>
+        <v>46155.60664190972</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.47028125</v>
+        <v>46155.63694791667</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>329</v>
@@ -8386,11 +8396,11 @@
         <v>331</v>
       </c>
       <c r="B119" s="8">
-        <v>46155.43998414352</v>
+        <v>46155.60665081019</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46155.47143363426</v>
+        <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>190</v>
@@ -8437,11 +8447,11 @@
         <v>333</v>
       </c>
       <c r="B120" s="5">
-        <v>46155.43999158565</v>
+        <v>46155.60665825232</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.47145516204</v>
+        <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8488,11 +8498,11 @@
         <v>335</v>
       </c>
       <c r="B121" s="8">
-        <v>46155.43999868055</v>
+        <v>46155.60666534722</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46155.47146984954</v>
+        <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>190</v>
@@ -8539,11 +8549,11 @@
         <v>336</v>
       </c>
       <c r="B122" s="5">
-        <v>46155.440005868055</v>
+        <v>46155.60667253472</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.47148512732</v>
+        <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8590,11 +8600,11 @@
         <v>337</v>
       </c>
       <c r="B123" s="8">
-        <v>46155.46924918982</v>
+        <v>46155.63591585648</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46155.47150540509</v>
+        <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>190</v>
@@ -8641,11 +8651,11 @@
         <v>338</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.44001283565</v>
+        <v>46155.606679502314</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.44022796296</v>
+        <v>46155.60689462963</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>339</v>
@@ -8688,11 +8698,11 @@
         <v>341</v>
       </c>
       <c r="B125" s="8">
-        <v>46155.44001667824</v>
+        <v>46155.60668334491</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46155.47136972222</v>
+        <v>46155.63803638889</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>342</v>
@@ -8749,11 +8759,11 @@
         <v>346</v>
       </c>
       <c r="B126" s="5">
-        <v>46155.4400250926</v>
+        <v>46155.606691759254</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.472361238426</v>
+        <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8800,11 +8810,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="8">
-        <v>46155.44003197917</v>
+        <v>46155.60669864583</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46155.47237116898</v>
+        <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>190</v>
@@ -8851,11 +8861,11 @@
         <v>349</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.44003949074</v>
+        <v>46155.60670615741</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.4723971412</v>
+        <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -8902,11 +8912,11 @@
         <v>351</v>
       </c>
       <c r="B129" s="8">
-        <v>46155.44004634259</v>
+        <v>46155.606713009256</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46155.47240892361</v>
+        <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>190</v>
@@ -8953,11 +8963,11 @@
         <v>352</v>
       </c>
       <c r="B130" s="5">
-        <v>46155.470488900464</v>
+        <v>46155.63715556713</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.47243658565</v>
+        <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>190</v>
@@ -9004,11 +9014,11 @@
         <v>353</v>
       </c>
       <c r="B131" s="8">
-        <v>46155.44005320602</v>
+        <v>46155.60671987268</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46155.47224594907</v>
+        <v>46155.638912615745</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>354</v>
@@ -9067,11 +9077,11 @@
         <v>355</v>
       </c>
       <c r="B132" s="5">
-        <v>46155.44005991898</v>
+        <v>46155.60672658565</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.47315957176</v>
+        <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9120,11 +9130,11 @@
         <v>357</v>
       </c>
       <c r="B133" s="8">
-        <v>46155.44006688657</v>
+        <v>46155.60673355324</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46155.47316949074</v>
+        <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>190</v>
@@ -9173,11 +9183,11 @@
         <v>359</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.44007386574</v>
+        <v>46155.60674053241</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.47317827547</v>
+        <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9226,11 +9236,11 @@
         <v>360</v>
       </c>
       <c r="B135" s="8">
-        <v>46155.44008075232</v>
+        <v>46155.60674741898</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46155.47320202546</v>
+        <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>190</v>
@@ -9279,11 +9289,11 @@
         <v>361</v>
       </c>
       <c r="B136" s="5">
-        <v>46155.471635995375</v>
+        <v>46155.63830266204</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.47323336806</v>
+        <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9330,11 +9340,11 @@
         <v>362</v>
       </c>
       <c r="B137" s="8">
-        <v>46155.44008733796</v>
+        <v>46155.60675400463</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46155.473694976856</v>
+        <v>46155.64036164352</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>363</v>
@@ -9393,11 +9403,11 @@
         <v>364</v>
       </c>
       <c r="B138" s="5">
-        <v>46155.44009438658</v>
+        <v>46155.60676105324</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46155.47595208333</v>
+        <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9444,11 +9454,11 @@
         <v>366</v>
       </c>
       <c r="B139" s="8">
-        <v>46155.44010346065</v>
+        <v>46155.60677012731</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46155.475964247686</v>
+        <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>190</v>
@@ -9495,11 +9505,11 @@
         <v>367</v>
       </c>
       <c r="B140" s="5">
-        <v>46155.44015070602</v>
+        <v>46155.60681737268</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46155.475974444445</v>
+        <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9546,11 +9556,11 @@
         <v>369</v>
       </c>
       <c r="B141" s="8">
-        <v>46155.440158819445</v>
+        <v>46155.60682548611</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46155.47598528935</v>
+        <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>190</v>
@@ -9597,11 +9607,11 @@
         <v>370</v>
       </c>
       <c r="B142" s="5">
-        <v>46155.47261759259</v>
+        <v>46155.63928425926</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46155.476001689814</v>
+        <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>190</v>
@@ -9648,11 +9658,11 @@
         <v>371</v>
       </c>
       <c r="B143" s="8">
-        <v>46155.440165625</v>
+        <v>46155.60683229167</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46155.47531915509</v>
+        <v>46155.641985821756</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>372</v>
@@ -9711,11 +9721,11 @@
         <v>374</v>
       </c>
       <c r="B144" s="5">
-        <v>46155.44017381944</v>
+        <v>46155.606840486114</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46155.47540736111</v>
+        <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9762,11 +9772,11 @@
         <v>375</v>
       </c>
       <c r="B145" s="8">
-        <v>46155.440180798614</v>
+        <v>46155.60684746528</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46155.47541702546</v>
+        <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>190</v>
@@ -9813,11 +9823,11 @@
         <v>376</v>
       </c>
       <c r="B146" s="5">
-        <v>46155.44018721065</v>
+        <v>46155.60685387731</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46155.47542673611</v>
+        <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -9864,11 +9874,11 @@
         <v>377</v>
       </c>
       <c r="B147" s="8">
-        <v>46155.44019435185</v>
+        <v>46155.60686101852</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46155.475440532406</v>
+        <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>190</v>
@@ -9915,11 +9925,11 @@
         <v>378</v>
       </c>
       <c r="B148" s="5">
-        <v>46155.47386108796</v>
+        <v>46155.64052775463</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46155.47546430556</v>
+        <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>
@@ -9966,11 +9976,11 @@
         <v>379</v>
       </c>
       <c r="B149" s="8">
-        <v>46155.440201307865</v>
+        <v>46155.60686797454</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46155.440229722226</v>
+        <v>46155.60689638889</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>380</v>
@@ -10013,11 +10023,11 @@
         <v>382</v>
       </c>
       <c r="B150" s="5">
-        <v>46155.44020540509</v>
+        <v>46155.60687207176</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46155.44023042824</v>
+        <v>46155.60689709491</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>383</v>
@@ -10076,11 +10086,11 @@
         <v>386</v>
       </c>
       <c r="B151" s="8">
-        <v>46155.44021259259</v>
+        <v>46155.606879259256</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46195.38009719907</v>
+        <v>46195.54676386574</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>387</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -2687,7 +2687,7 @@
         <v>46196.64233232639</v>
       </c>
       <c r="D18" s="5">
-        <v>46196.64234802083</v>
+        <v>46206.56478702546</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2752,7 +2752,7 @@
         <v>46204.9161715625</v>
       </c>
       <c r="D19" s="8">
-        <v>46204.916238564816</v>
+        <v>46206.564361412034</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2817,7 +2817,7 @@
         <v>46196.64393914352</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.643954976855</v>
+        <v>46206.564197789354</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2882,7 +2882,7 @@
         <v>46196.64456515046</v>
       </c>
       <c r="D21" s="8">
-        <v>46196.644582037035</v>
+        <v>46206.56396623843</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.608459560186</v>
+        <v>46209.1697228125</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5337,8 +5337,8 @@
       <c r="R62" s="5">
         <v>46216</v>
       </c>
-      <c r="S62" s="11" t="s">
-        <v>99</v>
+      <c r="S62" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.60624375</v>
+        <v>46209.63604493055</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -5039,9 +5039,11 @@
       <c r="B58" s="5">
         <v>46155.6061331713</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46209.63603707176</v>
+      </c>
       <c r="D58" s="5">
-        <v>46205.16849523148</v>
+        <v>46209.63605303241</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>207</v>
@@ -5089,10 +5091,10 @@
         <v>32</v>
       </c>
       <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="10" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U58" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5356,7 +5358,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46155.6064415162</v>
+        <v>46209.636648750005</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>221</v>
@@ -5466,7 +5468,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46155.60738728009</v>
+        <v>46209.636044467596</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5519,7 +5521,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.61677891204</v>
+        <v>46209.63604388889</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5572,7 +5574,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46155.6168003125</v>
+        <v>46209.63604545139</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -5625,7 +5627,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.61683189815</v>
+        <v>46209.63604590278</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5678,7 +5680,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46155.617393912034</v>
+        <v>46209.636043402774</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>228</v>
@@ -5729,9 +5731,11 @@
       <c r="B70" s="5">
         <v>46155.606212638886</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46209.63664067129</v>
+      </c>
       <c r="D70" s="5">
-        <v>46155.61775856481</v>
+        <v>46209.636658483796</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>238</v>
@@ -5779,10 +5783,10 @@
         <v>99</v>
       </c>
       <c r="T70" s="6">
-        <v>0</v>
-      </c>
-      <c r="U70" s="10" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U70" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -6057,9 +6061,11 @@
       <c r="B76" s="5">
         <v>46155.606291909724</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46209.635949918986</v>
+      </c>
       <c r="D76" s="5">
-        <v>46155.61911184028</v>
+        <v>46209.635966145834</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>248</v>
@@ -6107,10 +6113,10 @@
         <v>99</v>
       </c>
       <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="10" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U76" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -519,175 +519,175 @@
     <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
   </si>
   <si>
+    <t>1214777561549676</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1214777626638198</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1214739697907733</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214777626638213</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214777594225816</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4316</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214777594236456</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4316,propuesta Corte Laser OT 4316,Propuesta Corte plasma OT 4316,Propuesta Mecanizado OT 4316,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777293059955</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777293059971</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>check pruebas FAT, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777626730373</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214777626730389</t>
+  </si>
+  <si>
+    <t>1214777626758296</t>
+  </si>
+  <si>
+    <t>1214739697907775</t>
+  </si>
+  <si>
+    <t>1214777626758308</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1214777626758318</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1214777626772872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777594376340</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214777561694352</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777561694373</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777561549676</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1214777626638198</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1214739697907733</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214777626638213</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214777594225816</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4316</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214777594236456</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4316,propuesta Corte Laser OT 4316,Propuesta Corte plasma OT 4316,Propuesta Mecanizado OT 4316,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777293059955</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777293059971</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>check pruebas FAT, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777626730373</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214777626730389</t>
-  </si>
-  <si>
-    <t>1214777626758296</t>
-  </si>
-  <si>
-    <t>1214739697907775</t>
-  </si>
-  <si>
-    <t>1214777626758308</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1214777626758318</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214777626772872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777594376340</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214777561694352</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777561694373</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
   </si>
   <si>
     <t>1214777561702202</t>
@@ -4200,7 +4200,7 @@
         <v>46199.563258622686</v>
       </c>
       <c r="D43" s="8">
-        <v>46203.20832019676</v>
+        <v>46211.1922662963</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4244,8 +4244,8 @@
       <c r="R43" s="8">
         <v>46210</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>162</v>
+      <c r="S43" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4301,7 +4301,7 @@
         <v>83</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4323,7 +4323,7 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4356,7 +4356,7 @@
         <v>84</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4376,7 +4376,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4400,7 +4400,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4413,7 +4413,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4425,16 +4425,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4452,13 +4452,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>58</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4490,16 +4490,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4517,13 +4517,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4543,7 +4543,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4561,10 +4561,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>181</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>182</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4580,13 +4580,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4616,16 +4616,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4643,10 +4643,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4679,16 +4679,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4704,13 +4704,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O51" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4720,7 +4720,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4730,16 +4730,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4755,13 +4755,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4771,7 +4771,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4781,16 +4781,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4806,13 +4806,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4832,16 +4832,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4857,13 +4857,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4883,16 +4883,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4908,13 +4908,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4934,7 +4934,7 @@
         <v>46209.63604493055</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4958,7 +4958,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4971,7 +4971,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4981,16 +4981,16 @@
         <v>46205.60920457176</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5008,13 +5008,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>134</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5029,12 +5029,12 @@
         <v>0</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5046,7 +5046,7 @@
         <v>46209.63605303241</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5073,13 +5073,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5099,7 +5099,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5109,16 +5109,16 @@
         <v>46205.6096034838</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5136,13 +5136,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>143</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5157,12 +5157,12 @@
         <v>0</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5172,7 +5172,7 @@
         <v>46205.168491689816</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5199,13 +5199,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
@@ -5235,16 +5235,16 @@
         <v>46205.178365300926</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5262,13 +5262,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5277,13 +5277,13 @@
         <v>46212</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="T61" s="9">
         <v>0</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5298,7 +5298,7 @@
         <v>46209.1697228125</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5325,13 +5325,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5340,7 +5340,7 @@
         <v>46216</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5438,7 +5438,7 @@
         <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>221</v>
@@ -5768,7 +5768,7 @@
         <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>221</v>
@@ -6098,7 +6098,7 @@
         <v>221</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>221</v>
@@ -6394,7 +6394,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6447,10 +6447,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6466,7 +6466,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>111</v>
@@ -6508,10 +6508,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6529,7 +6529,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>102</v>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6571,10 +6571,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6592,7 +6592,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>120</v>
@@ -6613,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6634,10 +6634,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6655,7 +6655,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>153</v>
@@ -6676,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -7096,7 +7096,7 @@
         <v>271</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>271</v>
@@ -7414,7 +7414,7 @@
         <v>271</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>271</v>
@@ -7765,7 +7765,7 @@
         <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7816,7 +7816,7 @@
         <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7867,7 +7867,7 @@
         <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7918,7 +7918,7 @@
         <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7969,7 +7969,7 @@
         <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8083,7 +8083,7 @@
         <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8113,7 +8113,7 @@
         <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>322</v>
@@ -8136,7 +8136,7 @@
         <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8166,7 +8166,7 @@
         <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>322</v>
@@ -8189,7 +8189,7 @@
         <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8242,7 +8242,7 @@
         <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8295,7 +8295,7 @@
         <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8323,7 +8323,7 @@
         <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>322</v>
@@ -8409,7 +8409,7 @@
         <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8437,7 +8437,7 @@
         <v>329</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>332</v>
@@ -8460,7 +8460,7 @@
         <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8488,7 +8488,7 @@
         <v>329</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>334</v>
@@ -8511,7 +8511,7 @@
         <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8539,7 +8539,7 @@
         <v>329</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>332</v>
@@ -8562,7 +8562,7 @@
         <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8590,7 +8590,7 @@
         <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>334</v>
@@ -8613,7 +8613,7 @@
         <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8641,7 +8641,7 @@
         <v>329</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>334</v>
@@ -8772,7 +8772,7 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8800,7 +8800,7 @@
         <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>347</v>
@@ -8823,7 +8823,7 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8851,7 +8851,7 @@
         <v>342</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>347</v>
@@ -8874,7 +8874,7 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8902,7 +8902,7 @@
         <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>350</v>
@@ -8925,7 +8925,7 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -8953,7 +8953,7 @@
         <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>347</v>
@@ -8976,7 +8976,7 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9004,7 +9004,7 @@
         <v>342</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>347</v>
@@ -9090,7 +9090,7 @@
         <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9120,7 +9120,7 @@
         <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>356</v>
@@ -9143,7 +9143,7 @@
         <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9173,7 +9173,7 @@
         <v>354</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>358</v>
@@ -9196,7 +9196,7 @@
         <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9226,7 +9226,7 @@
         <v>354</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>356</v>
@@ -9249,7 +9249,7 @@
         <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9279,7 +9279,7 @@
         <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>358</v>
@@ -9302,7 +9302,7 @@
         <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9330,7 +9330,7 @@
         <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>356</v>
@@ -9416,7 +9416,7 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9444,7 +9444,7 @@
         <v>363</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>365</v>
@@ -9467,7 +9467,7 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9495,7 +9495,7 @@
         <v>363</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>365</v>
@@ -9518,7 +9518,7 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9546,7 +9546,7 @@
         <v>363</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>368</v>
@@ -9569,7 +9569,7 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9597,7 +9597,7 @@
         <v>363</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>368</v>
@@ -9620,7 +9620,7 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9648,7 +9648,7 @@
         <v>363</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>368</v>
@@ -9734,7 +9734,7 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9762,7 +9762,7 @@
         <v>372</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>372</v>
@@ -9785,7 +9785,7 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -9813,7 +9813,7 @@
         <v>372</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>372</v>
@@ -9836,7 +9836,7 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -9864,7 +9864,7 @@
         <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>372</v>
@@ -9887,7 +9887,7 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -9915,7 +9915,7 @@
         <v>372</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>372</v>
@@ -9938,7 +9938,7 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -9966,7 +9966,7 @@
         <v>372</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>372</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46205.178365300926</v>
+        <v>46212.16840913195</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.6162571875</v>
+        <v>46212.19508587963</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>224</v>
@@ -5449,8 +5449,8 @@
       <c r="R64" s="5">
         <v>46219</v>
       </c>
-      <c r="S64" s="11" t="s">
-        <v>99</v>
+      <c r="S64" s="12" t="s">
+        <v>218</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="388">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -630,6 +630,9 @@
     <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1214777626758318</t>
   </si>
   <si>
@@ -643,9 +646,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214777626772872</t>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46209.63604493055</v>
+        <v>46212.88596806713</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -4967,30 +4967,34 @@
       <c r="R56" s="6"/>
       <c r="S56" s="6"/>
       <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
+      <c r="U56" s="12" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46212.8859408912</v>
+      </c>
       <c r="D57" s="8">
-        <v>46205.60920457176</v>
+        <v>46212.88596140046</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5014,7 +5018,7 @@
         <v>134</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5026,10 +5030,10 @@
         <v>32</v>
       </c>
       <c r="T57" s="9">
-        <v>0</v>
-      </c>
-      <c r="U57" s="12" t="s">
-        <v>204</v>
+        <v>1</v>
+      </c>
+      <c r="U57" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5043,7 +5047,7 @@
         <v>46209.63603707176</v>
       </c>
       <c r="D58" s="5">
-        <v>46209.63605303241</v>
+        <v>46212.88595888889</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>206</v>
@@ -5115,10 +5119,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5157,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5230,9 +5234,11 @@
       <c r="B61" s="8">
         <v>46155.606156319445</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="8">
+        <v>46212.886193530096</v>
+      </c>
       <c r="D61" s="8">
-        <v>46212.16840913195</v>
+        <v>46212.88631315972</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5241,10 +5247,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5280,10 +5286,10 @@
         <v>218</v>
       </c>
       <c r="T61" s="9">
-        <v>0</v>
-      </c>
-      <c r="U61" s="12" t="s">
-        <v>204</v>
+        <v>1</v>
+      </c>
+      <c r="U61" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5293,9 +5299,11 @@
       <c r="B62" s="5">
         <v>46155.60616390046</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46212.886227650466</v>
+      </c>
       <c r="D62" s="5">
-        <v>46209.1697228125</v>
+        <v>46212.8864002662</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>217</v>
@@ -5343,10 +5351,10 @@
         <v>218</v>
       </c>
       <c r="T62" s="6">
-        <v>0</v>
-      </c>
-      <c r="U62" s="10" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U62" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5468,7 +5476,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46209.636044467596</v>
+        <v>46212.88623596064</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5521,7 +5529,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46209.63604388889</v>
+        <v>46212.88623552083</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5574,7 +5582,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46209.63604545139</v>
+        <v>46212.88623635417</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -5627,7 +5635,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46209.63604590278</v>
+        <v>46212.88623675926</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5680,7 +5688,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46209.636043402774</v>
+        <v>46212.886234907404</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>228</v>
@@ -6447,10 +6455,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6508,10 +6516,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6550,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6571,10 +6579,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6613,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6634,10 +6642,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6676,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -630,36 +630,36 @@
     <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
   </si>
   <si>
+    <t>1214777626758318</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214777626772872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1214777626758318</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214777626772872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
     <t>1214777594376340</t>
   </si>
   <si>
@@ -687,10 +687,10 @@
     <t>Control de calidad Mecanizado</t>
   </si>
   <si>
+    <t>1214777561702202</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777561702202</t>
   </si>
   <si>
     <t>1214777561721939</t>
@@ -3972,7 +3972,7 @@
         <v>46196.6948721875</v>
       </c>
       <c r="D39" s="8">
-        <v>46196.694887627316</v>
+        <v>46213.50701678241</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -4929,9 +4929,11 @@
       <c r="B56" s="5">
         <v>46155.60612125</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46213.50627616898</v>
+      </c>
       <c r="D56" s="5">
-        <v>46212.88596806713</v>
+        <v>46213.506286655094</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -4966,14 +4968,16 @@
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
       <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="12" t="s">
-        <v>199</v>
+      <c r="T56" s="6">
+        <v>1</v>
+      </c>
+      <c r="U56" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4985,16 +4989,16 @@
         <v>46212.88596140046</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5018,7 +5022,7 @@
         <v>134</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5038,7 +5042,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5047,10 +5051,10 @@
         <v>46209.63603707176</v>
       </c>
       <c r="D58" s="5">
-        <v>46212.88595888889</v>
+        <v>46213.50624159722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5080,10 +5084,10 @@
         <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5097,8 +5101,8 @@
       <c r="T58" s="6">
         <v>1</v>
       </c>
-      <c r="U58" s="11" t="s">
-        <v>33</v>
+      <c r="U58" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5108,9 +5112,11 @@
       <c r="B59" s="8">
         <v>46155.606141446755</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46213.50622202546</v>
+      </c>
       <c r="D59" s="8">
-        <v>46205.6096034838</v>
+        <v>46213.50624155093</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>210</v>
@@ -5119,10 +5125,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5158,10 +5164,10 @@
         <v>32</v>
       </c>
       <c r="T59" s="9">
-        <v>0</v>
-      </c>
-      <c r="U59" s="12" t="s">
-        <v>199</v>
+        <v>1</v>
+      </c>
+      <c r="U59" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5171,9 +5177,11 @@
       <c r="B60" s="5">
         <v>46155.60614949074</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46213.50626199074</v>
+      </c>
       <c r="D60" s="5">
-        <v>46205.168491689816</v>
+        <v>46213.506277974535</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5221,10 +5229,10 @@
         <v>32</v>
       </c>
       <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="10" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U60" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5238,7 +5246,7 @@
         <v>46212.886193530096</v>
       </c>
       <c r="D61" s="8">
-        <v>46212.88631315972</v>
+        <v>46213.17611152778</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5247,10 +5255,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5282,8 +5290,8 @@
       <c r="R61" s="8">
         <v>46212</v>
       </c>
-      <c r="S61" s="12" t="s">
-        <v>218</v>
+      <c r="S61" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T61" s="9">
         <v>1</v>
@@ -5294,7 +5302,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46155.60616390046</v>
@@ -5348,7 +5356,7 @@
         <v>46216</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5366,7 +5374,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46209.636648750005</v>
+        <v>46213.50618732639</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>221</v>
@@ -5458,7 +5466,7 @@
         <v>46219</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5476,7 +5484,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46212.88623596064</v>
+        <v>46213.50627252315</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5529,7 +5537,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46212.88623552083</v>
+        <v>46213.50627136574</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5582,7 +5590,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46212.88623635417</v>
+        <v>46213.50627376157</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -5635,7 +5643,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46212.88623675926</v>
+        <v>46213.506274942134</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5688,7 +5696,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46212.886234907404</v>
+        <v>46213.506269942125</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>228</v>
@@ -5739,11 +5747,9 @@
       <c r="B70" s="5">
         <v>46155.606212638886</v>
       </c>
-      <c r="C70" s="5">
-        <v>46209.63664067129</v>
-      </c>
+      <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46209.636658483796</v>
+        <v>46213.506173333335</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>238</v>
@@ -6069,11 +6075,9 @@
       <c r="B76" s="5">
         <v>46155.606291909724</v>
       </c>
-      <c r="C76" s="5">
-        <v>46209.635949918986</v>
-      </c>
+      <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46209.635966145834</v>
+        <v>46213.50618344908</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>248</v>
@@ -6455,10 +6459,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6516,10 +6520,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6558,7 +6562,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6579,10 +6583,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6621,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6642,10 +6646,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6684,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="389">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>francisca@zitron.com</t>
+  </si>
+  <si>
+    <t>Este proyecto contiene dos ventiladores horizontales y dos verticales. ZVR-1-22-90/6 (W22 Carcasa de Hierro Gris) MOTOR (2) 90 KW – 06 POLOS – 380 V -60 HZ- 1000 msnm. Resistente al fuego 250°C / 2 horas Sentido de giro bidireccional Frame: 250 Forma constructiva: B3T Protección: IP55 Refrigeración: TEFC Calentamiento: CLASE B Servicio: S1 Factor de Servicio: 1,15 Rendimiento: IE1 Aislamiento: clase H Arranque: VDF Caja de bornes en el exterior del ventilador Sondas: Sondas de temperatura PTC en los devanados Sondas de temperatura PTC 100 en cojinetes Sonda Stall (anti-bombeo) (Directo e inverso) Sonda de caudal (Directo e inverso) Sonda de vibraciones Sonda de rodamientos PT100 PT100 de temperatura de aire ZVRv-1-22-90/6 (W22 Carcasa de Hierro Gris) MOTOR (2) 90 KW – 06 POLOS – 380 V -60 HZ- 1000 msnm. Resistente al fuego 250°C / 2 horas Sentido de giro bidireccional Frame: 250 Forma constructiva: B3T Protección: IP5</t>
   </si>
   <si>
     <t>1214777481492618</t>
@@ -1939,7 +1942,7 @@
         <v>46161.62364042824</v>
       </c>
       <c r="D6" s="5">
-        <v>46161.623656701384</v>
+        <v>46213.76969591435</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1961,7 +1964,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1993,7 +1996,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="8">
         <v>46155.60573616898</v>
@@ -2005,7 +2008,7 @@
         <v>46161.62382879629</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>26</v>
@@ -2056,7 +2059,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="5">
         <v>46155.60574121527</v>
@@ -2068,7 +2071,7 @@
         <v>46161.62420805555</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -2087,7 +2090,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -2099,7 +2102,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q8" s="5">
         <v>46150</v>
@@ -2119,7 +2122,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="8">
         <v>46155.6057468287</v>
@@ -2131,7 +2134,7 @@
         <v>46175.873231562495</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>26</v>
@@ -2150,7 +2153,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>26</v>
@@ -2182,7 +2185,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="5">
         <v>46155.605614988424</v>
@@ -2194,7 +2197,7 @@
         <v>46204.91630894676</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -2218,7 +2221,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2235,7 +2238,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="8">
         <v>46155.605752372685</v>
@@ -2247,7 +2250,7 @@
         <v>46195.54676366899</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
@@ -2268,19 +2271,19 @@
         <v>26</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="8">
         <v>46153</v>
@@ -2300,7 +2303,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46155.60576009259</v>
@@ -2312,7 +2315,7 @@
         <v>46195.54676375</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2333,19 +2336,19 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="5">
         <v>46153</v>
@@ -2365,7 +2368,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" s="8">
         <v>46155.60576791667</v>
@@ -2377,7 +2380,7 @@
         <v>46195.546763645834</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -2404,13 +2407,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="8">
         <v>46153</v>
@@ -2430,7 +2433,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46155.605619849535</v>
@@ -2442,7 +2445,7 @@
         <v>46204.91621174768</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2466,7 +2469,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2483,7 +2486,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8">
         <v>46155.605784768515</v>
@@ -2495,7 +2498,7 @@
         <v>46161.624307349535</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2522,13 +2525,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="8">
         <v>46155</v>
@@ -2548,7 +2551,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46155.605792291666</v>
@@ -2560,7 +2563,7 @@
         <v>46161.62431424769</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2587,13 +2590,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q16" s="5">
         <v>46155</v>
@@ -2613,7 +2616,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="8">
         <v>46155.605799756944</v>
@@ -2625,16 +2628,16 @@
         <v>46197.502289386575</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17" s="8">
         <v>46155</v>
@@ -2652,13 +2655,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="8">
         <v>46155</v>
@@ -2678,7 +2681,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46155.60580746528</v>
@@ -2690,16 +2693,16 @@
         <v>46206.56478702546</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I18" s="5">
         <v>46185</v>
@@ -2717,13 +2720,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46185</v>
@@ -2743,7 +2746,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8">
         <v>46155.605814317125</v>
@@ -2755,16 +2758,16 @@
         <v>46206.564361412034</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I19" s="8">
         <v>46185</v>
@@ -2782,13 +2785,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="8">
         <v>46185</v>
@@ -2808,7 +2811,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46155.60582009259</v>
@@ -2820,16 +2823,16 @@
         <v>46206.564197789354</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I20" s="5">
         <v>46185</v>
@@ -2847,13 +2850,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2873,7 +2876,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="8">
         <v>46155.60582561343</v>
@@ -2885,16 +2888,16 @@
         <v>46206.56396623843</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I21" s="8">
         <v>46185</v>
@@ -2912,13 +2915,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="8">
         <v>46185</v>
@@ -2938,7 +2941,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46155.60562462963</v>
@@ -2948,7 +2951,7 @@
         <v>46205.6092119213</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2972,7 +2975,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2985,7 +2988,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46155.60583177084</v>
@@ -2997,16 +3000,16 @@
         <v>46182.67729332176</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46157</v>
@@ -3024,13 +3027,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="8">
         <v>46157</v>
@@ -3050,7 +3053,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46155.60583869213</v>
@@ -3062,16 +3065,16 @@
         <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3089,29 +3092,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="8">
         <v>46155.605845625</v>
@@ -3123,16 +3126,16 @@
         <v>46182.67726898148</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="8">
         <v>46161</v>
@@ -3150,29 +3153,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46155.60585226852</v>
@@ -3182,16 +3185,16 @@
         <v>46179.19528431713</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3209,13 +3212,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3230,12 +3233,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46155.605858807874</v>
@@ -3245,16 +3248,16 @@
         <v>46197.502279444445</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I27" s="8">
         <v>46157</v>
@@ -3272,29 +3275,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46155.605865289355</v>
@@ -3304,16 +3307,16 @@
         <v>46178.17124241898</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3331,29 +3334,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46155.605925254626</v>
@@ -3365,16 +3368,16 @@
         <v>46197.18498747685</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I29" s="8">
         <v>46157</v>
@@ -3392,13 +3395,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q29" s="8">
         <v>46157</v>
@@ -3418,7 +3421,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46155.605932488426</v>
@@ -3430,16 +3433,16 @@
         <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3457,29 +3460,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46155.605939444446</v>
@@ -3491,16 +3494,16 @@
         <v>46182.67711275463</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I31" s="8">
         <v>46168</v>
@@ -3518,29 +3521,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46155.605945868054</v>
@@ -3552,16 +3555,16 @@
         <v>46182.69372545139</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3579,29 +3582,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46155.60595229166</v>
@@ -3613,16 +3616,16 @@
         <v>46205.60921498842</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="8">
         <v>46189</v>
@@ -3640,13 +3643,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q33" s="8">
         <v>46189</v>
@@ -3666,7 +3669,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46155.60595878473</v>
@@ -3678,16 +3681,16 @@
         <v>46199.55831050926</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3705,29 +3708,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46155.60596540509</v>
@@ -3739,16 +3742,16 @@
         <v>46205.609188692135</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="8">
         <v>46191</v>
@@ -3760,35 +3763,35 @@
         <v>26</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46155.60597160879</v>
@@ -3800,16 +3803,16 @@
         <v>46205.60961208333</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3827,10 +3830,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3853,7 +3856,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8">
         <v>46155.605976770836</v>
@@ -3865,16 +3868,16 @@
         <v>46205.609533587965</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="8">
         <v>46189</v>
@@ -3892,13 +3895,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3908,7 +3911,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46155.60598313657</v>
@@ -3920,16 +3923,16 @@
         <v>46205.60958704861</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3947,13 +3950,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3963,7 +3966,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46155.60598890047</v>
@@ -3975,16 +3978,16 @@
         <v>46213.50701678241</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46189</v>
@@ -4002,10 +4005,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -4017,7 +4020,7 @@
         <v>46230</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4028,7 +4031,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46155.60599439815</v>
@@ -4040,16 +4043,16 @@
         <v>46196.69342819444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4067,13 +4070,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4083,7 +4086,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46155.606000196756</v>
@@ -4095,16 +4098,16 @@
         <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46198</v>
@@ -4122,13 +4125,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4138,7 +4141,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46155.60600616898</v>
@@ -4148,16 +4151,16 @@
         <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4175,10 +4178,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4191,7 +4194,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46155.60601071759</v>
@@ -4203,16 +4206,16 @@
         <v>46211.1922662963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="8">
         <v>46189</v>
@@ -4230,10 +4233,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4256,7 +4259,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4268,16 +4271,16 @@
         <v>46199.56319799769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4295,13 +4298,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4311,7 +4314,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4323,16 +4326,16 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I45" s="8">
         <v>46191</v>
@@ -4350,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4366,7 +4369,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4376,7 +4379,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4400,7 +4403,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4413,7 +4416,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4425,16 +4428,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4452,13 +4455,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4478,7 +4481,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4490,16 +4493,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4517,13 +4520,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4543,7 +4546,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4555,16 +4558,16 @@
         <v>46195.947667824075</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4580,13 +4583,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4595,7 +4598,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4606,7 +4609,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4616,16 +4619,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4643,10 +4646,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4658,18 +4661,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4679,16 +4682,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4704,13 +4707,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4720,7 +4723,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4730,16 +4733,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4755,13 +4758,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4771,7 +4774,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4781,16 +4784,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4806,13 +4809,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4822,7 +4825,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4832,16 +4835,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4857,13 +4860,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4873,7 +4876,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4883,16 +4886,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4908,13 +4911,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4924,7 +4927,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4936,7 +4939,7 @@
         <v>46213.506286655094</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4960,7 +4963,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4977,7 +4980,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4989,16 +4992,16 @@
         <v>46212.88596140046</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5016,13 +5019,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5042,7 +5045,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5054,16 +5057,16 @@
         <v>46213.50624159722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46204</v>
@@ -5081,13 +5084,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5102,12 +5105,12 @@
         <v>1</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5119,16 +5122,16 @@
         <v>46213.50624155093</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5146,13 +5149,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5172,7 +5175,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5184,16 +5187,16 @@
         <v>46213.506277974535</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I60" s="5">
         <v>46204</v>
@@ -5211,13 +5214,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5237,7 +5240,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
@@ -5249,16 +5252,16 @@
         <v>46213.17611152778</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5276,13 +5279,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5302,7 +5305,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46155.60616390046</v>
@@ -5314,16 +5317,16 @@
         <v>46212.8864002662</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I62" s="5">
         <v>46213</v>
@@ -5341,13 +5344,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5356,7 +5359,7 @@
         <v>46216</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5367,7 +5370,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="8">
         <v>46155.60617082176</v>
@@ -5377,7 +5380,7 @@
         <v>46213.50618732639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5401,7 +5404,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5414,7 +5417,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46155.60617413194</v>
@@ -5424,16 +5427,16 @@
         <v>46212.19508587963</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5451,13 +5454,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="5">
         <v>46217</v>
@@ -5466,18 +5469,18 @@
         <v>46219</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B65" s="8">
         <v>46155.60618260417</v>
@@ -5487,16 +5490,16 @@
         <v>46213.50627252315</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I65" s="8">
         <v>46217</v>
@@ -5514,13 +5517,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5530,7 +5533,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46155.60619106481</v>
@@ -5540,16 +5543,16 @@
         <v>46213.50627136574</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5567,13 +5570,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5583,7 +5586,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B67" s="8">
         <v>46155.60619835649</v>
@@ -5593,16 +5596,16 @@
         <v>46213.50627376157</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I67" s="8">
         <v>46217</v>
@@ -5620,13 +5623,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5636,7 +5639,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46155.60620543981</v>
@@ -5646,16 +5649,16 @@
         <v>46213.506274942134</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5673,13 +5676,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5689,7 +5692,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B69" s="8">
         <v>46155.60745351852</v>
@@ -5699,16 +5702,16 @@
         <v>46213.506269942125</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I69" s="8">
         <v>46217</v>
@@ -5726,13 +5729,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5742,7 +5745,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46155.606212638886</v>
@@ -5752,16 +5755,16 @@
         <v>46213.506173333335</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5779,13 +5782,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5794,7 +5797,7 @@
         <v>46226</v>
       </c>
       <c r="S70" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5805,7 +5808,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="8">
         <v>46155.60621899305</v>
@@ -5815,16 +5818,16 @@
         <v>46195.9476830787</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I71" s="8">
         <v>46220</v>
@@ -5842,13 +5845,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5858,7 +5861,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
         <v>46155.606226539356</v>
@@ -5868,16 +5871,16 @@
         <v>46195.9476728125</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5895,13 +5898,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5911,7 +5914,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B73" s="8">
         <v>46155.606234004634</v>
@@ -5921,16 +5924,16 @@
         <v>46195.94767699074</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I73" s="8">
         <v>46220</v>
@@ -5948,13 +5951,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5964,7 +5967,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46155.60628421296</v>
@@ -5974,16 +5977,16 @@
         <v>46195.94767966435</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -6001,13 +6004,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6017,7 +6020,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="8">
         <v>46155.607690034725</v>
@@ -6027,16 +6030,16 @@
         <v>46155.61937777778</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I75" s="8">
         <v>46220</v>
@@ -6054,13 +6057,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6070,7 +6073,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46155.606291909724</v>
@@ -6080,16 +6083,16 @@
         <v>46213.50618344908</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6107,13 +6110,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q76" s="5">
         <v>46227</v>
@@ -6122,7 +6125,7 @@
         <v>46227</v>
       </c>
       <c r="S76" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6133,7 +6136,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" s="8">
         <v>46155.60629884259</v>
@@ -6143,16 +6146,16 @@
         <v>46195.947673518516</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I77" s="8">
         <v>46227</v>
@@ -6170,13 +6173,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6186,7 +6189,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46155.60630622685</v>
@@ -6196,16 +6199,16 @@
         <v>46195.947674131945</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6223,13 +6226,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6239,7 +6242,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="8">
         <v>46155.6063134375</v>
@@ -6249,16 +6252,16 @@
         <v>46195.94768039352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I79" s="8">
         <v>46227</v>
@@ -6276,13 +6279,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6292,7 +6295,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46155.606319722225</v>
@@ -6302,16 +6305,16 @@
         <v>46195.94768090278</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6329,13 +6332,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6345,7 +6348,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B81" s="8">
         <v>46155.618322951384</v>
@@ -6355,16 +6358,16 @@
         <v>46155.620736377314</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6380,13 +6383,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6396,7 +6399,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B82" s="5">
         <v>46155.60632542824</v>
@@ -6406,7 +6409,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6430,7 +6433,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6443,7 +6446,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B83" s="8">
         <v>46155.60632868056</v>
@@ -6453,16 +6456,16 @@
         <v>46182.19947712963</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6478,13 +6481,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q83" s="8">
         <v>46181</v>
@@ -6499,12 +6502,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B84" s="5">
         <v>46155.60633650463</v>
@@ -6514,16 +6517,16 @@
         <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6541,13 +6544,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="5">
         <v>46164</v>
@@ -6562,12 +6565,12 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B85" s="8">
         <v>46155.60634402778</v>
@@ -6577,16 +6580,16 @@
         <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6604,13 +6607,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q85" s="8">
         <v>46197</v>
@@ -6625,12 +6628,12 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B86" s="5">
         <v>46155.60635177083</v>
@@ -6640,16 +6643,16 @@
         <v>46196.693516562504</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6667,13 +6670,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="5">
         <v>46231</v>
@@ -6682,18 +6685,18 @@
         <v>46231</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B87" s="8">
         <v>46155.606361921295</v>
@@ -6703,7 +6706,7 @@
         <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6727,7 +6730,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6740,7 +6743,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46155.60636525463</v>
@@ -6750,16 +6753,16 @@
         <v>46155.620355625</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I88" s="5">
         <v>46230</v>
@@ -6777,13 +6780,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q88" s="5">
         <v>46230</v>
@@ -6792,18 +6795,18 @@
         <v>46234</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B89" s="8">
         <v>46155.606374525465</v>
@@ -6813,16 +6816,16 @@
         <v>46155.621619502315</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I89" s="8">
         <v>46230</v>
@@ -6840,10 +6843,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>26</v>
@@ -6856,7 +6859,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46155.60638027778</v>
@@ -6866,16 +6869,16 @@
         <v>46155.62163603009</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I90" s="5">
         <v>46230</v>
@@ -6893,10 +6896,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6909,7 +6912,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B91" s="8">
         <v>46155.60638583334</v>
@@ -6919,16 +6922,16 @@
         <v>46155.62166074074</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I91" s="8">
         <v>46230</v>
@@ -6946,13 +6949,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6962,7 +6965,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46155.60639179398</v>
@@ -6972,16 +6975,16 @@
         <v>46155.62167399305</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I92" s="5">
         <v>46230</v>
@@ -6999,13 +7002,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7015,7 +7018,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B93" s="8">
         <v>46155.61975986111</v>
@@ -7025,16 +7028,16 @@
         <v>46155.62169508102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I93" s="8">
         <v>46230</v>
@@ -7052,13 +7055,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7068,7 +7071,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46155.60639783565</v>
@@ -7078,16 +7081,16 @@
         <v>46155.62191585648</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I94" s="5">
         <v>46237</v>
@@ -7105,13 +7108,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q94" s="5">
         <v>46237</v>
@@ -7120,18 +7123,18 @@
         <v>46237</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="8">
         <v>46155.60640402778</v>
@@ -7141,16 +7144,16 @@
         <v>46195.947681273145</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -7166,13 +7169,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7182,7 +7185,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B96" s="5">
         <v>46155.60641090278</v>
@@ -7192,16 +7195,16 @@
         <v>46195.94768182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7217,13 +7220,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7233,7 +7236,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B97" s="8">
         <v>46155.60641760417</v>
@@ -7243,16 +7246,16 @@
         <v>46195.94768232639</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="8">
@@ -7268,13 +7271,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7284,7 +7287,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46155.60642649306</v>
@@ -7294,16 +7297,16 @@
         <v>46195.947674641204</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7319,13 +7322,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7335,7 +7338,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B99" s="8">
         <v>46155.62115946759</v>
@@ -7345,16 +7348,16 @@
         <v>46155.64240027778</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7370,13 +7373,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7386,7 +7389,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B100" s="5">
         <v>46155.60648232639</v>
@@ -7396,16 +7399,16 @@
         <v>46155.631670462964</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I100" s="5">
         <v>46238</v>
@@ -7423,13 +7426,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q100" s="5">
         <v>46238</v>
@@ -7438,18 +7441,18 @@
         <v>46238</v>
       </c>
       <c r="S100" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B101" s="8">
         <v>46155.60649042824</v>
@@ -7459,16 +7462,16 @@
         <v>46195.947675324074</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
@@ -7484,13 +7487,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7500,7 +7503,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B102" s="5">
         <v>46155.6064993287</v>
@@ -7510,16 +7513,16 @@
         <v>46195.947678958335</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7535,13 +7538,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7551,7 +7554,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B103" s="8">
         <v>46155.606507951394</v>
@@ -7561,16 +7564,16 @@
         <v>46195.94768271991</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I103" s="9"/>
       <c r="J103" s="8">
@@ -7586,13 +7589,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7602,7 +7605,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B104" s="5">
         <v>46155.60651716436</v>
@@ -7612,16 +7615,16 @@
         <v>46195.94768359954</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7637,13 +7640,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7653,7 +7656,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B105" s="8">
         <v>46155.6221815162</v>
@@ -7663,16 +7666,16 @@
         <v>46155.63179349537</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I105" s="9"/>
       <c r="J105" s="8">
@@ -7688,13 +7691,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7704,7 +7707,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B106" s="5">
         <v>46155.60652579861</v>
@@ -7714,16 +7717,16 @@
         <v>46155.63455996528</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I106" s="5">
         <v>46239</v>
@@ -7741,13 +7744,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q106" s="5">
         <v>46239</v>
@@ -7756,18 +7759,18 @@
         <v>46239</v>
       </c>
       <c r="S106" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
       <c r="U106" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B107" s="8">
         <v>46155.606533032405</v>
@@ -7777,16 +7780,16 @@
         <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I107" s="9"/>
       <c r="J107" s="8">
@@ -7802,13 +7805,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7818,7 +7821,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B108" s="5">
         <v>46155.60654145833</v>
@@ -7828,16 +7831,16 @@
         <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7853,13 +7856,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7869,7 +7872,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B109" s="8">
         <v>46155.60655399306</v>
@@ -7879,16 +7882,16 @@
         <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
@@ -7904,13 +7907,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -7920,7 +7923,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
         <v>46155.60656262732</v>
@@ -7930,16 +7933,16 @@
         <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -7955,13 +7958,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7971,7 +7974,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B111" s="8">
         <v>46155.63011625</v>
@@ -7981,16 +7984,16 @@
         <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
@@ -8006,13 +8009,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8022,7 +8025,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B112" s="5">
         <v>46155.60657109953</v>
@@ -8032,16 +8035,16 @@
         <v>46155.63577444444</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I112" s="5">
         <v>46240</v>
@@ -8059,13 +8062,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q112" s="5">
         <v>46240</v>
@@ -8074,18 +8077,18 @@
         <v>46240</v>
       </c>
       <c r="S112" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B113" s="8">
         <v>46155.60657833333</v>
@@ -8095,16 +8098,16 @@
         <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I113" s="8">
         <v>46240</v>
@@ -8122,13 +8125,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8138,7 +8141,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B114" s="5">
         <v>46155.60658640046</v>
@@ -8148,16 +8151,16 @@
         <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I114" s="5">
         <v>46240</v>
@@ -8175,13 +8178,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8191,7 +8194,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B115" s="8">
         <v>46155.60659408565</v>
@@ -8201,16 +8204,16 @@
         <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I115" s="8">
         <v>46240</v>
@@ -8228,13 +8231,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8244,7 +8247,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B116" s="5">
         <v>46155.60660233797</v>
@@ -8254,16 +8257,16 @@
         <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I116" s="5">
         <v>46240</v>
@@ -8281,13 +8284,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8297,7 +8300,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B117" s="8">
         <v>46155.63398136574</v>
@@ -8307,16 +8310,16 @@
         <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8332,13 +8335,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8348,7 +8351,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B118" s="5">
         <v>46155.60664190972</v>
@@ -8358,16 +8361,16 @@
         <v>46155.63694791667</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I118" s="5">
         <v>46244</v>
@@ -8385,13 +8388,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q118" s="5">
         <v>46244</v>
@@ -8400,18 +8403,18 @@
         <v>46244</v>
       </c>
       <c r="S118" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
       </c>
       <c r="U118" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B119" s="8">
         <v>46155.60665081019</v>
@@ -8421,16 +8424,16 @@
         <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8446,13 +8449,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8462,7 +8465,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B120" s="5">
         <v>46155.60665825232</v>
@@ -8472,16 +8475,16 @@
         <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8497,13 +8500,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8513,7 +8516,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B121" s="8">
         <v>46155.60666534722</v>
@@ -8523,16 +8526,16 @@
         <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8548,13 +8551,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8564,7 +8567,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B122" s="5">
         <v>46155.60667253472</v>
@@ -8574,16 +8577,16 @@
         <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8599,13 +8602,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8615,7 +8618,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B123" s="8">
         <v>46155.63591585648</v>
@@ -8625,16 +8628,16 @@
         <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -8650,13 +8653,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8666,7 +8669,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B124" s="5">
         <v>46155.606679502314</v>
@@ -8676,7 +8679,7 @@
         <v>46155.60689462963</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>25</v>
@@ -8700,7 +8703,7 @@
         <v>26</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>26</v>
@@ -8713,7 +8716,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B125" s="8">
         <v>46155.60668334491</v>
@@ -8723,16 +8726,16 @@
         <v>46155.63803638889</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -8748,13 +8751,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q125" s="8">
         <v>46245</v>
@@ -8763,18 +8766,18 @@
         <v>46245</v>
       </c>
       <c r="S125" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
       </c>
       <c r="U125" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B126" s="5">
         <v>46155.606691759254</v>
@@ -8784,16 +8787,16 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8809,13 +8812,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8825,7 +8828,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B127" s="8">
         <v>46155.60669864583</v>
@@ -8835,16 +8838,16 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -8860,13 +8863,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -8876,7 +8879,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B128" s="5">
         <v>46155.60670615741</v>
@@ -8886,16 +8889,16 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8911,13 +8914,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8927,7 +8930,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B129" s="8">
         <v>46155.606713009256</v>
@@ -8937,16 +8940,16 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -8962,13 +8965,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -8978,7 +8981,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B130" s="5">
         <v>46155.63715556713</v>
@@ -8988,16 +8991,16 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9013,13 +9016,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9029,7 +9032,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B131" s="8">
         <v>46155.60671987268</v>
@@ -9039,16 +9042,16 @@
         <v>46155.638912615745</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I131" s="8">
         <v>46246</v>
@@ -9066,13 +9069,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q131" s="8">
         <v>46246</v>
@@ -9081,18 +9084,18 @@
         <v>46246</v>
       </c>
       <c r="S131" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
       </c>
       <c r="U131" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B132" s="5">
         <v>46155.60672658565</v>
@@ -9102,16 +9105,16 @@
         <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I132" s="5">
         <v>46246</v>
@@ -9129,13 +9132,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9145,7 +9148,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B133" s="8">
         <v>46155.60673355324</v>
@@ -9155,16 +9158,16 @@
         <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I133" s="8">
         <v>46246</v>
@@ -9182,13 +9185,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9198,7 +9201,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B134" s="5">
         <v>46155.60674053241</v>
@@ -9208,16 +9211,16 @@
         <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I134" s="5">
         <v>46246</v>
@@ -9235,13 +9238,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9251,7 +9254,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B135" s="8">
         <v>46155.60674741898</v>
@@ -9261,16 +9264,16 @@
         <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I135" s="8">
         <v>46246</v>
@@ -9288,13 +9291,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9304,7 +9307,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B136" s="5">
         <v>46155.63830266204</v>
@@ -9314,16 +9317,16 @@
         <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9339,13 +9342,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9355,7 +9358,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B137" s="8">
         <v>46155.60675400463</v>
@@ -9365,16 +9368,16 @@
         <v>46155.64036164352</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I137" s="8">
         <v>46247</v>
@@ -9392,13 +9395,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q137" s="8">
         <v>46247</v>
@@ -9407,18 +9410,18 @@
         <v>46247</v>
       </c>
       <c r="S137" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
       </c>
       <c r="U137" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B138" s="5">
         <v>46155.60676105324</v>
@@ -9428,16 +9431,16 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9453,13 +9456,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9469,7 +9472,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B139" s="8">
         <v>46155.60677012731</v>
@@ -9479,16 +9482,16 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9504,13 +9507,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9520,7 +9523,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B140" s="5">
         <v>46155.60681737268</v>
@@ -9530,16 +9533,16 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9555,13 +9558,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9571,7 +9574,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B141" s="8">
         <v>46155.60682548611</v>
@@ -9581,16 +9584,16 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9606,13 +9609,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9622,7 +9625,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B142" s="5">
         <v>46155.63928425926</v>
@@ -9632,16 +9635,16 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9657,13 +9660,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9673,7 +9676,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B143" s="8">
         <v>46155.60683229167</v>
@@ -9683,16 +9686,16 @@
         <v>46155.641985821756</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I143" s="8">
         <v>46248</v>
@@ -9710,13 +9713,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q143" s="8">
         <v>46248</v>
@@ -9725,18 +9728,18 @@
         <v>46248</v>
       </c>
       <c r="S143" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
       </c>
       <c r="U143" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B144" s="5">
         <v>46155.606840486114</v>
@@ -9746,16 +9749,16 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9771,13 +9774,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9787,7 +9790,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B145" s="8">
         <v>46155.60684746528</v>
@@ -9797,16 +9800,16 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9822,13 +9825,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -9838,7 +9841,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B146" s="5">
         <v>46155.60685387731</v>
@@ -9848,16 +9851,16 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9873,13 +9876,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9889,7 +9892,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B147" s="8">
         <v>46155.60686101852</v>
@@ -9899,16 +9902,16 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -9924,13 +9927,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -9940,7 +9943,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B148" s="5">
         <v>46155.64052775463</v>
@@ -9950,16 +9953,16 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -9975,13 +9978,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9991,7 +9994,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B149" s="8">
         <v>46155.60686797454</v>
@@ -10001,7 +10004,7 @@
         <v>46155.60689638889</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>25</v>
@@ -10025,7 +10028,7 @@
         <v>26</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -10038,7 +10041,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B150" s="5">
         <v>46155.60687207176</v>
@@ -10048,16 +10051,16 @@
         <v>46155.60689709491</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I150" s="5">
         <v>46251</v>
@@ -10075,13 +10078,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q150" s="5">
         <v>46251</v>
@@ -10090,18 +10093,18 @@
         <v>46255</v>
       </c>
       <c r="S150" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
       </c>
       <c r="U150" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B151" s="8">
         <v>46155.606879259256</v>
@@ -10111,7 +10114,7 @@
         <v>46195.54676386574</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10138,13 +10141,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q151" s="8">
         <v>46251</v>
@@ -10153,13 +10156,13 @@
         <v>46255</v>
       </c>
       <c r="S151" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T151" s="9">
         <v>0</v>
       </c>
       <c r="U151" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -645,7 +645,7 @@
     <t>victor.munoz@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1214777626772872</t>
@@ -4989,7 +4989,7 @@
         <v>46212.8859408912</v>
       </c>
       <c r="D57" s="8">
-        <v>46212.88596140046</v>
+        <v>46216.60285269676</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="389">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -308,6 +308,9 @@
     <t>Alabe OT 4316 ,Materiales corte Laser OT 4316,rodete OT 4316,Motor OT 4316</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1214777481578466</t>
   </si>
   <si>
@@ -658,9 +661,6 @@
   </si>
   <si>
     <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214777594376340</t>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46205.6092119213</v>
+        <v>46216.83238582176</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2984,11 +2984,13 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
+      <c r="U22" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>46155.60583177084</v>
@@ -3000,16 +3002,16 @@
         <v>46182.67729332176</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="8">
         <v>46157</v>
@@ -3030,7 +3032,7 @@
         <v>90</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>90</v>
@@ -3053,7 +3055,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46155.60583869213</v>
@@ -3065,16 +3067,16 @@
         <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3092,29 +3094,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="8">
         <v>46155.605845625</v>
@@ -3126,16 +3128,16 @@
         <v>46182.67726898148</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="8">
         <v>46161</v>
@@ -3153,48 +3155,50 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46155.60585226852</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46216.832365740745</v>
+      </c>
       <c r="D26" s="5">
-        <v>46179.19528431713</v>
+        <v>46216.83246247685</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3215,7 +3219,7 @@
         <v>90</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>90</v>
@@ -3230,34 +3234,36 @@
         <v>32</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="10" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="8">
         <v>46155.605858807874</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="8">
+        <v>46216.832309791665</v>
+      </c>
       <c r="D27" s="8">
-        <v>46197.502279444445</v>
+        <v>46216.83231204861</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="8">
         <v>46157</v>
@@ -3275,48 +3281,50 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>71</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46155.605865289355</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46216.83235039352</v>
+      </c>
       <c r="D28" s="5">
-        <v>46178.17124241898</v>
+        <v>46216.832352048616</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3334,29 +3342,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8">
         <v>46155.605925254626</v>
@@ -3368,16 +3376,16 @@
         <v>46197.18498747685</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="8">
         <v>46157</v>
@@ -3398,7 +3406,7 @@
         <v>90</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>90</v>
@@ -3421,7 +3429,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46155.605932488426</v>
@@ -3433,16 +3441,16 @@
         <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3460,29 +3468,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="8">
         <v>46155.605939444446</v>
@@ -3494,16 +3502,16 @@
         <v>46182.67711275463</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="8">
         <v>46168</v>
@@ -3521,29 +3529,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46155.605945868054</v>
@@ -3555,16 +3563,16 @@
         <v>46182.69372545139</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3582,29 +3590,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46155.60595229166</v>
@@ -3616,16 +3624,16 @@
         <v>46205.60921498842</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="8">
         <v>46189</v>
@@ -3646,7 +3654,7 @@
         <v>90</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>90</v>
@@ -3669,7 +3677,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46155.60595878473</v>
@@ -3681,16 +3689,16 @@
         <v>46199.55831050926</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3708,29 +3716,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="8">
         <v>46155.60596540509</v>
@@ -3742,16 +3750,16 @@
         <v>46205.609188692135</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="8">
         <v>46191</v>
@@ -3763,35 +3771,35 @@
         <v>26</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46155.60597160879</v>
@@ -3803,16 +3811,16 @@
         <v>46205.60961208333</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3833,7 +3841,7 @@
         <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3856,7 +3864,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="8">
         <v>46155.605976770836</v>
@@ -3874,10 +3882,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I37" s="8">
         <v>46189</v>
@@ -3895,13 +3903,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3911,7 +3919,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46155.60598313657</v>
@@ -3923,16 +3931,16 @@
         <v>46205.60958704861</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3950,13 +3958,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3966,7 +3974,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B39" s="8">
         <v>46155.60598890047</v>
@@ -3978,16 +3986,16 @@
         <v>46213.50701678241</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I39" s="8">
         <v>46189</v>
@@ -4008,7 +4016,7 @@
         <v>90</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -4020,7 +4028,7 @@
         <v>46230</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4031,7 +4039,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46155.60599439815</v>
@@ -4049,10 +4057,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4070,13 +4078,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4086,7 +4094,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="8">
         <v>46155.606000196756</v>
@@ -4098,16 +4106,16 @@
         <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46198</v>
@@ -4125,13 +4133,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>88</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4141,7 +4149,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46155.60600616898</v>
@@ -4151,16 +4159,16 @@
         <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4178,10 +4186,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4194,7 +4202,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B43" s="8">
         <v>46155.60601071759</v>
@@ -4206,16 +4214,16 @@
         <v>46211.1922662963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I43" s="8">
         <v>46189</v>
@@ -4236,7 +4244,7 @@
         <v>90</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4259,7 +4267,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4277,10 +4285,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4298,13 +4306,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4314,7 +4322,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4326,16 +4334,16 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I45" s="8">
         <v>46191</v>
@@ -4353,13 +4361,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4369,7 +4377,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4379,7 +4387,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4403,7 +4411,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4416,7 +4424,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4428,16 +4436,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4455,13 +4463,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4481,7 +4489,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4493,16 +4501,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4520,13 +4528,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4546,7 +4554,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4564,10 +4572,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4583,13 +4591,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4598,7 +4606,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4609,7 +4617,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4619,16 +4627,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4646,10 +4654,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4661,18 +4669,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4682,16 +4690,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4707,13 +4715,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4723,7 +4731,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4733,16 +4741,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4758,13 +4766,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4774,7 +4782,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4784,16 +4792,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4809,13 +4817,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4825,7 +4833,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4835,16 +4843,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4860,13 +4868,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4876,7 +4884,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4886,16 +4894,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4911,13 +4919,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4927,7 +4935,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4939,7 +4947,7 @@
         <v>46213.506286655094</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4963,7 +4971,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4980,7 +4988,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4992,16 +5000,16 @@
         <v>46216.60285269676</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5019,13 +5027,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5045,7 +5053,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5057,16 +5065,16 @@
         <v>46213.50624159722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I58" s="5">
         <v>46204</v>
@@ -5084,13 +5092,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5105,7 +5113,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5128,10 +5136,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5149,10 +5157,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>212</v>
@@ -5193,10 +5201,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I60" s="5">
         <v>46204</v>
@@ -5214,7 +5222,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>211</v>
@@ -5258,10 +5266,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5279,10 +5287,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>218</v>
@@ -5323,10 +5331,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I62" s="5">
         <v>46213</v>
@@ -5344,7 +5352,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>217</v>
@@ -5475,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5797,7 +5805,7 @@
         <v>46226</v>
       </c>
       <c r="S70" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -6089,10 +6097,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6125,7 +6133,7 @@
         <v>46227</v>
       </c>
       <c r="S76" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6152,10 +6160,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I77" s="8">
         <v>46227</v>
@@ -6205,10 +6213,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6258,10 +6266,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I79" s="8">
         <v>46227</v>
@@ -6311,10 +6319,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6364,10 +6372,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6409,7 +6417,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6453,7 +6461,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46182.19947712963</v>
+        <v>46216.83236861111</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>260</v>
@@ -6462,10 +6470,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6481,10 +6489,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>261</v>
@@ -6501,8 +6509,8 @@
       <c r="T83" s="9">
         <v>0</v>
       </c>
-      <c r="U83" s="10" t="s">
-        <v>101</v>
+      <c r="U83" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6523,10 +6531,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6544,10 +6552,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>264</v>
@@ -6565,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6586,10 +6594,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6607,10 +6615,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>267</v>
@@ -6628,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6649,10 +6657,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6670,10 +6678,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>270</v>
@@ -6685,13 +6693,13 @@
         <v>46231</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6795,13 +6803,13 @@
         <v>46234</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7123,13 +7131,13 @@
         <v>46237</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7441,13 +7449,13 @@
         <v>46238</v>
       </c>
       <c r="S100" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7759,13 +7767,13 @@
         <v>46239</v>
       </c>
       <c r="S106" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
       <c r="U106" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -7780,7 +7788,7 @@
         <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7831,7 +7839,7 @@
         <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7882,7 +7890,7 @@
         <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7933,7 +7941,7 @@
         <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7984,7 +7992,7 @@
         <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8077,13 +8085,13 @@
         <v>46240</v>
       </c>
       <c r="S112" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8098,7 +8106,7 @@
         <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8128,7 +8136,7 @@
         <v>321</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>323</v>
@@ -8151,7 +8159,7 @@
         <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8181,7 +8189,7 @@
         <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>323</v>
@@ -8204,7 +8212,7 @@
         <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8257,7 +8265,7 @@
         <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8310,7 +8318,7 @@
         <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8338,7 +8346,7 @@
         <v>321</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>323</v>
@@ -8403,13 +8411,13 @@
         <v>46244</v>
       </c>
       <c r="S118" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
       </c>
       <c r="U118" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -8424,7 +8432,7 @@
         <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8452,7 +8460,7 @@
         <v>330</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>333</v>
@@ -8475,7 +8483,7 @@
         <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8503,7 +8511,7 @@
         <v>330</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>335</v>
@@ -8526,7 +8534,7 @@
         <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8554,7 +8562,7 @@
         <v>330</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>333</v>
@@ -8577,7 +8585,7 @@
         <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8605,7 +8613,7 @@
         <v>330</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>335</v>
@@ -8628,7 +8636,7 @@
         <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8656,7 +8664,7 @@
         <v>330</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>335</v>
@@ -8766,13 +8774,13 @@
         <v>46245</v>
       </c>
       <c r="S125" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
       </c>
       <c r="U125" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -8787,7 +8795,7 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8815,7 +8823,7 @@
         <v>343</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>348</v>
@@ -8838,7 +8846,7 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8866,7 +8874,7 @@
         <v>343</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>348</v>
@@ -8889,7 +8897,7 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8917,7 +8925,7 @@
         <v>343</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>351</v>
@@ -8940,7 +8948,7 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -8968,7 +8976,7 @@
         <v>343</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>348</v>
@@ -8991,7 +8999,7 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9019,7 +9027,7 @@
         <v>343</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>348</v>
@@ -9084,13 +9092,13 @@
         <v>46246</v>
       </c>
       <c r="S131" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
       </c>
       <c r="U131" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -9105,7 +9113,7 @@
         <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9135,7 +9143,7 @@
         <v>355</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>357</v>
@@ -9158,7 +9166,7 @@
         <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9188,7 +9196,7 @@
         <v>355</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>359</v>
@@ -9211,7 +9219,7 @@
         <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9241,7 +9249,7 @@
         <v>355</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>357</v>
@@ -9264,7 +9272,7 @@
         <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9294,7 +9302,7 @@
         <v>355</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>359</v>
@@ -9317,7 +9325,7 @@
         <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9345,7 +9353,7 @@
         <v>355</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>357</v>
@@ -9410,13 +9418,13 @@
         <v>46247</v>
       </c>
       <c r="S137" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
       </c>
       <c r="U137" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -9431,7 +9439,7 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9459,7 +9467,7 @@
         <v>364</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>366</v>
@@ -9482,7 +9490,7 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9510,7 +9518,7 @@
         <v>364</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>366</v>
@@ -9533,7 +9541,7 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9561,7 +9569,7 @@
         <v>364</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>369</v>
@@ -9584,7 +9592,7 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9612,7 +9620,7 @@
         <v>364</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>369</v>
@@ -9635,7 +9643,7 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9663,7 +9671,7 @@
         <v>364</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>369</v>
@@ -9728,13 +9736,13 @@
         <v>46248</v>
       </c>
       <c r="S143" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
       </c>
       <c r="U143" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
@@ -9749,7 +9757,7 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9777,7 +9785,7 @@
         <v>373</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>373</v>
@@ -9800,7 +9808,7 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -9828,7 +9836,7 @@
         <v>373</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>373</v>
@@ -9851,7 +9859,7 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -9879,7 +9887,7 @@
         <v>373</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>373</v>
@@ -9902,7 +9910,7 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -9930,7 +9938,7 @@
         <v>373</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>373</v>
@@ -9953,7 +9961,7 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -9981,7 +9989,7 @@
         <v>373</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>373</v>
@@ -10093,13 +10101,13 @@
         <v>46255</v>
       </c>
       <c r="S150" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
       </c>
       <c r="U150" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
@@ -10156,13 +10164,13 @@
         <v>46255</v>
       </c>
       <c r="S151" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T151" s="9">
         <v>0</v>
       </c>
       <c r="U151" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -693,28 +693,28 @@
     <t>1214777561702202</t>
   </si>
   <si>
+    <t>1214777561721939</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Control de calidad Armado,Armado</t>
+  </si>
+  <si>
+    <t>1214777561721949</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777561721939</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Control de calidad Armado,Armado</t>
-  </si>
-  <si>
-    <t>1214777561721949</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
     <t>1214777561722180</t>
@@ -5322,7 +5322,7 @@
         <v>46212.886227650466</v>
       </c>
       <c r="D62" s="5">
-        <v>46212.8864002662</v>
+        <v>46217.18131804398</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5366,8 +5366,8 @@
       <c r="R62" s="5">
         <v>46216</v>
       </c>
-      <c r="S62" s="12" t="s">
-        <v>220</v>
+      <c r="S62" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46155.60617082176</v>
@@ -5388,7 +5388,7 @@
         <v>46213.50618732639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5412,7 +5412,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46155.60617413194</v>
@@ -5435,16 +5435,16 @@
         <v>46212.19508587963</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5462,13 +5462,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>215</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46217</v>
@@ -5477,7 +5477,7 @@
         <v>46219</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5504,10 +5504,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I65" s="8">
         <v>46217</v>
@@ -5525,7 +5525,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>230</v>
@@ -5557,10 +5557,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5578,7 +5578,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>233</v>
@@ -5610,10 +5610,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I67" s="8">
         <v>46217</v>
@@ -5631,7 +5631,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>235</v>
@@ -5663,10 +5663,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5684,7 +5684,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>235</v>
@@ -5716,10 +5716,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I69" s="8">
         <v>46217</v>
@@ -5737,7 +5737,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>235</v>
@@ -5769,10 +5769,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5790,13 +5790,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5832,10 +5832,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I71" s="8">
         <v>46220</v>
@@ -5885,10 +5885,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5938,10 +5938,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I73" s="8">
         <v>46220</v>
@@ -5991,10 +5991,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -6044,10 +6044,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I75" s="8">
         <v>46220</v>
@@ -6118,13 +6118,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>215</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q76" s="5">
         <v>46227</v>
@@ -9382,10 +9382,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I137" s="8">
         <v>46247</v>
@@ -9445,10 +9445,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9496,10 +9496,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9547,10 +9547,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9598,10 +9598,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9649,10 +9649,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9700,10 +9700,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I143" s="8">
         <v>46248</v>
@@ -9763,10 +9763,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9814,10 +9814,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9865,10 +9865,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9916,10 +9916,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -9967,10 +9967,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="386">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -248,9 +248,6 @@
     <t>propuesta nucleo rodeteOT 4316</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Generación OC Rodete OT 4316,Propuesta compras:</t>
   </si>
   <si>
@@ -258,12 +255,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser OT 4316</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2634,11 +2625,9 @@
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="8">
         <v>46155</v>
       </c>
@@ -2661,7 +2650,7 @@
         <v>55</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="8">
         <v>46155</v>
@@ -2681,7 +2670,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="5">
         <v>46155.60580746528</v>
@@ -2693,17 +2682,15 @@
         <v>46206.56478702546</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46185</v>
       </c>
@@ -2723,10 +2710,10 @@
         <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="5">
         <v>46185</v>
@@ -2746,7 +2733,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B19" s="8">
         <v>46155.605814317125</v>
@@ -2758,17 +2745,15 @@
         <v>46206.564361412034</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="9"/>
       <c r="I19" s="8">
         <v>46185</v>
       </c>
@@ -2788,10 +2773,10 @@
         <v>62</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="8">
         <v>46185</v>
@@ -2811,7 +2796,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5">
         <v>46155.60582009259</v>
@@ -2823,17 +2808,15 @@
         <v>46206.564197789354</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46185</v>
       </c>
@@ -2853,10 +2836,10 @@
         <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2876,7 +2859,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B21" s="8">
         <v>46155.60582561343</v>
@@ -2888,17 +2871,15 @@
         <v>46206.56396623843</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="8">
         <v>46185</v>
       </c>
@@ -2918,10 +2899,10 @@
         <v>62</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="8">
         <v>46185</v>
@@ -2941,7 +2922,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5">
         <v>46155.60562462963</v>
@@ -2951,7 +2932,7 @@
         <v>46216.83238582176</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2975,7 +2956,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2985,12 +2966,12 @@
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
       <c r="U22" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46155.60583177084</v>
@@ -3002,16 +2983,16 @@
         <v>46182.67729332176</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I23" s="8">
         <v>46157</v>
@@ -3029,13 +3010,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q23" s="8">
         <v>46157</v>
@@ -3055,7 +3036,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46155.60583869213</v>
@@ -3067,16 +3048,16 @@
         <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3094,29 +3075,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B25" s="8">
         <v>46155.605845625</v>
@@ -3128,16 +3109,16 @@
         <v>46182.67726898148</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I25" s="8">
         <v>46161</v>
@@ -3155,29 +3136,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46155.60585226852</v>
@@ -3189,16 +3170,16 @@
         <v>46216.83246247685</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3216,13 +3197,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3242,7 +3223,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B27" s="8">
         <v>46155.605858807874</v>
@@ -3254,16 +3235,16 @@
         <v>46216.83231204861</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I27" s="8">
         <v>46157</v>
@@ -3281,29 +3262,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>71</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46155.605865289355</v>
@@ -3315,16 +3296,16 @@
         <v>46216.832352048616</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3342,29 +3323,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="O28" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="O28" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46155.605925254626</v>
@@ -3376,16 +3357,16 @@
         <v>46197.18498747685</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I29" s="8">
         <v>46157</v>
@@ -3403,13 +3384,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q29" s="8">
         <v>46157</v>
@@ -3429,7 +3410,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46155.605932488426</v>
@@ -3441,16 +3422,16 @@
         <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3468,29 +3449,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46155.605939444446</v>
@@ -3502,16 +3483,16 @@
         <v>46182.67711275463</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I31" s="8">
         <v>46168</v>
@@ -3529,29 +3510,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>119</v>
-      </c>
       <c r="P31" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46155.605945868054</v>
@@ -3563,16 +3544,16 @@
         <v>46182.69372545139</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3590,29 +3571,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46155.60595229166</v>
@@ -3624,16 +3605,16 @@
         <v>46205.60921498842</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I33" s="8">
         <v>46189</v>
@@ -3651,13 +3632,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q33" s="8">
         <v>46189</v>
@@ -3677,7 +3658,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46155.60595878473</v>
@@ -3689,16 +3670,16 @@
         <v>46199.55831050926</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3716,29 +3697,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46155.60596540509</v>
@@ -3750,16 +3731,16 @@
         <v>46205.609188692135</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I35" s="8">
         <v>46191</v>
@@ -3771,35 +3752,35 @@
         <v>26</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="M35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46155.60597160879</v>
@@ -3811,16 +3792,16 @@
         <v>46205.60961208333</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3838,10 +3819,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3864,7 +3845,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46155.605976770836</v>
@@ -3876,16 +3857,16 @@
         <v>46205.609533587965</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I37" s="8">
         <v>46189</v>
@@ -3903,13 +3884,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="P37" s="9" t="s">
         <v>140</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>143</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3919,7 +3900,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46155.60598313657</v>
@@ -3931,16 +3912,16 @@
         <v>46205.60958704861</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3958,13 +3939,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3974,7 +3955,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46155.60598890047</v>
@@ -3986,16 +3967,16 @@
         <v>46213.50701678241</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I39" s="8">
         <v>46189</v>
@@ -4013,10 +3994,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -4028,7 +4009,7 @@
         <v>46230</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4039,7 +4020,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46155.60599439815</v>
@@ -4051,16 +4032,16 @@
         <v>46196.69342819444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4078,13 +4059,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4094,7 +4075,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46155.606000196756</v>
@@ -4106,16 +4087,16 @@
         <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I41" s="8">
         <v>46198</v>
@@ -4133,13 +4114,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4149,7 +4130,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46155.60600616898</v>
@@ -4159,16 +4140,16 @@
         <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4186,10 +4167,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4202,7 +4183,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46155.60601071759</v>
@@ -4214,16 +4195,16 @@
         <v>46211.1922662963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I43" s="8">
         <v>46189</v>
@@ -4241,10 +4222,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4267,7 +4248,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4279,16 +4260,16 @@
         <v>46199.56319799769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4306,13 +4287,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4322,7 +4303,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4334,16 +4315,16 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I45" s="8">
         <v>46191</v>
@@ -4361,13 +4342,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4377,7 +4358,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4387,7 +4368,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4411,7 +4392,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4424,7 +4405,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4436,16 +4417,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4463,13 +4444,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4489,7 +4470,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4501,16 +4482,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4528,13 +4509,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4554,7 +4535,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4566,16 +4547,16 @@
         <v>46195.947667824075</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4591,13 +4572,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4606,7 +4587,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4617,7 +4598,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4627,16 +4608,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4654,10 +4635,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4669,18 +4650,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4690,16 +4671,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4715,13 +4696,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4731,7 +4712,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4741,16 +4722,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4766,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4782,7 +4763,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4792,16 +4773,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4817,13 +4798,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4833,7 +4814,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4843,16 +4824,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4868,13 +4849,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4884,7 +4865,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4894,16 +4875,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4919,13 +4900,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4935,7 +4916,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4947,7 +4928,7 @@
         <v>46213.506286655094</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4971,7 +4952,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4988,7 +4969,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -5000,16 +4981,16 @@
         <v>46216.60285269676</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5027,13 +5008,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5053,7 +5034,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5065,16 +5046,16 @@
         <v>46213.50624159722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I58" s="5">
         <v>46204</v>
@@ -5092,13 +5073,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5113,12 +5094,12 @@
         <v>1</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5130,16 +5111,16 @@
         <v>46213.50624155093</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5157,13 +5138,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5183,7 +5164,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5195,16 +5176,16 @@
         <v>46213.506277974535</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I60" s="5">
         <v>46204</v>
@@ -5222,13 +5203,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5248,7 +5229,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
@@ -5260,16 +5241,16 @@
         <v>46213.17611152778</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5287,13 +5268,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5313,7 +5294,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46155.60616390046</v>
@@ -5325,16 +5306,16 @@
         <v>46217.18131804398</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I62" s="5">
         <v>46213</v>
@@ -5352,13 +5333,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5378,7 +5359,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46155.60617082176</v>
@@ -5388,7 +5369,7 @@
         <v>46213.50618732639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5412,7 +5393,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5425,7 +5406,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46155.60617413194</v>
@@ -5435,16 +5416,16 @@
         <v>46212.19508587963</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5462,13 +5443,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q64" s="5">
         <v>46217</v>
@@ -5477,18 +5458,18 @@
         <v>46219</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46155.60618260417</v>
@@ -5498,16 +5479,16 @@
         <v>46213.50627252315</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I65" s="8">
         <v>46217</v>
@@ -5525,13 +5506,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5541,7 +5522,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46155.60619106481</v>
@@ -5551,16 +5532,16 @@
         <v>46213.50627136574</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5578,13 +5559,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5594,7 +5575,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B67" s="8">
         <v>46155.60619835649</v>
@@ -5604,16 +5585,16 @@
         <v>46213.50627376157</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I67" s="8">
         <v>46217</v>
@@ -5631,13 +5612,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5647,7 +5628,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46155.60620543981</v>
@@ -5657,16 +5638,16 @@
         <v>46213.506274942134</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5684,13 +5665,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5700,7 +5681,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46155.60745351852</v>
@@ -5710,16 +5691,16 @@
         <v>46213.506269942125</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I69" s="8">
         <v>46217</v>
@@ -5737,13 +5718,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5753,7 +5734,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46155.606212638886</v>
@@ -5763,16 +5744,16 @@
         <v>46213.506173333335</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5790,13 +5771,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5805,7 +5786,7 @@
         <v>46226</v>
       </c>
       <c r="S70" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5816,7 +5797,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B71" s="8">
         <v>46155.60621899305</v>
@@ -5826,16 +5807,16 @@
         <v>46195.9476830787</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I71" s="8">
         <v>46220</v>
@@ -5853,13 +5834,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5869,7 +5850,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46155.606226539356</v>
@@ -5879,16 +5860,16 @@
         <v>46195.9476728125</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5906,13 +5887,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5922,7 +5903,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B73" s="8">
         <v>46155.606234004634</v>
@@ -5932,16 +5913,16 @@
         <v>46195.94767699074</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I73" s="8">
         <v>46220</v>
@@ -5959,13 +5940,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>244</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5975,7 +5956,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46155.60628421296</v>
@@ -5985,16 +5966,16 @@
         <v>46195.94767966435</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -6012,13 +5993,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6028,7 +6009,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B75" s="8">
         <v>46155.607690034725</v>
@@ -6038,16 +6019,16 @@
         <v>46155.61937777778</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I75" s="8">
         <v>46220</v>
@@ -6065,13 +6046,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6081,7 +6062,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46155.606291909724</v>
@@ -6091,16 +6072,16 @@
         <v>46213.50618344908</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6118,13 +6099,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q76" s="5">
         <v>46227</v>
@@ -6133,7 +6114,7 @@
         <v>46227</v>
       </c>
       <c r="S76" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6144,7 +6125,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B77" s="8">
         <v>46155.60629884259</v>
@@ -6154,16 +6135,16 @@
         <v>46195.947673518516</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I77" s="8">
         <v>46227</v>
@@ -6181,13 +6162,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6197,7 +6178,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46155.60630622685</v>
@@ -6207,16 +6188,16 @@
         <v>46195.947674131945</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6234,13 +6215,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6250,7 +6231,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B79" s="8">
         <v>46155.6063134375</v>
@@ -6260,16 +6241,16 @@
         <v>46195.94768039352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I79" s="8">
         <v>46227</v>
@@ -6287,13 +6268,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6303,7 +6284,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B80" s="5">
         <v>46155.606319722225</v>
@@ -6313,16 +6294,16 @@
         <v>46195.94768090278</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6340,13 +6321,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6356,7 +6337,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B81" s="8">
         <v>46155.618322951384</v>
@@ -6366,16 +6347,16 @@
         <v>46155.620736377314</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6391,13 +6372,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6407,7 +6388,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46155.60632542824</v>
@@ -6417,7 +6398,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6441,7 +6422,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6454,7 +6435,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B83" s="8">
         <v>46155.60632868056</v>
@@ -6464,16 +6445,16 @@
         <v>46216.83236861111</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6489,13 +6470,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q83" s="8">
         <v>46181</v>
@@ -6510,12 +6491,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B84" s="5">
         <v>46155.60633650463</v>
@@ -6525,16 +6506,16 @@
         <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6552,13 +6533,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q84" s="5">
         <v>46164</v>
@@ -6573,12 +6554,12 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B85" s="8">
         <v>46155.60634402778</v>
@@ -6588,16 +6569,16 @@
         <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6615,13 +6596,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Q85" s="8">
         <v>46197</v>
@@ -6636,12 +6617,12 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B86" s="5">
         <v>46155.60635177083</v>
@@ -6651,16 +6632,16 @@
         <v>46196.693516562504</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6678,13 +6659,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q86" s="5">
         <v>46231</v>
@@ -6693,18 +6674,18 @@
         <v>46231</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46155.606361921295</v>
@@ -6714,7 +6695,7 @@
         <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6738,7 +6719,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6751,7 +6732,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46155.60636525463</v>
@@ -6761,17 +6742,15 @@
         <v>46155.620355625</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="5">
         <v>46230</v>
       </c>
@@ -6788,13 +6767,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q88" s="5">
         <v>46230</v>
@@ -6803,18 +6782,18 @@
         <v>46234</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B89" s="8">
         <v>46155.606374525465</v>
@@ -6824,17 +6803,15 @@
         <v>46155.621619502315</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="9"/>
       <c r="I89" s="8">
         <v>46230</v>
       </c>
@@ -6851,10 +6828,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="O89" s="9" t="s">
         <v>275</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>26</v>
@@ -6867,7 +6844,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46155.60638027778</v>
@@ -6877,17 +6854,15 @@
         <v>46155.62163603009</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="5">
         <v>46230</v>
       </c>
@@ -6904,10 +6879,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O90" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6920,7 +6895,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B91" s="8">
         <v>46155.60638583334</v>
@@ -6930,17 +6905,15 @@
         <v>46155.62166074074</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="9"/>
       <c r="I91" s="8">
         <v>46230</v>
       </c>
@@ -6957,13 +6930,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6973,7 +6946,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B92" s="5">
         <v>46155.60639179398</v>
@@ -6983,17 +6956,15 @@
         <v>46155.62167399305</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="5">
         <v>46230</v>
       </c>
@@ -7010,13 +6981,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7026,7 +6997,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B93" s="8">
         <v>46155.61975986111</v>
@@ -7036,17 +7007,15 @@
         <v>46155.62169508102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="9"/>
       <c r="I93" s="8">
         <v>46230</v>
       </c>
@@ -7063,13 +7032,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7079,7 +7048,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B94" s="5">
         <v>46155.60639783565</v>
@@ -7089,17 +7058,15 @@
         <v>46155.62191585648</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46237</v>
       </c>
@@ -7116,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q94" s="5">
         <v>46237</v>
@@ -7131,18 +7098,18 @@
         <v>46237</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B95" s="8">
         <v>46155.60640402778</v>
@@ -7152,17 +7119,15 @@
         <v>46195.947681273145</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="9"/>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
         <v>46237</v>
@@ -7177,13 +7142,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="O95" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>286</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>289</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7193,7 +7158,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B96" s="5">
         <v>46155.60641090278</v>
@@ -7203,17 +7168,15 @@
         <v>46195.94768182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
         <v>46237</v>
@@ -7228,13 +7191,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>286</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7244,7 +7207,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B97" s="8">
         <v>46155.60641760417</v>
@@ -7254,17 +7217,15 @@
         <v>46195.94768232639</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H97" s="9"/>
       <c r="I97" s="9"/>
       <c r="J97" s="8">
         <v>46237</v>
@@ -7279,13 +7240,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7295,7 +7256,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B98" s="5">
         <v>46155.60642649306</v>
@@ -7305,17 +7266,15 @@
         <v>46195.947674641204</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
         <v>46237</v>
@@ -7330,13 +7289,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7346,7 +7305,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B99" s="8">
         <v>46155.62115946759</v>
@@ -7356,17 +7315,15 @@
         <v>46155.64240027778</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="9"/>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
         <v>46237</v>
@@ -7381,13 +7338,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7397,7 +7354,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B100" s="5">
         <v>46155.60648232639</v>
@@ -7407,17 +7364,15 @@
         <v>46155.631670462964</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="5">
         <v>46238</v>
       </c>
@@ -7434,13 +7389,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q100" s="5">
         <v>46238</v>
@@ -7449,18 +7404,18 @@
         <v>46238</v>
       </c>
       <c r="S100" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B101" s="8">
         <v>46155.60649042824</v>
@@ -7470,17 +7425,15 @@
         <v>46195.947675324074</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="9"/>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
         <v>46238</v>
@@ -7495,13 +7448,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7511,7 +7464,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B102" s="5">
         <v>46155.6064993287</v>
@@ -7521,17 +7474,15 @@
         <v>46195.947678958335</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
         <v>46238</v>
@@ -7546,13 +7497,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7562,7 +7513,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B103" s="8">
         <v>46155.606507951394</v>
@@ -7572,17 +7523,15 @@
         <v>46195.94768271991</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="9"/>
       <c r="I103" s="9"/>
       <c r="J103" s="8">
         <v>46238</v>
@@ -7597,13 +7546,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O103" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="P103" s="9" t="s">
         <v>299</v>
-      </c>
-      <c r="P103" s="9" t="s">
-        <v>302</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7613,7 +7562,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B104" s="5">
         <v>46155.60651716436</v>
@@ -7623,17 +7572,15 @@
         <v>46195.94768359954</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H104" s="6"/>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
         <v>46238</v>
@@ -7648,13 +7595,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7664,7 +7611,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B105" s="8">
         <v>46155.6221815162</v>
@@ -7674,17 +7621,15 @@
         <v>46155.63179349537</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="9"/>
       <c r="I105" s="9"/>
       <c r="J105" s="8">
         <v>46238</v>
@@ -7699,13 +7644,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7715,7 +7660,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B106" s="5">
         <v>46155.60652579861</v>
@@ -7725,17 +7670,15 @@
         <v>46155.63455996528</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
       <c r="I106" s="5">
         <v>46239</v>
       </c>
@@ -7752,13 +7695,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q106" s="5">
         <v>46239</v>
@@ -7767,18 +7710,18 @@
         <v>46239</v>
       </c>
       <c r="S106" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
       <c r="U106" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B107" s="8">
         <v>46155.606533032405</v>
@@ -7788,17 +7731,15 @@
         <v>46195.94767760417</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H107" s="9"/>
       <c r="I107" s="9"/>
       <c r="J107" s="8">
         <v>46239</v>
@@ -7813,13 +7754,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="O107" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="O107" s="9" t="s">
-        <v>311</v>
-      </c>
       <c r="P107" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7829,7 +7770,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B108" s="5">
         <v>46155.60654145833</v>
@@ -7839,17 +7780,15 @@
         <v>46195.947678344906</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
         <v>46239</v>
@@ -7864,13 +7803,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="O108" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="O108" s="6" t="s">
-        <v>311</v>
-      </c>
       <c r="P108" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7880,7 +7819,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B109" s="8">
         <v>46155.60655399306</v>
@@ -7890,17 +7829,15 @@
         <v>46195.947675868054</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="9"/>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
         <v>46239</v>
@@ -7915,13 +7852,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -7931,7 +7868,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B110" s="5">
         <v>46155.60656262732</v>
@@ -7941,17 +7878,15 @@
         <v>46195.947676435186</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46239</v>
@@ -7966,13 +7901,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7982,7 +7917,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B111" s="8">
         <v>46155.63011625</v>
@@ -7992,17 +7927,15 @@
         <v>46155.63465961805</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="9"/>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
         <v>46239</v>
@@ -8017,13 +7950,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8033,7 +7966,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B112" s="5">
         <v>46155.60657109953</v>
@@ -8043,17 +7976,15 @@
         <v>46155.63577444444</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="5">
         <v>46240</v>
       </c>
@@ -8070,13 +8001,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q112" s="5">
         <v>46240</v>
@@ -8085,18 +8016,18 @@
         <v>46240</v>
       </c>
       <c r="S112" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B113" s="8">
         <v>46155.60657833333</v>
@@ -8106,17 +8037,15 @@
         <v>46155.635128090275</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H113" s="9"/>
       <c r="I113" s="8">
         <v>46240</v>
       </c>
@@ -8133,13 +8062,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8149,7 +8078,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B114" s="5">
         <v>46155.60658640046</v>
@@ -8159,17 +8088,15 @@
         <v>46155.63525575231</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H114" s="6"/>
       <c r="I114" s="5">
         <v>46240</v>
       </c>
@@ -8186,13 +8113,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8202,7 +8129,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B115" s="8">
         <v>46155.60659408565</v>
@@ -8212,17 +8139,15 @@
         <v>46155.635268750004</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H115" s="9"/>
       <c r="I115" s="8">
         <v>46240</v>
       </c>
@@ -8239,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8255,7 +8180,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B116" s="5">
         <v>46155.60660233797</v>
@@ -8265,17 +8190,15 @@
         <v>46155.635292569445</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H116" s="6"/>
       <c r="I116" s="5">
         <v>46240</v>
       </c>
@@ -8292,13 +8215,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8308,7 +8231,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B117" s="8">
         <v>46155.63398136574</v>
@@ -8318,17 +8241,15 @@
         <v>46155.63581856481</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H117" s="9"/>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
         <v>46240</v>
@@ -8343,13 +8264,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8359,7 +8280,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B118" s="5">
         <v>46155.60664190972</v>
@@ -8369,17 +8290,15 @@
         <v>46155.63694791667</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H118" s="6"/>
       <c r="I118" s="5">
         <v>46244</v>
       </c>
@@ -8396,13 +8315,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Q118" s="5">
         <v>46244</v>
@@ -8411,18 +8330,18 @@
         <v>46244</v>
       </c>
       <c r="S118" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
       </c>
       <c r="U118" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B119" s="8">
         <v>46155.60665081019</v>
@@ -8432,17 +8351,15 @@
         <v>46155.63810030093</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="9"/>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
         <v>46244</v>
@@ -8457,13 +8374,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="O119" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="P119" s="9" t="s">
         <v>330</v>
-      </c>
-      <c r="O119" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="P119" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8473,7 +8390,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B120" s="5">
         <v>46155.60665825232</v>
@@ -8483,17 +8400,15 @@
         <v>46155.6381218287</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H120" s="6"/>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
         <v>46244</v>
@@ -8508,13 +8423,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8524,7 +8439,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B121" s="8">
         <v>46155.60666534722</v>
@@ -8534,17 +8449,15 @@
         <v>46155.63813651621</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="9"/>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
         <v>46244</v>
@@ -8559,13 +8472,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="O121" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="P121" s="9" t="s">
         <v>330</v>
-      </c>
-      <c r="O121" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="P121" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8575,7 +8488,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B122" s="5">
         <v>46155.60667253472</v>
@@ -8585,17 +8498,15 @@
         <v>46155.63815179398</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
         <v>46244</v>
@@ -8610,13 +8521,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8626,7 +8537,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B123" s="8">
         <v>46155.63591585648</v>
@@ -8636,17 +8547,15 @@
         <v>46155.63817207176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="9"/>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
         <v>46244</v>
@@ -8661,13 +8570,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8677,7 +8586,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B124" s="5">
         <v>46155.606679502314</v>
@@ -8687,7 +8596,7 @@
         <v>46155.60689462963</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>25</v>
@@ -8711,7 +8620,7 @@
         <v>26</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>26</v>
@@ -8724,7 +8633,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B125" s="8">
         <v>46155.60668334491</v>
@@ -8734,16 +8643,16 @@
         <v>46155.63803638889</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -8759,13 +8668,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="Q125" s="8">
         <v>46245</v>
@@ -8774,18 +8683,18 @@
         <v>46245</v>
       </c>
       <c r="S125" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
       </c>
       <c r="U125" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B126" s="5">
         <v>46155.606691759254</v>
@@ -8795,16 +8704,16 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8820,13 +8729,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8836,7 +8745,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B127" s="8">
         <v>46155.60669864583</v>
@@ -8846,16 +8755,16 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -8871,13 +8780,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -8887,7 +8796,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B128" s="5">
         <v>46155.60670615741</v>
@@ -8897,16 +8806,16 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8922,13 +8831,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8938,7 +8847,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B129" s="8">
         <v>46155.606713009256</v>
@@ -8948,16 +8857,16 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -8973,13 +8882,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -8989,7 +8898,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B130" s="5">
         <v>46155.63715556713</v>
@@ -8999,16 +8908,16 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9024,13 +8933,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9040,7 +8949,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B131" s="8">
         <v>46155.60671987268</v>
@@ -9050,17 +8959,15 @@
         <v>46155.638912615745</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H131" s="9"/>
       <c r="I131" s="8">
         <v>46246</v>
       </c>
@@ -9077,13 +8984,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="Q131" s="8">
         <v>46246</v>
@@ -9092,18 +8999,18 @@
         <v>46246</v>
       </c>
       <c r="S131" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
       </c>
       <c r="U131" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B132" s="5">
         <v>46155.60672658565</v>
@@ -9113,17 +9020,15 @@
         <v>46155.639826238425</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H132" s="6"/>
       <c r="I132" s="5">
         <v>46246</v>
       </c>
@@ -9140,13 +9045,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9156,7 +9061,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B133" s="8">
         <v>46155.60673355324</v>
@@ -9166,17 +9071,15 @@
         <v>46155.63983615741</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H133" s="9"/>
       <c r="I133" s="8">
         <v>46246</v>
       </c>
@@ -9193,13 +9096,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9209,7 +9112,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B134" s="5">
         <v>46155.60674053241</v>
@@ -9219,17 +9122,15 @@
         <v>46155.639844942125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H134" s="6"/>
       <c r="I134" s="5">
         <v>46246</v>
       </c>
@@ -9246,13 +9147,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9262,7 +9163,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B135" s="8">
         <v>46155.60674741898</v>
@@ -9272,17 +9173,15 @@
         <v>46155.63986869213</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H135" s="9"/>
       <c r="I135" s="8">
         <v>46246</v>
       </c>
@@ -9299,13 +9198,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9315,7 +9214,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B136" s="5">
         <v>46155.63830266204</v>
@@ -9325,17 +9224,15 @@
         <v>46155.63990003472</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H136" s="6"/>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
         <v>46246</v>
@@ -9350,13 +9247,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9366,7 +9263,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B137" s="8">
         <v>46155.60675400463</v>
@@ -9376,16 +9273,16 @@
         <v>46155.64036164352</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I137" s="8">
         <v>46247</v>
@@ -9403,13 +9300,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="Q137" s="8">
         <v>46247</v>
@@ -9418,18 +9315,18 @@
         <v>46247</v>
       </c>
       <c r="S137" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
       </c>
       <c r="U137" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B138" s="5">
         <v>46155.60676105324</v>
@@ -9439,16 +9336,16 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9464,13 +9361,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9480,7 +9377,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B139" s="8">
         <v>46155.60677012731</v>
@@ -9490,16 +9387,16 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9515,13 +9412,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9531,7 +9428,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B140" s="5">
         <v>46155.60681737268</v>
@@ -9541,16 +9438,16 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9566,13 +9463,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9582,7 +9479,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B141" s="8">
         <v>46155.60682548611</v>
@@ -9592,16 +9489,16 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9617,13 +9514,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9633,7 +9530,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B142" s="5">
         <v>46155.63928425926</v>
@@ -9643,16 +9540,16 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9668,13 +9565,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9684,7 +9581,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B143" s="8">
         <v>46155.60683229167</v>
@@ -9694,16 +9591,16 @@
         <v>46155.641985821756</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I143" s="8">
         <v>46248</v>
@@ -9721,13 +9618,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="Q143" s="8">
         <v>46248</v>
@@ -9736,18 +9633,18 @@
         <v>46248</v>
       </c>
       <c r="S143" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
       </c>
       <c r="U143" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B144" s="5">
         <v>46155.606840486114</v>
@@ -9757,16 +9654,16 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9782,13 +9679,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9798,7 +9695,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B145" s="8">
         <v>46155.60684746528</v>
@@ -9808,16 +9705,16 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9833,13 +9730,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -9849,7 +9746,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B146" s="5">
         <v>46155.60685387731</v>
@@ -9859,16 +9756,16 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9884,13 +9781,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9900,7 +9797,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B147" s="8">
         <v>46155.60686101852</v>
@@ -9910,16 +9807,16 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -9935,13 +9832,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -9951,7 +9848,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B148" s="5">
         <v>46155.64052775463</v>
@@ -9961,16 +9858,16 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -9986,13 +9883,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10002,7 +9899,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B149" s="8">
         <v>46155.60686797454</v>
@@ -10012,7 +9909,7 @@
         <v>46155.60689638889</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>25</v>
@@ -10036,7 +9933,7 @@
         <v>26</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -10049,7 +9946,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B150" s="5">
         <v>46155.60687207176</v>
@@ -10059,16 +9956,16 @@
         <v>46155.60689709491</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="I150" s="5">
         <v>46251</v>
@@ -10086,13 +9983,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="Q150" s="5">
         <v>46251</v>
@@ -10101,18 +9998,18 @@
         <v>46255</v>
       </c>
       <c r="S150" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
       </c>
       <c r="U150" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B151" s="8">
         <v>46155.606879259256</v>
@@ -10122,7 +10019,7 @@
         <v>46195.54676386574</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10149,13 +10046,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="Q151" s="8">
         <v>46251</v>
@@ -10164,13 +10061,13 @@
         <v>46255</v>
       </c>
       <c r="S151" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T151" s="9">
         <v>0</v>
       </c>
       <c r="U151" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46212.19508587963</v>
+        <v>46219.168197604165</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46213.50627252315</v>
+        <v>46219.16819976852</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46213.50627136574</v>
+        <v>46219.16819619213</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46213.50627376157</v>
+        <v>46219.168200960645</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>226</v>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46213.506274942134</v>
+        <v>46219.16820241898</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>226</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46213.506269942125</v>
+        <v>46219.16814042824</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>226</v>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46213.506173333335</v>
+        <v>46219.20782984953</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5785,8 +5785,8 @@
       <c r="R70" s="5">
         <v>46226</v>
       </c>
-      <c r="S70" s="11" t="s">
-        <v>98</v>
+      <c r="S70" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -705,43 +705,43 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
+    <t>1214777561722180</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777481868346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214777594413806</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214777594413833</t>
+  </si>
+  <si>
+    <t>1214739697907735</t>
+  </si>
+  <si>
+    <t>1214777594424435</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777561722180</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777481868346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214777594413806</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214777594413833</t>
-  </si>
-  <si>
-    <t>1214739697907735</t>
-  </si>
-  <si>
-    <t>1214777594424435</t>
-  </si>
-  <si>
-    <t>Armado</t>
   </si>
   <si>
     <t>1214777626832401</t>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46219.168197604165</v>
+        <v>46220.189402627315</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5457,8 +5457,8 @@
       <c r="R64" s="5">
         <v>46219</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>224</v>
+      <c r="S64" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46155.60618260417</v>
@@ -5479,7 +5479,7 @@
         <v>46219.16819976852</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5509,10 +5509,10 @@
         <v>221</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>227</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>228</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46155.60619106481</v>
@@ -5532,7 +5532,7 @@
         <v>46219.16819619213</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5562,10 +5562,10 @@
         <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B67" s="8">
         <v>46155.60619835649</v>
@@ -5585,7 +5585,7 @@
         <v>46219.168200960645</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5615,10 +5615,10 @@
         <v>221</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46155.60620543981</v>
@@ -5638,7 +5638,7 @@
         <v>46219.16820241898</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5668,10 +5668,10 @@
         <v>221</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5681,7 +5681,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46155.60745351852</v>
@@ -5691,7 +5691,7 @@
         <v>46219.16814042824</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5721,10 +5721,10 @@
         <v>221</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46155.606212638886</v>
@@ -5744,7 +5744,7 @@
         <v>46219.20782984953</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5786,7 +5786,7 @@
         <v>46226</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5807,7 +5807,7 @@
         <v>46195.9476830787</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5834,7 +5834,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>238</v>
@@ -5860,7 +5860,7 @@
         <v>46195.9476728125</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5887,7 +5887,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>238</v>
@@ -5913,7 +5913,7 @@
         <v>46195.94767699074</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5940,7 +5940,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>238</v>
@@ -5966,7 +5966,7 @@
         <v>46195.94767966435</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5993,7 +5993,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>238</v>
@@ -6019,7 +6019,7 @@
         <v>46155.61937777778</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6046,10 +6046,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>241</v>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46213.50618344908</v>
+        <v>46220.19536815972</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>246</v>
@@ -6113,8 +6113,8 @@
       <c r="R76" s="5">
         <v>46227</v>
       </c>
-      <c r="S76" s="11" t="s">
-        <v>98</v>
+      <c r="S76" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6135,7 +6135,7 @@
         <v>46195.947673518516</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6188,7 +6188,7 @@
         <v>46195.947674131945</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6241,7 +6241,7 @@
         <v>46195.94768039352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6294,7 +6294,7 @@
         <v>46195.94768090278</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6347,7 +6347,7 @@
         <v>46155.620736377314</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6375,7 +6375,7 @@
         <v>246</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>248</v>
@@ -6803,7 +6803,7 @@
         <v>46155.621619502315</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6854,7 +6854,7 @@
         <v>46155.62163603009</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6905,7 +6905,7 @@
         <v>46155.62166074074</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6933,7 +6933,7 @@
         <v>272</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>278</v>
@@ -6956,7 +6956,7 @@
         <v>46155.62167399305</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6984,7 +6984,7 @@
         <v>272</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>280</v>
@@ -7007,7 +7007,7 @@
         <v>46155.62169508102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7035,10 +7035,10 @@
         <v>272</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7119,7 +7119,7 @@
         <v>46195.947681273145</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7168,7 +7168,7 @@
         <v>46195.94768182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7217,7 +7217,7 @@
         <v>46195.94768232639</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7266,7 +7266,7 @@
         <v>46195.947674641204</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7315,7 +7315,7 @@
         <v>46155.64240027778</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7341,7 +7341,7 @@
         <v>283</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>290</v>
@@ -7425,7 +7425,7 @@
         <v>46195.947675324074</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7474,7 +7474,7 @@
         <v>46195.947678958335</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7523,7 +7523,7 @@
         <v>46195.94768271991</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7572,7 +7572,7 @@
         <v>46195.94768359954</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7621,7 +7621,7 @@
         <v>46155.63179349537</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7647,7 +7647,7 @@
         <v>294</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>303</v>
@@ -7953,7 +7953,7 @@
         <v>305</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>316</v>
@@ -8167,7 +8167,7 @@
         <v>318</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>323</v>
@@ -8218,7 +8218,7 @@
         <v>318</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>323</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="387">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -248,6 +248,9 @@
     <t>propuesta nucleo rodeteOT 4316</t>
   </si>
   <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
     <t>Generación OC Rodete OT 4316,Propuesta compras:</t>
   </si>
   <si>
@@ -480,6 +483,9 @@
     <t>Generacion OC Fabricación Externa OT 4316,Fabricación estructura proveedor externo OT 4316</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214777561529541</t>
   </si>
   <si>
@@ -739,9 +745,6 @@
   </si>
   <si>
     <t>Armado</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214777626832401</t>
@@ -2616,7 +2619,7 @@
         <v>46197.50227302083</v>
       </c>
       <c r="D17" s="8">
-        <v>46197.502289386575</v>
+        <v>46223.58748662037</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2625,9 +2628,11 @@
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I17" s="8">
         <v>46155</v>
       </c>
@@ -2650,7 +2655,7 @@
         <v>55</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="8">
         <v>46155</v>
@@ -2670,7 +2675,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46155.60580746528</v>
@@ -2679,18 +2684,20 @@
         <v>46196.64233232639</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.56478702546</v>
+        <v>46223.58748332176</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I18" s="5">
         <v>46185</v>
       </c>
@@ -2710,10 +2717,10 @@
         <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="5">
         <v>46185</v>
@@ -2733,7 +2740,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="8">
         <v>46155.605814317125</v>
@@ -2742,18 +2749,20 @@
         <v>46204.9161715625</v>
       </c>
       <c r="D19" s="8">
-        <v>46206.564361412034</v>
+        <v>46223.58747894676</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I19" s="8">
         <v>46185</v>
       </c>
@@ -2773,10 +2782,10 @@
         <v>62</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="8">
         <v>46185</v>
@@ -2796,7 +2805,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5">
         <v>46155.60582009259</v>
@@ -2805,18 +2814,20 @@
         <v>46196.64393914352</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.564197789354</v>
+        <v>46223.58747597222</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I20" s="5">
         <v>46185</v>
       </c>
@@ -2836,10 +2847,10 @@
         <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2859,7 +2870,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="8">
         <v>46155.60582561343</v>
@@ -2868,18 +2879,20 @@
         <v>46196.64456515046</v>
       </c>
       <c r="D21" s="8">
-        <v>46206.56396623843</v>
+        <v>46223.58747038194</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I21" s="8">
         <v>46185</v>
       </c>
@@ -2899,10 +2912,10 @@
         <v>62</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="8">
         <v>46185</v>
@@ -2922,7 +2935,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46155.60562462963</v>
@@ -2932,7 +2945,7 @@
         <v>46216.83238582176</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2956,7 +2969,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2966,12 +2979,12 @@
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
       <c r="U22" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46155.60583177084</v>
@@ -2983,16 +2996,16 @@
         <v>46182.67729332176</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I23" s="8">
         <v>46157</v>
@@ -3010,13 +3023,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q23" s="8">
         <v>46157</v>
@@ -3036,7 +3049,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46155.60583869213</v>
@@ -3048,16 +3061,16 @@
         <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3075,29 +3088,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" s="8">
         <v>46155.605845625</v>
@@ -3109,16 +3122,16 @@
         <v>46182.67726898148</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I25" s="8">
         <v>46161</v>
@@ -3136,29 +3149,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46155.60585226852</v>
@@ -3170,16 +3183,16 @@
         <v>46216.83246247685</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3197,13 +3210,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3223,7 +3236,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46155.605858807874</v>
@@ -3235,16 +3248,16 @@
         <v>46216.83231204861</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I27" s="8">
         <v>46157</v>
@@ -3262,29 +3275,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>71</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46155.605865289355</v>
@@ -3296,16 +3309,16 @@
         <v>46216.832352048616</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3323,29 +3336,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46155.605925254626</v>
@@ -3357,16 +3370,16 @@
         <v>46197.18498747685</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I29" s="8">
         <v>46157</v>
@@ -3384,13 +3397,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q29" s="8">
         <v>46157</v>
@@ -3410,7 +3423,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46155.605932488426</v>
@@ -3422,16 +3435,16 @@
         <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3449,29 +3462,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46155.605939444446</v>
@@ -3483,16 +3496,16 @@
         <v>46182.67711275463</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I31" s="8">
         <v>46168</v>
@@ -3510,29 +3523,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46155.605945868054</v>
@@ -3544,16 +3557,16 @@
         <v>46182.69372545139</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3571,29 +3584,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46155.60595229166</v>
@@ -3605,16 +3618,16 @@
         <v>46205.60921498842</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I33" s="8">
         <v>46189</v>
@@ -3632,13 +3645,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q33" s="8">
         <v>46189</v>
@@ -3658,7 +3671,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46155.60595878473</v>
@@ -3670,16 +3683,16 @@
         <v>46199.55831050926</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3697,29 +3710,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46155.60596540509</v>
@@ -3731,16 +3744,16 @@
         <v>46205.609188692135</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I35" s="8">
         <v>46191</v>
@@ -3752,35 +3765,35 @@
         <v>26</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46155.60597160879</v>
@@ -3792,16 +3805,16 @@
         <v>46205.60961208333</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3819,10 +3832,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3845,7 +3858,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46155.605976770836</v>
@@ -3857,16 +3870,16 @@
         <v>46205.609533587965</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I37" s="8">
         <v>46189</v>
@@ -3884,13 +3897,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3900,7 +3913,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46155.60598313657</v>
@@ -3912,16 +3925,16 @@
         <v>46205.60958704861</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3939,13 +3952,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3955,7 +3968,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46155.60598890047</v>
@@ -3964,19 +3977,19 @@
         <v>46196.6948721875</v>
       </c>
       <c r="D39" s="8">
-        <v>46213.50701678241</v>
+        <v>46223.18303170139</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="8">
         <v>46189</v>
@@ -3994,10 +4007,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -4008,8 +4021,8 @@
       <c r="R39" s="8">
         <v>46230</v>
       </c>
-      <c r="S39" s="11" t="s">
-        <v>98</v>
+      <c r="S39" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4020,7 +4033,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46155.60599439815</v>
@@ -4032,16 +4045,16 @@
         <v>46196.69342819444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4059,13 +4072,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4075,7 +4088,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46155.606000196756</v>
@@ -4087,16 +4100,16 @@
         <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I41" s="8">
         <v>46198</v>
@@ -4114,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4130,7 +4143,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46155.60600616898</v>
@@ -4140,16 +4153,16 @@
         <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4167,10 +4180,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4183,7 +4196,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46155.60601071759</v>
@@ -4195,16 +4208,16 @@
         <v>46211.1922662963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I43" s="8">
         <v>46189</v>
@@ -4222,10 +4235,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4248,7 +4261,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4260,16 +4273,16 @@
         <v>46199.56319799769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4287,13 +4300,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4303,7 +4316,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4315,16 +4328,16 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I45" s="8">
         <v>46191</v>
@@ -4342,13 +4355,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4358,7 +4371,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4368,7 +4381,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4392,7 +4405,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4405,7 +4418,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4417,16 +4430,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4444,13 +4457,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4470,7 +4483,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4482,16 +4495,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4509,13 +4522,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4535,7 +4548,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4547,16 +4560,16 @@
         <v>46195.947667824075</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4572,13 +4585,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4587,7 +4600,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4598,7 +4611,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4608,16 +4621,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4635,10 +4648,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4650,18 +4663,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4671,16 +4684,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4696,13 +4709,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4712,7 +4725,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4722,16 +4735,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4747,13 +4760,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4763,7 +4776,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4773,16 +4786,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4798,13 +4811,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4814,7 +4827,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4824,16 +4837,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4849,13 +4862,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4865,7 +4878,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4875,16 +4888,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4900,13 +4913,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4916,7 +4929,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4928,7 +4941,7 @@
         <v>46213.506286655094</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4952,7 +4965,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4969,7 +4982,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4981,16 +4994,16 @@
         <v>46216.60285269676</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5008,13 +5021,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5034,7 +5047,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5046,16 +5059,16 @@
         <v>46213.50624159722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46204</v>
@@ -5073,13 +5086,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5094,12 +5107,12 @@
         <v>1</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5111,16 +5124,16 @@
         <v>46213.50624155093</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5138,13 +5151,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5164,7 +5177,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5176,16 +5189,16 @@
         <v>46213.506277974535</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I60" s="5">
         <v>46204</v>
@@ -5203,13 +5216,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5229,7 +5242,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
@@ -5241,16 +5254,16 @@
         <v>46213.17611152778</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5268,13 +5281,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5294,7 +5307,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46155.60616390046</v>
@@ -5306,16 +5319,16 @@
         <v>46217.18131804398</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I62" s="5">
         <v>46213</v>
@@ -5333,13 +5346,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5359,7 +5372,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B63" s="8">
         <v>46155.60617082176</v>
@@ -5369,7 +5382,7 @@
         <v>46213.50618732639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5393,7 +5406,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5406,7 +5419,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46155.60617413194</v>
@@ -5416,16 +5429,16 @@
         <v>46220.189402627315</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5443,13 +5456,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q64" s="5">
         <v>46217</v>
@@ -5464,12 +5477,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46155.60618260417</v>
@@ -5479,16 +5492,16 @@
         <v>46219.16819976852</v>
       </c>
       <c r="E65" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I65" s="8">
         <v>46217</v>
@@ -5506,13 +5519,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5522,7 +5535,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46155.60619106481</v>
@@ -5532,16 +5545,16 @@
         <v>46219.16819619213</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5559,13 +5572,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5575,7 +5588,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46155.60619835649</v>
@@ -5585,16 +5598,16 @@
         <v>46219.168200960645</v>
       </c>
       <c r="E67" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I67" s="8">
         <v>46217</v>
@@ -5612,13 +5625,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5628,7 +5641,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46155.60620543981</v>
@@ -5638,16 +5651,16 @@
         <v>46219.16820241898</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5665,13 +5678,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5681,7 +5694,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B69" s="8">
         <v>46155.60745351852</v>
@@ -5691,16 +5704,16 @@
         <v>46219.16814042824</v>
       </c>
       <c r="E69" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I69" s="8">
         <v>46217</v>
@@ -5718,13 +5731,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5734,7 +5747,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46155.606212638886</v>
@@ -5744,16 +5757,16 @@
         <v>46219.20782984953</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5771,13 +5784,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5786,7 +5799,7 @@
         <v>46226</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>236</v>
+        <v>150</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5797,7 +5810,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46155.60621899305</v>
@@ -5807,16 +5820,16 @@
         <v>46195.9476830787</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I71" s="8">
         <v>46220</v>
@@ -5834,13 +5847,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5850,7 +5863,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46155.606226539356</v>
@@ -5860,16 +5873,16 @@
         <v>46195.9476728125</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5887,13 +5900,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5903,7 +5916,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46155.606234004634</v>
@@ -5913,16 +5926,16 @@
         <v>46195.94767699074</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I73" s="8">
         <v>46220</v>
@@ -5940,13 +5953,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5956,7 +5969,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46155.60628421296</v>
@@ -5966,16 +5979,16 @@
         <v>46195.94767966435</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -5993,13 +6006,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6009,7 +6022,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="8">
         <v>46155.607690034725</v>
@@ -6019,16 +6032,16 @@
         <v>46155.61937777778</v>
       </c>
       <c r="E75" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I75" s="8">
         <v>46220</v>
@@ -6046,13 +6059,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6062,7 +6075,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46155.606291909724</v>
@@ -6072,16 +6085,16 @@
         <v>46220.19536815972</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6099,13 +6112,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q76" s="5">
         <v>46227</v>
@@ -6114,7 +6127,7 @@
         <v>46227</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>236</v>
+        <v>150</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6125,7 +6138,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B77" s="8">
         <v>46155.60629884259</v>
@@ -6135,16 +6148,16 @@
         <v>46195.947673518516</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I77" s="8">
         <v>46227</v>
@@ -6162,13 +6175,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6178,7 +6191,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46155.60630622685</v>
@@ -6188,16 +6201,16 @@
         <v>46195.947674131945</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6215,13 +6228,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6231,7 +6244,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46155.6063134375</v>
@@ -6241,16 +6254,16 @@
         <v>46195.94768039352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I79" s="8">
         <v>46227</v>
@@ -6268,13 +6281,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6284,7 +6297,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46155.606319722225</v>
@@ -6294,16 +6307,16 @@
         <v>46195.94768090278</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6321,13 +6334,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6337,7 +6350,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B81" s="8">
         <v>46155.618322951384</v>
@@ -6347,16 +6360,16 @@
         <v>46155.620736377314</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6372,13 +6385,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6388,7 +6401,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5">
         <v>46155.60632542824</v>
@@ -6398,7 +6411,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6422,7 +6435,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6435,7 +6448,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B83" s="8">
         <v>46155.60632868056</v>
@@ -6445,16 +6458,16 @@
         <v>46216.83236861111</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6470,13 +6483,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="8">
         <v>46181</v>
@@ -6491,12 +6504,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
         <v>46155.60633650463</v>
@@ -6506,16 +6519,16 @@
         <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6533,13 +6546,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q84" s="5">
         <v>46164</v>
@@ -6554,12 +6567,12 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B85" s="8">
         <v>46155.60634402778</v>
@@ -6569,16 +6582,16 @@
         <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6596,13 +6609,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="8">
         <v>46197</v>
@@ -6617,12 +6630,12 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46155.60635177083</v>
@@ -6632,16 +6645,16 @@
         <v>46196.693516562504</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6659,13 +6672,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q86" s="5">
         <v>46231</v>
@@ -6674,18 +6687,18 @@
         <v>46231</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
         <v>46155.606361921295</v>
@@ -6695,7 +6708,7 @@
         <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6719,7 +6732,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6732,25 +6745,27 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B88" s="5">
         <v>46155.60636525463</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.620355625</v>
+        <v>46223.58828070602</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I88" s="5">
         <v>46230</v>
       </c>
@@ -6767,13 +6782,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q88" s="5">
         <v>46230</v>
@@ -6782,36 +6797,38 @@
         <v>46234</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" s="8">
         <v>46155.606374525465</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.621619502315</v>
+        <v>46223.58759539352</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I89" s="8">
         <v>46230</v>
       </c>
@@ -6828,10 +6845,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>26</v>
@@ -6844,25 +6861,27 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46155.60638027778</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.62163603009</v>
+        <v>46223.58759473379</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I90" s="5">
         <v>46230</v>
       </c>
@@ -6879,10 +6898,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6895,25 +6914,27 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46155.60638583334</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46155.62166074074</v>
+        <v>46223.58759408565</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I91" s="8">
         <v>46230</v>
       </c>
@@ -6930,13 +6951,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6946,25 +6967,27 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46155.60639179398</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.62167399305</v>
+        <v>46223.5875934375</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I92" s="5">
         <v>46230</v>
       </c>
@@ -6981,13 +7004,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6997,25 +7020,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B93" s="8">
         <v>46155.61975986111</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46155.62169508102</v>
+        <v>46223.58759278935</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I93" s="8">
         <v>46230</v>
       </c>
@@ -7032,13 +7057,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7048,25 +7073,27 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46155.60639783565</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.62191585648</v>
+        <v>46223.588280069445</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I94" s="5">
         <v>46237</v>
       </c>
@@ -7083,13 +7110,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q94" s="5">
         <v>46237</v>
@@ -7098,36 +7125,38 @@
         <v>46237</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B95" s="8">
         <v>46155.60640402778</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.947681273145</v>
+        <v>46223.58770425926</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
         <v>46237</v>
@@ -7142,13 +7171,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7158,25 +7187,27 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46155.60641090278</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.94768182871</v>
+        <v>46223.58770364583</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
         <v>46237</v>
@@ -7191,13 +7222,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7207,25 +7238,27 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B97" s="8">
         <v>46155.60641760417</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.94768232639</v>
+        <v>46223.58770305556</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I97" s="9"/>
       <c r="J97" s="8">
         <v>46237</v>
@@ -7240,13 +7273,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7256,25 +7289,27 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
         <v>46155.60642649306</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.947674641204</v>
+        <v>46223.587702488425</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
         <v>46237</v>
@@ -7289,13 +7324,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7305,25 +7340,27 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B99" s="8">
         <v>46155.62115946759</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46155.64240027778</v>
+        <v>46223.587701909724</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
         <v>46237</v>
@@ -7338,13 +7375,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7354,25 +7391,27 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B100" s="5">
         <v>46155.60648232639</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.631670462964</v>
+        <v>46223.58827945602</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I100" s="5">
         <v>46238</v>
       </c>
@@ -7389,13 +7428,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q100" s="5">
         <v>46238</v>
@@ -7404,36 +7443,38 @@
         <v>46238</v>
       </c>
       <c r="S100" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B101" s="8">
         <v>46155.60649042824</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.947675324074</v>
+        <v>46223.58782059028</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
         <v>46238</v>
@@ -7448,13 +7489,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7464,25 +7505,27 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B102" s="5">
         <v>46155.6064993287</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.947678958335</v>
+        <v>46223.58781990741</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
         <v>46238</v>
@@ -7497,13 +7540,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7513,25 +7556,27 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B103" s="8">
         <v>46155.606507951394</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.94768271991</v>
+        <v>46223.587819259265</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I103" s="9"/>
       <c r="J103" s="8">
         <v>46238</v>
@@ -7546,13 +7591,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7562,25 +7607,27 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B104" s="5">
         <v>46155.60651716436</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46195.94768359954</v>
+        <v>46223.58781857639</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
         <v>46238</v>
@@ -7595,13 +7642,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7611,25 +7658,27 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B105" s="8">
         <v>46155.6221815162</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46155.63179349537</v>
+        <v>46223.587817928244</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I105" s="9"/>
       <c r="J105" s="8">
         <v>46238</v>
@@ -7644,13 +7693,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7660,25 +7709,27 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B106" s="5">
         <v>46155.60652579861</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.63455996528</v>
+        <v>46223.58827881944</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I106" s="5">
         <v>46239</v>
       </c>
@@ -7695,13 +7746,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q106" s="5">
         <v>46239</v>
@@ -7710,36 +7761,38 @@
         <v>46239</v>
       </c>
       <c r="S106" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
       <c r="U106" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B107" s="8">
         <v>46155.606533032405</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46195.94767760417</v>
+        <v>46223.587958344906</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I107" s="9"/>
       <c r="J107" s="8">
         <v>46239</v>
@@ -7754,13 +7807,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7770,25 +7823,27 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B108" s="5">
         <v>46155.60654145833</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46195.947678344906</v>
+        <v>46223.58795771991</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
         <v>46239</v>
@@ -7803,13 +7858,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7819,25 +7874,27 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B109" s="8">
         <v>46155.60655399306</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46195.947675868054</v>
+        <v>46223.587957094904</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
         <v>46239</v>
@@ -7852,13 +7909,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -7868,25 +7925,27 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B110" s="5">
         <v>46155.60656262732</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46195.947676435186</v>
+        <v>46223.58795648148</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46239</v>
@@ -7901,13 +7960,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7917,25 +7976,27 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B111" s="8">
         <v>46155.63011625</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46155.63465961805</v>
+        <v>46223.58795587963</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
         <v>46239</v>
@@ -7950,13 +8011,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -7966,25 +8027,27 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B112" s="5">
         <v>46155.60657109953</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.63577444444</v>
+        <v>46223.58827820602</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I112" s="5">
         <v>46240</v>
       </c>
@@ -8001,13 +8064,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q112" s="5">
         <v>46240</v>
@@ -8016,36 +8079,38 @@
         <v>46240</v>
       </c>
       <c r="S112" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B113" s="8">
         <v>46155.60657833333</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46155.635128090275</v>
+        <v>46223.58806811343</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I113" s="8">
         <v>46240</v>
       </c>
@@ -8062,13 +8127,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8078,25 +8143,27 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B114" s="5">
         <v>46155.60658640046</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.63525575231</v>
+        <v>46223.588067488425</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I114" s="5">
         <v>46240</v>
       </c>
@@ -8113,13 +8180,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8129,25 +8196,27 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B115" s="8">
         <v>46155.60659408565</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46155.635268750004</v>
+        <v>46223.58806685185</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I115" s="8">
         <v>46240</v>
       </c>
@@ -8164,13 +8233,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8180,25 +8249,27 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B116" s="5">
         <v>46155.60660233797</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.635292569445</v>
+        <v>46223.588066192126</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H116" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I116" s="5">
         <v>46240</v>
       </c>
@@ -8215,13 +8286,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8231,25 +8302,27 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B117" s="8">
         <v>46155.63398136574</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46155.63581856481</v>
+        <v>46223.58806555555</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
         <v>46240</v>
@@ -8264,13 +8337,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8280,25 +8353,27 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B118" s="5">
         <v>46155.60664190972</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.63694791667</v>
+        <v>46223.588277523144</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I118" s="5">
         <v>46244</v>
       </c>
@@ -8315,13 +8390,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q118" s="5">
         <v>46244</v>
@@ -8330,36 +8405,38 @@
         <v>46244</v>
       </c>
       <c r="S118" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
       </c>
       <c r="U118" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B119" s="8">
         <v>46155.60665081019</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46155.63810030093</v>
+        <v>46223.58818715278</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
         <v>46244</v>
@@ -8374,13 +8451,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8390,25 +8467,27 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B120" s="5">
         <v>46155.60665825232</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.6381218287</v>
+        <v>46223.588186493056</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
         <v>46244</v>
@@ -8423,13 +8502,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8439,25 +8518,27 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B121" s="8">
         <v>46155.60666534722</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46155.63813651621</v>
+        <v>46223.58818568287</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
         <v>46244</v>
@@ -8472,13 +8553,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8488,25 +8569,27 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B122" s="5">
         <v>46155.60667253472</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.63815179398</v>
+        <v>46223.588184837965</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
         <v>46244</v>
@@ -8521,13 +8604,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8537,25 +8620,27 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B123" s="8">
         <v>46155.63591585648</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46155.63817207176</v>
+        <v>46223.58818416667</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
         <v>46244</v>
@@ -8570,13 +8655,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8586,7 +8671,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B124" s="5">
         <v>46155.606679502314</v>
@@ -8596,7 +8681,7 @@
         <v>46155.60689462963</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>25</v>
@@ -8620,7 +8705,7 @@
         <v>26</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>26</v>
@@ -8633,7 +8718,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B125" s="8">
         <v>46155.60668334491</v>
@@ -8643,16 +8728,16 @@
         <v>46155.63803638889</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -8668,13 +8753,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q125" s="8">
         <v>46245</v>
@@ -8683,18 +8768,18 @@
         <v>46245</v>
       </c>
       <c r="S125" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
       </c>
       <c r="U125" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B126" s="5">
         <v>46155.606691759254</v>
@@ -8704,16 +8789,16 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8729,13 +8814,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8745,7 +8830,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B127" s="8">
         <v>46155.60669864583</v>
@@ -8755,16 +8840,16 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -8780,13 +8865,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -8796,7 +8881,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46155.60670615741</v>
@@ -8806,16 +8891,16 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8831,13 +8916,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8847,7 +8932,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B129" s="8">
         <v>46155.606713009256</v>
@@ -8857,16 +8942,16 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -8882,13 +8967,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -8898,7 +8983,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B130" s="5">
         <v>46155.63715556713</v>
@@ -8908,16 +8993,16 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -8933,13 +9018,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8949,25 +9034,27 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B131" s="8">
         <v>46155.60671987268</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46155.638912615745</v>
+        <v>46223.58841814815</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H131" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I131" s="8">
         <v>46246</v>
       </c>
@@ -8984,13 +9071,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q131" s="8">
         <v>46246</v>
@@ -8999,36 +9086,38 @@
         <v>46246</v>
       </c>
       <c r="S131" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
       </c>
       <c r="U131" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B132" s="5">
         <v>46155.60672658565</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.639826238425</v>
+        <v>46223.58837571759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H132" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I132" s="5">
         <v>46246</v>
       </c>
@@ -9045,13 +9134,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9061,25 +9150,27 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B133" s="8">
         <v>46155.60673355324</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46155.63983615741</v>
+        <v>46223.58837508102</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H133" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I133" s="8">
         <v>46246</v>
       </c>
@@ -9096,13 +9187,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9112,25 +9203,27 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B134" s="5">
         <v>46155.60674053241</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.639844942125</v>
+        <v>46223.588374375</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H134" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I134" s="5">
         <v>46246</v>
       </c>
@@ -9147,13 +9240,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9163,25 +9256,27 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B135" s="8">
         <v>46155.60674741898</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46155.63986869213</v>
+        <v>46223.58837366899</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H135" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="I135" s="8">
         <v>46246</v>
       </c>
@@ -9198,13 +9293,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9214,25 +9309,27 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B136" s="5">
         <v>46155.63830266204</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.63990003472</v>
+        <v>46223.58837290509</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H136" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
         <v>46246</v>
@@ -9247,13 +9344,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9263,7 +9360,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B137" s="8">
         <v>46155.60675400463</v>
@@ -9273,16 +9370,16 @@
         <v>46155.64036164352</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I137" s="8">
         <v>46247</v>
@@ -9300,13 +9397,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q137" s="8">
         <v>46247</v>
@@ -9315,18 +9412,18 @@
         <v>46247</v>
       </c>
       <c r="S137" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
       </c>
       <c r="U137" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B138" s="5">
         <v>46155.60676105324</v>
@@ -9336,16 +9433,16 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9361,13 +9458,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9377,7 +9474,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B139" s="8">
         <v>46155.60677012731</v>
@@ -9387,16 +9484,16 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9412,13 +9509,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9428,7 +9525,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B140" s="5">
         <v>46155.60681737268</v>
@@ -9438,16 +9535,16 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9463,13 +9560,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9479,7 +9576,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B141" s="8">
         <v>46155.60682548611</v>
@@ -9489,16 +9586,16 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9514,13 +9611,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9530,7 +9627,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B142" s="5">
         <v>46155.63928425926</v>
@@ -9540,16 +9637,16 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9565,13 +9662,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9581,7 +9678,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B143" s="8">
         <v>46155.60683229167</v>
@@ -9591,16 +9688,16 @@
         <v>46155.641985821756</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I143" s="8">
         <v>46248</v>
@@ -9618,13 +9715,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q143" s="8">
         <v>46248</v>
@@ -9633,18 +9730,18 @@
         <v>46248</v>
       </c>
       <c r="S143" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
       </c>
       <c r="U143" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B144" s="5">
         <v>46155.606840486114</v>
@@ -9654,16 +9751,16 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9679,13 +9776,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9695,7 +9792,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B145" s="8">
         <v>46155.60684746528</v>
@@ -9705,16 +9802,16 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9730,13 +9827,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -9746,7 +9843,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B146" s="5">
         <v>46155.60685387731</v>
@@ -9756,16 +9853,16 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9781,13 +9878,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9797,7 +9894,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B147" s="8">
         <v>46155.60686101852</v>
@@ -9807,16 +9904,16 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -9832,13 +9929,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -9848,7 +9945,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B148" s="5">
         <v>46155.64052775463</v>
@@ -9858,16 +9955,16 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -9883,13 +9980,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9899,7 +9996,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B149" s="8">
         <v>46155.60686797454</v>
@@ -9909,7 +10006,7 @@
         <v>46155.60689638889</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>25</v>
@@ -9933,7 +10030,7 @@
         <v>26</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -9946,7 +10043,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B150" s="5">
         <v>46155.60687207176</v>
@@ -9956,16 +10053,16 @@
         <v>46155.60689709491</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I150" s="5">
         <v>46251</v>
@@ -9983,13 +10080,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q150" s="5">
         <v>46251</v>
@@ -9998,18 +10095,18 @@
         <v>46255</v>
       </c>
       <c r="S150" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
       </c>
       <c r="U150" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B151" s="8">
         <v>46155.606879259256</v>
@@ -10019,7 +10116,7 @@
         <v>46195.54676386574</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10046,13 +10143,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q151" s="8">
         <v>46251</v>
@@ -10061,13 +10158,13 @@
         <v>46255</v>
       </c>
       <c r="S151" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T151" s="9">
         <v>0</v>
       </c>
       <c r="U151" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -6642,7 +6642,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46196.693516562504</v>
+        <v>46224.177094502316</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>267</v>
@@ -6686,8 +6686,8 @@
       <c r="R86" s="5">
         <v>46231</v>
       </c>
-      <c r="S86" s="11" t="s">
-        <v>99</v>
+      <c r="S86" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="388">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodeteOT 4316</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2631,7 +2634,7 @@
         <v>72</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" s="8">
         <v>46155</v>
@@ -2655,7 +2658,7 @@
         <v>55</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="8">
         <v>46155</v>
@@ -2675,7 +2678,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46155.60580746528</v>
@@ -2687,7 +2690,7 @@
         <v>46223.58748332176</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2696,7 +2699,7 @@
         <v>72</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" s="5">
         <v>46185</v>
@@ -2717,10 +2720,10 @@
         <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46185</v>
@@ -2740,7 +2743,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="8">
         <v>46155.605814317125</v>
@@ -2752,7 +2755,7 @@
         <v>46223.58747894676</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2761,7 +2764,7 @@
         <v>72</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" s="8">
         <v>46185</v>
@@ -2782,10 +2785,10 @@
         <v>62</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="8">
         <v>46185</v>
@@ -2805,7 +2808,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46155.60582009259</v>
@@ -2817,7 +2820,7 @@
         <v>46223.58747597222</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2826,7 +2829,7 @@
         <v>72</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" s="5">
         <v>46185</v>
@@ -2847,10 +2850,10 @@
         <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2870,7 +2873,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8">
         <v>46155.60582561343</v>
@@ -2882,7 +2885,7 @@
         <v>46223.58747038194</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2891,7 +2894,7 @@
         <v>72</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" s="8">
         <v>46185</v>
@@ -2912,10 +2915,10 @@
         <v>62</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46185</v>
@@ -2935,7 +2938,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46155.60562462963</v>
@@ -2945,7 +2948,7 @@
         <v>46216.83238582176</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2969,7 +2972,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2979,12 +2982,12 @@
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
       <c r="U22" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46155.60583177084</v>
@@ -2996,16 +2999,16 @@
         <v>46182.67729332176</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46157</v>
@@ -3023,13 +3026,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q23" s="8">
         <v>46157</v>
@@ -3049,7 +3052,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46155.60583869213</v>
@@ -3061,16 +3064,16 @@
         <v>46182.653276006946</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3088,29 +3091,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="8">
         <v>46155.605845625</v>
@@ -3122,16 +3125,16 @@
         <v>46182.67726898148</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="8">
         <v>46161</v>
@@ -3149,29 +3152,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46155.60585226852</v>
@@ -3183,16 +3186,16 @@
         <v>46216.83246247685</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3210,13 +3213,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3236,7 +3239,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46155.605858807874</v>
@@ -3248,16 +3251,16 @@
         <v>46216.83231204861</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I27" s="8">
         <v>46157</v>
@@ -3275,29 +3278,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>71</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46155.605865289355</v>
@@ -3309,16 +3312,16 @@
         <v>46216.832352048616</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3336,29 +3339,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46155.605925254626</v>
@@ -3370,16 +3373,16 @@
         <v>46197.18498747685</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I29" s="8">
         <v>46157</v>
@@ -3397,13 +3400,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q29" s="8">
         <v>46157</v>
@@ -3423,7 +3426,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46155.605932488426</v>
@@ -3435,16 +3438,16 @@
         <v>46182.65308653935</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3462,29 +3465,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46155.605939444446</v>
@@ -3496,16 +3499,16 @@
         <v>46182.67711275463</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I31" s="8">
         <v>46168</v>
@@ -3523,29 +3526,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46155.605945868054</v>
@@ -3557,16 +3560,16 @@
         <v>46182.69372545139</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3584,29 +3587,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46155.60595229166</v>
@@ -3618,16 +3621,16 @@
         <v>46205.60921498842</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="8">
         <v>46189</v>
@@ -3645,13 +3648,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q33" s="8">
         <v>46189</v>
@@ -3671,7 +3674,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46155.60595878473</v>
@@ -3683,16 +3686,16 @@
         <v>46199.55831050926</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3710,29 +3713,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46155.60596540509</v>
@@ -3744,16 +3747,16 @@
         <v>46205.609188692135</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="8">
         <v>46191</v>
@@ -3765,35 +3768,35 @@
         <v>26</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46155.60597160879</v>
@@ -3805,16 +3808,16 @@
         <v>46205.60961208333</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3832,10 +3835,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3858,7 +3861,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8">
         <v>46155.605976770836</v>
@@ -3870,16 +3873,16 @@
         <v>46205.609533587965</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="8">
         <v>46189</v>
@@ -3897,13 +3900,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3913,7 +3916,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46155.60598313657</v>
@@ -3925,16 +3928,16 @@
         <v>46205.60958704861</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3952,13 +3955,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3968,7 +3971,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46155.60598890047</v>
@@ -3980,16 +3983,16 @@
         <v>46223.18303170139</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46189</v>
@@ -4007,10 +4010,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -4022,7 +4025,7 @@
         <v>46230</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4033,7 +4036,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46155.60599439815</v>
@@ -4045,16 +4048,16 @@
         <v>46196.69342819444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4072,13 +4075,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4088,7 +4091,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="8">
         <v>46155.606000196756</v>
@@ -4100,16 +4103,16 @@
         <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46198</v>
@@ -4127,13 +4130,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4143,7 +4146,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46155.60600616898</v>
@@ -4153,16 +4156,16 @@
         <v>46196.69350203704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4180,10 +4183,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4196,7 +4199,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B43" s="8">
         <v>46155.60601071759</v>
@@ -4208,16 +4211,16 @@
         <v>46211.1922662963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="8">
         <v>46189</v>
@@ -4235,10 +4238,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4261,7 +4264,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4273,16 +4276,16 @@
         <v>46199.56319799769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4300,13 +4303,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4316,7 +4319,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4328,16 +4331,16 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I45" s="8">
         <v>46191</v>
@@ -4355,13 +4358,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4371,7 +4374,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4381,7 +4384,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4405,7 +4408,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4418,7 +4421,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4430,16 +4433,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4457,13 +4460,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4483,7 +4486,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4495,16 +4498,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4522,13 +4525,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4548,7 +4551,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4560,16 +4563,16 @@
         <v>46195.947667824075</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4585,13 +4588,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4600,7 +4603,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4611,7 +4614,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4621,16 +4624,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4648,10 +4651,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4663,18 +4666,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4684,16 +4687,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4709,13 +4712,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4725,7 +4728,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4735,16 +4738,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4760,13 +4763,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4776,7 +4779,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4786,16 +4789,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4811,13 +4814,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4827,7 +4830,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4837,16 +4840,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4862,13 +4865,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4878,7 +4881,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4888,16 +4891,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4913,13 +4916,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4929,7 +4932,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4941,7 +4944,7 @@
         <v>46213.506286655094</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4965,7 +4968,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4982,7 +4985,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4994,16 +4997,16 @@
         <v>46216.60285269676</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5021,13 +5024,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5047,7 +5050,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5059,16 +5062,16 @@
         <v>46213.50624159722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I58" s="5">
         <v>46204</v>
@@ -5086,13 +5089,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5107,12 +5110,12 @@
         <v>1</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5124,16 +5127,16 @@
         <v>46213.50624155093</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5151,13 +5154,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5177,7 +5180,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5189,16 +5192,16 @@
         <v>46213.506277974535</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I60" s="5">
         <v>46204</v>
@@ -5216,13 +5219,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5242,7 +5245,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
@@ -5254,16 +5257,16 @@
         <v>46213.17611152778</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5281,13 +5284,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5307,7 +5310,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46155.60616390046</v>
@@ -5319,16 +5322,16 @@
         <v>46217.18131804398</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I62" s="5">
         <v>46213</v>
@@ -5346,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5372,7 +5375,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46155.60617082176</v>
@@ -5382,7 +5385,7 @@
         <v>46213.50618732639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5406,7 +5409,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5419,7 +5422,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46155.60617413194</v>
@@ -5429,16 +5432,16 @@
         <v>46220.189402627315</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5456,13 +5459,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46217</v>
@@ -5477,12 +5480,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46155.60618260417</v>
@@ -5492,16 +5495,16 @@
         <v>46219.16819976852</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I65" s="8">
         <v>46217</v>
@@ -5519,13 +5522,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5535,7 +5538,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46155.60619106481</v>
@@ -5545,16 +5548,16 @@
         <v>46219.16819619213</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5572,13 +5575,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5588,7 +5591,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="8">
         <v>46155.60619835649</v>
@@ -5598,16 +5601,16 @@
         <v>46219.168200960645</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I67" s="8">
         <v>46217</v>
@@ -5625,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5641,7 +5644,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46155.60620543981</v>
@@ -5651,16 +5654,16 @@
         <v>46219.16820241898</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5678,13 +5681,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5694,7 +5697,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" s="8">
         <v>46155.60745351852</v>
@@ -5704,16 +5707,16 @@
         <v>46219.16814042824</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I69" s="8">
         <v>46217</v>
@@ -5731,13 +5734,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5747,7 +5750,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46155.606212638886</v>
@@ -5757,16 +5760,16 @@
         <v>46219.20782984953</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5784,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5799,7 +5802,7 @@
         <v>46226</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5810,7 +5813,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46155.60621899305</v>
@@ -5820,16 +5823,16 @@
         <v>46195.9476830787</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I71" s="8">
         <v>46220</v>
@@ -5847,13 +5850,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5863,7 +5866,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46155.606226539356</v>
@@ -5873,16 +5876,16 @@
         <v>46195.9476728125</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5900,13 +5903,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5916,7 +5919,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46155.606234004634</v>
@@ -5926,16 +5929,16 @@
         <v>46195.94767699074</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I73" s="8">
         <v>46220</v>
@@ -5953,13 +5956,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5969,7 +5972,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46155.60628421296</v>
@@ -5979,16 +5982,16 @@
         <v>46195.94767966435</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -6006,13 +6009,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6022,7 +6025,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="8">
         <v>46155.607690034725</v>
@@ -6032,16 +6035,16 @@
         <v>46155.61937777778</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I75" s="8">
         <v>46220</v>
@@ -6059,13 +6062,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6075,7 +6078,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46155.606291909724</v>
@@ -6085,16 +6088,16 @@
         <v>46220.19536815972</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6112,13 +6115,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q76" s="5">
         <v>46227</v>
@@ -6127,7 +6130,7 @@
         <v>46227</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6138,7 +6141,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46155.60629884259</v>
@@ -6148,16 +6151,16 @@
         <v>46195.947673518516</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I77" s="8">
         <v>46227</v>
@@ -6175,13 +6178,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6191,7 +6194,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46155.60630622685</v>
@@ -6201,16 +6204,16 @@
         <v>46195.947674131945</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6228,13 +6231,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6244,7 +6247,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46155.6063134375</v>
@@ -6254,16 +6257,16 @@
         <v>46195.94768039352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I79" s="8">
         <v>46227</v>
@@ -6281,13 +6284,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6297,7 +6300,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46155.606319722225</v>
@@ -6307,16 +6310,16 @@
         <v>46195.94768090278</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6334,13 +6337,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6350,7 +6353,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B81" s="8">
         <v>46155.618322951384</v>
@@ -6360,16 +6363,16 @@
         <v>46155.620736377314</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6385,13 +6388,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6401,7 +6404,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46155.60632542824</v>
@@ -6411,7 +6414,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6435,7 +6438,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6448,7 +6451,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B83" s="8">
         <v>46155.60632868056</v>
@@ -6458,16 +6461,16 @@
         <v>46216.83236861111</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6483,13 +6486,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="8">
         <v>46181</v>
@@ -6504,12 +6507,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46155.60633650463</v>
@@ -6519,16 +6522,16 @@
         <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6546,13 +6549,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q84" s="5">
         <v>46164</v>
@@ -6567,12 +6570,12 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46155.60634402778</v>
@@ -6582,16 +6585,16 @@
         <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6609,13 +6612,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q85" s="8">
         <v>46197</v>
@@ -6630,12 +6633,12 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46155.60635177083</v>
@@ -6645,16 +6648,16 @@
         <v>46224.177094502316</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6672,13 +6675,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="5">
         <v>46231</v>
@@ -6687,18 +6690,18 @@
         <v>46231</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B87" s="8">
         <v>46155.606361921295</v>
@@ -6708,7 +6711,7 @@
         <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6732,7 +6735,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6745,7 +6748,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46155.60636525463</v>
@@ -6755,7 +6758,7 @@
         <v>46223.58828070602</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6764,7 +6767,7 @@
         <v>72</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" s="5">
         <v>46230</v>
@@ -6782,13 +6785,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q88" s="5">
         <v>46230</v>
@@ -6797,18 +6800,18 @@
         <v>46234</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="8">
         <v>46155.606374525465</v>
@@ -6818,7 +6821,7 @@
         <v>46223.58759539352</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6827,7 +6830,7 @@
         <v>72</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" s="8">
         <v>46230</v>
@@ -6845,10 +6848,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>26</v>
@@ -6861,7 +6864,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46155.60638027778</v>
@@ -6871,7 +6874,7 @@
         <v>46223.58759473379</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6880,7 +6883,7 @@
         <v>72</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" s="5">
         <v>46230</v>
@@ -6898,10 +6901,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6914,7 +6917,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46155.60638583334</v>
@@ -6924,7 +6927,7 @@
         <v>46223.58759408565</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6933,7 +6936,7 @@
         <v>72</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" s="8">
         <v>46230</v>
@@ -6951,13 +6954,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6967,7 +6970,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46155.60639179398</v>
@@ -6977,7 +6980,7 @@
         <v>46223.5875934375</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6986,7 +6989,7 @@
         <v>72</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I92" s="5">
         <v>46230</v>
@@ -7004,13 +7007,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7020,7 +7023,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
         <v>46155.61975986111</v>
@@ -7030,7 +7033,7 @@
         <v>46223.58759278935</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7039,7 +7042,7 @@
         <v>72</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I93" s="8">
         <v>46230</v>
@@ -7057,13 +7060,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7073,7 +7076,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46155.60639783565</v>
@@ -7083,7 +7086,7 @@
         <v>46223.588280069445</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7092,7 +7095,7 @@
         <v>72</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" s="5">
         <v>46237</v>
@@ -7110,13 +7113,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q94" s="5">
         <v>46237</v>
@@ -7125,18 +7128,18 @@
         <v>46237</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B95" s="8">
         <v>46155.60640402778</v>
@@ -7146,7 +7149,7 @@
         <v>46223.58770425926</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7155,7 +7158,7 @@
         <v>72</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -7171,13 +7174,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7187,7 +7190,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46155.60641090278</v>
@@ -7197,7 +7200,7 @@
         <v>46223.58770364583</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7206,7 +7209,7 @@
         <v>72</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7222,13 +7225,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7238,7 +7241,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B97" s="8">
         <v>46155.60641760417</v>
@@ -7248,7 +7251,7 @@
         <v>46223.58770305556</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7257,7 +7260,7 @@
         <v>72</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="8">
@@ -7273,13 +7276,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7289,7 +7292,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46155.60642649306</v>
@@ -7299,7 +7302,7 @@
         <v>46223.587702488425</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7308,7 +7311,7 @@
         <v>72</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7324,13 +7327,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7340,7 +7343,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B99" s="8">
         <v>46155.62115946759</v>
@@ -7350,7 +7353,7 @@
         <v>46223.587701909724</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7359,7 +7362,7 @@
         <v>72</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7375,13 +7378,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7391,7 +7394,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46155.60648232639</v>
@@ -7401,7 +7404,7 @@
         <v>46223.58827945602</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7410,7 +7413,7 @@
         <v>72</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I100" s="5">
         <v>46238</v>
@@ -7428,13 +7431,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q100" s="5">
         <v>46238</v>
@@ -7443,18 +7446,18 @@
         <v>46238</v>
       </c>
       <c r="S100" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B101" s="8">
         <v>46155.60649042824</v>
@@ -7464,7 +7467,7 @@
         <v>46223.58782059028</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7473,7 +7476,7 @@
         <v>72</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
@@ -7489,13 +7492,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7505,7 +7508,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B102" s="5">
         <v>46155.6064993287</v>
@@ -7515,7 +7518,7 @@
         <v>46223.58781990741</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7524,7 +7527,7 @@
         <v>72</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7540,13 +7543,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7556,7 +7559,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B103" s="8">
         <v>46155.606507951394</v>
@@ -7566,7 +7569,7 @@
         <v>46223.587819259265</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7575,7 +7578,7 @@
         <v>72</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I103" s="9"/>
       <c r="J103" s="8">
@@ -7591,13 +7594,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7607,7 +7610,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B104" s="5">
         <v>46155.60651716436</v>
@@ -7617,7 +7620,7 @@
         <v>46223.58781857639</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7626,7 +7629,7 @@
         <v>72</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7642,13 +7645,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7658,7 +7661,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B105" s="8">
         <v>46155.6221815162</v>
@@ -7668,7 +7671,7 @@
         <v>46223.587817928244</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7677,7 +7680,7 @@
         <v>72</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I105" s="9"/>
       <c r="J105" s="8">
@@ -7693,13 +7696,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7709,7 +7712,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B106" s="5">
         <v>46155.60652579861</v>
@@ -7719,7 +7722,7 @@
         <v>46223.58827881944</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7728,7 +7731,7 @@
         <v>72</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I106" s="5">
         <v>46239</v>
@@ -7746,13 +7749,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q106" s="5">
         <v>46239</v>
@@ -7761,18 +7764,18 @@
         <v>46239</v>
       </c>
       <c r="S106" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
       <c r="U106" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B107" s="8">
         <v>46155.606533032405</v>
@@ -7782,7 +7785,7 @@
         <v>46223.587958344906</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7791,7 +7794,7 @@
         <v>72</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I107" s="9"/>
       <c r="J107" s="8">
@@ -7807,13 +7810,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7823,7 +7826,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
         <v>46155.60654145833</v>
@@ -7833,7 +7836,7 @@
         <v>46223.58795771991</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7842,7 +7845,7 @@
         <v>72</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7858,13 +7861,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7874,7 +7877,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B109" s="8">
         <v>46155.60655399306</v>
@@ -7884,7 +7887,7 @@
         <v>46223.587957094904</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7893,7 +7896,7 @@
         <v>72</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
@@ -7909,13 +7912,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -7925,7 +7928,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B110" s="5">
         <v>46155.60656262732</v>
@@ -7935,7 +7938,7 @@
         <v>46223.58795648148</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7944,7 +7947,7 @@
         <v>72</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -7960,13 +7963,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7976,7 +7979,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B111" s="8">
         <v>46155.63011625</v>
@@ -7986,7 +7989,7 @@
         <v>46223.58795587963</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -7995,7 +7998,7 @@
         <v>72</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
@@ -8011,13 +8014,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8027,7 +8030,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
         <v>46155.60657109953</v>
@@ -8037,7 +8040,7 @@
         <v>46223.58827820602</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8046,7 +8049,7 @@
         <v>72</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I112" s="5">
         <v>46240</v>
@@ -8064,13 +8067,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q112" s="5">
         <v>46240</v>
@@ -8079,18 +8082,18 @@
         <v>46240</v>
       </c>
       <c r="S112" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B113" s="8">
         <v>46155.60657833333</v>
@@ -8100,7 +8103,7 @@
         <v>46223.58806811343</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8109,7 +8112,7 @@
         <v>72</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I113" s="8">
         <v>46240</v>
@@ -8127,13 +8130,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8143,7 +8146,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
         <v>46155.60658640046</v>
@@ -8153,7 +8156,7 @@
         <v>46223.588067488425</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8162,7 +8165,7 @@
         <v>72</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I114" s="5">
         <v>46240</v>
@@ -8180,13 +8183,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8196,7 +8199,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B115" s="8">
         <v>46155.60659408565</v>
@@ -8206,7 +8209,7 @@
         <v>46223.58806685185</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8215,7 +8218,7 @@
         <v>72</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I115" s="8">
         <v>46240</v>
@@ -8233,13 +8236,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8249,7 +8252,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B116" s="5">
         <v>46155.60660233797</v>
@@ -8259,7 +8262,7 @@
         <v>46223.588066192126</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8268,7 +8271,7 @@
         <v>72</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I116" s="5">
         <v>46240</v>
@@ -8286,13 +8289,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8302,7 +8305,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B117" s="8">
         <v>46155.63398136574</v>
@@ -8312,7 +8315,7 @@
         <v>46223.58806555555</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8321,7 +8324,7 @@
         <v>72</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8337,13 +8340,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8353,7 +8356,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B118" s="5">
         <v>46155.60664190972</v>
@@ -8363,7 +8366,7 @@
         <v>46223.588277523144</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8372,7 +8375,7 @@
         <v>72</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I118" s="5">
         <v>46244</v>
@@ -8390,13 +8393,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q118" s="5">
         <v>46244</v>
@@ -8405,18 +8408,18 @@
         <v>46244</v>
       </c>
       <c r="S118" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
       </c>
       <c r="U118" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B119" s="8">
         <v>46155.60665081019</v>
@@ -8426,7 +8429,7 @@
         <v>46223.58818715278</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8435,7 +8438,7 @@
         <v>72</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8451,13 +8454,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8467,7 +8470,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B120" s="5">
         <v>46155.60665825232</v>
@@ -8477,7 +8480,7 @@
         <v>46223.588186493056</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8486,7 +8489,7 @@
         <v>72</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8502,13 +8505,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8518,7 +8521,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B121" s="8">
         <v>46155.60666534722</v>
@@ -8528,7 +8531,7 @@
         <v>46223.58818568287</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8537,7 +8540,7 @@
         <v>72</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8553,13 +8556,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8569,7 +8572,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B122" s="5">
         <v>46155.60667253472</v>
@@ -8579,7 +8582,7 @@
         <v>46223.588184837965</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8588,7 +8591,7 @@
         <v>72</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8604,13 +8607,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8620,7 +8623,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B123" s="8">
         <v>46155.63591585648</v>
@@ -8630,7 +8633,7 @@
         <v>46223.58818416667</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8639,7 +8642,7 @@
         <v>72</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -8655,13 +8658,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8671,7 +8674,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B124" s="5">
         <v>46155.606679502314</v>
@@ -8681,7 +8684,7 @@
         <v>46155.60689462963</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>25</v>
@@ -8705,7 +8708,7 @@
         <v>26</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>26</v>
@@ -8718,7 +8721,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B125" s="8">
         <v>46155.60668334491</v>
@@ -8728,16 +8731,16 @@
         <v>46155.63803638889</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -8753,13 +8756,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q125" s="8">
         <v>46245</v>
@@ -8768,18 +8771,18 @@
         <v>46245</v>
       </c>
       <c r="S125" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
       </c>
       <c r="U125" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B126" s="5">
         <v>46155.606691759254</v>
@@ -8789,16 +8792,16 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8814,13 +8817,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8830,7 +8833,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B127" s="8">
         <v>46155.60669864583</v>
@@ -8840,16 +8843,16 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -8865,13 +8868,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -8881,7 +8884,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B128" s="5">
         <v>46155.60670615741</v>
@@ -8891,16 +8894,16 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8916,13 +8919,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8932,7 +8935,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B129" s="8">
         <v>46155.606713009256</v>
@@ -8942,16 +8945,16 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -8967,13 +8970,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -8983,7 +8986,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B130" s="5">
         <v>46155.63715556713</v>
@@ -8993,16 +8996,16 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9018,13 +9021,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9034,7 +9037,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B131" s="8">
         <v>46155.60671987268</v>
@@ -9044,7 +9047,7 @@
         <v>46223.58841814815</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9053,7 +9056,7 @@
         <v>72</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I131" s="8">
         <v>46246</v>
@@ -9071,13 +9074,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q131" s="8">
         <v>46246</v>
@@ -9086,18 +9089,18 @@
         <v>46246</v>
       </c>
       <c r="S131" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
       </c>
       <c r="U131" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B132" s="5">
         <v>46155.60672658565</v>
@@ -9107,7 +9110,7 @@
         <v>46223.58837571759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9116,7 +9119,7 @@
         <v>72</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I132" s="5">
         <v>46246</v>
@@ -9134,13 +9137,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9150,7 +9153,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B133" s="8">
         <v>46155.60673355324</v>
@@ -9160,7 +9163,7 @@
         <v>46223.58837508102</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9169,7 +9172,7 @@
         <v>72</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I133" s="8">
         <v>46246</v>
@@ -9187,13 +9190,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9203,7 +9206,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B134" s="5">
         <v>46155.60674053241</v>
@@ -9213,7 +9216,7 @@
         <v>46223.588374375</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9222,7 +9225,7 @@
         <v>72</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I134" s="5">
         <v>46246</v>
@@ -9240,13 +9243,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9256,7 +9259,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B135" s="8">
         <v>46155.60674741898</v>
@@ -9266,7 +9269,7 @@
         <v>46223.58837366899</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9275,7 +9278,7 @@
         <v>72</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I135" s="8">
         <v>46246</v>
@@ -9293,13 +9296,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9309,7 +9312,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B136" s="5">
         <v>46155.63830266204</v>
@@ -9319,7 +9322,7 @@
         <v>46223.58837290509</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9328,7 +9331,7 @@
         <v>72</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9344,13 +9347,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9360,7 +9363,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B137" s="8">
         <v>46155.60675400463</v>
@@ -9370,16 +9373,16 @@
         <v>46155.64036164352</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I137" s="8">
         <v>46247</v>
@@ -9397,13 +9400,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q137" s="8">
         <v>46247</v>
@@ -9412,18 +9415,18 @@
         <v>46247</v>
       </c>
       <c r="S137" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
       </c>
       <c r="U137" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B138" s="5">
         <v>46155.60676105324</v>
@@ -9433,16 +9436,16 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9458,13 +9461,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9474,7 +9477,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B139" s="8">
         <v>46155.60677012731</v>
@@ -9484,16 +9487,16 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9509,13 +9512,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9525,7 +9528,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B140" s="5">
         <v>46155.60681737268</v>
@@ -9535,16 +9538,16 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9560,13 +9563,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9576,7 +9579,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B141" s="8">
         <v>46155.60682548611</v>
@@ -9586,16 +9589,16 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9611,13 +9614,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9627,7 +9630,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B142" s="5">
         <v>46155.63928425926</v>
@@ -9637,16 +9640,16 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9662,13 +9665,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9678,7 +9681,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B143" s="8">
         <v>46155.60683229167</v>
@@ -9688,16 +9691,16 @@
         <v>46155.641985821756</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I143" s="8">
         <v>46248</v>
@@ -9715,13 +9718,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q143" s="8">
         <v>46248</v>
@@ -9730,18 +9733,18 @@
         <v>46248</v>
       </c>
       <c r="S143" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
       </c>
       <c r="U143" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B144" s="5">
         <v>46155.606840486114</v>
@@ -9751,16 +9754,16 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9776,13 +9779,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9792,7 +9795,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B145" s="8">
         <v>46155.60684746528</v>
@@ -9802,16 +9805,16 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9827,13 +9830,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -9843,7 +9846,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B146" s="5">
         <v>46155.60685387731</v>
@@ -9853,16 +9856,16 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9878,13 +9881,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9894,7 +9897,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B147" s="8">
         <v>46155.60686101852</v>
@@ -9904,16 +9907,16 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -9929,13 +9932,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -9945,7 +9948,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B148" s="5">
         <v>46155.64052775463</v>
@@ -9955,16 +9958,16 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -9980,13 +9983,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9996,7 +9999,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B149" s="8">
         <v>46155.60686797454</v>
@@ -10006,7 +10009,7 @@
         <v>46155.60689638889</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>25</v>
@@ -10030,7 +10033,7 @@
         <v>26</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -10043,7 +10046,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B150" s="5">
         <v>46155.60687207176</v>
@@ -10053,16 +10056,16 @@
         <v>46155.60689709491</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I150" s="5">
         <v>46251</v>
@@ -10080,13 +10083,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q150" s="5">
         <v>46251</v>
@@ -10095,18 +10098,18 @@
         <v>46255</v>
       </c>
       <c r="S150" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
       </c>
       <c r="U150" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B151" s="8">
         <v>46155.606879259256</v>
@@ -10116,7 +10119,7 @@
         <v>46195.54676386574</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10143,13 +10146,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q151" s="8">
         <v>46251</v>
@@ -10158,13 +10161,13 @@
         <v>46255</v>
       </c>
       <c r="S151" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T151" s="9">
         <v>0</v>
       </c>
       <c r="U151" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -5757,7 +5757,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46219.20782984953</v>
+        <v>46226.16794501158</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>238</v>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.9476830787</v>
+        <v>46226.16794724537</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>228</v>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.9476728125</v>
+        <v>46226.16793981481</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.94767699074</v>
+        <v>46226.167942141205</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>228</v>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.94767966435</v>
+        <v>46226.1679434375</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>228</v>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46155.61937777778</v>
+        <v>46226.16795292824</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>228</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.69350203704</v>
+        <v>46230.168518125</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46226.16794501158</v>
+        <v>46227.19015055556</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>238</v>
@@ -5801,8 +5801,8 @@
       <c r="R70" s="5">
         <v>46226</v>
       </c>
-      <c r="S70" s="12" t="s">
-        <v>151</v>
+      <c r="S70" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46220.19536815972</v>
+        <v>46228.168985682874</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>248</v>
@@ -6129,8 +6129,8 @@
       <c r="R76" s="5">
         <v>46227</v>
       </c>
-      <c r="S76" s="12" t="s">
-        <v>151</v>
+      <c r="S76" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.947673518516</v>
+        <v>46227.16857658565</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>228</v>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.947674131945</v>
+        <v>46227.16857197917</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>228</v>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.94768039352</v>
+        <v>46227.1685733912</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>228</v>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.94768090278</v>
+        <v>46227.16857782408</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>228</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46155.620736377314</v>
+        <v>46227.16852841435</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>228</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46223.58828070602</v>
+        <v>46227.18063835648</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>274</v>
@@ -6799,8 +6799,8 @@
       <c r="R88" s="5">
         <v>46234</v>
       </c>
-      <c r="S88" s="11" t="s">
-        <v>100</v>
+      <c r="S88" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46223.588280069445</v>
+        <v>46230.18689565972</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -7127,8 +7127,8 @@
       <c r="R94" s="5">
         <v>46237</v>
       </c>
-      <c r="S94" s="11" t="s">
-        <v>100</v>
+      <c r="S94" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -486,361 +486,361 @@
     <t>Generacion OC Fabricación Externa OT 4316,Fabricación estructura proveedor externo OT 4316</t>
   </si>
   <si>
+    <t>1214777561529541</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4316,Fabricación estructura proveedor externo OT 4316</t>
+  </si>
+  <si>
+    <t>1214777481739477</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4316,Control de calidad fabricación externa  OT 4316,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214777561549650</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4316</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214777561549666</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1214777561549676</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1214777626638198</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1214739697907733</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214777626638213</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214777594225816</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4316</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214777594236456</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4316,propuesta Corte Laser OT 4316,Propuesta Corte plasma OT 4316,Propuesta Mecanizado OT 4316,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777293059955</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777293059971</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>check pruebas FAT, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777626730373</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214777626730389</t>
+  </si>
+  <si>
+    <t>1214777626758296</t>
+  </si>
+  <si>
+    <t>1214739697907775</t>
+  </si>
+  <si>
+    <t>1214777626758308</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1214777626758318</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214777626772872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777594376340</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214777561694352</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777561694373</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214777561702202</t>
+  </si>
+  <si>
+    <t>1214777561721939</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Control de calidad Armado,Armado</t>
+  </si>
+  <si>
+    <t>1214777561721949</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>1214777561722180</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777481868346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214777594413806</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214777594413833</t>
+  </si>
+  <si>
+    <t>1214739697907735</t>
+  </si>
+  <si>
+    <t>1214777594424435</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1214777626832401</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,check planos</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,Armado</t>
+  </si>
+  <si>
+    <t>1214777293166745</t>
+  </si>
+  <si>
+    <t>Armado,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777481903037</t>
+  </si>
+  <si>
+    <t>1214777561693151</t>
+  </si>
+  <si>
+    <t>1214739697907737</t>
+  </si>
+  <si>
+    <t>1214777594459054</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214777594459075</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT4316  ZVN 1-9-25/4,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214777293216113</t>
+  </si>
+  <si>
+    <t>1214777293224523</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777594502664</t>
+  </si>
+  <si>
+    <t>1214739697907750</t>
+  </si>
+  <si>
+    <t>1214777594502686</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214777626941208</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777626943342</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:</t>
+  </si>
+  <si>
+    <t>1214777626943368</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Bodega:, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777482036119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Revestimiento</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777561529541</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4316,Fabricación estructura proveedor externo OT 4316</t>
-  </si>
-  <si>
-    <t>1214777481739477</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4316,Control de calidad fabricación externa  OT 4316,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214777561549650</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4316</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214777561549666</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1214777561549676</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1214777626638198</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1214739697907733</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214777626638213</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214777594225816</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4316</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214777594236456</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4316,propuesta Corte Laser OT 4316,Propuesta Corte plasma OT 4316,Propuesta Mecanizado OT 4316,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777293059955</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777293059971</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>check pruebas FAT, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777626730373</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214777626730389</t>
-  </si>
-  <si>
-    <t>1214777626758296</t>
-  </si>
-  <si>
-    <t>1214739697907775</t>
-  </si>
-  <si>
-    <t>1214777626758308</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1214777626758318</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214777626772872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777594376340</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214777561694352</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777561694373</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214777561702202</t>
-  </si>
-  <si>
-    <t>1214777561721939</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Control de calidad Armado,Armado</t>
-  </si>
-  <si>
-    <t>1214777561721949</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>1214777561722180</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777481868346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214777594413806</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214777594413833</t>
-  </si>
-  <si>
-    <t>1214739697907735</t>
-  </si>
-  <si>
-    <t>1214777594424435</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1214777626832401</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,check planos</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,Armado</t>
-  </si>
-  <si>
-    <t>1214777293166745</t>
-  </si>
-  <si>
-    <t>Armado,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777481903037</t>
-  </si>
-  <si>
-    <t>1214777561693151</t>
-  </si>
-  <si>
-    <t>1214739697907737</t>
-  </si>
-  <si>
-    <t>1214777594459054</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214777594459075</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT4316  ZVN 1-9-25/4,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214777293216113</t>
-  </si>
-  <si>
-    <t>1214777293224523</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777594502664</t>
-  </si>
-  <si>
-    <t>1214739697907750</t>
-  </si>
-  <si>
-    <t>1214777594502686</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214777626941208</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777626943342</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:</t>
-  </si>
-  <si>
-    <t>1214777626943368</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Bodega:, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777482036119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Revestimiento</t>
   </si>
   <si>
     <t>1214777561915411</t>
@@ -3980,7 +3980,7 @@
         <v>46196.6948721875</v>
       </c>
       <c r="D39" s="8">
-        <v>46223.18303170139</v>
+        <v>46231.17694027778</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>147</v>
@@ -4024,8 +4024,8 @@
       <c r="R39" s="8">
         <v>46230</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>151</v>
+      <c r="S39" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4036,7 +4036,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46155.60599439815</v>
@@ -4081,7 +4081,7 @@
         <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4091,7 +4091,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46155.606000196756</v>
@@ -4103,7 +4103,7 @@
         <v>46196.69349420139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
@@ -4136,7 +4136,7 @@
         <v>87</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46155.60600616898</v>
@@ -4156,16 +4156,16 @@
         <v>46230.168518125</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4186,7 +4186,7 @@
         <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4199,7 +4199,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46155.60601071759</v>
@@ -4211,7 +4211,7 @@
         <v>46211.1922662963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4241,7 +4241,7 @@
         <v>89</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46155.60601423611</v>
@@ -4303,13 +4303,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46155.60601877315</v>
@@ -4331,7 +4331,7 @@
         <v>46199.56324628472</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4358,13 +4358,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46155.60562939815</v>
@@ -4384,7 +4384,7 @@
         <v>46197.71336900463</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4408,7 +4408,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46155.60602364583</v>
@@ -4433,16 +4433,16 @@
         <v>46197.71427196759</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46162</v>
@@ -4460,13 +4460,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46162</v>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46155.606031076386</v>
@@ -4498,16 +4498,16 @@
         <v>46197.71433108796</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4525,13 +4525,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4551,7 +4551,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46155.606038645834</v>
@@ -4569,10 +4569,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4588,13 +4588,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46184</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46155.606091747686</v>
@@ -4624,16 +4624,16 @@
         <v>46155.63491418981</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4651,10 +4651,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4687,16 +4687,16 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4712,13 +4712,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4738,16 +4738,16 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4763,13 +4763,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4779,7 +4779,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4789,16 +4789,16 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4814,13 +4814,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4840,16 +4840,16 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4865,13 +4865,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4891,16 +4891,16 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4916,13 +4916,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4932,7 +4932,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4944,7 +4944,7 @@
         <v>46213.506286655094</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4968,7 +4968,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -4997,16 +4997,16 @@
         <v>46216.60285269676</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5024,13 +5024,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>135</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5062,16 +5062,16 @@
         <v>46213.50624159722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I58" s="5">
         <v>46204</v>
@@ -5089,13 +5089,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5127,16 +5127,16 @@
         <v>46213.50624155093</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5154,13 +5154,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>144</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5180,7 +5180,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5192,16 +5192,16 @@
         <v>46213.506277974535</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I60" s="5">
         <v>46204</v>
@@ -5219,13 +5219,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5245,7 +5245,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
@@ -5257,16 +5257,16 @@
         <v>46213.17611152778</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5284,13 +5284,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5310,7 +5310,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46155.60616390046</v>
@@ -5322,16 +5322,16 @@
         <v>46217.18131804398</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I62" s="5">
         <v>46213</v>
@@ -5349,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B63" s="8">
         <v>46155.60617082176</v>
@@ -5385,7 +5385,7 @@
         <v>46213.50618732639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5409,7 +5409,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46155.60617413194</v>
@@ -5432,16 +5432,16 @@
         <v>46220.189402627315</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5459,13 +5459,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q64" s="5">
         <v>46217</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46155.60618260417</v>
@@ -5495,16 +5495,16 @@
         <v>46219.16819976852</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I65" s="8">
         <v>46217</v>
@@ -5522,13 +5522,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5538,7 +5538,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46155.60619106481</v>
@@ -5548,16 +5548,16 @@
         <v>46219.16819619213</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5575,13 +5575,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5591,7 +5591,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46155.60619835649</v>
@@ -5601,16 +5601,16 @@
         <v>46219.168200960645</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I67" s="8">
         <v>46217</v>
@@ -5628,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46155.60620543981</v>
@@ -5654,16 +5654,16 @@
         <v>46219.16820241898</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5681,13 +5681,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B69" s="8">
         <v>46155.60745351852</v>
@@ -5707,16 +5707,16 @@
         <v>46219.16814042824</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I69" s="8">
         <v>46217</v>
@@ -5734,13 +5734,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46155.606212638886</v>
@@ -5760,16 +5760,16 @@
         <v>46227.19015055556</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5787,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5813,7 +5813,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46155.60621899305</v>
@@ -5823,16 +5823,16 @@
         <v>46226.16794724537</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I71" s="8">
         <v>46220</v>
@@ -5850,13 +5850,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5866,7 +5866,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46155.606226539356</v>
@@ -5876,16 +5876,16 @@
         <v>46226.16793981481</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5903,13 +5903,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5919,7 +5919,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46155.606234004634</v>
@@ -5929,16 +5929,16 @@
         <v>46226.167942141205</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I73" s="8">
         <v>46220</v>
@@ -5956,13 +5956,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5972,7 +5972,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46155.60628421296</v>
@@ -5982,16 +5982,16 @@
         <v>46226.1679434375</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -6009,13 +6009,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6025,7 +6025,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B75" s="8">
         <v>46155.607690034725</v>
@@ -6035,16 +6035,16 @@
         <v>46226.16795292824</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I75" s="8">
         <v>46220</v>
@@ -6062,13 +6062,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6078,7 +6078,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46155.606291909724</v>
@@ -6088,16 +6088,16 @@
         <v>46228.168985682874</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6115,13 +6115,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q76" s="5">
         <v>46227</v>
@@ -6141,7 +6141,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B77" s="8">
         <v>46155.60629884259</v>
@@ -6151,16 +6151,16 @@
         <v>46227.16857658565</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I77" s="8">
         <v>46227</v>
@@ -6178,13 +6178,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46155.60630622685</v>
@@ -6204,16 +6204,16 @@
         <v>46227.16857197917</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I78" s="5">
         <v>46227</v>
@@ -6231,13 +6231,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6247,7 +6247,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46155.6063134375</v>
@@ -6257,16 +6257,16 @@
         <v>46227.1685733912</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I79" s="8">
         <v>46227</v>
@@ -6284,13 +6284,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46155.606319722225</v>
@@ -6310,16 +6310,16 @@
         <v>46227.16857782408</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I80" s="5">
         <v>46227</v>
@@ -6337,13 +6337,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6353,7 +6353,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B81" s="8">
         <v>46155.618322951384</v>
@@ -6363,16 +6363,16 @@
         <v>46227.16852841435</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6388,13 +6388,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6404,7 +6404,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5">
         <v>46155.60632542824</v>
@@ -6414,7 +6414,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6438,7 +6438,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6451,7 +6451,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B83" s="8">
         <v>46155.60632868056</v>
@@ -6461,16 +6461,16 @@
         <v>46216.83236861111</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6486,13 +6486,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="8">
         <v>46181</v>
@@ -6512,7 +6512,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
         <v>46155.60633650463</v>
@@ -6522,16 +6522,16 @@
         <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6549,13 +6549,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q84" s="5">
         <v>46164</v>
@@ -6575,7 +6575,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B85" s="8">
         <v>46155.60634402778</v>
@@ -6585,16 +6585,16 @@
         <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6612,13 +6612,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>121</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="8">
         <v>46197</v>
@@ -6638,26 +6638,26 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46155.60635177083</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46224.177094502316</v>
+        <v>46231.16805121528</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6675,13 +6675,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q86" s="5">
         <v>46231</v>
@@ -6690,7 +6690,7 @@
         <v>46231</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>151</v>
+        <v>269</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6800,7 +6800,7 @@
         <v>46234</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>151</v>
+        <v>269</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6821,7 +6821,7 @@
         <v>46223.58759539352</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6874,7 +6874,7 @@
         <v>46223.58759473379</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6927,7 +6927,7 @@
         <v>46223.58759408565</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6957,7 +6957,7 @@
         <v>274</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>280</v>
@@ -6980,7 +6980,7 @@
         <v>46223.5875934375</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7010,7 +7010,7 @@
         <v>274</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>282</v>
@@ -7033,7 +7033,7 @@
         <v>46223.58759278935</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7063,10 +7063,10 @@
         <v>274</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7116,7 +7116,7 @@
         <v>271</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>271</v>
@@ -7128,7 +7128,7 @@
         <v>46237</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>151</v>
+        <v>269</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>46223.58770425926</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7200,7 +7200,7 @@
         <v>46223.58770364583</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7251,7 +7251,7 @@
         <v>46223.58770305556</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7302,7 +7302,7 @@
         <v>46223.587702488425</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7353,7 +7353,7 @@
         <v>46223.587701909724</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7381,7 +7381,7 @@
         <v>285</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>292</v>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46223.58827945602</v>
+        <v>46231.16978491898</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7434,7 +7434,7 @@
         <v>271</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>271</v>
@@ -7445,8 +7445,8 @@
       <c r="R100" s="5">
         <v>46238</v>
       </c>
-      <c r="S100" s="11" t="s">
-        <v>100</v>
+      <c r="S100" s="12" t="s">
+        <v>269</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7467,7 +7467,7 @@
         <v>46223.58782059028</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7518,7 +7518,7 @@
         <v>46223.58781990741</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7569,7 +7569,7 @@
         <v>46223.587819259265</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7620,7 +7620,7 @@
         <v>46223.58781857639</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7671,7 +7671,7 @@
         <v>46223.587817928244</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7699,7 +7699,7 @@
         <v>296</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>305</v>
@@ -7785,7 +7785,7 @@
         <v>46223.587958344906</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7836,7 +7836,7 @@
         <v>46223.58795771991</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7887,7 +7887,7 @@
         <v>46223.587957094904</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7938,7 +7938,7 @@
         <v>46223.58795648148</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7989,7 +7989,7 @@
         <v>46223.58795587963</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8017,7 +8017,7 @@
         <v>307</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>318</v>
@@ -8103,7 +8103,7 @@
         <v>46223.58806811343</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8133,7 +8133,7 @@
         <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>322</v>
@@ -8156,7 +8156,7 @@
         <v>46223.588067488425</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8186,7 +8186,7 @@
         <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>322</v>
@@ -8209,7 +8209,7 @@
         <v>46223.58806685185</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8239,7 +8239,7 @@
         <v>320</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>325</v>
@@ -8262,7 +8262,7 @@
         <v>46223.588066192126</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8292,7 +8292,7 @@
         <v>320</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>325</v>
@@ -8315,7 +8315,7 @@
         <v>46223.58806555555</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8343,7 +8343,7 @@
         <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>322</v>
@@ -8429,7 +8429,7 @@
         <v>46223.58818715278</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8457,7 +8457,7 @@
         <v>329</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>332</v>
@@ -8480,7 +8480,7 @@
         <v>46223.588186493056</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8508,7 +8508,7 @@
         <v>329</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>334</v>
@@ -8531,7 +8531,7 @@
         <v>46223.58818568287</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8559,7 +8559,7 @@
         <v>329</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>332</v>
@@ -8582,7 +8582,7 @@
         <v>46223.588184837965</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8610,7 +8610,7 @@
         <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>334</v>
@@ -8633,7 +8633,7 @@
         <v>46223.58818416667</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8661,7 +8661,7 @@
         <v>329</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>334</v>
@@ -8792,7 +8792,7 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8820,7 +8820,7 @@
         <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>347</v>
@@ -8843,7 +8843,7 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8871,7 +8871,7 @@
         <v>342</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>347</v>
@@ -8894,7 +8894,7 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8922,7 +8922,7 @@
         <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>350</v>
@@ -8945,7 +8945,7 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -8973,7 +8973,7 @@
         <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>347</v>
@@ -8996,7 +8996,7 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9024,7 +9024,7 @@
         <v>342</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>347</v>
@@ -9110,7 +9110,7 @@
         <v>46223.58837571759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9140,7 +9140,7 @@
         <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>356</v>
@@ -9163,7 +9163,7 @@
         <v>46223.58837508102</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9193,7 +9193,7 @@
         <v>354</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>358</v>
@@ -9216,7 +9216,7 @@
         <v>46223.588374375</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9246,7 +9246,7 @@
         <v>354</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>356</v>
@@ -9269,7 +9269,7 @@
         <v>46223.58837366899</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9299,7 +9299,7 @@
         <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>358</v>
@@ -9322,7 +9322,7 @@
         <v>46223.58837290509</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9350,7 +9350,7 @@
         <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>356</v>
@@ -9379,10 +9379,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I137" s="8">
         <v>46247</v>
@@ -9436,16 +9436,16 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9464,7 +9464,7 @@
         <v>363</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>365</v>
@@ -9487,16 +9487,16 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9515,7 +9515,7 @@
         <v>363</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>365</v>
@@ -9538,16 +9538,16 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9566,7 +9566,7 @@
         <v>363</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>368</v>
@@ -9589,16 +9589,16 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9617,7 +9617,7 @@
         <v>363</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>368</v>
@@ -9640,16 +9640,16 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9668,7 +9668,7 @@
         <v>363</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>368</v>
@@ -9697,10 +9697,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I143" s="8">
         <v>46248</v>
@@ -9754,16 +9754,16 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9782,7 +9782,7 @@
         <v>372</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>372</v>
@@ -9805,16 +9805,16 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9833,7 +9833,7 @@
         <v>372</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>372</v>
@@ -9856,16 +9856,16 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9884,7 +9884,7 @@
         <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>372</v>
@@ -9907,16 +9907,16 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -9935,7 +9935,7 @@
         <v>372</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>372</v>
@@ -9958,16 +9958,16 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -9986,7 +9986,7 @@
         <v>372</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>372</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -127,7 +127,27 @@
     <t>francisca@zitron.com</t>
   </si>
   <si>
-    <t>Este proyecto contiene dos ventiladores horizontales y dos verticales. ZVR-1-22-90/6 (W22 Carcasa de Hierro Gris) MOTOR (2) 90 KW – 06 POLOS – 380 V -60 HZ- 1000 msnm. Resistente al fuego 250°C / 2 horas Sentido de giro bidireccional Frame: 250 Forma constructiva: B3T Protección: IP55 Refrigeración: TEFC Calentamiento: CLASE B Servicio: S1 Factor de Servicio: 1,15 Rendimiento: IE1 Aislamiento: clase H Arranque: VDF Caja de bornes en el exterior del ventilador Sondas: Sondas de temperatura PTC en los devanados Sondas de temperatura PTC 100 en cojinetes Sonda Stall (anti-bombeo) (Directo e inverso) Sonda de caudal (Directo e inverso) Sonda de vibraciones Sonda de rodamientos PT100 PT100 de temperatura de aire ZVRv-1-22-90/6 (W22 Carcasa de Hierro Gris) MOTOR (2) 90 KW – 06 POLOS – 380 V -60 HZ- 1000 msnm. Resistente al fuego 250°C / 2 horas Sentido de giro bidireccional Frame: 250 Forma constructiva: B3T Protección: IP5</t>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1546 se tiene 5 ventiladores ZVN 1-9-25/4 para Xemortiz (Torex Gold):  
+    Fabricación / Planos:
+·         O/4316 - Ventilador ZVN 1-9-25/4 con motor por definir.
+·         Alcance: Carcasa
+    Selección de Rodete:
+        Rodete de placas s/plano 4999.00
+        Alabe s/ plano 4999.01
+        Z8 N590
+        Código 300000
+        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
+    Tratamiento superficial estándar Zitron:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001 Blanco.
+    Datos eléctricos motor:
+·         Motor 25 kW, 460V, 2 Polos, IE3, 60HZ
+·         Frame por definir
+    Fecha de entrega: 22-06-2026
+Quedo atenta.
+Saludos,</t>
   </si>
   <si>
     <t>1214777481492618</t>
@@ -840,25 +860,25 @@
     <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Revestimiento</t>
   </si>
   <si>
+    <t>1214777561915411</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,Pruebas FAT,Montaje motor,Montaje Alabe,Revestimiento,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214777561915421</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Recepcion fabricación externa </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777561915411</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,Pruebas FAT,Montaje motor,Montaje Alabe,Revestimiento,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214777561915421</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Recepcion fabricación externa </t>
   </si>
   <si>
     <t>1214777626999692</t>
@@ -1939,7 +1959,7 @@
         <v>46161.62364042824</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.76969591435</v>
+        <v>46232.53297554398</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2002,7 +2022,7 @@
         <v>46161.62365674769</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.62382879629</v>
+        <v>46232.53318608797</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>40</v>
@@ -2024,7 +2044,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>26</v>
@@ -6645,7 +6665,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46231.16805121528</v>
+        <v>46232.17399734954</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>267</v>
@@ -6689,8 +6709,8 @@
       <c r="R86" s="5">
         <v>46231</v>
       </c>
-      <c r="S86" s="12" t="s">
-        <v>269</v>
+      <c r="S86" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6701,7 +6721,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
         <v>46155.606361921295</v>
@@ -6711,7 +6731,7 @@
         <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6735,7 +6755,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6748,7 +6768,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B88" s="5">
         <v>46155.60636525463</v>
@@ -6758,7 +6778,7 @@
         <v>46227.18063835648</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6785,13 +6805,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q88" s="5">
         <v>46230</v>
@@ -6800,7 +6820,7 @@
         <v>46234</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6848,7 +6868,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>277</v>
@@ -6901,7 +6921,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>277</v>
@@ -6954,7 +6974,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>227</v>
@@ -7007,7 +7027,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>227</v>
@@ -7060,7 +7080,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>227</v>
@@ -7113,13 +7133,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>214</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q94" s="5">
         <v>46237</v>
@@ -7128,7 +7148,7 @@
         <v>46237</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7431,13 +7451,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>214</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q100" s="5">
         <v>46238</v>
@@ -7446,7 +7466,7 @@
         <v>46238</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7719,7 +7739,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46223.58827881944</v>
+        <v>46232.19695251157</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>307</v>
@@ -7749,13 +7769,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>308</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q106" s="5">
         <v>46239</v>
@@ -7763,8 +7783,8 @@
       <c r="R106" s="5">
         <v>46239</v>
       </c>
-      <c r="S106" s="11" t="s">
-        <v>100</v>
+      <c r="S106" s="12" t="s">
+        <v>275</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -8067,13 +8087,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>308</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q112" s="5">
         <v>46240</v>
@@ -8393,7 +8413,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>308</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -8057,7 +8057,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46223.58827820602</v>
+        <v>46233.16823633102</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>320</v>
@@ -8101,8 +8101,8 @@
       <c r="R112" s="5">
         <v>46240</v>
       </c>
-      <c r="S112" s="11" t="s">
-        <v>100</v>
+      <c r="S112" s="12" t="s">
+        <v>275</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -620,6 +620,9 @@
     <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214777293059971</t>
   </si>
   <si>
@@ -876,9 +879,6 @@
   </si>
   <si>
     <t xml:space="preserve">OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214777626999692</t>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.63491418981</v>
+        <v>46234.17252638889</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4685,8 +4685,8 @@
       <c r="R50" s="5">
         <v>46241</v>
       </c>
-      <c r="S50" s="11" t="s">
-        <v>100</v>
+      <c r="S50" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4707,7 +4707,7 @@
         <v>46155.64216699074</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4735,10 +4735,10 @@
         <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4748,7 +4748,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4758,7 +4758,7 @@
         <v>46155.6421837963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4786,10 +4786,10 @@
         <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4799,7 +4799,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4809,7 +4809,7 @@
         <v>46155.64219278935</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
@@ -4837,10 +4837,10 @@
         <v>185</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4860,7 +4860,7 @@
         <v>46155.64220083333</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4888,10 +4888,10 @@
         <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4911,7 +4911,7 @@
         <v>46155.64223084491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -4939,10 +4939,10 @@
         <v>185</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4964,7 +4964,7 @@
         <v>46213.506286655094</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4988,7 +4988,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5005,7 +5005,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -5017,16 +5017,16 @@
         <v>46216.60285269676</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5044,13 +5044,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>135</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5082,7 +5082,7 @@
         <v>46213.50624159722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5109,13 +5109,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5147,16 +5147,16 @@
         <v>46213.50624155093</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5174,13 +5174,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>144</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5212,7 +5212,7 @@
         <v>46213.506277974535</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5239,13 +5239,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
@@ -5277,16 +5277,16 @@
         <v>46213.17611152778</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5304,13 +5304,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>166</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46155.60616390046</v>
@@ -5342,7 +5342,7 @@
         <v>46217.18131804398</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5369,13 +5369,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46155.60617082176</v>
@@ -5405,7 +5405,7 @@
         <v>46213.50618732639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5429,7 +5429,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46155.60617413194</v>
@@ -5452,16 +5452,16 @@
         <v>46220.189402627315</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5479,13 +5479,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46217</v>
@@ -5505,7 +5505,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46155.60618260417</v>
@@ -5515,16 +5515,16 @@
         <v>46219.16819976852</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I65" s="8">
         <v>46217</v>
@@ -5542,13 +5542,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5558,7 +5558,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46155.60619106481</v>
@@ -5568,16 +5568,16 @@
         <v>46219.16819619213</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5595,13 +5595,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5611,7 +5611,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="8">
         <v>46155.60619835649</v>
@@ -5621,16 +5621,16 @@
         <v>46219.168200960645</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I67" s="8">
         <v>46217</v>
@@ -5648,13 +5648,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46155.60620543981</v>
@@ -5674,16 +5674,16 @@
         <v>46219.16820241898</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5701,13 +5701,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" s="8">
         <v>46155.60745351852</v>
@@ -5727,16 +5727,16 @@
         <v>46219.16814042824</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I69" s="8">
         <v>46217</v>
@@ -5754,13 +5754,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46155.606212638886</v>
@@ -5780,16 +5780,16 @@
         <v>46227.19015055556</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5807,13 +5807,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46155.60621899305</v>
@@ -5843,16 +5843,16 @@
         <v>46226.16794724537</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I71" s="8">
         <v>46220</v>
@@ -5870,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46155.606226539356</v>
@@ -5896,16 +5896,16 @@
         <v>46226.16793981481</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5923,13 +5923,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46155.606234004634</v>
@@ -5949,16 +5949,16 @@
         <v>46226.167942141205</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I73" s="8">
         <v>46220</v>
@@ -5976,13 +5976,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5992,7 +5992,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46155.60628421296</v>
@@ -6002,16 +6002,16 @@
         <v>46226.1679434375</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -6029,13 +6029,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="8">
         <v>46155.607690034725</v>
@@ -6055,16 +6055,16 @@
         <v>46226.16795292824</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I75" s="8">
         <v>46220</v>
@@ -6082,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6098,7 +6098,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46155.606291909724</v>
@@ -6108,7 +6108,7 @@
         <v>46228.168985682874</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6135,13 +6135,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q76" s="5">
         <v>46227</v>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46155.60629884259</v>
@@ -6171,7 +6171,7 @@
         <v>46227.16857658565</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6198,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6214,7 +6214,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46155.60630622685</v>
@@ -6224,7 +6224,7 @@
         <v>46227.16857197917</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6251,13 +6251,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6267,7 +6267,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46155.6063134375</v>
@@ -6277,7 +6277,7 @@
         <v>46227.1685733912</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6304,13 +6304,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6320,7 +6320,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46155.606319722225</v>
@@ -6330,7 +6330,7 @@
         <v>46227.16857782408</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6357,13 +6357,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6373,7 +6373,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B81" s="8">
         <v>46155.618322951384</v>
@@ -6383,7 +6383,7 @@
         <v>46227.16852841435</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6408,13 +6408,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6424,7 +6424,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46155.60632542824</v>
@@ -6434,7 +6434,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6458,7 +6458,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6471,7 +6471,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B83" s="8">
         <v>46155.60632868056</v>
@@ -6481,16 +6481,16 @@
         <v>46216.83236861111</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6506,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="8">
         <v>46181</v>
@@ -6532,7 +6532,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46155.60633650463</v>
@@ -6542,16 +6542,16 @@
         <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6569,13 +6569,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q84" s="5">
         <v>46164</v>
@@ -6595,7 +6595,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46155.60634402778</v>
@@ -6605,16 +6605,16 @@
         <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6632,13 +6632,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>121</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q85" s="8">
         <v>46197</v>
@@ -6658,7 +6658,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46155.60635177083</v>
@@ -6668,16 +6668,16 @@
         <v>46232.17399734954</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6695,13 +6695,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>154</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="5">
         <v>46231</v>
@@ -6721,7 +6721,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B87" s="8">
         <v>46155.606361921295</v>
@@ -6731,7 +6731,7 @@
         <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6755,7 +6755,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6768,17 +6768,17 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46155.60636525463</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46227.18063835648</v>
+        <v>46234.16955126157</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6805,13 +6805,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q88" s="5">
         <v>46230</v>
@@ -6820,7 +6820,7 @@
         <v>46234</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6838,10 +6838,10 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46223.58759539352</v>
+        <v>46234.16955460648</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6868,7 +6868,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>277</v>
@@ -6891,10 +6891,10 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46223.58759473379</v>
+        <v>46234.16955314815</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6921,7 +6921,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>277</v>
@@ -6944,10 +6944,10 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46223.58759408565</v>
+        <v>46234.16954859954</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6974,10 +6974,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>280</v>
@@ -6997,10 +6997,10 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46223.5875934375</v>
+        <v>46234.169549872684</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7027,10 +7027,10 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>282</v>
@@ -7050,10 +7050,10 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46223.58759278935</v>
+        <v>46234.169515648144</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7080,13 +7080,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7133,13 +7133,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q94" s="5">
         <v>46237</v>
@@ -7148,7 +7148,7 @@
         <v>46237</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7169,7 +7169,7 @@
         <v>46223.58770425926</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7220,7 +7220,7 @@
         <v>46223.58770364583</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7271,7 +7271,7 @@
         <v>46223.58770305556</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7322,7 +7322,7 @@
         <v>46223.587702488425</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7373,7 +7373,7 @@
         <v>46223.587701909724</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7401,7 +7401,7 @@
         <v>285</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>292</v>
@@ -7451,13 +7451,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q100" s="5">
         <v>46238</v>
@@ -7466,7 +7466,7 @@
         <v>46238</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7487,7 +7487,7 @@
         <v>46223.58782059028</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7538,7 +7538,7 @@
         <v>46223.58781990741</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7589,7 +7589,7 @@
         <v>46223.587819259265</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7640,7 +7640,7 @@
         <v>46223.58781857639</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7691,7 +7691,7 @@
         <v>46223.587817928244</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7719,7 +7719,7 @@
         <v>296</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>305</v>
@@ -7769,13 +7769,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>308</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q106" s="5">
         <v>46239</v>
@@ -7784,7 +7784,7 @@
         <v>46239</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -7805,7 +7805,7 @@
         <v>46223.587958344906</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7856,7 +7856,7 @@
         <v>46223.58795771991</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7907,7 +7907,7 @@
         <v>46223.587957094904</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7958,7 +7958,7 @@
         <v>46223.58795648148</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8009,7 +8009,7 @@
         <v>46223.58795587963</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8037,7 +8037,7 @@
         <v>307</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>318</v>
@@ -8087,13 +8087,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>308</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q112" s="5">
         <v>46240</v>
@@ -8102,7 +8102,7 @@
         <v>46240</v>
       </c>
       <c r="S112" s="12" t="s">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
@@ -8123,7 +8123,7 @@
         <v>46223.58806811343</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8153,7 +8153,7 @@
         <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>322</v>
@@ -8176,7 +8176,7 @@
         <v>46223.588067488425</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8206,7 +8206,7 @@
         <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>322</v>
@@ -8229,7 +8229,7 @@
         <v>46223.58806685185</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8259,7 +8259,7 @@
         <v>320</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>325</v>
@@ -8282,7 +8282,7 @@
         <v>46223.588066192126</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8312,7 +8312,7 @@
         <v>320</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>325</v>
@@ -8335,7 +8335,7 @@
         <v>46223.58806555555</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8363,7 +8363,7 @@
         <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>322</v>
@@ -8413,7 +8413,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>308</v>
@@ -8449,7 +8449,7 @@
         <v>46223.58818715278</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8477,7 +8477,7 @@
         <v>329</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>332</v>
@@ -8500,7 +8500,7 @@
         <v>46223.588186493056</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8528,7 +8528,7 @@
         <v>329</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>334</v>
@@ -8551,7 +8551,7 @@
         <v>46223.58818568287</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8579,7 +8579,7 @@
         <v>329</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>332</v>
@@ -8602,7 +8602,7 @@
         <v>46223.588184837965</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8630,7 +8630,7 @@
         <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>334</v>
@@ -8653,7 +8653,7 @@
         <v>46223.58818416667</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8681,7 +8681,7 @@
         <v>329</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>334</v>
@@ -8812,7 +8812,7 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8840,7 +8840,7 @@
         <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>347</v>
@@ -8863,7 +8863,7 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8891,7 +8891,7 @@
         <v>342</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>347</v>
@@ -8914,7 +8914,7 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8942,7 +8942,7 @@
         <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>350</v>
@@ -8965,7 +8965,7 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -8993,7 +8993,7 @@
         <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>347</v>
@@ -9016,7 +9016,7 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9044,7 +9044,7 @@
         <v>342</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>347</v>
@@ -9130,7 +9130,7 @@
         <v>46223.58837571759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9160,7 +9160,7 @@
         <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>356</v>
@@ -9183,7 +9183,7 @@
         <v>46223.58837508102</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9213,7 +9213,7 @@
         <v>354</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>358</v>
@@ -9236,7 +9236,7 @@
         <v>46223.588374375</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9266,7 +9266,7 @@
         <v>354</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>356</v>
@@ -9289,7 +9289,7 @@
         <v>46223.58837366899</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9319,7 +9319,7 @@
         <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>358</v>
@@ -9342,7 +9342,7 @@
         <v>46223.58837290509</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9370,7 +9370,7 @@
         <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>356</v>
@@ -9399,10 +9399,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I137" s="8">
         <v>46247</v>
@@ -9456,16 +9456,16 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9484,7 +9484,7 @@
         <v>363</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>365</v>
@@ -9507,16 +9507,16 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9535,7 +9535,7 @@
         <v>363</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>365</v>
@@ -9558,16 +9558,16 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9586,7 +9586,7 @@
         <v>363</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>368</v>
@@ -9609,16 +9609,16 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9637,7 +9637,7 @@
         <v>363</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>368</v>
@@ -9660,16 +9660,16 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9688,7 +9688,7 @@
         <v>363</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>368</v>
@@ -9717,10 +9717,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I143" s="8">
         <v>46248</v>
@@ -9774,16 +9774,16 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9802,7 +9802,7 @@
         <v>372</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>372</v>
@@ -9825,16 +9825,16 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9853,7 +9853,7 @@
         <v>372</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>372</v>
@@ -9876,16 +9876,16 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9904,7 +9904,7 @@
         <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>372</v>
@@ -9927,16 +9927,16 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -9955,7 +9955,7 @@
         <v>372</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>372</v>
@@ -9978,16 +9978,16 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10006,7 +10006,7 @@
         <v>372</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>372</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -3703,7 +3703,7 @@
         <v>46199.55808454861</v>
       </c>
       <c r="D34" s="5">
-        <v>46199.55831050926</v>
+        <v>46234.93956866898</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46234.16955126157</v>
+        <v>46235.18961810185</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>274</v>
@@ -6819,8 +6819,8 @@
       <c r="R88" s="5">
         <v>46234</v>
       </c>
-      <c r="S88" s="12" t="s">
-        <v>189</v>
+      <c r="S88" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46235.18961810185</v>
+        <v>46237.53806709491</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>274</v>
@@ -6825,8 +6825,8 @@
       <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="U88" s="10" t="s">
-        <v>101</v>
+      <c r="U88" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46230.18689565972</v>
+        <v>46237.53810893519</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -7153,8 +7153,8 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="10" t="s">
-        <v>101</v>
+      <c r="U94" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46223.58770425926</v>
+        <v>46237.16900178241</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>228</v>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46223.58770364583</v>
+        <v>46237.169003159725</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>228</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46223.58770305556</v>
+        <v>46237.16900524306</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>228</v>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46223.587702488425</v>
+        <v>46237.16900667824</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>228</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46223.587701909724</v>
+        <v>46237.16896111111</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>228</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46231.16978491898</v>
+        <v>46237.5381290625</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7471,8 +7471,8 @@
       <c r="T100" s="6">
         <v>0</v>
       </c>
-      <c r="U100" s="10" t="s">
-        <v>101</v>
+      <c r="U100" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46232.19695251157</v>
+        <v>46237.538152407404</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>307</v>
@@ -7789,8 +7789,8 @@
       <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="U106" s="10" t="s">
-        <v>101</v>
+      <c r="U106" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46233.16823633102</v>
+        <v>46237.538172465276</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>320</v>
@@ -8107,8 +8107,8 @@
       <c r="T112" s="6">
         <v>0</v>
       </c>
-      <c r="U112" s="10" t="s">
-        <v>101</v>
+      <c r="U112" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46223.588277523144</v>
+        <v>46237.16716700231</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>329</v>
@@ -8427,8 +8427,8 @@
       <c r="R118" s="5">
         <v>46244</v>
       </c>
-      <c r="S118" s="11" t="s">
-        <v>100</v>
+      <c r="S118" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46223.58841814815</v>
+        <v>46237.5382402199</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>354</v>
@@ -9114,8 +9114,8 @@
       <c r="T131" s="9">
         <v>0</v>
       </c>
-      <c r="U131" s="10" t="s">
-        <v>101</v>
+      <c r="U131" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -7103,7 +7103,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46237.53810893519</v>
+        <v>46238.19323280093</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -7147,8 +7147,8 @@
       <c r="R94" s="5">
         <v>46237</v>
       </c>
-      <c r="S94" s="12" t="s">
-        <v>189</v>
+      <c r="S94" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46237.5381290625</v>
+        <v>46238.16814222222</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46223.58782059028</v>
+        <v>46238.168144247684</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>228</v>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46223.58781990741</v>
+        <v>46238.168145497686</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>228</v>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46223.587819259265</v>
+        <v>46238.16814678241</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>228</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46223.58781857639</v>
+        <v>46238.168148067125</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>228</v>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46223.587817928244</v>
+        <v>46238.16811709491</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>228</v>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46155.63803638889</v>
+        <v>46238.196791435184</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>342</v>
@@ -8790,8 +8790,8 @@
       <c r="R125" s="8">
         <v>46245</v>
       </c>
-      <c r="S125" s="11" t="s">
-        <v>100</v>
+      <c r="S125" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46238.16814222222</v>
+        <v>46239.17785746528</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7465,8 +7465,8 @@
       <c r="R100" s="5">
         <v>46238</v>
       </c>
-      <c r="S100" s="12" t="s">
-        <v>189</v>
+      <c r="S100" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46237.538152407404</v>
+        <v>46239.168117546295</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>307</v>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46223.587958344906</v>
+        <v>46239.16811965278</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>191</v>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46223.58795771991</v>
+        <v>46239.16812105324</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>191</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46223.587957094904</v>
+        <v>46239.16811622685</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>191</v>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46223.58795648148</v>
+        <v>46239.16812241898</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>191</v>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46223.58795587963</v>
+        <v>46239.16809390046</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>191</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46237.5382402199</v>
+        <v>46239.17350260417</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>354</v>
@@ -9108,8 +9108,8 @@
       <c r="R131" s="8">
         <v>46246</v>
       </c>
-      <c r="S131" s="11" t="s">
-        <v>100</v>
+      <c r="S131" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46239.168117546295</v>
+        <v>46240.185729212964</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>307</v>
@@ -7783,8 +7783,8 @@
       <c r="R106" s="5">
         <v>46239</v>
       </c>
-      <c r="S106" s="12" t="s">
-        <v>189</v>
+      <c r="S106" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46237.538172465276</v>
+        <v>46240.16791725694</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>320</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46223.58806811343</v>
+        <v>46240.16792071759</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>191</v>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46223.588067488425</v>
+        <v>46240.16792202546</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>191</v>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46223.58806685185</v>
+        <v>46240.167923182875</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>191</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46223.588066192126</v>
+        <v>46240.167919444444</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>191</v>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46223.58806555555</v>
+        <v>46240.16789377315</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>191</v>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46155.64036164352</v>
+        <v>46240.170404386576</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>363</v>
@@ -9434,8 +9434,8 @@
       <c r="R137" s="8">
         <v>46247</v>
       </c>
-      <c r="S137" s="11" t="s">
-        <v>100</v>
+      <c r="S137" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46234.17252638889</v>
+        <v>46241.168423344905</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46155.64216699074</v>
+        <v>46241.168425219905</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>191</v>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.6421837963</v>
+        <v>46241.16842649305</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46155.64219278935</v>
+        <v>46241.1684277662</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.64220083333</v>
+        <v>46241.168428993056</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46155.64223084491</v>
+        <v>46241.16840126157</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46240.16791725694</v>
+        <v>46241.17269857639</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>320</v>
@@ -8101,8 +8101,8 @@
       <c r="R112" s="5">
         <v>46240</v>
       </c>
-      <c r="S112" s="12" t="s">
-        <v>189</v>
+      <c r="S112" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46155.641985821756</v>
+        <v>46241.2033084375</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>372</v>
@@ -9752,8 +9752,8 @@
       <c r="R143" s="8">
         <v>46248</v>
       </c>
-      <c r="S143" s="11" t="s">
-        <v>100</v>
+      <c r="S143" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -620,430 +620,430 @@
     <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
   </si>
   <si>
+    <t>1214777293059971</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>check pruebas FAT, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777626730373</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214777626730389</t>
+  </si>
+  <si>
+    <t>1214777626758296</t>
+  </si>
+  <si>
+    <t>1214739697907775</t>
+  </si>
+  <si>
+    <t>1214777626758308</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1214777626758318</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214777626772872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777594376340</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214777561694352</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777561694373</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214777561702202</t>
+  </si>
+  <si>
+    <t>1214777561721939</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Control de calidad Armado,Armado</t>
+  </si>
+  <si>
+    <t>1214777561721949</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>1214777561722180</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777481868346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214777594413806</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214777594413833</t>
+  </si>
+  <si>
+    <t>1214739697907735</t>
+  </si>
+  <si>
+    <t>1214777594424435</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1214777626832401</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,check planos</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,Armado</t>
+  </si>
+  <si>
+    <t>1214777293166745</t>
+  </si>
+  <si>
+    <t>Armado,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777481903037</t>
+  </si>
+  <si>
+    <t>1214777561693151</t>
+  </si>
+  <si>
+    <t>1214739697907737</t>
+  </si>
+  <si>
+    <t>1214777594459054</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214777594459075</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT4316  ZVN 1-9-25/4,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214777293216113</t>
+  </si>
+  <si>
+    <t>1214777293224523</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777594502664</t>
+  </si>
+  <si>
+    <t>1214739697907750</t>
+  </si>
+  <si>
+    <t>1214777594502686</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214777626941208</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777626943342</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:</t>
+  </si>
+  <si>
+    <t>1214777626943368</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Bodega:, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777482036119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214777561915411</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,Pruebas FAT,Montaje motor,Montaje Alabe,Revestimiento,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214777561915421</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214777626999692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4316  ZVN 1-9-25/4,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214777594607647</t>
+  </si>
+  <si>
+    <t>1214777482092477</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777482092499</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214739697907756</t>
+  </si>
+  <si>
+    <t>1214777561943713</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214777594624665</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214777594624691</t>
+  </si>
+  <si>
+    <t>1214777594627061</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,OT4316  ZVN 1-9-25/4,check planos</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777594628289</t>
+  </si>
+  <si>
+    <t>1214739697907760</t>
+  </si>
+  <si>
+    <t>1214777293295044</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214777293396922</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>1214777562060273</t>
+  </si>
+  <si>
+    <t>1214777594697797</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214777627132925</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,check planos,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214739697907764</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214777482243155</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777482243176</t>
+  </si>
+  <si>
+    <t>Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>Montaje motor, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777482260833</t>
+  </si>
+  <si>
+    <t>1214777293442422</t>
+  </si>
+  <si>
+    <t>OT4316  ZVN 1-9-25/4,check planos,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214777482283900</t>
+  </si>
+  <si>
+    <t>check planos,OT4316  ZVN 1-9-25/4,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214739697907767</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Montaje motor</t>
+  </si>
+  <si>
+    <t>1214777293454096</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214777482288345</t>
+  </si>
+  <si>
+    <t>Pruebas FAT, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777482288371</t>
+  </si>
+  <si>
+    <t>1214777594777196</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214777293457715</t>
+  </si>
+  <si>
+    <t>1214739697907771</t>
+  </si>
+  <si>
+    <t>1214777627033605</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777293059971</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>check pruebas FAT, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777626730373</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214777626730389</t>
-  </si>
-  <si>
-    <t>1214777626758296</t>
-  </si>
-  <si>
-    <t>1214739697907775</t>
-  </si>
-  <si>
-    <t>1214777626758308</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1214777626758318</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214777626772872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777594376340</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214777561694352</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777561694373</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214777561702202</t>
-  </si>
-  <si>
-    <t>1214777561721939</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Control de calidad Armado,Armado</t>
-  </si>
-  <si>
-    <t>1214777561721949</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>1214777561722180</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777481868346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214777594413806</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214777594413833</t>
-  </si>
-  <si>
-    <t>1214739697907735</t>
-  </si>
-  <si>
-    <t>1214777594424435</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1214777626832401</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,check planos</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,Armado</t>
-  </si>
-  <si>
-    <t>1214777293166745</t>
-  </si>
-  <si>
-    <t>Armado,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777481903037</t>
-  </si>
-  <si>
-    <t>1214777561693151</t>
-  </si>
-  <si>
-    <t>1214739697907737</t>
-  </si>
-  <si>
-    <t>1214777594459054</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214777594459075</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT4316  ZVN 1-9-25/4,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214777293216113</t>
-  </si>
-  <si>
-    <t>1214777293224523</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777594502664</t>
-  </si>
-  <si>
-    <t>1214739697907750</t>
-  </si>
-  <si>
-    <t>1214777594502686</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214777626941208</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777626943342</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Bodega:</t>
-  </si>
-  <si>
-    <t>1214777626943368</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Bodega:, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777482036119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214777561915411</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,Pruebas FAT,Montaje motor,Montaje Alabe,Revestimiento,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214777561915421</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,OT4316  ZVN 1-9-25/4,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214777626999692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4316  ZVN 1-9-25/4,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214777594607647</t>
-  </si>
-  <si>
-    <t>1214777482092477</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777482092499</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214739697907756</t>
-  </si>
-  <si>
-    <t>1214777561943713</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214777594624665</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214777594624691</t>
-  </si>
-  <si>
-    <t>1214777594627061</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,OT4316  ZVN 1-9-25/4,check planos</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777594628289</t>
-  </si>
-  <si>
-    <t>1214739697907760</t>
-  </si>
-  <si>
-    <t>1214777293295044</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214777293396922</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>1214777562060273</t>
-  </si>
-  <si>
-    <t>1214777594697797</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214777627132925</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,check planos,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214739697907764</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214777482243155</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777482243176</t>
-  </si>
-  <si>
-    <t>Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje motor, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777482260833</t>
-  </si>
-  <si>
-    <t>1214777293442422</t>
-  </si>
-  <si>
-    <t>OT4316  ZVN 1-9-25/4,check planos,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214777482283900</t>
-  </si>
-  <si>
-    <t>check planos,OT4316  ZVN 1-9-25/4,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214739697907767</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Montaje motor</t>
-  </si>
-  <si>
-    <t>1214777293454096</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214777482288345</t>
-  </si>
-  <si>
-    <t>Pruebas FAT, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777482288371</t>
-  </si>
-  <si>
-    <t>1214777594777196</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214777293457715</t>
-  </si>
-  <si>
-    <t>1214739697907771</t>
-  </si>
-  <si>
-    <t>1214777627033605</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1214777627256225</t>
@@ -2707,7 +2707,7 @@
         <v>46196.64233232639</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.58748332176</v>
+        <v>46241.92358274305</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46241.168423344905</v>
+        <v>46242.169572060186</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4685,8 +4685,8 @@
       <c r="R50" s="5">
         <v>46241</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>189</v>
+      <c r="S50" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46155.60610010417</v>
@@ -4707,7 +4707,7 @@
         <v>46241.168425219905</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4735,10 +4735,10 @@
         <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4748,7 +4748,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46155.606106273146</v>
@@ -4758,7 +4758,7 @@
         <v>46241.16842649305</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4786,10 +4786,10 @@
         <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4799,7 +4799,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46155.60611204861</v>
@@ -4809,7 +4809,7 @@
         <v>46241.1684277662</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
@@ -4837,10 +4837,10 @@
         <v>185</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.60611671297</v>
@@ -4860,7 +4860,7 @@
         <v>46241.168428993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4888,10 +4888,10 @@
         <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46155.63491277778</v>
@@ -4911,7 +4911,7 @@
         <v>46241.16840126157</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -4939,10 +4939,10 @@
         <v>185</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46155.60612125</v>
@@ -4964,7 +4964,7 @@
         <v>46213.506286655094</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4988,7 +4988,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5005,7 +5005,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46155.60612483796</v>
@@ -5017,16 +5017,16 @@
         <v>46216.60285269676</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46202</v>
@@ -5044,13 +5044,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>135</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46202</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46155.6061331713</v>
@@ -5082,7 +5082,7 @@
         <v>46213.50624159722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5109,13 +5109,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46174</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46155.606141446755</v>
@@ -5147,16 +5147,16 @@
         <v>46213.50624155093</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I59" s="8">
         <v>46202</v>
@@ -5174,13 +5174,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>144</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="8">
         <v>46202</v>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46155.60614949074</v>
@@ -5212,7 +5212,7 @@
         <v>46213.506277974535</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5239,13 +5239,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46174</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46155.606156319445</v>
@@ -5277,16 +5277,16 @@
         <v>46213.17611152778</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I61" s="8">
         <v>46211</v>
@@ -5304,13 +5304,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>166</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="8">
         <v>46211</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46155.60616390046</v>
@@ -5342,7 +5342,7 @@
         <v>46217.18131804398</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5369,13 +5369,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46213</v>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B63" s="8">
         <v>46155.60617082176</v>
@@ -5405,7 +5405,7 @@
         <v>46213.50618732639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5429,7 +5429,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46155.60617413194</v>
@@ -5452,16 +5452,16 @@
         <v>46220.189402627315</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5479,13 +5479,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q64" s="5">
         <v>46217</v>
@@ -5505,7 +5505,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46155.60618260417</v>
@@ -5515,16 +5515,16 @@
         <v>46219.16819976852</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I65" s="8">
         <v>46217</v>
@@ -5542,13 +5542,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5558,7 +5558,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46155.60619106481</v>
@@ -5568,16 +5568,16 @@
         <v>46219.16819619213</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5595,13 +5595,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5611,7 +5611,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46155.60619835649</v>
@@ -5621,16 +5621,16 @@
         <v>46219.168200960645</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I67" s="8">
         <v>46217</v>
@@ -5648,13 +5648,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46155.60620543981</v>
@@ -5674,16 +5674,16 @@
         <v>46219.16820241898</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I68" s="5">
         <v>46217</v>
@@ -5701,13 +5701,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B69" s="8">
         <v>46155.60745351852</v>
@@ -5727,16 +5727,16 @@
         <v>46219.16814042824</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I69" s="8">
         <v>46217</v>
@@ -5754,13 +5754,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46155.606212638886</v>
@@ -5780,16 +5780,16 @@
         <v>46227.19015055556</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5807,13 +5807,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46155.60621899305</v>
@@ -5843,16 +5843,16 @@
         <v>46226.16794724537</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I71" s="8">
         <v>46220</v>
@@ -5870,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46155.606226539356</v>
@@ -5896,16 +5896,16 @@
         <v>46226.16793981481</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5923,13 +5923,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46155.606234004634</v>
@@ -5949,16 +5949,16 @@
         <v>46226.167942141205</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I73" s="8">
         <v>46220</v>
@@ -5976,13 +5976,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5992,7 +5992,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46155.60628421296</v>
@@ -6002,16 +6002,16 @@
         <v>46226.1679434375</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I74" s="5">
         <v>46220</v>
@@ -6029,13 +6029,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B75" s="8">
         <v>46155.607690034725</v>
@@ -6055,16 +6055,16 @@
         <v>46226.16795292824</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I75" s="8">
         <v>46220</v>
@@ -6082,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6098,7 +6098,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46155.606291909724</v>
@@ -6108,7 +6108,7 @@
         <v>46228.168985682874</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6135,13 +6135,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q76" s="5">
         <v>46227</v>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B77" s="8">
         <v>46155.60629884259</v>
@@ -6171,7 +6171,7 @@
         <v>46227.16857658565</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6198,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6214,7 +6214,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46155.60630622685</v>
@@ -6224,7 +6224,7 @@
         <v>46227.16857197917</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6251,13 +6251,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6267,7 +6267,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46155.6063134375</v>
@@ -6277,7 +6277,7 @@
         <v>46227.1685733912</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6304,13 +6304,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6320,7 +6320,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46155.606319722225</v>
@@ -6330,7 +6330,7 @@
         <v>46227.16857782408</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6357,13 +6357,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6373,7 +6373,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B81" s="8">
         <v>46155.618322951384</v>
@@ -6383,7 +6383,7 @@
         <v>46227.16852841435</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6408,13 +6408,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6424,7 +6424,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5">
         <v>46155.60632542824</v>
@@ -6434,7 +6434,7 @@
         <v>46155.60644350694</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6458,7 +6458,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6471,7 +6471,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B83" s="8">
         <v>46155.60632868056</v>
@@ -6481,16 +6481,16 @@
         <v>46216.83236861111</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6506,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="8">
         <v>46181</v>
@@ -6532,7 +6532,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
         <v>46155.60633650463</v>
@@ -6542,16 +6542,16 @@
         <v>46182.677286018516</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I84" s="5">
         <v>46164</v>
@@ -6569,13 +6569,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q84" s="5">
         <v>46164</v>
@@ -6595,7 +6595,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B85" s="8">
         <v>46155.60634402778</v>
@@ -6605,16 +6605,16 @@
         <v>46198.182506087964</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6632,13 +6632,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>121</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="8">
         <v>46197</v>
@@ -6658,7 +6658,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46155.60635177083</v>
@@ -6668,16 +6668,16 @@
         <v>46232.17399734954</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I86" s="5">
         <v>46231</v>
@@ -6695,13 +6695,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>154</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q86" s="5">
         <v>46231</v>
@@ -6721,7 +6721,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
         <v>46155.606361921295</v>
@@ -6731,7 +6731,7 @@
         <v>46155.606780057875</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6755,7 +6755,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6768,7 +6768,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B88" s="5">
         <v>46155.60636525463</v>
@@ -6778,7 +6778,7 @@
         <v>46237.53806709491</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6805,13 +6805,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q88" s="5">
         <v>46230</v>
@@ -6831,7 +6831,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B89" s="8">
         <v>46155.606374525465</v>
@@ -6841,7 +6841,7 @@
         <v>46234.16955460648</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6868,10 +6868,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>26</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46155.60638027778</v>
@@ -6894,7 +6894,7 @@
         <v>46234.16955314815</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6921,10 +6921,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46155.60638583334</v>
@@ -6947,7 +6947,7 @@
         <v>46234.16954859954</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6974,13 +6974,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6990,7 +6990,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46155.60639179398</v>
@@ -7000,7 +7000,7 @@
         <v>46234.169549872684</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7027,13 +7027,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7043,7 +7043,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="8">
         <v>46155.61975986111</v>
@@ -7053,7 +7053,7 @@
         <v>46234.169515648144</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7080,13 +7080,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7096,7 +7096,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46155.60639783565</v>
@@ -7106,7 +7106,7 @@
         <v>46238.19323280093</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7133,13 +7133,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q94" s="5">
         <v>46237</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B95" s="8">
         <v>46155.60640402778</v>
@@ -7169,7 +7169,7 @@
         <v>46237.16900178241</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7194,13 +7194,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>287</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>288</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46155.60641090278</v>
@@ -7220,7 +7220,7 @@
         <v>46237.169003159725</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7245,13 +7245,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7261,7 +7261,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B97" s="8">
         <v>46155.60641760417</v>
@@ -7271,7 +7271,7 @@
         <v>46237.16900524306</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7296,13 +7296,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O97" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>291</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>292</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7312,7 +7312,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
         <v>46155.60642649306</v>
@@ -7322,7 +7322,7 @@
         <v>46237.16900667824</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7347,13 +7347,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>291</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>292</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7363,7 +7363,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B99" s="8">
         <v>46155.62115946759</v>
@@ -7373,7 +7373,7 @@
         <v>46237.16896111111</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7398,13 +7398,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B100" s="5">
         <v>46155.60648232639</v>
@@ -7424,7 +7424,7 @@
         <v>46239.17785746528</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7451,13 +7451,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q100" s="5">
         <v>46238</v>
@@ -7477,7 +7477,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B101" s="8">
         <v>46155.60649042824</v>
@@ -7487,7 +7487,7 @@
         <v>46238.168144247684</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7512,13 +7512,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7528,7 +7528,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B102" s="5">
         <v>46155.6064993287</v>
@@ -7538,7 +7538,7 @@
         <v>46238.168145497686</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7563,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B103" s="8">
         <v>46155.606507951394</v>
@@ -7589,7 +7589,7 @@
         <v>46238.16814678241</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7614,13 +7614,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7630,7 +7630,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B104" s="5">
         <v>46155.60651716436</v>
@@ -7640,7 +7640,7 @@
         <v>46238.168148067125</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7665,13 +7665,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B105" s="8">
         <v>46155.6221815162</v>
@@ -7691,7 +7691,7 @@
         <v>46238.16811709491</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7716,13 +7716,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7732,7 +7732,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B106" s="5">
         <v>46155.60652579861</v>
@@ -7742,7 +7742,7 @@
         <v>46240.185729212964</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7769,13 +7769,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q106" s="5">
         <v>46239</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B107" s="8">
         <v>46155.606533032405</v>
@@ -7805,7 +7805,7 @@
         <v>46239.16811965278</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7830,13 +7830,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O107" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="P107" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>311</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7846,7 +7846,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B108" s="5">
         <v>46155.60654145833</v>
@@ -7856,7 +7856,7 @@
         <v>46239.16812105324</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7881,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O108" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>311</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7897,7 +7897,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B109" s="8">
         <v>46155.60655399306</v>
@@ -7907,7 +7907,7 @@
         <v>46239.16811622685</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7932,13 +7932,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B110" s="5">
         <v>46155.60656262732</v>
@@ -7958,7 +7958,7 @@
         <v>46239.16812241898</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7983,13 +7983,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7999,7 +7999,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B111" s="8">
         <v>46155.63011625</v>
@@ -8009,7 +8009,7 @@
         <v>46239.16809390046</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8034,13 +8034,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8050,7 +8050,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B112" s="5">
         <v>46155.60657109953</v>
@@ -8060,7 +8060,7 @@
         <v>46241.17269857639</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8087,13 +8087,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q112" s="5">
         <v>46240</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B113" s="8">
         <v>46155.60657833333</v>
@@ -8123,7 +8123,7 @@
         <v>46240.16792071759</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8150,13 +8150,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8166,7 +8166,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B114" s="5">
         <v>46155.60658640046</v>
@@ -8176,7 +8176,7 @@
         <v>46240.16792202546</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8203,13 +8203,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B115" s="8">
         <v>46155.60659408565</v>
@@ -8229,7 +8229,7 @@
         <v>46240.167923182875</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8256,13 +8256,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8272,7 +8272,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B116" s="5">
         <v>46155.60660233797</v>
@@ -8282,7 +8282,7 @@
         <v>46240.167919444444</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8309,13 +8309,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8325,7 +8325,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B117" s="8">
         <v>46155.63398136574</v>
@@ -8335,7 +8335,7 @@
         <v>46240.16789377315</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8360,13 +8360,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8376,7 +8376,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B118" s="5">
         <v>46155.60664190972</v>
@@ -8386,7 +8386,7 @@
         <v>46237.16716700231</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8413,13 +8413,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q118" s="5">
         <v>46244</v>
@@ -8428,7 +8428,7 @@
         <v>46244</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>189</v>
+        <v>330</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
@@ -8449,7 +8449,7 @@
         <v>46223.58818715278</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8474,10 +8474,10 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>332</v>
@@ -8500,7 +8500,7 @@
         <v>46223.588186493056</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8525,10 +8525,10 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>334</v>
@@ -8551,7 +8551,7 @@
         <v>46223.58818568287</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8576,10 +8576,10 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>332</v>
@@ -8602,7 +8602,7 @@
         <v>46223.588184837965</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8627,10 +8627,10 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>334</v>
@@ -8653,7 +8653,7 @@
         <v>46223.58818416667</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8678,10 +8678,10 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>334</v>
@@ -8791,7 +8791,7 @@
         <v>46245</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>189</v>
+        <v>330</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
@@ -8812,7 +8812,7 @@
         <v>46155.6390279051</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8840,7 +8840,7 @@
         <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>347</v>
@@ -8863,7 +8863,7 @@
         <v>46155.639037835645</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8891,7 +8891,7 @@
         <v>342</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>347</v>
@@ -8914,7 +8914,7 @@
         <v>46155.639063807874</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8942,7 +8942,7 @@
         <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>350</v>
@@ -8965,7 +8965,7 @@
         <v>46155.63907559028</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -8993,7 +8993,7 @@
         <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>347</v>
@@ -9016,7 +9016,7 @@
         <v>46155.63910325231</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9044,7 +9044,7 @@
         <v>342</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>347</v>
@@ -9097,7 +9097,7 @@
         <v>339</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>339</v>
@@ -9109,7 +9109,7 @@
         <v>46246</v>
       </c>
       <c r="S131" s="12" t="s">
-        <v>189</v>
+        <v>330</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
@@ -9130,7 +9130,7 @@
         <v>46223.58837571759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9160,7 +9160,7 @@
         <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>356</v>
@@ -9183,7 +9183,7 @@
         <v>46223.58837508102</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9213,7 +9213,7 @@
         <v>354</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>358</v>
@@ -9236,7 +9236,7 @@
         <v>46223.588374375</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9266,7 +9266,7 @@
         <v>354</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>356</v>
@@ -9289,7 +9289,7 @@
         <v>46223.58837366899</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9319,7 +9319,7 @@
         <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>358</v>
@@ -9342,7 +9342,7 @@
         <v>46223.58837290509</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9370,7 +9370,7 @@
         <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>356</v>
@@ -9399,10 +9399,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I137" s="8">
         <v>46247</v>
@@ -9423,7 +9423,7 @@
         <v>339</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P137" s="9" t="s">
         <v>339</v>
@@ -9435,7 +9435,7 @@
         <v>46247</v>
       </c>
       <c r="S137" s="12" t="s">
-        <v>189</v>
+        <v>330</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
@@ -9456,16 +9456,16 @@
         <v>46155.642618750004</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9484,7 +9484,7 @@
         <v>363</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>365</v>
@@ -9507,16 +9507,16 @@
         <v>46155.64263091436</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9535,7 +9535,7 @@
         <v>363</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>365</v>
@@ -9558,16 +9558,16 @@
         <v>46155.64264111111</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9586,7 +9586,7 @@
         <v>363</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>368</v>
@@ -9609,16 +9609,16 @@
         <v>46155.64265195602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9637,7 +9637,7 @@
         <v>363</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>368</v>
@@ -9660,16 +9660,16 @@
         <v>46155.64266835648</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9688,7 +9688,7 @@
         <v>363</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>368</v>
@@ -9717,10 +9717,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I143" s="8">
         <v>46248</v>
@@ -9741,7 +9741,7 @@
         <v>339</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>373</v>
@@ -9753,7 +9753,7 @@
         <v>46248</v>
       </c>
       <c r="S143" s="12" t="s">
-        <v>189</v>
+        <v>330</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
@@ -9774,16 +9774,16 @@
         <v>46155.64207402778</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9802,7 +9802,7 @@
         <v>372</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>372</v>
@@ -9825,16 +9825,16 @@
         <v>46155.64208369213</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9853,7 +9853,7 @@
         <v>372</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>372</v>
@@ -9876,16 +9876,16 @@
         <v>46155.64209340278</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9904,7 +9904,7 @@
         <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>372</v>
@@ -9927,16 +9927,16 @@
         <v>46155.64210719908</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -9955,7 +9955,7 @@
         <v>372</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>372</v>
@@ -9978,16 +9978,16 @@
         <v>46155.64213097222</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10006,7 +10006,7 @@
         <v>372</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>372</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -8383,7 +8383,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46237.16716700231</v>
+        <v>46243.53887505787</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>328</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -8383,7 +8383,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46243.53887505787</v>
+        <v>46244.168210324075</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>328</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46223.58818715278</v>
+        <v>46244.16821231482</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>190</v>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46223.588186493056</v>
+        <v>46244.16820616898</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46223.58818568287</v>
+        <v>46244.16820789352</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>190</v>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46223.588184837965</v>
+        <v>46244.16820909722</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46223.58818416667</v>
+        <v>46244.16819239584</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>190</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1043,52 +1043,52 @@
     <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>1214777627256225</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214777562157816</t>
+  </si>
+  <si>
+    <t>RE-PINTADO, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777562157837</t>
+  </si>
+  <si>
+    <t>1214777589644682</t>
+  </si>
+  <si>
+    <t>1214739697907780</t>
+  </si>
+  <si>
+    <t>1214777627303748</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Embalaje,Despacho,PACKING LIST</t>
+  </si>
+  <si>
+    <t>1214777627303758</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,RE-PINTADO, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777627256225</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214777562157816</t>
-  </si>
-  <si>
-    <t>RE-PINTADO, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777562157837</t>
-  </si>
-  <si>
-    <t>1214777589644682</t>
-  </si>
-  <si>
-    <t>1214739697907780</t>
-  </si>
-  <si>
-    <t>1214777627303748</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,Despacho,PACKING LIST</t>
-  </si>
-  <si>
-    <t>1214777627303758</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,RE-PINTADO, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
   </si>
   <si>
     <t>1214777562172193</t>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46244.168210324075</v>
+        <v>46245.183908101855</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>328</v>
@@ -8427,8 +8427,8 @@
       <c r="R118" s="5">
         <v>46244</v>
       </c>
-      <c r="S118" s="12" t="s">
-        <v>330</v>
+      <c r="S118" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
@@ -8439,7 +8439,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B119" s="8">
         <v>46155.60665081019</v>
@@ -8480,7 +8480,7 @@
         <v>190</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8490,7 +8490,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B120" s="5">
         <v>46155.60665825232</v>
@@ -8531,7 +8531,7 @@
         <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8541,7 +8541,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B121" s="8">
         <v>46155.60666534722</v>
@@ -8582,7 +8582,7 @@
         <v>190</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B122" s="5">
         <v>46155.60667253472</v>
@@ -8633,7 +8633,7 @@
         <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8643,7 +8643,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B123" s="8">
         <v>46155.63591585648</v>
@@ -8684,7 +8684,7 @@
         <v>190</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8694,7 +8694,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B124" s="5">
         <v>46155.606679502314</v>
@@ -8704,7 +8704,7 @@
         <v>46155.60689462963</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>25</v>
@@ -8728,7 +8728,7 @@
         <v>26</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>26</v>
@@ -8741,26 +8741,26 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B125" s="8">
         <v>46155.60668334491</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46238.196791435184</v>
+        <v>46245.16773925926</v>
       </c>
       <c r="E125" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G125" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="F125" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G125" s="9" t="s">
+      <c r="H125" s="9" t="s">
         <v>343</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>344</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -8776,13 +8776,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q125" s="8">
         <v>46245</v>
@@ -8791,7 +8791,7 @@
         <v>46245</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.6390279051</v>
+        <v>46245.16770908565</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8818,10 +8818,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>343</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>344</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8837,7 +8837,7 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>190</v>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46155.639037835645</v>
+        <v>46245.16771032407</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>190</v>
@@ -8869,10 +8869,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="H127" s="9" t="s">
         <v>343</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>344</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -8888,7 +8888,7 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>190</v>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.639063807874</v>
+        <v>46245.16773751157</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -8920,10 +8920,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>343</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>344</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8939,7 +8939,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>190</v>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46155.63907559028</v>
+        <v>46245.16774123843</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>190</v>
@@ -8971,10 +8971,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="H129" s="9" t="s">
         <v>343</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>344</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -8990,7 +8990,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>190</v>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.63910325231</v>
+        <v>46245.16769219907</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>190</v>
@@ -9022,10 +9022,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>343</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>344</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9041,7 +9041,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>190</v>
@@ -9094,13 +9094,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>307</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q131" s="8">
         <v>46246</v>
@@ -9109,7 +9109,7 @@
         <v>46246</v>
       </c>
       <c r="S131" s="12" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
@@ -9420,13 +9420,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>307</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q137" s="8">
         <v>46247</v>
@@ -9435,7 +9435,7 @@
         <v>46247</v>
       </c>
       <c r="S137" s="12" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
@@ -9738,7 +9738,7 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>307</v>
@@ -9753,7 +9753,7 @@
         <v>46248</v>
       </c>
       <c r="S143" s="12" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1088,34 +1088,34 @@
     <t xml:space="preserve"> OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,RE-PINTADO, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
   </si>
   <si>
+    <t>1214777562172193</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777562187802</t>
+  </si>
+  <si>
+    <t>1214777562187823</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1214777627325078</t>
+  </si>
+  <si>
+    <t>1214739697907789</t>
+  </si>
+  <si>
+    <t>1214777562227087</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777562172193</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777562187802</t>
-  </si>
-  <si>
-    <t>1214777562187823</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1214777627325078</t>
-  </si>
-  <si>
-    <t>1214739697907789</t>
-  </si>
-  <si>
-    <t>1214777562227087</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
   </si>
   <si>
     <t>1214777562227108</t>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46245.16773925926</v>
+        <v>46246.192134826386</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>341</v>
@@ -8790,8 +8790,8 @@
       <c r="R125" s="8">
         <v>46245</v>
       </c>
-      <c r="S125" s="12" t="s">
-        <v>345</v>
+      <c r="S125" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B126" s="5">
         <v>46155.606691759254</v>
@@ -8843,7 +8843,7 @@
         <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8853,7 +8853,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B127" s="8">
         <v>46155.60669864583</v>
@@ -8894,7 +8894,7 @@
         <v>190</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -8904,7 +8904,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46155.60670615741</v>
@@ -8945,7 +8945,7 @@
         <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8955,7 +8955,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B129" s="8">
         <v>46155.606713009256</v>
@@ -8996,7 +8996,7 @@
         <v>190</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9006,7 +9006,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B130" s="5">
         <v>46155.63715556713</v>
@@ -9047,7 +9047,7 @@
         <v>190</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9057,17 +9057,17 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B131" s="8">
         <v>46155.60671987268</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46239.17350260417</v>
+        <v>46246.168159085646</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9109,7 +9109,7 @@
         <v>46246</v>
       </c>
       <c r="S131" s="12" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46223.58837571759</v>
+        <v>46246.1681611574</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9157,7 +9157,7 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>190</v>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46223.58837508102</v>
+        <v>46246.16816508102</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>190</v>
@@ -9210,7 +9210,7 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>190</v>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46223.588374375</v>
+        <v>46246.16816266204</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9263,7 +9263,7 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>190</v>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46223.58837366899</v>
+        <v>46246.16816386574</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>190</v>
@@ -9316,7 +9316,7 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>190</v>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46223.58837290509</v>
+        <v>46246.16811372685</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9367,7 +9367,7 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>190</v>
@@ -9435,7 +9435,7 @@
         <v>46247</v>
       </c>
       <c r="S137" s="12" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
@@ -9753,7 +9753,7 @@
         <v>46248</v>
       </c>
       <c r="S143" s="12" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1115,34 +1115,34 @@
     <t>Embalaje</t>
   </si>
   <si>
+    <t>1214777562227108</t>
+  </si>
+  <si>
+    <t>Embalaje, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777627350151</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Embalaje</t>
+  </si>
+  <si>
+    <t>1214777562268573</t>
+  </si>
+  <si>
+    <t>1214777562268595</t>
+  </si>
+  <si>
+    <t>1214739697907793</t>
+  </si>
+  <si>
+    <t>1214777627350478</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777562227108</t>
-  </si>
-  <si>
-    <t>Embalaje, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777627350151</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT4316  ZVN 1-9-25/4,Embalaje</t>
-  </si>
-  <si>
-    <t>1214777562268573</t>
-  </si>
-  <si>
-    <t>1214777562268595</t>
-  </si>
-  <si>
-    <t>1214739697907793</t>
-  </si>
-  <si>
-    <t>1214777627350478</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
   </si>
   <si>
     <t>1214777627351699</t>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46246.168159085646</v>
+        <v>46247.17463043981</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>353</v>
@@ -9108,8 +9108,8 @@
       <c r="R131" s="8">
         <v>46246</v>
       </c>
-      <c r="S131" s="12" t="s">
-        <v>354</v>
+      <c r="S131" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T131" s="9">
         <v>0</v>
@@ -9120,7 +9120,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B132" s="5">
         <v>46155.60672658565</v>
@@ -9163,7 +9163,7 @@
         <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B133" s="8">
         <v>46155.60673355324</v>
@@ -9216,7 +9216,7 @@
         <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9226,7 +9226,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B134" s="5">
         <v>46155.60674053241</v>
@@ -9269,7 +9269,7 @@
         <v>190</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9279,7 +9279,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B135" s="8">
         <v>46155.60674741898</v>
@@ -9322,7 +9322,7 @@
         <v>190</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9332,7 +9332,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B136" s="5">
         <v>46155.63830266204</v>
@@ -9373,7 +9373,7 @@
         <v>190</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9383,17 +9383,17 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B137" s="8">
         <v>46155.60675400463</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46240.170404386576</v>
+        <v>46247.16774318287</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9435,7 +9435,7 @@
         <v>46247</v>
       </c>
       <c r="S137" s="12" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46155.642618750004</v>
+        <v>46247.167744872684</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9481,7 +9481,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>190</v>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46155.64263091436</v>
+        <v>46247.16774606481</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>190</v>
@@ -9532,7 +9532,7 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O139" s="9" t="s">
         <v>190</v>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46155.64264111111</v>
+        <v>46247.16774079861</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9583,7 +9583,7 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>190</v>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46155.64265195602</v>
+        <v>46247.16774200232</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>190</v>
@@ -9634,7 +9634,7 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>190</v>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46155.64266835648</v>
+        <v>46247.16771978009</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>190</v>
@@ -9685,7 +9685,7 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>190</v>
@@ -9753,7 +9753,7 @@
         <v>46248</v>
       </c>
       <c r="S143" s="12" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1142,37 +1142,37 @@
     <t>PACKING LIST</t>
   </si>
   <si>
+    <t>1214777627351699</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Planos Preliminar, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777627351725</t>
+  </si>
+  <si>
+    <t>1214777562157902</t>
+  </si>
+  <si>
+    <t>PACKING LIST, OT4316  ZVN 1-9-25/4</t>
+  </si>
+  <si>
+    <t>1214777594982622</t>
+  </si>
+  <si>
+    <t>1214739697907797</t>
+  </si>
+  <si>
+    <t>1214777594998438</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Costos,Logistica:,Gestion</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777627351699</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Planos Preliminar, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777627351725</t>
-  </si>
-  <si>
-    <t>1214777562157902</t>
-  </si>
-  <si>
-    <t>PACKING LIST, OT4316  ZVN 1-9-25/4</t>
-  </si>
-  <si>
-    <t>1214777594982622</t>
-  </si>
-  <si>
-    <t>1214739697907797</t>
-  </si>
-  <si>
-    <t>1214777594998438</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Costos,Logistica:,Gestion</t>
   </si>
   <si>
     <t>1214777594998459</t>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46247.16774318287</v>
+        <v>46248.17317589121</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>362</v>
@@ -9434,8 +9434,8 @@
       <c r="R137" s="8">
         <v>46247</v>
       </c>
-      <c r="S137" s="12" t="s">
-        <v>363</v>
+      <c r="S137" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T137" s="9">
         <v>0</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B138" s="5">
         <v>46155.60676105324</v>
@@ -9487,7 +9487,7 @@
         <v>190</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9497,7 +9497,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B139" s="8">
         <v>46155.60677012731</v>
@@ -9538,7 +9538,7 @@
         <v>190</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9548,7 +9548,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B140" s="5">
         <v>46155.60681737268</v>
@@ -9589,7 +9589,7 @@
         <v>190</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9599,7 +9599,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B141" s="8">
         <v>46155.60682548611</v>
@@ -9640,7 +9640,7 @@
         <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B142" s="5">
         <v>46155.63928425926</v>
@@ -9691,7 +9691,7 @@
         <v>190</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9701,17 +9701,17 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B143" s="8">
         <v>46155.60683229167</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46241.2033084375</v>
+        <v>46248.168568124995</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -9744,7 +9744,7 @@
         <v>307</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q143" s="8">
         <v>46248</v>
@@ -9753,7 +9753,7 @@
         <v>46248</v>
       </c>
       <c r="S143" s="12" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46155.64207402778</v>
+        <v>46248.168570243055</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9799,13 +9799,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46155.64208369213</v>
+        <v>46248.168571574075</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>190</v>
@@ -9850,13 +9850,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O145" s="9" t="s">
         <v>190</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46155.64209340278</v>
+        <v>46248.16857436343</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -9901,13 +9901,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46155.64210719908</v>
+        <v>46248.16857642361</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>190</v>
@@ -9952,13 +9952,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O147" s="9" t="s">
         <v>190</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46155.64213097222</v>
+        <v>46248.16856126157</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>
@@ -10003,13 +10003,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46155.60689709491</v>
+        <v>46248.18478618056</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>383</v>
@@ -10106,7 +10106,7 @@
         <v>380</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>380</v>
@@ -10117,8 +10117,8 @@
       <c r="R150" s="5">
         <v>46255</v>
       </c>
-      <c r="S150" s="11" t="s">
-        <v>100</v>
+      <c r="S150" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46195.54676386574</v>
+        <v>46248.18478640047</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>387</v>
@@ -10169,7 +10169,7 @@
         <v>380</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>380</v>
@@ -10180,8 +10180,8 @@
       <c r="R151" s="8">
         <v>46255</v>
       </c>
-      <c r="S151" s="11" t="s">
-        <v>100</v>
+      <c r="S151" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="T151" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -1172,43 +1172,43 @@
     <t>Costos,Logistica:,Gestion</t>
   </si>
   <si>
+    <t>1214777594998459</t>
+  </si>
+  <si>
+    <t>1214777627427769</t>
+  </si>
+  <si>
+    <t>1214777627432151</t>
+  </si>
+  <si>
+    <t>1214777627432173</t>
+  </si>
+  <si>
+    <t>1214739697907801</t>
+  </si>
+  <si>
+    <t>1214777595018647</t>
+  </si>
+  <si>
+    <t>Cierre proyecto:</t>
+  </si>
+  <si>
+    <t>Costos,Gestion</t>
+  </si>
+  <si>
+    <t>1214777595018657</t>
+  </si>
+  <si>
+    <t>Gestion</t>
+  </si>
+  <si>
+    <t>Nicolás</t>
+  </si>
+  <si>
+    <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214777594998459</t>
-  </si>
-  <si>
-    <t>1214777627427769</t>
-  </si>
-  <si>
-    <t>1214777627432151</t>
-  </si>
-  <si>
-    <t>1214777627432173</t>
-  </si>
-  <si>
-    <t>1214739697907801</t>
-  </si>
-  <si>
-    <t>1214777595018647</t>
-  </si>
-  <si>
-    <t>Cierre proyecto:</t>
-  </si>
-  <si>
-    <t>Costos,Gestion</t>
-  </si>
-  <si>
-    <t>1214777595018657</t>
-  </si>
-  <si>
-    <t>Gestion</t>
-  </si>
-  <si>
-    <t>Nicolás</t>
-  </si>
-  <si>
-    <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
     <t>1214777595028211</t>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46248.168568124995</v>
+        <v>46249.173422210646</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>371</v>
@@ -9752,8 +9752,8 @@
       <c r="R143" s="8">
         <v>46248</v>
       </c>
-      <c r="S143" s="12" t="s">
-        <v>373</v>
+      <c r="S143" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B144" s="5">
         <v>46155.606840486114</v>
@@ -9815,7 +9815,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B145" s="8">
         <v>46155.60684746528</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B146" s="5">
         <v>46155.60685387731</v>
@@ -9917,7 +9917,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B147" s="8">
         <v>46155.60686101852</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B148" s="5">
         <v>46155.64052775463</v>
@@ -10019,7 +10019,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B149" s="8">
         <v>46155.60686797454</v>
@@ -10029,7 +10029,7 @@
         <v>46155.60689638889</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>25</v>
@@ -10053,7 +10053,7 @@
         <v>26</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -10066,7 +10066,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B150" s="5">
         <v>46155.60687207176</v>
@@ -10076,16 +10076,16 @@
         <v>46248.18478618056</v>
       </c>
       <c r="E150" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G150" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="F150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G150" s="6" t="s">
+      <c r="H150" s="6" t="s">
         <v>384</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>385</v>
       </c>
       <c r="I150" s="5">
         <v>46251</v>
@@ -10103,13 +10103,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>371</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q150" s="5">
         <v>46251</v>
@@ -10118,7 +10118,7 @@
         <v>46255</v>
       </c>
       <c r="S150" s="12" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
@@ -10166,13 +10166,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>371</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q151" s="8">
         <v>46251</v>
@@ -10181,7 +10181,7 @@
         <v>46255</v>
       </c>
       <c r="S151" s="12" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="T151" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46248.18478618056</v>
+        <v>46255.16822709491</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>382</v>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46248.18478640047</v>
+        <v>46255.16822908565</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>387</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="387">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -1206,9 +1206,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214777595028211</t>
@@ -10073,7 +10070,7 @@
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46255.16822709491</v>
+        <v>46256.181118622684</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>382</v>
@@ -10117,8 +10114,8 @@
       <c r="R150" s="5">
         <v>46255</v>
       </c>
-      <c r="S150" s="12" t="s">
-        <v>385</v>
+      <c r="S150" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T150" s="6">
         <v>0</v>
@@ -10129,17 +10126,17 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B151" s="8">
         <v>46155.606879259256</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46255.16822908565</v>
+        <v>46256.18111871528</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10180,8 +10177,8 @@
       <c r="R151" s="8">
         <v>46255</v>
       </c>
-      <c r="S151" s="12" t="s">
-        <v>385</v>
+      <c r="S151" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T151" s="9">
         <v>0</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="387">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -4396,9 +4396,11 @@
       <c r="B46" s="5">
         <v>46155.60562939815</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46258.53813252314</v>
+      </c>
       <c r="D46" s="5">
-        <v>46197.71336900463</v>
+        <v>46258.5381453125</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4433,8 +4435,12 @@
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
@@ -4636,9 +4642,11 @@
       <c r="B50" s="5">
         <v>46155.606091747686</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46258.538111828704</v>
+      </c>
       <c r="D50" s="5">
-        <v>46242.169572060186</v>
+        <v>46258.53813342593</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4686,10 +4694,10 @@
         <v>32</v>
       </c>
       <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="10" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U50" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="387">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -4646,7 +4646,7 @@
         <v>46258.538111828704</v>
       </c>
       <c r="D50" s="5">
-        <v>46258.53813342593</v>
+        <v>46258.57707180556</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4696,8 +4696,8 @@
       <c r="T50" s="6">
         <v>1</v>
       </c>
-      <c r="U50" s="11" t="s">
-        <v>33</v>
+      <c r="U50" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4707,9 +4707,11 @@
       <c r="B51" s="8">
         <v>46155.60610010417</v>
       </c>
-      <c r="C51" s="9"/>
+      <c r="C51" s="8">
+        <v>46258.577051597225</v>
+      </c>
       <c r="D51" s="8">
-        <v>46241.168425219905</v>
+        <v>46258.57705591436</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>190</v>
@@ -4758,9 +4760,11 @@
       <c r="B52" s="5">
         <v>46155.606106273146</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46258.5770528125</v>
+      </c>
       <c r="D52" s="5">
-        <v>46241.16842649305</v>
+        <v>46258.577056319446</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4809,9 +4813,11 @@
       <c r="B53" s="8">
         <v>46155.60611204861</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46258.5770533912</v>
+      </c>
       <c r="D53" s="8">
-        <v>46241.1684277662</v>
+        <v>46258.57705670139</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>190</v>
@@ -4860,9 +4866,11 @@
       <c r="B54" s="5">
         <v>46155.60611671297</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46258.57705393519</v>
+      </c>
       <c r="D54" s="5">
-        <v>46241.168428993056</v>
+        <v>46258.577057083334</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4911,9 +4919,11 @@
       <c r="B55" s="8">
         <v>46155.63491277778</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="8">
+        <v>46258.57705450231</v>
+      </c>
       <c r="D55" s="8">
-        <v>46241.16840126157</v>
+        <v>46258.5770574537</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>190</v>
@@ -5407,7 +5417,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46213.50618732639</v>
+        <v>46258.5764857176</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>220</v>
@@ -5443,7 +5453,9 @@
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
       <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="U63" s="12" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -5452,9 +5464,11 @@
       <c r="B64" s="5">
         <v>46155.60617413194</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46258.576325682865</v>
+      </c>
       <c r="D64" s="5">
-        <v>46220.189402627315</v>
+        <v>46258.576338506944</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>223</v>
@@ -5502,10 +5516,10 @@
         <v>32</v>
       </c>
       <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="10" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U64" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5515,9 +5529,11 @@
       <c r="B65" s="8">
         <v>46155.60618260417</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46258.57630584491</v>
+      </c>
       <c r="D65" s="8">
-        <v>46219.16819976852</v>
+        <v>46258.576309930555</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>227</v>
@@ -5568,9 +5584,11 @@
       <c r="B66" s="5">
         <v>46155.60619106481</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46258.57630677083</v>
+      </c>
       <c r="D66" s="5">
-        <v>46219.16819619213</v>
+        <v>46258.57631045139</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>227</v>
@@ -5621,9 +5639,11 @@
       <c r="B67" s="8">
         <v>46155.60619835649</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46258.57630741898</v>
+      </c>
       <c r="D67" s="8">
-        <v>46219.168200960645</v>
+        <v>46258.576310902776</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>227</v>
@@ -5674,9 +5694,11 @@
       <c r="B68" s="5">
         <v>46155.60620543981</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46258.576308020834</v>
+      </c>
       <c r="D68" s="5">
-        <v>46219.16820241898</v>
+        <v>46258.57631128472</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5727,9 +5749,11 @@
       <c r="B69" s="8">
         <v>46155.60745351852</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="8">
+        <v>46258.576308564814</v>
+      </c>
       <c r="D69" s="8">
-        <v>46219.16814042824</v>
+        <v>46258.576311701385</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>227</v>
@@ -5780,9 +5804,11 @@
       <c r="B70" s="5">
         <v>46155.606212638886</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46258.57639849537</v>
+      </c>
       <c r="D70" s="5">
-        <v>46227.19015055556</v>
+        <v>46258.576406099535</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>237</v>
@@ -5832,8 +5858,8 @@
       <c r="T70" s="6">
         <v>1</v>
       </c>
-      <c r="U70" s="11" t="s">
-        <v>33</v>
+      <c r="U70" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5843,9 +5869,11 @@
       <c r="B71" s="8">
         <v>46155.60621899305</v>
       </c>
-      <c r="C71" s="9"/>
+      <c r="C71" s="8">
+        <v>46258.5763809375</v>
+      </c>
       <c r="D71" s="8">
-        <v>46226.16794724537</v>
+        <v>46258.576384444445</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>227</v>
@@ -5896,9 +5924,11 @@
       <c r="B72" s="5">
         <v>46155.606226539356</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46258.576381701394</v>
+      </c>
       <c r="D72" s="5">
-        <v>46226.16793981481</v>
+        <v>46258.57638479167</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>227</v>
@@ -5949,9 +5979,11 @@
       <c r="B73" s="8">
         <v>46155.606234004634</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46258.576382280095</v>
+      </c>
       <c r="D73" s="8">
-        <v>46226.167942141205</v>
+        <v>46258.57638508102</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>227</v>
@@ -6002,9 +6034,11 @@
       <c r="B74" s="5">
         <v>46155.60628421296</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46258.57638274306</v>
+      </c>
       <c r="D74" s="5">
-        <v>46226.1679434375</v>
+        <v>46258.57638537037</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>227</v>
@@ -6055,9 +6089,11 @@
       <c r="B75" s="8">
         <v>46155.607690034725</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46258.576383252315</v>
+      </c>
       <c r="D75" s="8">
-        <v>46226.16795292824</v>
+        <v>46258.57638565972</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>227</v>
@@ -6108,9 +6144,11 @@
       <c r="B76" s="5">
         <v>46155.606291909724</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46258.5764700463</v>
+      </c>
       <c r="D76" s="5">
-        <v>46228.168985682874</v>
+        <v>46258.57647641204</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>247</v>
@@ -6160,8 +6198,8 @@
       <c r="T76" s="6">
         <v>1</v>
       </c>
-      <c r="U76" s="11" t="s">
-        <v>33</v>
+      <c r="U76" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6171,9 +6209,11 @@
       <c r="B77" s="8">
         <v>46155.60629884259</v>
       </c>
-      <c r="C77" s="9"/>
+      <c r="C77" s="8">
+        <v>46258.57644853009</v>
+      </c>
       <c r="D77" s="8">
-        <v>46227.16857658565</v>
+        <v>46258.576453657406</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>227</v>
@@ -6224,9 +6264,11 @@
       <c r="B78" s="5">
         <v>46155.60630622685</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46258.57644978009</v>
+      </c>
       <c r="D78" s="5">
-        <v>46227.16857197917</v>
+        <v>46258.57645414352</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>227</v>
@@ -6277,9 +6319,11 @@
       <c r="B79" s="8">
         <v>46155.6063134375</v>
       </c>
-      <c r="C79" s="9"/>
+      <c r="C79" s="8">
+        <v>46258.576450520835</v>
+      </c>
       <c r="D79" s="8">
-        <v>46227.1685733912</v>
+        <v>46258.576454699076</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>227</v>
@@ -6330,9 +6374,11 @@
       <c r="B80" s="5">
         <v>46155.606319722225</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46258.57645123843</v>
+      </c>
       <c r="D80" s="5">
-        <v>46227.16857782408</v>
+        <v>46258.576455069444</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>227</v>
@@ -6383,9 +6429,11 @@
       <c r="B81" s="8">
         <v>46155.618322951384</v>
       </c>
-      <c r="C81" s="9"/>
+      <c r="C81" s="8">
+        <v>46258.57645197917</v>
+      </c>
       <c r="D81" s="8">
-        <v>46227.16852841435</v>
+        <v>46258.57645547454</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>227</v>
@@ -6434,9 +6482,11 @@
       <c r="B82" s="5">
         <v>46155.60632542824</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46258.576531412036</v>
+      </c>
       <c r="D82" s="5">
-        <v>46155.60644350694</v>
+        <v>46258.57654385417</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>198</v>
@@ -6471,8 +6521,12 @@
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
       <c r="S82" s="6"/>
-      <c r="T82" s="6"/>
-      <c r="U82" s="6"/>
+      <c r="T82" s="6">
+        <v>1</v>
+      </c>
+      <c r="U82" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
@@ -6481,9 +6535,11 @@
       <c r="B83" s="8">
         <v>46155.60632868056</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="8">
+        <v>46258.57650766204</v>
+      </c>
       <c r="D83" s="8">
-        <v>46216.83236861111</v>
+        <v>46258.576532418985</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>258</v>
@@ -6529,10 +6585,10 @@
         <v>32</v>
       </c>
       <c r="T83" s="9">
-        <v>0</v>
-      </c>
-      <c r="U83" s="12" t="s">
-        <v>91</v>
+        <v>1</v>
+      </c>
+      <c r="U83" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6542,9 +6598,11 @@
       <c r="B84" s="5">
         <v>46155.60633650463</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46258.57650851852</v>
+      </c>
       <c r="D84" s="5">
-        <v>46182.677286018516</v>
+        <v>46258.576532569445</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>261</v>
@@ -6592,10 +6650,10 @@
         <v>32</v>
       </c>
       <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="12" t="s">
-        <v>91</v>
+        <v>1</v>
+      </c>
+      <c r="U84" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6605,9 +6663,11 @@
       <c r="B85" s="8">
         <v>46155.60634402778</v>
       </c>
-      <c r="C85" s="9"/>
+      <c r="C85" s="8">
+        <v>46258.57650913195</v>
+      </c>
       <c r="D85" s="8">
-        <v>46198.182506087964</v>
+        <v>46258.57653314815</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>264</v>
@@ -6655,10 +6715,10 @@
         <v>32</v>
       </c>
       <c r="T85" s="9">
-        <v>0</v>
-      </c>
-      <c r="U85" s="12" t="s">
-        <v>91</v>
+        <v>1</v>
+      </c>
+      <c r="U85" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6668,9 +6728,11 @@
       <c r="B86" s="5">
         <v>46155.60635177083</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46258.57650976852</v>
+      </c>
       <c r="D86" s="5">
-        <v>46232.17399734954</v>
+        <v>46258.57653244213</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>267</v>
@@ -6718,10 +6780,10 @@
         <v>32</v>
       </c>
       <c r="T86" s="6">
-        <v>0</v>
-      </c>
-      <c r="U86" s="12" t="s">
-        <v>91</v>
+        <v>1</v>
+      </c>
+      <c r="U86" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6733,7 +6795,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46155.606780057875</v>
+        <v>46258.57700428241</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -6778,9 +6840,11 @@
       <c r="B88" s="5">
         <v>46155.60636525463</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46258.57664170139</v>
+      </c>
       <c r="D88" s="5">
-        <v>46237.53806709491</v>
+        <v>46258.57665181713</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>273</v>
@@ -6828,10 +6892,10 @@
         <v>32</v>
       </c>
       <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="11" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="U88" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6841,9 +6905,11 @@
       <c r="B89" s="8">
         <v>46155.606374525465</v>
       </c>
-      <c r="C89" s="9"/>
+      <c r="C89" s="8">
+        <v>46258.57662290509</v>
+      </c>
       <c r="D89" s="8">
-        <v>46234.16955460648</v>
+        <v>46258.57662731482</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>227</v>
@@ -6894,9 +6960,11 @@
       <c r="B90" s="5">
         <v>46155.60638027778</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46258.57662365741</v>
+      </c>
       <c r="D90" s="5">
-        <v>46234.16955314815</v>
+        <v>46258.57662788194</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>227</v>
@@ -6947,9 +7015,11 @@
       <c r="B91" s="8">
         <v>46155.60638583334</v>
       </c>
-      <c r="C91" s="9"/>
+      <c r="C91" s="8">
+        <v>46258.57662417824</v>
+      </c>
       <c r="D91" s="8">
-        <v>46234.16954859954</v>
+        <v>46258.576628379626</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>227</v>
@@ -7000,9 +7070,11 @@
       <c r="B92" s="5">
         <v>46155.60639179398</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46258.576624884256</v>
+      </c>
       <c r="D92" s="5">
-        <v>46234.169549872684</v>
+        <v>46258.57662886574</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>227</v>
@@ -7053,9 +7125,11 @@
       <c r="B93" s="8">
         <v>46155.61975986111</v>
       </c>
-      <c r="C93" s="9"/>
+      <c r="C93" s="8">
+        <v>46258.57662555556</v>
+      </c>
       <c r="D93" s="8">
-        <v>46234.169515648144</v>
+        <v>46258.576629247684</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>227</v>
@@ -7106,9 +7180,11 @@
       <c r="B94" s="5">
         <v>46155.60639783565</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46258.57671572917</v>
+      </c>
       <c r="D94" s="5">
-        <v>46238.19323280093</v>
+        <v>46258.57673027778</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>284</v>
@@ -7156,10 +7232,10 @@
         <v>32</v>
       </c>
       <c r="T94" s="6">
-        <v>0</v>
-      </c>
-      <c r="U94" s="12" t="s">
-        <v>91</v>
+        <v>1</v>
+      </c>
+      <c r="U94" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7169,9 +7245,11 @@
       <c r="B95" s="8">
         <v>46155.60640402778</v>
       </c>
-      <c r="C95" s="9"/>
+      <c r="C95" s="8">
+        <v>46258.57669618056</v>
+      </c>
       <c r="D95" s="8">
-        <v>46237.16900178241</v>
+        <v>46258.57670055555</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>227</v>
@@ -7220,9 +7298,11 @@
       <c r="B96" s="5">
         <v>46155.60641090278</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46258.576697199074</v>
+      </c>
       <c r="D96" s="5">
-        <v>46237.169003159725</v>
+        <v>46258.57670097222</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>227</v>
@@ -7271,9 +7351,11 @@
       <c r="B97" s="8">
         <v>46155.60641760417</v>
       </c>
-      <c r="C97" s="9"/>
+      <c r="C97" s="8">
+        <v>46258.57669789351</v>
+      </c>
       <c r="D97" s="8">
-        <v>46237.16900524306</v>
+        <v>46258.57670130787</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>227</v>
@@ -7322,9 +7404,11 @@
       <c r="B98" s="5">
         <v>46155.60642649306</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46258.57669854167</v>
+      </c>
       <c r="D98" s="5">
-        <v>46237.16900667824</v>
+        <v>46258.576701620375</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>227</v>
@@ -7373,9 +7457,11 @@
       <c r="B99" s="8">
         <v>46155.62115946759</v>
       </c>
-      <c r="C99" s="9"/>
+      <c r="C99" s="8">
+        <v>46258.57669916667</v>
+      </c>
       <c r="D99" s="8">
-        <v>46237.16896111111</v>
+        <v>46258.57670200232</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>227</v>
@@ -7424,9 +7510,11 @@
       <c r="B100" s="5">
         <v>46155.60648232639</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46258.576797002315</v>
+      </c>
       <c r="D100" s="5">
-        <v>46239.17785746528</v>
+        <v>46258.57680844907</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>295</v>
@@ -7474,10 +7562,10 @@
         <v>32</v>
       </c>
       <c r="T100" s="6">
-        <v>0</v>
-      </c>
-      <c r="U100" s="12" t="s">
-        <v>91</v>
+        <v>1</v>
+      </c>
+      <c r="U100" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7487,9 +7575,11 @@
       <c r="B101" s="8">
         <v>46155.60649042824</v>
       </c>
-      <c r="C101" s="9"/>
+      <c r="C101" s="8">
+        <v>46258.57677641204</v>
+      </c>
       <c r="D101" s="8">
-        <v>46238.168144247684</v>
+        <v>46258.57678079861</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>227</v>
@@ -7538,9 +7628,11 @@
       <c r="B102" s="5">
         <v>46155.6064993287</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46258.57677745371</v>
+      </c>
       <c r="D102" s="5">
-        <v>46238.168145497686</v>
+        <v>46258.57678125</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>227</v>
@@ -7589,9 +7681,11 @@
       <c r="B103" s="8">
         <v>46155.606507951394</v>
       </c>
-      <c r="C103" s="9"/>
+      <c r="C103" s="8">
+        <v>46258.57677814815</v>
+      </c>
       <c r="D103" s="8">
-        <v>46238.16814678241</v>
+        <v>46258.57678159722</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>227</v>
@@ -7640,9 +7734,11 @@
       <c r="B104" s="5">
         <v>46155.60651716436</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46258.576778773146</v>
+      </c>
       <c r="D104" s="5">
-        <v>46238.168148067125</v>
+        <v>46258.576781932876</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>227</v>
@@ -7691,9 +7787,11 @@
       <c r="B105" s="8">
         <v>46155.6221815162</v>
       </c>
-      <c r="C105" s="9"/>
+      <c r="C105" s="8">
+        <v>46258.57677939815</v>
+      </c>
       <c r="D105" s="8">
-        <v>46238.16811709491</v>
+        <v>46258.57678228009</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>227</v>
@@ -7742,9 +7840,11 @@
       <c r="B106" s="5">
         <v>46155.60652579861</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46258.57688172454</v>
+      </c>
       <c r="D106" s="5">
-        <v>46240.185729212964</v>
+        <v>46258.57689305556</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>306</v>
@@ -7792,10 +7892,10 @@
         <v>32</v>
       </c>
       <c r="T106" s="6">
-        <v>0</v>
-      </c>
-      <c r="U106" s="12" t="s">
-        <v>91</v>
+        <v>1</v>
+      </c>
+      <c r="U106" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -7805,9 +7905,11 @@
       <c r="B107" s="8">
         <v>46155.606533032405</v>
       </c>
-      <c r="C107" s="9"/>
+      <c r="C107" s="8">
+        <v>46258.57686241898</v>
+      </c>
       <c r="D107" s="8">
-        <v>46239.16811965278</v>
+        <v>46258.576867407406</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>190</v>
@@ -7856,9 +7958,11 @@
       <c r="B108" s="5">
         <v>46155.60654145833</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5">
+        <v>46258.57686350694</v>
+      </c>
       <c r="D108" s="5">
-        <v>46239.16812105324</v>
+        <v>46258.576867916665</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>190</v>
@@ -7907,9 +8011,11 @@
       <c r="B109" s="8">
         <v>46155.60655399306</v>
       </c>
-      <c r="C109" s="9"/>
+      <c r="C109" s="8">
+        <v>46258.57686431713</v>
+      </c>
       <c r="D109" s="8">
-        <v>46239.16811622685</v>
+        <v>46258.576868344906</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>190</v>
@@ -7958,9 +8064,11 @@
       <c r="B110" s="5">
         <v>46155.60656262732</v>
       </c>
-      <c r="C110" s="6"/>
+      <c r="C110" s="5">
+        <v>46258.5768650463</v>
+      </c>
       <c r="D110" s="5">
-        <v>46239.16812241898</v>
+        <v>46258.576868738426</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -8009,9 +8117,11 @@
       <c r="B111" s="8">
         <v>46155.63011625</v>
       </c>
-      <c r="C111" s="9"/>
+      <c r="C111" s="8">
+        <v>46258.57686598379</v>
+      </c>
       <c r="D111" s="8">
-        <v>46239.16809390046</v>
+        <v>46258.57686913194</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>190</v>
@@ -8060,9 +8170,11 @@
       <c r="B112" s="5">
         <v>46155.60657109953</v>
       </c>
-      <c r="C112" s="6"/>
+      <c r="C112" s="5">
+        <v>46258.57699693287</v>
+      </c>
       <c r="D112" s="5">
-        <v>46241.17269857639</v>
+        <v>46258.57700788195</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>319</v>
@@ -8110,10 +8222,10 @@
         <v>32</v>
       </c>
       <c r="T112" s="6">
-        <v>0</v>
-      </c>
-      <c r="U112" s="12" t="s">
-        <v>91</v>
+        <v>1</v>
+      </c>
+      <c r="U112" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8123,9 +8235,11 @@
       <c r="B113" s="8">
         <v>46155.60657833333</v>
       </c>
-      <c r="C113" s="9"/>
+      <c r="C113" s="8">
+        <v>46258.57697778935</v>
+      </c>
       <c r="D113" s="8">
-        <v>46240.16792071759</v>
+        <v>46258.57698217593</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>190</v>
@@ -8176,9 +8290,11 @@
       <c r="B114" s="5">
         <v>46155.60658640046</v>
       </c>
-      <c r="C114" s="6"/>
+      <c r="C114" s="5">
+        <v>46258.57697872685</v>
+      </c>
       <c r="D114" s="5">
-        <v>46240.16792202546</v>
+        <v>46258.57698262732</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>190</v>
@@ -8229,9 +8345,11 @@
       <c r="B115" s="8">
         <v>46155.60659408565</v>
       </c>
-      <c r="C115" s="9"/>
+      <c r="C115" s="8">
+        <v>46258.57697940972</v>
+      </c>
       <c r="D115" s="8">
-        <v>46240.167923182875</v>
+        <v>46258.576982997685</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>190</v>
@@ -8282,9 +8400,11 @@
       <c r="B116" s="5">
         <v>46155.60660233797</v>
       </c>
-      <c r="C116" s="6"/>
+      <c r="C116" s="5">
+        <v>46258.57698006944</v>
+      </c>
       <c r="D116" s="5">
-        <v>46240.167919444444</v>
+        <v>46258.57698331018</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8335,9 +8455,11 @@
       <c r="B117" s="8">
         <v>46155.63398136574</v>
       </c>
-      <c r="C117" s="9"/>
+      <c r="C117" s="8">
+        <v>46258.5769807176</v>
+      </c>
       <c r="D117" s="8">
-        <v>46240.16789377315</v>
+        <v>46258.57698363426</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>190</v>
@@ -8451,7 +8573,7 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46244.16821231482</v>
+        <v>46258.57706458333</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>190</v>
@@ -8502,7 +8624,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46244.16820616898</v>
+        <v>46258.57706256944</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8553,7 +8675,7 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46244.16820789352</v>
+        <v>46258.57706253472</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>190</v>
@@ -8604,7 +8726,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46244.16820909722</v>
+        <v>46258.577062592594</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8655,7 +8777,7 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46244.16819239584</v>
+        <v>46258.57706246528</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>190</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -5417,7 +5417,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46258.5764857176</v>
+        <v>46260.579079814815</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>220</v>
@@ -5453,8 +5453,8 @@
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
       <c r="T63" s="9"/>
-      <c r="U63" s="12" t="s">
-        <v>91</v>
+      <c r="U63" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5808,7 +5808,7 @@
         <v>46258.57639849537</v>
       </c>
       <c r="D70" s="5">
-        <v>46258.576406099535</v>
+        <v>46260.57911795139</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>237</v>
@@ -5858,8 +5858,8 @@
       <c r="T70" s="6">
         <v>1</v>
       </c>
-      <c r="U70" s="12" t="s">
-        <v>91</v>
+      <c r="U70" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -6148,7 +6148,7 @@
         <v>46258.5764700463</v>
       </c>
       <c r="D76" s="5">
-        <v>46258.57647641204</v>
+        <v>46260.57913484954</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>247</v>
@@ -6198,8 +6198,8 @@
       <c r="T76" s="6">
         <v>1</v>
       </c>
-      <c r="U76" s="12" t="s">
-        <v>91</v>
+      <c r="U76" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6844,7 +6844,7 @@
         <v>46258.57664170139</v>
       </c>
       <c r="D88" s="5">
-        <v>46258.57665181713</v>
+        <v>46260.57918943287</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>273</v>
@@ -6894,8 +6894,8 @@
       <c r="T88" s="6">
         <v>1</v>
       </c>
-      <c r="U88" s="12" t="s">
-        <v>91</v>
+      <c r="U88" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46245.183908101855</v>
+        <v>46260.579217418985</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>328</v>
@@ -8560,8 +8560,8 @@
       <c r="T118" s="6">
         <v>0</v>
       </c>
-      <c r="U118" s="10" t="s">
-        <v>101</v>
+      <c r="U118" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46247.17463043981</v>
+        <v>46260.57928197917</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>353</v>
@@ -9241,8 +9241,8 @@
       <c r="T131" s="9">
         <v>0</v>
       </c>
-      <c r="U131" s="12" t="s">
-        <v>91</v>
+      <c r="U131" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46248.17317589121</v>
+        <v>46260.57930319445</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>362</v>
@@ -9567,8 +9567,8 @@
       <c r="T137" s="9">
         <v>0</v>
       </c>
-      <c r="U137" s="10" t="s">
-        <v>101</v>
+      <c r="U137" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="387">
   <si>
     <t>50001546 - XEMORTIZ</t>
   </si>
@@ -5415,9 +5415,11 @@
       <c r="B63" s="8">
         <v>46155.60617082176</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46260.64293943287</v>
+      </c>
       <c r="D63" s="8">
-        <v>46260.579079814815</v>
+        <v>46260.64295446759</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>220</v>
@@ -5452,7 +5454,9 @@
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
-      <c r="T63" s="9"/>
+      <c r="T63" s="9">
+        <v>1</v>
+      </c>
       <c r="U63" s="11" t="s">
         <v>33</v>
       </c>
@@ -6795,7 +6799,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46258.57700428241</v>
+        <v>46260.64235780093</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -6831,7 +6835,9 @@
       <c r="R87" s="9"/>
       <c r="S87" s="9"/>
       <c r="T87" s="9"/>
-      <c r="U87" s="9"/>
+      <c r="U87" s="12" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
@@ -8508,9 +8514,11 @@
       <c r="B118" s="5">
         <v>46155.60664190972</v>
       </c>
-      <c r="C118" s="6"/>
+      <c r="C118" s="5">
+        <v>46260.6423377662</v>
+      </c>
       <c r="D118" s="5">
-        <v>46260.579217418985</v>
+        <v>46260.642349120375</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>328</v>
@@ -8558,10 +8566,10 @@
         <v>32</v>
       </c>
       <c r="T118" s="6">
-        <v>0</v>
-      </c>
-      <c r="U118" s="11" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="U118" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -8571,9 +8579,11 @@
       <c r="B119" s="8">
         <v>46155.60665081019</v>
       </c>
-      <c r="C119" s="9"/>
+      <c r="C119" s="8">
+        <v>46260.64231520833</v>
+      </c>
       <c r="D119" s="8">
-        <v>46258.57706458333</v>
+        <v>46260.64231946759</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>190</v>
@@ -8622,9 +8632,11 @@
       <c r="B120" s="5">
         <v>46155.60665825232</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="5">
+        <v>46260.642316087964</v>
+      </c>
       <c r="D120" s="5">
-        <v>46258.57706256944</v>
+        <v>46260.64231998843</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8673,9 +8685,11 @@
       <c r="B121" s="8">
         <v>46155.60666534722</v>
       </c>
-      <c r="C121" s="9"/>
+      <c r="C121" s="8">
+        <v>46260.64231671296</v>
+      </c>
       <c r="D121" s="8">
-        <v>46258.57706253472</v>
+        <v>46260.64232047454</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>190</v>
@@ -8724,9 +8738,11 @@
       <c r="B122" s="5">
         <v>46155.60667253472</v>
       </c>
-      <c r="C122" s="6"/>
+      <c r="C122" s="5">
+        <v>46260.642317199075</v>
+      </c>
       <c r="D122" s="5">
-        <v>46258.577062592594</v>
+        <v>46260.64232087963</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8775,9 +8791,11 @@
       <c r="B123" s="8">
         <v>46155.63591585648</v>
       </c>
-      <c r="C123" s="9"/>
+      <c r="C123" s="8">
+        <v>46260.64231782407</v>
+      </c>
       <c r="D123" s="8">
-        <v>46258.57706246528</v>
+        <v>46260.6423212963</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>190</v>
@@ -8828,7 +8846,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.60689462963</v>
+        <v>46260.642775</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>338</v>
@@ -8875,7 +8893,7 @@
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46246.192134826386</v>
+        <v>46260.64234953704</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>341</v>
@@ -8936,7 +8954,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46245.16770908565</v>
+        <v>46260.642328622685</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8987,7 +9005,7 @@
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46245.16771032407</v>
+        <v>46260.642331759256</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>190</v>
@@ -9038,7 +9056,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46245.16773751157</v>
+        <v>46260.642328773145</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -9089,7 +9107,7 @@
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46245.16774123843</v>
+        <v>46260.64233192129</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>190</v>
@@ -9140,7 +9158,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46245.16769219907</v>
+        <v>46260.642331875</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>190</v>
@@ -9189,9 +9207,11 @@
       <c r="B131" s="8">
         <v>46155.60671987268</v>
       </c>
-      <c r="C131" s="9"/>
+      <c r="C131" s="8">
+        <v>46260.64265844907</v>
+      </c>
       <c r="D131" s="8">
-        <v>46260.57928197917</v>
+        <v>46260.64267006944</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>353</v>
@@ -9239,10 +9259,10 @@
         <v>32</v>
       </c>
       <c r="T131" s="9">
-        <v>0</v>
-      </c>
-      <c r="U131" s="11" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="U131" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -9252,9 +9272,11 @@
       <c r="B132" s="5">
         <v>46155.60672658565</v>
       </c>
-      <c r="C132" s="6"/>
+      <c r="C132" s="5">
+        <v>46260.64242549769</v>
+      </c>
       <c r="D132" s="5">
-        <v>46246.1681611574</v>
+        <v>46260.64242690972</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9305,9 +9327,11 @@
       <c r="B133" s="8">
         <v>46155.60673355324</v>
       </c>
-      <c r="C133" s="9"/>
+      <c r="C133" s="8">
+        <v>46260.6424750463</v>
+      </c>
       <c r="D133" s="8">
-        <v>46246.16816508102</v>
+        <v>46260.64247767361</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>190</v>
@@ -9358,9 +9382,11 @@
       <c r="B134" s="5">
         <v>46155.60674053241</v>
       </c>
-      <c r="C134" s="6"/>
+      <c r="C134" s="5">
+        <v>46260.64252721065</v>
+      </c>
       <c r="D134" s="5">
-        <v>46246.16816266204</v>
+        <v>46260.642528993056</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9411,9 +9437,11 @@
       <c r="B135" s="8">
         <v>46155.60674741898</v>
       </c>
-      <c r="C135" s="9"/>
+      <c r="C135" s="8">
+        <v>46260.64259072917</v>
+      </c>
       <c r="D135" s="8">
-        <v>46246.16816386574</v>
+        <v>46260.642592013886</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>190</v>
@@ -9464,9 +9492,11 @@
       <c r="B136" s="5">
         <v>46155.63830266204</v>
       </c>
-      <c r="C136" s="6"/>
+      <c r="C136" s="5">
+        <v>46260.64264464121</v>
+      </c>
       <c r="D136" s="5">
-        <v>46246.16811372685</v>
+        <v>46260.64264611111</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9515,9 +9545,11 @@
       <c r="B137" s="8">
         <v>46155.60675400463</v>
       </c>
-      <c r="C137" s="9"/>
+      <c r="C137" s="8">
+        <v>46260.64276806713</v>
+      </c>
       <c r="D137" s="8">
-        <v>46260.57930319445</v>
+        <v>46260.64277840278</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>362</v>
@@ -9565,10 +9597,10 @@
         <v>32</v>
       </c>
       <c r="T137" s="9">
-        <v>0</v>
-      </c>
-      <c r="U137" s="11" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="U137" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -9578,9 +9610,11 @@
       <c r="B138" s="5">
         <v>46155.60676105324</v>
       </c>
-      <c r="C138" s="6"/>
+      <c r="C138" s="5">
+        <v>46260.642747453705</v>
+      </c>
       <c r="D138" s="5">
-        <v>46247.167744872684</v>
+        <v>46260.64275222222</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9629,9 +9663,11 @@
       <c r="B139" s="8">
         <v>46155.60677012731</v>
       </c>
-      <c r="C139" s="9"/>
+      <c r="C139" s="8">
+        <v>46260.642748495375</v>
+      </c>
       <c r="D139" s="8">
-        <v>46247.16774606481</v>
+        <v>46260.642752685184</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>190</v>
@@ -9680,9 +9716,11 @@
       <c r="B140" s="5">
         <v>46155.60681737268</v>
       </c>
-      <c r="C140" s="6"/>
+      <c r="C140" s="5">
+        <v>46260.642749328705</v>
+      </c>
       <c r="D140" s="5">
-        <v>46247.16774079861</v>
+        <v>46260.642753148146</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9731,9 +9769,11 @@
       <c r="B141" s="8">
         <v>46155.60682548611</v>
       </c>
-      <c r="C141" s="9"/>
+      <c r="C141" s="8">
+        <v>46260.64275002315</v>
+      </c>
       <c r="D141" s="8">
-        <v>46247.16774200232</v>
+        <v>46260.642753576394</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>190</v>
@@ -9782,9 +9822,11 @@
       <c r="B142" s="5">
         <v>46155.63928425926</v>
       </c>
-      <c r="C142" s="6"/>
+      <c r="C142" s="5">
+        <v>46260.64275072917</v>
+      </c>
       <c r="D142" s="5">
-        <v>46247.16771978009</v>
+        <v>46260.64275396991</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>190</v>
@@ -9898,7 +9940,7 @@
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46248.168570243055</v>
+        <v>46260.64276216435</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9949,7 +9991,7 @@
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46248.168571574075</v>
+        <v>46260.642762627314</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>190</v>
@@ -10000,7 +10042,7 @@
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46248.16857436343</v>
+        <v>46260.64276206019</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -10051,7 +10093,7 @@
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46248.16857642361</v>
+        <v>46260.64276164352</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>190</v>
@@ -10102,7 +10144,7 @@
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46248.16856126157</v>
+        <v>46260.64276171297</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>

--- a/data/50001546 - XEMORTIZ.xlsx
+++ b/data/50001546 - XEMORTIZ.xlsx
@@ -2208,7 +2208,7 @@
         <v>46204.91629298611</v>
       </c>
       <c r="D10" s="5">
-        <v>46204.91630894676</v>
+        <v>46263.76562392361</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
